--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Yöntem" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 Kaynaklar'!$A$4:$H$1271</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 Kaynaklar'!$A$4:$H$1273</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02 Alan adı özeti'!$A$4:$E$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03 Yöntem'!$A$4:$A$23</definedName>
   </definedNames>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1271"/>
+  <dimension ref="A1:H1273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -507,7 +507,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VitrA e-ticaret büyüme fırsatları · kaynak siteler ve sayfalar (1267 satır, 65 alan adı)</t>
+          <t>VitrA e-ticaret büyüme fırsatları · kaynak siteler ve sayfalar (1269 satır, 65 alan adı)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>02 Makro Ortam ve Ödeme Gücü · 22 Sonraki Adımlar</t>
+          <t>02 Makro Ortam ve Ödeme Gücü · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 21 Kanal Rolleri ve Etkileşim Modeli · 22 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 22 Kanal Rolleri ve Etkileşim Modeli · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 12 Yeni Kategori ve Segment Fırsatları · 22 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 12 Yeni Kategori ve Segment Fırsatları · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 08 Google Arama Sonuçları ve AI Overview · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 21 Kanal Rolleri ve Etkileşim Modeli · 22 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 08 Google Arama Sonuçları ve AI Overview · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 22 Kanal Rolleri ve Etkileşim Modeli · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>04 SSG ve BM: Derin Talep İncelemesi · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>04 SSG ve BM: Derin Talep İncelemesi · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>04 SSG ve BM: Derin Talep İncelemesi · 08 Google Arama Sonuçları ve AI Overview · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 22 Sonraki Adımlar</t>
+          <t>04 SSG ve BM: Derin Talep İncelemesi · 08 Google Arama Sonuçları ve AI Overview · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>04 SSG ve BM: Derin Talep İncelemesi · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 21 Kanal Rolleri ve Etkileşim Modeli · 22 Sonraki Adımlar</t>
+          <t>04 SSG ve BM: Derin Talep İncelemesi · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 22 Kanal Rolleri ve Etkileşim Modeli · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 07 Marka Aramaları ve Autocomplete · 09 YouTube: Montaj, Tamir ve Karar Videoları · 11 Katalog ve Talep Eşleşmesi · 13 Set, Komple Banyo ve Ürün + Hizmet · 21 Kanal Rolleri ve Etkileşim Modeli · 22 Sonraki Adımlar</t>
+          <t>05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 07 Marka Aramaları ve Autocomplete · 09 YouTube: Montaj, Tamir ve Karar Videoları · 11 Katalog ve Talep Eşleşmesi · 13 Set, Komple Banyo ve Ürün + Hizmet · 22 Kanal Rolleri ve Etkileşim Modeli · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>06 Organik Kanal Performansı · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>06 Organik Kanal Performansı · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>07 Marka Aramaları ve Autocomplete · 21 Kanal Rolleri ve Etkileşim Modeli · 22 Sonraki Adımlar</t>
+          <t>07 Marka Aramaları ve Autocomplete · 22 Kanal Rolleri ve Etkileşim Modeli · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>07 Marka Aramaları ve Autocomplete · 08 Google Arama Sonuçları ve AI Overview · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları · 21 Kanal Rolleri ve Etkileşim Modeli · 22 Sonraki Adımlar</t>
+          <t>07 Marka Aramaları ve Autocomplete · 08 Google Arama Sonuçları ve AI Overview · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları · 22 Kanal Rolleri ve Etkileşim Modeli · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>08 Google Arama Sonuçları ve AI Overview · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>08 Google Arama Sonuçları ve AI Overview · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 22 Sonraki Adımlar</t>
+          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 22 Sonraki Adımlar</t>
+          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>10 Şikayetvar: Satış Sonrası Deneyim · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>10 Şikayetvar: Satış Sonrası Deneyim · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>10 Şikayetvar: Satış Sonrası Deneyim · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 19 Kanal Politikaları ve Keşif Kanalları · 22 Sonraki Adımlar</t>
+          <t>10 Şikayetvar: Satış Sonrası Deneyim · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 20 Kanal Politikaları ve Keşif Kanalları · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 21 Kanal Rolleri ve Etkileşim Modeli · 22 Sonraki Adımlar</t>
+          <t>11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 22 Kanal Rolleri ve Etkileşim Modeli · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 19 Kanal Politikaları ve Keşif Kanalları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Kanal Politikaları ve Keşif Kanalları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 19 Kanal Politikaları ve Keşif Kanalları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Kanal Politikaları ve Keşif Kanalları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 19 Kanal Politikaları ve Keşif Kanalları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Kanal Politikaları ve Keşif Kanalları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 21 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Sonraki Adımlar</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E228" s="6" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="D229" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E229" s="6" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="D243" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="D248" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E248" s="6" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="D249" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="D250" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="D251" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E251" s="6" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="D252" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E252" s="6" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="D253" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E253" s="6" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D254" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E254" s="6" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="D257" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E257" s="6" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="D267" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E267" s="6" t="inlineStr">
@@ -12097,7 +12097,7 @@
       </c>
       <c r="D277" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E277" s="6" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="D278" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E278" s="6" t="inlineStr">
@@ -12559,7 +12559,7 @@
       </c>
       <c r="D288" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E288" s="6" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="D289" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E289" s="6" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="D290" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E290" s="6" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="D291" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E291" s="6" t="inlineStr">
@@ -12769,7 +12769,7 @@
       </c>
       <c r="D293" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E293" s="6" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="D295" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E295" s="6" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="D297" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E297" s="6" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="D298" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E298" s="6" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="D299" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E299" s="6" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="D303" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E303" s="6" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="D304" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E304" s="6" t="inlineStr">
@@ -15247,7 +15247,7 @@
       </c>
       <c r="D352" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E352" s="6" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="D354" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E354" s="6" t="inlineStr">
@@ -15457,7 +15457,7 @@
       </c>
       <c r="D357" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E357" s="6" t="inlineStr">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="D367" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E367" s="6" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="D369" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E369" s="6" t="inlineStr">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="D373" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E373" s="6" t="inlineStr">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="D374" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E374" s="6" t="inlineStr">
@@ -16465,7 +16465,7 @@
       </c>
       <c r="D381" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E381" s="6" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="D384" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E384" s="6" t="inlineStr">
@@ -16843,7 +16843,7 @@
       </c>
       <c r="D390" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E390" s="6" t="inlineStr">
@@ -17053,7 +17053,7 @@
       </c>
       <c r="D395" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E395" s="6" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="D396" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E396" s="6" t="inlineStr">
@@ -29947,7 +29947,7 @@
       </c>
       <c r="D702" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E702" s="6" t="inlineStr">
@@ -29989,7 +29989,7 @@
       </c>
       <c r="D703" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E703" s="6" t="inlineStr">
@@ -30031,7 +30031,7 @@
       </c>
       <c r="D704" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E704" s="6" t="inlineStr">
@@ -30409,7 +30409,7 @@
       </c>
       <c r="D713" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E713" s="6" t="inlineStr">
@@ -30493,7 +30493,7 @@
       </c>
       <c r="D715" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E715" s="6" t="inlineStr">
@@ -30619,7 +30619,7 @@
       </c>
       <c r="D718" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E718" s="6" t="inlineStr">
@@ -30703,7 +30703,7 @@
       </c>
       <c r="D720" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E720" s="6" t="inlineStr">
@@ -30745,7 +30745,7 @@
       </c>
       <c r="D721" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E721" s="6" t="inlineStr">
@@ -30829,7 +30829,7 @@
       </c>
       <c r="D723" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E723" s="6" t="inlineStr">
@@ -30913,7 +30913,7 @@
       </c>
       <c r="D725" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E725" s="6" t="inlineStr">
@@ -36289,7 +36289,7 @@
       </c>
       <c r="D853" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E853" s="6" t="inlineStr">
@@ -42883,7 +42883,7 @@
       </c>
       <c r="D1010" s="6" t="inlineStr">
         <is>
-          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1010" s="6" t="inlineStr">
@@ -46984,237 +46984,237 @@
     <row r="1108" ht="43.5" customHeight="1">
       <c r="A1108" s="5" t="inlineStr">
         <is>
+          <t>https://merchant.hepsiburada.com</t>
+        </is>
+      </c>
+      <c r="B1108" s="6" t="inlineStr">
+        <is>
+          <t>hepsiburada.com</t>
+        </is>
+      </c>
+      <c r="C1108" s="6" t="inlineStr">
+        <is>
+          <t>Hepsiburada satıcı paneli: ürün performansı (hak ediş), görüntülenme, iptal ve değerlendirme raporları</t>
+        </is>
+      </c>
+      <c r="D1108" s="6" t="inlineStr">
+        <is>
+          <t>18 VitrA Resmi Mağaza: Pazaryeri Panel Verisi</t>
+        </is>
+      </c>
+      <c r="E1108" s="6" t="inlineStr">
+        <is>
+          <t>Komisyon, kargo, hizmet bedeli ve kampanya indirimi oranları; 949 SKU görüntülenme ve dönüşüm; 369 iptal nedeni; 204 SKU değerlendirme</t>
+        </is>
+      </c>
+      <c r="F1108" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1108" s="6" t="inlineStr">
+        <is>
+          <t>satıcı paneli dışa aktarımı (kullanıcı tarafından iletildi)</t>
+        </is>
+      </c>
+      <c r="H1108" s="7" t="inlineStr">
+        <is>
+          <t>D31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109" ht="57" customHeight="1">
+      <c r="A1109" s="5" t="inlineStr">
+        <is>
+          <t>https://partner.trendyol.com</t>
+        </is>
+      </c>
+      <c r="B1109" s="6" t="inlineStr">
+        <is>
+          <t>trendyol.com</t>
+        </is>
+      </c>
+      <c r="C1109" s="6" t="inlineStr">
+        <is>
+          <t>Trendyol satıcı paneli (VitrA resmi mağazası): satış, sipariş dağılımı, mağaza, operasyon, favori-görüntüleme, ürün ve satıcı değerlendirmeleri, ürün ve sipariş soruları, Trendyol'un Enleri</t>
+        </is>
+      </c>
+      <c r="D1109" s="6" t="inlineStr">
+        <is>
+          <t>18 VitrA Resmi Mağaza: Pazaryeri Panel Verisi</t>
+        </is>
+      </c>
+      <c r="E1109" s="6" t="inlineStr">
+        <is>
+          <t>Çeyreklik net adet, iptal, iade, indirim ve komisyon oranları; müşteri profili; ürün görüntülenme ve dönüşüm; 1.023 ürün ve 149 satıcı değerlendirmesi; 352 ürün sorusu; 9 kategori × 5 liste Enleri (Eylül 2026). Ciro tutarı rapora alınmadı</t>
+        </is>
+      </c>
+      <c r="F1109" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1109" s="6" t="inlineStr">
+        <is>
+          <t>satıcı paneli dışa aktarımı (kullanıcı tarafından iletildi)</t>
+        </is>
+      </c>
+      <c r="H1109" s="7" t="inlineStr">
+        <is>
+          <t>D31</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110" ht="43.5" customHeight="1">
+      <c r="A1110" s="5" t="inlineStr">
+        <is>
           <t>https://www.akakce.com/{kategori}/en-ucuz-{ürün-adı},{ürün-no}.html</t>
         </is>
       </c>
-      <c r="B1108" s="6" t="inlineStr">
+      <c r="B1110" s="6" t="inlineStr">
         <is>
           <t>akakce.com</t>
         </is>
       </c>
-      <c r="C1108" s="6" t="inlineStr">
+      <c r="C1110" s="6" t="inlineStr">
         <is>
           <t>Akakçe ürün sayfaları: VitrA ve Artema SKU'ları için satıcı listesi ve en düşük fiyat</t>
         </is>
       </c>
-      <c r="D1108" s="6" t="inlineStr">
-        <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
-        </is>
-      </c>
-      <c r="E1108" s="6" t="inlineStr">
+      <c r="D1110" s="6" t="inlineStr">
+        <is>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="E1110" s="6" t="inlineStr">
         <is>
           <t>24 ürün sayfası (29 SKU'dan eşleşen); satıcı, mecra, fiyat, kargo ve stok bilgisi (liste ilk 16 satıcıyla sınırlı); eşleşme doğruluğu için eşleşme ürün adresi slug'ından yapıldı</t>
         </is>
       </c>
-      <c r="F1108" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1108" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1108" s="7" t="inlineStr">
+      <c r="F1110" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1110" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1110" s="7" t="inlineStr">
         <is>
           <t>D27</t>
         </is>
       </c>
     </row>
-    <row r="1109" ht="43.5" customHeight="1">
-      <c r="A1109" s="5" t="inlineStr">
+    <row r="1111" ht="43.5" customHeight="1">
+      <c r="A1111" s="5" t="inlineStr">
         <is>
           <t>https://www.cimri.com/{kategori}/en-ucuz-{ürün-adı}-fiyatlari,{ürün-no}</t>
         </is>
       </c>
-      <c r="B1109" s="6" t="inlineStr">
+      <c r="B1111" s="6" t="inlineStr">
         <is>
           <t>cimri.com</t>
         </is>
       </c>
-      <c r="C1109" s="6" t="inlineStr">
+      <c r="C1111" s="6" t="inlineStr">
         <is>
           <t>Cimri ürün sayfaları: VitrA ve Artema SKU'ları için satıcı teklif listesi</t>
         </is>
       </c>
-      <c r="D1109" s="6" t="inlineStr">
-        <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
-        </is>
-      </c>
-      <c r="E1109" s="6" t="inlineStr">
+      <c r="D1111" s="6" t="inlineStr">
+        <is>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="E1111" s="6" t="inlineStr">
         <is>
           <t>19 ürün sayfası, 110 teklif; mecra, satıcı, fiyat, kargo ve kupon kodlu fiyat; 10'dan fazla teklifte 'fiyat teklifini gör' düğmesiyle liste genişletildi</t>
         </is>
       </c>
-      <c r="F1109" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1109" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1109" s="7" t="inlineStr">
+      <c r="F1111" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1111" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1111" s="7" t="inlineStr">
         <is>
           <t>D28</t>
         </is>
       </c>
     </row>
-    <row r="1110" ht="57" customHeight="1">
-      <c r="A1110" s="5" t="inlineStr">
+    <row r="1112" ht="57" customHeight="1">
+      <c r="A1112" s="5" t="inlineStr">
         <is>
           <t>https://www.cimri.com/{marka}-{kategori}?page={n}</t>
         </is>
       </c>
-      <c r="B1110" s="6" t="inlineStr">
+      <c r="B1112" s="6" t="inlineStr">
         <is>
           <t>cimri.com</t>
         </is>
       </c>
-      <c r="C1110" s="6" t="inlineStr">
+      <c r="C1112" s="6" t="inlineStr">
         <is>
           <t>Cimri marka ve kategori liste sayfaları: SKU eşleştirme için derin sayfa taraması</t>
         </is>
       </c>
-      <c r="D1110" s="6" t="inlineStr">
-        <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
-        </is>
-      </c>
-      <c r="E1110" s="6" t="inlineStr">
+      <c r="D1112" s="6" t="inlineStr">
+        <is>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="E1112" s="6" t="inlineStr">
         <is>
           <t>46 liste sayfası: VitrA klozet ve asma klozet 1-3, lavabo 1-7, banyo dolabı 1-6, rezervuar 1-4; Artema lavabo bataryası 1-8, banyo bataryası 1-5, ankastre banyo bataryası 1-3, duş seti 1-4, ara musluk 1-2; bu sayfalardan 9 SKU daha eşleşti</t>
         </is>
       </c>
-      <c r="F1110" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1110" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1110" s="7" t="inlineStr">
+      <c r="F1112" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1112" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1112" s="7" t="inlineStr">
         <is>
           <t>D28</t>
-        </is>
-      </c>
-    </row>
-    <row r="1111" ht="30" customHeight="1">
-      <c r="A1111" s="5" t="inlineStr">
-        <is>
-          <t>https://api.dataforseo.com/v3/merchant/google/products/task_post</t>
-        </is>
-      </c>
-      <c r="B1111" s="6" t="inlineStr">
-        <is>
-          <t>dataforseo.com</t>
-        </is>
-      </c>
-      <c r="C1111" s="6" t="inlineStr">
-        <is>
-          <t>Google Shopping ürün ve satıcı verisi (merchant/google/products ve sellers)</t>
-        </is>
-      </c>
-      <c r="D1111" s="6" t="inlineStr">
-        <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
-        </is>
-      </c>
-      <c r="E1111" s="6" t="inlineStr">
-        <is>
-          <t>30 kelime × 120 listeleme; 12 ürün için 24 satıcı listesi; asenkron task_post ve task_get/advanced</t>
-        </is>
-      </c>
-      <c r="F1111" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1111" s="6" t="inlineStr">
-        <is>
-          <t>API (DataForSEO)</t>
-        </is>
-      </c>
-      <c r="H1111" s="7" t="inlineStr">
-        <is>
-          <t>D25</t>
-        </is>
-      </c>
-    </row>
-    <row r="1112" ht="43.5" customHeight="1">
-      <c r="A1112" s="5" t="inlineStr">
-        <is>
-          <t>https://shopping.google.com</t>
-        </is>
-      </c>
-      <c r="B1112" s="6" t="inlineStr">
-        <is>
-          <t>google.com</t>
-        </is>
-      </c>
-      <c r="C1112" s="6" t="inlineStr">
-        <is>
-          <t>Google Shopping ilanları: kategori bazında fiyat, mecra ve satıcı dağılımı; VitrA ve Artema ürünlerinin satıcı listeleri</t>
-        </is>
-      </c>
-      <c r="D1112" s="6" t="inlineStr">
-        <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 22 Sonraki Adımlar</t>
-        </is>
-      </c>
-      <c r="E1112" s="6" t="inlineStr">
-        <is>
-          <t>27 kategori + 3 marka kelimesi × ilk 120 ilan; 12 VitrA ve Artema ürünü için 24 satıcı listesi; VitrA Online genel 27 kelimenin 12'sinde yer alıyor; Türkiye, masaüstü</t>
-        </is>
-      </c>
-      <c r="F1112" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1112" s="6" t="inlineStr">
-        <is>
-          <t>API (DataForSEO merchant)</t>
-        </is>
-      </c>
-      <c r="H1112" s="7" t="inlineStr">
-        <is>
-          <t>D25</t>
         </is>
       </c>
     </row>
     <row r="1113" ht="30" customHeight="1">
       <c r="A1113" s="5" t="inlineStr">
         <is>
-          <t>https://www.google.com.tr/search?q=site:akakce.com+{ürün+kodu}</t>
+          <t>https://api.dataforseo.com/v3/merchant/google/products/task_post</t>
         </is>
       </c>
       <c r="B1113" s="6" t="inlineStr">
         <is>
-          <t>google.com.tr</t>
+          <t>dataforseo.com</t>
         </is>
       </c>
       <c r="C1113" s="6" t="inlineStr">
         <is>
-          <t>Akakçe ve Cimri sonuçlarının Google SERP özetlerinden okunması (doğrudan erişim sınırlı kaldığında yedek yol)</t>
+          <t>Google Shopping ürün ve satıcı verisi (merchant/google/products ve sellers)</t>
         </is>
       </c>
       <c r="D1113" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1113" s="6" t="inlineStr">
         <is>
-          <t>Kategori site: sorguları, kategori liste sorguları ve VitrA/Artema ürün kodu sorguları; başlık, en düşük fiyat ve seçenek sayısı</t>
+          <t>30 kelime × 120 listeleme; 12 ürün için 24 satıcı listesi; asenkron task_post ve task_get/advanced</t>
         </is>
       </c>
       <c r="F1113" s="7" t="inlineStr">
@@ -47224,7 +47224,7 @@
       </c>
       <c r="G1113" s="6" t="inlineStr">
         <is>
-          <t>API (DataForSEO SERP)</t>
+          <t>API (DataForSEO)</t>
         </is>
       </c>
       <c r="H1113" s="7" t="inlineStr">
@@ -47233,30 +47233,30 @@
         </is>
       </c>
     </row>
-    <row r="1114" ht="30" customHeight="1">
+    <row r="1114" ht="43.5" customHeight="1">
       <c r="A1114" s="5" t="inlineStr">
         <is>
-          <t>https://www.hepsiburada.com/{ürün-adı}-pm-{HBC-kodu}</t>
+          <t>https://shopping.google.com</t>
         </is>
       </c>
       <c r="B1114" s="6" t="inlineStr">
         <is>
-          <t>hepsiburada.com</t>
+          <t>google.com</t>
         </is>
       </c>
       <c r="C1114" s="6" t="inlineStr">
         <is>
-          <t>Hepsiburada ürün sayfaları: 29 VitrA ve Artema SKU'sunun buybox, satıcı ve kampanya fiyatı</t>
+          <t>Google Shopping ilanları: kategori bazında fiyat, mecra ve satıcı dağılımı; VitrA ve Artema ürünlerinin satıcı listeleri</t>
         </is>
       </c>
       <c r="D1114" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E1114" s="6" t="inlineStr">
         <is>
-          <t>29 SKU için arama ve satıcı listesi (6 parti); buybox satıcısı, VitrA mağazası, en düşük diğer satıcı, kampanya fiyatı</t>
+          <t>27 kategori + 3 marka kelimesi × ilk 120 ilan; 12 VitrA ve Artema ürünü için 24 satıcı listesi; VitrA Online genel 27 kelimenin 12'sinde yer alıyor; Türkiye, masaüstü</t>
         </is>
       </c>
       <c r="F1114" s="7" t="inlineStr">
@@ -47266,39 +47266,39 @@
       </c>
       <c r="G1114" s="6" t="inlineStr">
         <is>
-          <t>tarayıcı (Playwright)</t>
+          <t>API (DataForSEO merchant)</t>
         </is>
       </c>
       <c r="H1114" s="7" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D25</t>
         </is>
       </c>
     </row>
     <row r="1115" ht="30" customHeight="1">
       <c r="A1115" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/artema-vitra-gr-set-768-1851tp740-2240a4145829a41441-800-2025-gomme-set-soft-bakir/p/5001431803</t>
+          <t>https://www.google.com.tr/search?q=site:akakce.com+{ürün+kodu}</t>
         </is>
       </c>
       <c r="B1115" s="6" t="inlineStr">
         <is>
-          <t>koctas.com.tr</t>
+          <t>google.com.tr</t>
         </is>
       </c>
       <c r="C1115" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: V8 Gömme Rezervuar Seti (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Akakçe ve Cimri sonuçlarının Google SERP özetlerinden okunması (doğrudan erişim sınırlı kaldığında yedek yol)</t>
         </is>
       </c>
       <c r="D1115" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1115" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 9.000 TL; satıcı: Newbanyo</t>
+          <t>Kategori site: sorguları, kategori liste sorguları ve VitrA/Artema ürün kodu sorguları; başlık, en düşük fiyat ve seçenek sayısı</t>
         </is>
       </c>
       <c r="F1115" s="7" t="inlineStr">
@@ -47308,39 +47308,39 @@
       </c>
       <c r="G1115" s="6" t="inlineStr">
         <is>
-          <t>tarayıcı (Playwright)</t>
+          <t>API (DataForSEO SERP)</t>
         </is>
       </c>
       <c r="H1115" s="7" t="inlineStr">
         <is>
-          <t>D26</t>
-        </is>
-      </c>
-    </row>
-    <row r="1116" ht="43.5" customHeight="1">
+          <t>D25</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116" ht="30" customHeight="1">
       <c r="A1116" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/kobos-artema-minimax-s-banyo-bataryasi-a41994/p/5000190223</t>
+          <t>https://www.hepsiburada.com/{ürün-adı}-pm-{HBC-kodu}</t>
         </is>
       </c>
       <c r="B1116" s="6" t="inlineStr">
         <is>
-          <t>koctas.com.tr</t>
+          <t>hepsiburada.com</t>
         </is>
       </c>
       <c r="C1116" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: Minimax S Banyo Bataryası (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Hepsiburada ürün sayfaları: 29 VitrA ve Artema SKU'sunun buybox, satıcı ve kampanya fiyatı</t>
         </is>
       </c>
       <c r="D1116" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1116" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 4742,7 TL, sepette 4.500 TL; satıcı: Banyoline; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>29 SKU için arama ve satıcı listesi (6 parti); buybox satıcısı, VitrA mağazası, en düşük diğer satıcı, kampanya fiyatı</t>
         </is>
       </c>
       <c r="F1116" s="7" t="inlineStr">
@@ -47362,7 +47362,7 @@
     <row r="1117" ht="30" customHeight="1">
       <c r="A1117" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/orka-vitra-mia-banyo-boy-dolabi-parlak-beyaz-66166/p/5002584857</t>
+          <t>https://www.koctas.com.tr/artema-vitra-gr-set-768-1851tp740-2240a4145829a41441-800-2025-gomme-set-soft-bakir/p/5001431803</t>
         </is>
       </c>
       <c r="B1117" s="6" t="inlineStr">
@@ -47372,17 +47372,17 @@
       </c>
       <c r="C1117" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: Mia Boy Dolabı (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: V8 Gömme Rezervuar Seti (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1117" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1117" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 14744,9 TL; satıcı: Banyoatelier; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı 9.000 TL; satıcı: Newbanyo</t>
         </is>
       </c>
       <c r="F1117" s="7" t="inlineStr">
@@ -47404,7 +47404,7 @@
     <row r="1118" ht="43.5" customHeight="1">
       <c r="A1118" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-arkitekt-ses-yok-kapak-model-2-opal-yavas-kapanir-nuvoplast-109-003-909/p/5002747747</t>
+          <t>https://www.koctas.com.tr/kobos-artema-minimax-s-banyo-bataryasi-a41994/p/5000190223</t>
         </is>
       </c>
       <c r="B1118" s="6" t="inlineStr">
@@ -47414,17 +47414,17 @@
       </c>
       <c r="C1118" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: Universal Klozet Kapağı (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: Minimax S Banyo Bataryası (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1118" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1118" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 1.799 TL; satıcı: Bataryamarket; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı 4742,7 TL, sepette 4.500 TL; satıcı: Banyoline; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1118" s="7" t="inlineStr">
@@ -47446,7 +47446,7 @@
     <row r="1119" ht="30" customHeight="1">
       <c r="A1119" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-asma-klozet-sento-rim-ex-kanalsiz-7748b003-0559/p/5002747769</t>
+          <t>https://www.koctas.com.tr/orka-vitra-mia-banyo-boy-dolabi-parlak-beyaz-66166/p/5002584857</t>
         </is>
       </c>
       <c r="B1119" s="6" t="inlineStr">
@@ -47456,17 +47456,17 @@
       </c>
       <c r="C1119" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: Sento Asma Klozet (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: Mia Boy Dolabı (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1119" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1119" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 18.095 TL; satıcı: Hace Yapı</t>
+          <t>Koçtaş liste fiyatı 14744,9 TL; satıcı: Banyoatelier; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1119" s="7" t="inlineStr">
@@ -47488,7 +47488,7 @@
     <row r="1120" ht="43.5" customHeight="1">
       <c r="A1120" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-flow-round-lavabo-bataryasi-a42923/p/5003035907</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-arkitekt-ses-yok-kapak-model-2-opal-yavas-kapanir-nuvoplast-109-003-909/p/5002747747</t>
         </is>
       </c>
       <c r="B1120" s="6" t="inlineStr">
@@ -47498,17 +47498,17 @@
       </c>
       <c r="C1120" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: Flow Round Lavabo Bataryası (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: Universal Klozet Kapağı (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1120" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1120" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 3.998 TL, sepette 3.998 TL; satıcı: Serhat Yapı</t>
+          <t>Koçtaş liste fiyatı 1.799 TL; satıcı: Bataryamarket; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1120" s="7" t="inlineStr">
@@ -47530,7 +47530,7 @@
     <row r="1121" ht="30" customHeight="1">
       <c r="A1121" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-integra-7041b003-0090-rim-ex-asma-klozet-54-cm-beyaz/p/5000568297</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-asma-klozet-sento-rim-ex-kanalsiz-7748b003-0559/p/5002747769</t>
         </is>
       </c>
       <c r="B1121" s="6" t="inlineStr">
@@ -47540,17 +47540,17 @@
       </c>
       <c r="C1121" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: Integra Asma klozet (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: Sento Asma Klozet (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1121" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1121" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 11852,6 TL, sepette 10667,3 TL; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı 18.095 TL; satıcı: Hace Yapı</t>
         </is>
       </c>
       <c r="F1121" s="7" t="inlineStr">
@@ -47569,10 +47569,10 @@
         </is>
       </c>
     </row>
-    <row r="1122" ht="30" customHeight="1">
+    <row r="1122" ht="43.5" customHeight="1">
       <c r="A1122" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-klozet-ic-takimi-tek-basmali-rezervuar-ic-takimi-330b-1314/p/5000219065</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-flow-round-lavabo-bataryasi-a42923/p/5003035907</t>
         </is>
       </c>
       <c r="B1122" s="6" t="inlineStr">
@@ -47582,17 +47582,17 @@
       </c>
       <c r="C1122" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: İç Takım (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: Flow Round Lavabo Bataryası (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1122" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1122" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 961,5 TL, sepette 961,5 TL; satıcı: Evdeniste</t>
+          <t>Koçtaş liste fiyatı 3.998 TL, sepette 3.998 TL; satıcı: Serhat Yapı</t>
         </is>
       </c>
       <c r="F1122" s="7" t="inlineStr">
@@ -47614,7 +47614,7 @@
     <row r="1123" ht="30" customHeight="1">
       <c r="A1123" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-mat-siyah-8-cm-gomme-rezervuar-seti-800-1896/p/5002014782</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-integra-7041b003-0090-rim-ex-asma-klozet-54-cm-beyaz/p/5000568297</t>
         </is>
       </c>
       <c r="B1123" s="6" t="inlineStr">
@@ -47624,17 +47624,17 @@
       </c>
       <c r="C1123" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: V8 Gömme Rezervuar Seti (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: Integra Asma klozet (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1123" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1123" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 6778,6 TL; satıcı: Evdeniste</t>
+          <t>Koçtaş liste fiyatı 11852,6 TL, sepette 10667,3 TL; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1123" s="7" t="inlineStr">
@@ -47656,7 +47656,7 @@
     <row r="1124" ht="30" customHeight="1">
       <c r="A1124" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-mia-banyo-dolabi-seti-80cm-cekmeceli-altin-mese-67093/p/5002741327</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-klozet-ic-takimi-tek-basmali-rezervuar-ic-takimi-330b-1314/p/5000219065</t>
         </is>
       </c>
       <c r="B1124" s="6" t="inlineStr">
@@ -47666,17 +47666,17 @@
       </c>
       <c r="C1124" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: Mia Banyo Dolabı Seti (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: İç Takım (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1124" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1124" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 20562,9 TL; satıcı: Banyoatelier</t>
+          <t>Koçtaş liste fiyatı 961,5 TL, sepette 961,5 TL; satıcı: Evdeniste</t>
         </is>
       </c>
       <c r="F1124" s="7" t="inlineStr">
@@ -47698,7 +47698,7 @@
     <row r="1125" ht="30" customHeight="1">
       <c r="A1125" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-s20-lavabo-50-cm-5501l003-0001/p/5002077744</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-mat-siyah-8-cm-gomme-rezervuar-seti-800-1896/p/5002014782</t>
         </is>
       </c>
       <c r="B1125" s="6" t="inlineStr">
@@ -47708,17 +47708,17 @@
       </c>
       <c r="C1125" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: S20 Lavabo (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: V8 Gömme Rezervuar Seti (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1125" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1125" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 5690,5 TL, sepette 5121,5 TL; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı 6778,6 TL; satıcı: Evdeniste</t>
         </is>
       </c>
       <c r="F1125" s="7" t="inlineStr">
@@ -47740,7 +47740,7 @@
     <row r="1126" ht="30" customHeight="1">
       <c r="A1126" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-s20-square-asma-klozet-5505l003-0868-kapak-harictir-/p/5000188364</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-mia-banyo-dolabi-seti-80cm-cekmeceli-altin-mese-67093/p/5002741327</t>
         </is>
       </c>
       <c r="B1126" s="6" t="inlineStr">
@@ -47750,17 +47750,17 @@
       </c>
       <c r="C1126" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: S20 Asma Klozet (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: Mia Banyo Dolabı Seti (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1126" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1126" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 7655,4 TL, sepette 6889,9 TL; satıcı: Evdema</t>
+          <t>Koçtaş liste fiyatı 20562,9 TL; satıcı: Banyoatelier</t>
         </is>
       </c>
       <c r="F1126" s="7" t="inlineStr">
@@ -47782,7 +47782,7 @@
     <row r="1127" ht="30" customHeight="1">
       <c r="A1127" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-s20-tezgahalti-lavabo-38-cm-5473b003-0618/p/5001980632</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-s20-lavabo-50-cm-5501l003-0001/p/5002077744</t>
         </is>
       </c>
       <c r="B1127" s="6" t="inlineStr">
@@ -47792,17 +47792,17 @@
       </c>
       <c r="C1127" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: S20 Tezgahaltı Lavabo (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: S20 Lavabo (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1127" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1127" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 5813,2 TL, sepette 5231,8 TL; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı 5690,5 TL, sepette 5121,5 TL; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1127" s="7" t="inlineStr">
@@ -47824,7 +47824,7 @@
     <row r="1128" ht="30" customHeight="1">
       <c r="A1128" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-sento-80-cm-mat-beyaz-kapakli-banyo-dolabi-alt-modul-lavabo-60785/p/5000429579</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-s20-square-asma-klozet-5505l003-0868-kapak-harictir-/p/5000188364</t>
         </is>
       </c>
       <c r="B1128" s="6" t="inlineStr">
@@ -47834,17 +47834,17 @@
       </c>
       <c r="C1128" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: Sento Lavabo Dolabı (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: S20 Asma Klozet (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1128" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1128" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 32941,3 TL, sepette 28000,1 TL; satıcı: Banyoline</t>
+          <t>Koçtaş liste fiyatı 7655,4 TL, sepette 6889,9 TL; satıcı: Evdema</t>
         </is>
       </c>
       <c r="F1128" s="7" t="inlineStr">
@@ -47866,7 +47866,7 @@
     <row r="1129" ht="30" customHeight="1">
       <c r="A1129" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-universal-2-nuvoplast-soft-klozet-kapagi-121-003-909/p/5000219070</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-s20-tezgahalti-lavabo-38-cm-5473b003-0618/p/5001980632</t>
         </is>
       </c>
       <c r="B1129" s="6" t="inlineStr">
@@ -47876,17 +47876,17 @@
       </c>
       <c r="C1129" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: Universal Klozet Kapağı (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: S20 Tezgahaltı Lavabo (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1129" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1129" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 1764,5 TL; satıcı: Evdeniste</t>
+          <t>Koçtaş liste fiyatı 5813,2 TL, sepette 5231,8 TL; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1129" s="7" t="inlineStr">
@@ -47905,10 +47905,10 @@
         </is>
       </c>
     </row>
-    <row r="1130" ht="43.5" customHeight="1">
+    <row r="1130" ht="30" customHeight="1">
       <c r="A1130" s="5" t="inlineStr">
         <is>
-          <t>https://www.koctas.com.tr/vitra-vitra-v8-asma-klozetler-icin-gomme-rezervuar-768-1851-01/p/5000623346</t>
+          <t>https://www.koctas.com.tr/vitra-vitra-sento-80-cm-mat-beyaz-kapakli-banyo-dolabi-alt-modul-lavabo-60785/p/5000429579</t>
         </is>
       </c>
       <c r="B1130" s="6" t="inlineStr">
@@ -47918,17 +47918,17 @@
       </c>
       <c r="C1130" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş ürün sayfası: V-Fix Prime 8cm Asma Klozetler için Gömme Rezervuar (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+          <t>Koçtaş ürün sayfası: Sento Lavabo Dolabı (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
         </is>
       </c>
       <c r="D1130" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1130" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 5.605 TL, sepette 5044,5 TL; satıcı: Banyome</t>
+          <t>Koçtaş liste fiyatı 32941,3 TL, sepette 28000,1 TL; satıcı: Banyoline</t>
         </is>
       </c>
       <c r="F1130" s="7" t="inlineStr">
@@ -47950,163 +47950,163 @@
     <row r="1131" ht="30" customHeight="1">
       <c r="A1131" s="5" t="inlineStr">
         <is>
+          <t>https://www.koctas.com.tr/vitra-vitra-universal-2-nuvoplast-soft-klozet-kapagi-121-003-909/p/5000219070</t>
+        </is>
+      </c>
+      <c r="B1131" s="6" t="inlineStr">
+        <is>
+          <t>koctas.com.tr</t>
+        </is>
+      </c>
+      <c r="C1131" s="6" t="inlineStr">
+        <is>
+          <t>Koçtaş ürün sayfası: Universal Klozet Kapağı (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+        </is>
+      </c>
+      <c r="D1131" s="6" t="inlineStr">
+        <is>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="E1131" s="6" t="inlineStr">
+        <is>
+          <t>Koçtaş liste fiyatı 1764,5 TL; satıcı: Evdeniste</t>
+        </is>
+      </c>
+      <c r="F1131" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1131" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Playwright)</t>
+        </is>
+      </c>
+      <c r="H1131" s="7" t="inlineStr">
+        <is>
+          <t>D26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132" ht="43.5" customHeight="1">
+      <c r="A1132" s="5" t="inlineStr">
+        <is>
+          <t>https://www.koctas.com.tr/vitra-vitra-v8-asma-klozetler-icin-gomme-rezervuar-768-1851-01/p/5000623346</t>
+        </is>
+      </c>
+      <c r="B1132" s="6" t="inlineStr">
+        <is>
+          <t>koctas.com.tr</t>
+        </is>
+      </c>
+      <c r="C1132" s="6" t="inlineStr">
+        <is>
+          <t>Koçtaş ürün sayfası: V-Fix Prime 8cm Asma Klozetler için Gömme Rezervuar (kanal fiyat karşılaştırması için Koçtaş liste ve sepet fiyatı)</t>
+        </is>
+      </c>
+      <c r="D1132" s="6" t="inlineStr">
+        <is>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="E1132" s="6" t="inlineStr">
+        <is>
+          <t>Koçtaş liste fiyatı 5.605 TL, sepette 5044,5 TL; satıcı: Banyome</t>
+        </is>
+      </c>
+      <c r="F1132" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1132" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Playwright)</t>
+        </is>
+      </c>
+      <c r="H1132" s="7" t="inlineStr">
+        <is>
+          <t>D26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133" ht="30" customHeight="1">
+      <c r="A1133" s="5" t="inlineStr">
+        <is>
           <t>https://www.trendyol.com/sr?wc=104210&amp;sst=BEST_SELLER</t>
         </is>
       </c>
-      <c r="B1131" s="6" t="inlineStr">
+      <c r="B1133" s="6" t="inlineStr">
         <is>
           <t>trendyol.com</t>
         </is>
       </c>
-      <c r="C1131" s="6" t="inlineStr">
+      <c r="C1133" s="6" t="inlineStr">
         <is>
           <t>Trendyol banyo aksesuar seti çok satanlar listesi (ilk 36 ürün: satıcı, indirim ve 3. taraf payı)</t>
         </is>
       </c>
-      <c r="D1131" s="6" t="inlineStr">
-        <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
-        </is>
-      </c>
-      <c r="E1131" s="6" t="inlineStr">
+      <c r="D1133" s="6" t="inlineStr">
+        <is>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="E1133" s="6" t="inlineStr">
         <is>
           <t>ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi</t>
         </is>
       </c>
-      <c r="F1131" s="7" t="inlineStr">
+      <c r="F1133" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1131" s="6" t="inlineStr">
+      <c r="G1133" s="6" t="inlineStr">
         <is>
           <t>API (Apify)</t>
         </is>
       </c>
-      <c r="H1131" s="7" t="inlineStr">
+      <c r="H1133" s="7" t="inlineStr">
         <is>
           <t>D26</t>
         </is>
       </c>
     </row>
-    <row r="1132" ht="30" customHeight="1">
-      <c r="A1132" s="5" t="inlineStr">
+    <row r="1134" ht="30" customHeight="1">
+      <c r="A1134" s="5" t="inlineStr">
         <is>
           <t>https://www.trendyol.com/sr?wc=166316&amp;sst=BEST_SELLER</t>
         </is>
       </c>
-      <c r="B1132" s="6" t="inlineStr">
+      <c r="B1134" s="6" t="inlineStr">
         <is>
           <t>trendyol.com</t>
         </is>
       </c>
-      <c r="C1132" s="6" t="inlineStr">
+      <c r="C1134" s="6" t="inlineStr">
         <is>
           <t>Trendyol çamaşır makinesi dolabı çok satanlar listesi (ilk 36 ürün: satıcı, indirim ve 3. taraf payı)</t>
         </is>
       </c>
-      <c r="D1132" s="6" t="inlineStr">
-        <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
-        </is>
-      </c>
-      <c r="E1132" s="6" t="inlineStr">
+      <c r="D1134" s="6" t="inlineStr">
+        <is>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="E1134" s="6" t="inlineStr">
         <is>
           <t>ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi</t>
         </is>
       </c>
-      <c r="F1132" s="7" t="inlineStr">
+      <c r="F1134" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1132" s="6" t="inlineStr">
+      <c r="G1134" s="6" t="inlineStr">
         <is>
           <t>API (Apify)</t>
-        </is>
-      </c>
-      <c r="H1132" s="7" t="inlineStr">
-        <is>
-          <t>D26</t>
-        </is>
-      </c>
-    </row>
-    <row r="1133" ht="43.5" customHeight="1">
-      <c r="A1133" s="5" t="inlineStr">
-        <is>
-          <t>https://www.trendyol.com/{marka}/{ürün-adı}-p-{ürün-no}</t>
-        </is>
-      </c>
-      <c r="B1133" s="6" t="inlineStr">
-        <is>
-          <t>trendyol.com</t>
-        </is>
-      </c>
-      <c r="C1133" s="6" t="inlineStr">
-        <is>
-          <t>Trendyol çok satan ürün sayfaları: fiyat, marka, satıcı, değerlendirme (14 kategori × 36 ürün)</t>
-        </is>
-      </c>
-      <c r="D1133" s="6" t="inlineStr">
-        <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
-        </is>
-      </c>
-      <c r="E1133" s="6" t="inlineStr">
-        <is>
-          <t>504 ürün kaydı (ilk 36 × 14 kategori); SSG kategorilerinde satışın %78-89'u 3. taraf satıcıda; banyo mobilyası ve duşakabin listelerinde marka mağazaları öne çıkıyor</t>
-        </is>
-      </c>
-      <c r="F1133" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1133" s="6" t="inlineStr">
-        <is>
-          <t>API (Apify)</t>
-        </is>
-      </c>
-      <c r="H1133" s="7" t="inlineStr">
-        <is>
-          <t>D26</t>
-        </is>
-      </c>
-    </row>
-    <row r="1134" ht="43.5" customHeight="1">
-      <c r="A1134" s="5" t="inlineStr">
-        <is>
-          <t>https://www.vitra.com.tr/asma-klozetler-icin-gomme-rezervuarlar/v-fix-prime-8cm-asma-klozetler-icin-gomme-rezervuar-p-768-1851-01</t>
-        </is>
-      </c>
-      <c r="B1134" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr</t>
-        </is>
-      </c>
-      <c r="C1134" s="6" t="inlineStr">
-        <is>
-          <t>VitrA ürün sayfası: V-Fix Prime 8cm Asma Klozetler için Gömme Rezervuar (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
-        </is>
-      </c>
-      <c r="D1134" s="6" t="inlineStr">
-        <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
-        </is>
-      </c>
-      <c r="E1134" s="6" t="inlineStr">
-        <is>
-          <t>kod 768-1851-01; liste fiyatı 5.730 TL; sepette 5.157 TL; stokta; en düşük liste fiyatı 4923,9 TL (TY 3P (YAPIEVİ)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
-        </is>
-      </c>
-      <c r="F1134" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1134" s="6" t="inlineStr">
-        <is>
-          <t>curl · tarayıcı (Playwright)</t>
         </is>
       </c>
       <c r="H1134" s="7" t="inlineStr">
@@ -48118,27 +48118,27 @@
     <row r="1135" ht="43.5" customHeight="1">
       <c r="A1135" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/asma-klozetler/integra-asma-klozet-beyaz-p-7041b003-0090</t>
+          <t>https://www.trendyol.com/{marka}/{ürün-adı}-p-{ürün-no}</t>
         </is>
       </c>
       <c r="B1135" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr</t>
+          <t>trendyol.com</t>
         </is>
       </c>
       <c r="C1135" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Integra Asma klozet (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>Trendyol çok satan ürün sayfaları: fiyat, marka, satıcı, değerlendirme (14 kategori × 36 ürün)</t>
         </is>
       </c>
       <c r="D1135" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1135" s="6" t="inlineStr">
         <is>
-          <t>kod 7041B003-0090; liste fiyatı 12.027 TL; sepette 10824,3 TL; stokta; en düşük liste fiyatı 11852,6 TL (TY 3P (Evdema)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>504 ürün kaydı (ilk 36 × 14 kategori); SSG kategorilerinde satışın %78-89'u 3. taraf satıcıda; banyo mobilyası ve duşakabin listelerinde marka mağazaları öne çıkıyor</t>
         </is>
       </c>
       <c r="F1135" s="7" t="inlineStr">
@@ -48148,7 +48148,7 @@
       </c>
       <c r="G1135" s="6" t="inlineStr">
         <is>
-          <t>curl · tarayıcı (Playwright)</t>
+          <t>API (Apify)</t>
         </is>
       </c>
       <c r="H1135" s="7" t="inlineStr">
@@ -48160,7 +48160,7 @@
     <row r="1136" ht="43.5" customHeight="1">
       <c r="A1136" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/asma-klozetler/s20-asma-klozet-beyaz-p-5505l003-0868</t>
+          <t>https://www.vitra.com.tr/asma-klozetler-icin-gomme-rezervuarlar/v-fix-prime-8cm-asma-klozetler-icin-gomme-rezervuar-p-768-1851-01</t>
         </is>
       </c>
       <c r="B1136" s="6" t="inlineStr">
@@ -48170,17 +48170,17 @@
       </c>
       <c r="C1136" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: S20 Asma Klozet (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: V-Fix Prime 8cm Asma Klozetler için Gömme Rezervuar (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1136" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1136" s="6" t="inlineStr">
         <is>
-          <t>kod 5505L003-0868; liste fiyatı 6.455 TL; sepette 5809,5 TL; stokta yok; en düşük liste fiyatı 6.455 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 768-1851-01; liste fiyatı 5.730 TL; sepette 5.157 TL; stokta; en düşük liste fiyatı 4923,9 TL (TY 3P (YAPIEVİ)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1136" s="7" t="inlineStr">
@@ -48202,7 +48202,7 @@
     <row r="1137" ht="43.5" customHeight="1">
       <c r="A1137" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/asma-klozetler/s50-asma-klozet-beyaz-p-5618l003-0850</t>
+          <t>https://www.vitra.com.tr/asma-klozetler/integra-asma-klozet-beyaz-p-7041b003-0090</t>
         </is>
       </c>
       <c r="B1137" s="6" t="inlineStr">
@@ -48212,17 +48212,17 @@
       </c>
       <c r="C1137" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: S50 Asma Klozet (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Integra Asma klozet (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1137" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1137" s="6" t="inlineStr">
         <is>
-          <t>kod 5618L003-0850; liste fiyatı 8.663 TL; sepette 7363,6 TL; stokta yok; en düşük liste fiyatı 8.663 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 7041B003-0090; liste fiyatı 12.027 TL; sepette 10824,3 TL; stokta; en düşük liste fiyatı 11852,6 TL (TY 3P (Evdema)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1137" s="7" t="inlineStr">
@@ -48244,7 +48244,7 @@
     <row r="1138" ht="43.5" customHeight="1">
       <c r="A1138" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/asma-klozetler/sento-asma-klozet-beyaz-p-7748b003-0559</t>
+          <t>https://www.vitra.com.tr/asma-klozetler/s20-asma-klozet-beyaz-p-5505l003-0868</t>
         </is>
       </c>
       <c r="B1138" s="6" t="inlineStr">
@@ -48254,17 +48254,17 @@
       </c>
       <c r="C1138" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Sento Asma Klozet (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: S20 Asma Klozet (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1138" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1138" s="6" t="inlineStr">
         <is>
-          <t>kod 7748B003-0559; liste fiyatı 14.767 TL; sepette 12552,0 TL; stokta; en düşük liste fiyatı 14.767 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 5505L003-0868; liste fiyatı 6.455 TL; sepette 5809,5 TL; stokta yok; en düşük liste fiyatı 6.455 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1138" s="7" t="inlineStr">
@@ -48286,7 +48286,7 @@
     <row r="1139" ht="43.5" customHeight="1">
       <c r="A1139" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/banyo-boy-dolaplari/mia-boy-dolabi-parlak-beyaz-p-66166</t>
+          <t>https://www.vitra.com.tr/asma-klozetler/s50-asma-klozet-beyaz-p-5618l003-0850</t>
         </is>
       </c>
       <c r="B1139" s="6" t="inlineStr">
@@ -48296,17 +48296,17 @@
       </c>
       <c r="C1139" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Mia Boy Dolabı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: S50 Asma Klozet (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1139" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1139" s="6" t="inlineStr">
         <is>
-          <t>kod 66166; liste fiyatı 9.992 TL; sepette 8493,2 TL; stokta; en düşük liste fiyatı 9.992 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 5618L003-0850; liste fiyatı 8.663 TL; sepette 7363,6 TL; stokta yok; en düşük liste fiyatı 8.663 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1139" s="7" t="inlineStr">
@@ -48328,7 +48328,7 @@
     <row r="1140" ht="43.5" customHeight="1">
       <c r="A1140" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/banyo-boy-dolaplari/sento-boy-dolabi-mat-beyaz-p-60848</t>
+          <t>https://www.vitra.com.tr/asma-klozetler/sento-asma-klozet-beyaz-p-7748b003-0559</t>
         </is>
       </c>
       <c r="B1140" s="6" t="inlineStr">
@@ -48338,17 +48338,17 @@
       </c>
       <c r="C1140" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Sento Boy Dolabı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Sento Asma Klozet (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1140" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1140" s="6" t="inlineStr">
         <is>
-          <t>kod 60848; liste fiyatı 27.377 TL; sepette 23270,5 TL; stokta; en düşük liste fiyatı 27.377 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 7748B003-0559; liste fiyatı 14.767 TL; sepette 12552,0 TL; stokta; en düşük liste fiyatı 14.767 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1140" s="7" t="inlineStr">
@@ -48370,7 +48370,7 @@
     <row r="1141" ht="43.5" customHeight="1">
       <c r="A1141" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/banyo-set-modulleri/mia-banyo-dolabi-seti-altin-mese-p-67093</t>
+          <t>https://www.vitra.com.tr/banyo-boy-dolaplari/mia-boy-dolabi-parlak-beyaz-p-66166</t>
         </is>
       </c>
       <c r="B1141" s="6" t="inlineStr">
@@ -48380,17 +48380,17 @@
       </c>
       <c r="C1141" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Mia Banyo Dolabı Seti (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Mia Boy Dolabı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1141" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1141" s="6" t="inlineStr">
         <is>
-          <t>kod 67093; liste fiyatı 13.881 TL; sepette 12492,9 TL; stokta yok; en düşük liste fiyatı 12.500 TL (HB buybox (Damla Yapıı)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 66166; liste fiyatı 9.992 TL; sepette 8493,2 TL; stokta; en düşük liste fiyatı 9.992 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1141" s="7" t="inlineStr">
@@ -48412,7 +48412,7 @@
     <row r="1142" ht="43.5" customHeight="1">
       <c r="A1142" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/banyo-set-modulleri/mia-banyo-dolabi-seti-parlak-antrasit-p-75102</t>
+          <t>https://www.vitra.com.tr/banyo-boy-dolaplari/sento-boy-dolabi-mat-beyaz-p-60848</t>
         </is>
       </c>
       <c r="B1142" s="6" t="inlineStr">
@@ -48422,17 +48422,17 @@
       </c>
       <c r="C1142" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Mia Banyo Dolabı Seti (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Sento Boy Dolabı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1142" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1142" s="6" t="inlineStr">
         <is>
-          <t>kod 75102; liste fiyatı 12.387 TL; sepette 11148,3 TL; stokta yok; en düşük liste fiyatı 12.387 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 60848; liste fiyatı 27.377 TL; sepette 23270,5 TL; stokta; en düşük liste fiyatı 27.377 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1142" s="7" t="inlineStr">
@@ -48454,7 +48454,7 @@
     <row r="1143" ht="43.5" customHeight="1">
       <c r="A1143" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/dus-setleri/flow-round-ankastre-banyo-seti-krom-p-a49321</t>
+          <t>https://www.vitra.com.tr/banyo-set-modulleri/mia-banyo-dolabi-seti-altin-mese-p-67093</t>
         </is>
       </c>
       <c r="B1143" s="6" t="inlineStr">
@@ -48464,17 +48464,17 @@
       </c>
       <c r="C1143" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Flow Round Ankastre Banyo Seti (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Mia Banyo Dolabı Seti (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1143" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1143" s="6" t="inlineStr">
         <is>
-          <t>kod A49321; liste fiyatı 16.578 TL; sepette 14091,3 TL; stokta yok; en düşük liste fiyatı 13.450 TL (HB buybox (Cemretesyapi)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 67093; liste fiyatı 13.881 TL; sepette 12492,9 TL; stokta yok; en düşük liste fiyatı 12.500 TL (HB buybox (Damla Yapıı)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1143" s="7" t="inlineStr">
@@ -48496,7 +48496,7 @@
     <row r="1144" ht="43.5" customHeight="1">
       <c r="A1144" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/duvardan-banyo-bataryalari/flow-round-banyo-bataryasi-krom-p-a43057</t>
+          <t>https://www.vitra.com.tr/banyo-set-modulleri/mia-banyo-dolabi-seti-parlak-antrasit-p-75102</t>
         </is>
       </c>
       <c r="B1144" s="6" t="inlineStr">
@@ -48506,17 +48506,17 @@
       </c>
       <c r="C1144" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Flow Round Banyo Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Mia Banyo Dolabı Seti (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1144" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1144" s="6" t="inlineStr">
         <is>
-          <t>kod A43057; liste fiyatı 7.112 TL; sepette 6045,2 TL; stokta yok; en düşük liste fiyatı 4.190 TL (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 75102; liste fiyatı 12.387 TL; sepette 11148,3 TL; stokta yok; en düşük liste fiyatı 12.387 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1144" s="7" t="inlineStr">
@@ -48538,7 +48538,7 @@
     <row r="1145" ht="43.5" customHeight="1">
       <c r="A1145" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/duvardan-banyo-bataryalari/minimax-s-banyo-bataryasi-krom-p-a41994</t>
+          <t>https://www.vitra.com.tr/dus-setleri/flow-round-ankastre-banyo-seti-krom-p-a49321</t>
         </is>
       </c>
       <c r="B1145" s="6" t="inlineStr">
@@ -48548,17 +48548,17 @@
       </c>
       <c r="C1145" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Minimax S Banyo Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Flow Round Ankastre Banyo Seti (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1145" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1145" s="6" t="inlineStr">
         <is>
-          <t>kod A41994; liste fiyatı 5.907 TL; sepette 5316,3 TL; stokta yok; en düşük liste fiyatı 4.390 TL (TY 3P (AL-BA HOME)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A49321; liste fiyatı 16.578 TL; sepette 14091,3 TL; stokta yok; en düşük liste fiyatı 13.450 TL (HB buybox (Cemretesyapi)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1145" s="7" t="inlineStr">
@@ -48580,7 +48580,7 @@
     <row r="1146" ht="43.5" customHeight="1">
       <c r="A1146" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/gomme-rezervuar-setleri/v8-gomme-rezervuar-seti-p-800-1896</t>
+          <t>https://www.vitra.com.tr/duvardan-banyo-bataryalari/flow-round-banyo-bataryasi-krom-p-a43057</t>
         </is>
       </c>
       <c r="B1146" s="6" t="inlineStr">
@@ -48590,17 +48590,17 @@
       </c>
       <c r="C1146" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: V8 Gömme Rezervuar Seti (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Flow Round Banyo Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1146" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1146" s="6" t="inlineStr">
         <is>
-          <t>kod 800-1896; liste fiyatı 8.385 TL; stokta yok; en düşük liste fiyatı 5438,6 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A43057; liste fiyatı 7.112 TL; sepette 6045,2 TL; stokta yok; en düşük liste fiyatı 4.190 TL (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1146" s="7" t="inlineStr">
@@ -48622,7 +48622,7 @@
     <row r="1147" ht="43.5" customHeight="1">
       <c r="A1147" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/gomme-rezervuar-setleri/v8-gomme-rezervuar-seti-p-800-2025</t>
+          <t>https://www.vitra.com.tr/duvardan-banyo-bataryalari/minimax-s-banyo-bataryasi-krom-p-a41994</t>
         </is>
       </c>
       <c r="B1147" s="6" t="inlineStr">
@@ -48632,17 +48632,17 @@
       </c>
       <c r="C1147" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: V8 Gömme Rezervuar Seti (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Minimax S Banyo Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1147" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1147" s="6" t="inlineStr">
         <is>
-          <t>kod 800-2025; liste fiyatı 11.042 TL; stokta yok; en düşük liste fiyatı 9.000 TL (Koçtaş); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A41994; liste fiyatı 5.907 TL; sepette 5316,3 TL; stokta yok; en düşük liste fiyatı 4.390 TL (TY 3P (AL-BA HOME)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1147" s="7" t="inlineStr">
@@ -48664,7 +48664,7 @@
     <row r="1148" ht="43.5" customHeight="1">
       <c r="A1148" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/klozet-kapaklari/universal-klozet-kapagi-beyaz-p-109-003-909</t>
+          <t>https://www.vitra.com.tr/gomme-rezervuar-setleri/v8-gomme-rezervuar-seti-p-800-1896</t>
         </is>
       </c>
       <c r="B1148" s="6" t="inlineStr">
@@ -48674,17 +48674,17 @@
       </c>
       <c r="C1148" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Universal Klozet Kapağı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: V8 Gömme Rezervuar Seti (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1148" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1148" s="6" t="inlineStr">
         <is>
-          <t>kod 109-003-909; liste fiyatı 1.720 TL; sepette 1.462 TL; stokta; en düşük liste fiyatı 1.190 TL (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 800-1896; liste fiyatı 8.385 TL; stokta yok; en düşük liste fiyatı 5438,6 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1148" s="7" t="inlineStr">
@@ -48706,7 +48706,7 @@
     <row r="1149" ht="43.5" customHeight="1">
       <c r="A1149" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/klozet-kapaklari/universal-klozet-kapagi-beyaz-p-121-003-909</t>
+          <t>https://www.vitra.com.tr/gomme-rezervuar-setleri/v8-gomme-rezervuar-seti-p-800-2025</t>
         </is>
       </c>
       <c r="B1149" s="6" t="inlineStr">
@@ -48716,17 +48716,17 @@
       </c>
       <c r="C1149" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Universal Klozet Kapağı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: V8 Gömme Rezervuar Seti (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1149" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1149" s="6" t="inlineStr">
         <is>
-          <t>kod 121-003-909; liste fiyatı 1.720 TL; sepette 1.462 TL; stokta; en düşük liste fiyatı 1426,6 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 800-2025; liste fiyatı 11.042 TL; stokta yok; en düşük liste fiyatı 9.000 TL (Koçtaş); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1149" s="7" t="inlineStr">
@@ -48748,7 +48748,7 @@
     <row r="1150" ht="43.5" customHeight="1">
       <c r="A1150" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/klozet-kapaklari/universal-klozet-kapagi-beyaz-p-84-003-009</t>
+          <t>https://www.vitra.com.tr/klozet-kapaklari/universal-klozet-kapagi-beyaz-p-109-003-909</t>
         </is>
       </c>
       <c r="B1150" s="6" t="inlineStr">
@@ -48763,12 +48763,12 @@
       </c>
       <c r="D1150" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1150" s="6" t="inlineStr">
         <is>
-          <t>kod 84-003-009; liste fiyatı 2.612 TL; sepette 2220,2 TL; stokta; en düşük liste fiyatı 1900,9 TL (HB buybox (GEYLANİ DAYANIKLI TÜKETİM)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 109-003-909; liste fiyatı 1.720 TL; sepette 1.462 TL; stokta; en düşük liste fiyatı 1.190 TL (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1150" s="7" t="inlineStr">
@@ -48790,7 +48790,7 @@
     <row r="1151" ht="43.5" customHeight="1">
       <c r="A1151" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/lavabo-dahil-lavabo-dolaplari/sento-lavabo-dolabi-mat-beyaz-p-60785</t>
+          <t>https://www.vitra.com.tr/klozet-kapaklari/universal-klozet-kapagi-beyaz-p-121-003-909</t>
         </is>
       </c>
       <c r="B1151" s="6" t="inlineStr">
@@ -48800,17 +48800,17 @@
       </c>
       <c r="C1151" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Sento Lavabo Dolabı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Universal Klozet Kapağı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1151" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1151" s="6" t="inlineStr">
         <is>
-          <t>kod 60785; liste fiyatı 32.596 TL; sepette 27706,6 TL; stokta; en düşük liste fiyatı 32.596 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 121-003-909; liste fiyatı 1.720 TL; sepette 1.462 TL; stokta; en düşük liste fiyatı 1426,6 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1151" s="7" t="inlineStr">
@@ -48832,7 +48832,7 @@
     <row r="1152" ht="43.5" customHeight="1">
       <c r="A1152" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/lavabo-dahil-lavabo-dolaplari/sento-lavabo-dolabi-mat-beyaz-p-60812</t>
+          <t>https://www.vitra.com.tr/klozet-kapaklari/universal-klozet-kapagi-beyaz-p-84-003-009</t>
         </is>
       </c>
       <c r="B1152" s="6" t="inlineStr">
@@ -48842,17 +48842,17 @@
       </c>
       <c r="C1152" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Sento Lavabo Dolabı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Universal Klozet Kapağı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1152" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1152" s="6" t="inlineStr">
         <is>
-          <t>kod 60812; liste fiyatı 29.464 TL; sepette 26517,6 TL; stokta yok; en düşük liste fiyatı 29.464 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 84-003-009; liste fiyatı 2.612 TL; sepette 2220,2 TL; stokta; en düşük liste fiyatı 1900,9 TL (HB buybox (GEYLANİ DAYANIKLI TÜKETİM)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1152" s="7" t="inlineStr">
@@ -48874,7 +48874,7 @@
     <row r="1153" ht="43.5" customHeight="1">
       <c r="A1153" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/musluk-ve-ara-musluklar/filtreli-ara-musluk-krom-p-a45200</t>
+          <t>https://www.vitra.com.tr/lavabo-dahil-lavabo-dolaplari/sento-lavabo-dolabi-mat-beyaz-p-60785</t>
         </is>
       </c>
       <c r="B1153" s="6" t="inlineStr">
@@ -48884,17 +48884,17 @@
       </c>
       <c r="C1153" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Filtreli Ara Musluk (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Sento Lavabo Dolabı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1153" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1153" s="6" t="inlineStr">
         <is>
-          <t>kod A45200; liste fiyatı 427 TL; sepette 362,9 TL; stokta; en düşük liste fiyatı 311,1 TL (TY 3P (YAPIEVİ)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 60785; liste fiyatı 32.596 TL; sepette 27706,6 TL; stokta; en düşük liste fiyatı 32.596 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1153" s="7" t="inlineStr">
@@ -48916,7 +48916,7 @@
     <row r="1154" ht="43.5" customHeight="1">
       <c r="A1154" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/musluk-ve-ara-musluklar/filtreli-camasir-muslugu-krom-p-a45228</t>
+          <t>https://www.vitra.com.tr/lavabo-dahil-lavabo-dolaplari/sento-lavabo-dolabi-mat-beyaz-p-60812</t>
         </is>
       </c>
       <c r="B1154" s="6" t="inlineStr">
@@ -48926,17 +48926,17 @@
       </c>
       <c r="C1154" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Filtreli Çamaşır Musluğu (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Sento Lavabo Dolabı (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1154" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1154" s="6" t="inlineStr">
         <is>
-          <t>kod A45228; liste fiyatı 427 TL; sepette 362,9 TL; stokta; en düşük liste fiyatı 360 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 60812; liste fiyatı 29.464 TL; sepette 26517,6 TL; stokta yok; en düşük liste fiyatı 29.464 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1154" s="7" t="inlineStr">
@@ -48958,7 +48958,7 @@
     <row r="1155" ht="43.5" customHeight="1">
       <c r="A1155" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/rezervuar-ve-klozet-ic-takimlari/ic-takim-p-330b1314</t>
+          <t>https://www.vitra.com.tr/musluk-ve-ara-musluklar/filtreli-ara-musluk-krom-p-a45200</t>
         </is>
       </c>
       <c r="B1155" s="6" t="inlineStr">
@@ -48968,17 +48968,17 @@
       </c>
       <c r="C1155" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: İç Takım (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Filtreli Ara Musluk (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1155" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1155" s="6" t="inlineStr">
         <is>
-          <t>kod 330B1314; liste fiyatı 896 TL; sepette 761,6 TL; stokta; en düşük liste fiyatı 675 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A45200; liste fiyatı 427 TL; sepette 362,9 TL; stokta; en düşük liste fiyatı 311,1 TL (TY 3P (YAPIEVİ)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1155" s="7" t="inlineStr">
@@ -49000,7 +49000,7 @@
     <row r="1156" ht="43.5" customHeight="1">
       <c r="A1156" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/standart-lavabo-ve-ayaklari/s20-lavabo-beyaz-p-5501l003-0001</t>
+          <t>https://www.vitra.com.tr/musluk-ve-ara-musluklar/filtreli-camasir-muslugu-krom-p-a45228</t>
         </is>
       </c>
       <c r="B1156" s="6" t="inlineStr">
@@ -49010,17 +49010,17 @@
       </c>
       <c r="C1156" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: S20 Lavabo (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Filtreli Çamaşır Musluğu (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1156" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1156" s="6" t="inlineStr">
         <is>
-          <t>kod 5501L003-0001; liste fiyatı 4.791 TL; sepette 4072,3 TL; stokta yok; en düşük liste fiyatı 4.791 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A45228; liste fiyatı 427 TL; sepette 362,9 TL; stokta; en düşük liste fiyatı 360 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1156" s="7" t="inlineStr">
@@ -49042,7 +49042,7 @@
     <row r="1157" ht="43.5" customHeight="1">
       <c r="A1157" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/takim-klozetler/zentrum-takim-klozet-beyaz-p-7783l003-0092</t>
+          <t>https://www.vitra.com.tr/rezervuar-ve-klozet-ic-takimlari/ic-takim-p-330b1314</t>
         </is>
       </c>
       <c r="B1157" s="6" t="inlineStr">
@@ -49052,17 +49052,17 @@
       </c>
       <c r="C1157" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Zentrum Takım Klozet (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: İç Takım (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1157" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1157" s="6" t="inlineStr">
         <is>
-          <t>kod 7783L003-0092; liste fiyatı 8.813 TL; sepette 7931,7 TL; stokta yok; en düşük liste fiyatı 8.813 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 330B1314; liste fiyatı 896 TL; sepette 761,6 TL; stokta; en düşük liste fiyatı 675 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1157" s="7" t="inlineStr">
@@ -49084,7 +49084,7 @@
     <row r="1158" ht="43.5" customHeight="1">
       <c r="A1158" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/tek-armatur-delikli-lavabo-bataryalari/flow-round-lavabo-bataryasi-krom-p-a42923</t>
+          <t>https://www.vitra.com.tr/standart-lavabo-ve-ayaklari/s20-lavabo-beyaz-p-5501l003-0001</t>
         </is>
       </c>
       <c r="B1158" s="6" t="inlineStr">
@@ -49094,17 +49094,17 @@
       </c>
       <c r="C1158" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Flow Round Lavabo Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: S20 Lavabo (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1158" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1158" s="6" t="inlineStr">
         <is>
-          <t>kod A42923; liste fiyatı 4.707 TL; sepette 4000,9 TL; stokta yok; en düşük liste fiyatı 2.999 TL (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 5501L003-0001; liste fiyatı 4.791 TL; sepette 4072,3 TL; stokta yok; en düşük liste fiyatı 4.791 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1158" s="7" t="inlineStr">
@@ -49126,7 +49126,7 @@
     <row r="1159" ht="43.5" customHeight="1">
       <c r="A1159" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/tek-armatur-delikli-lavabo-bataryalari/shift-t10-lavabo-bataryasi-krom-p-a43715</t>
+          <t>https://www.vitra.com.tr/takim-klozetler/zentrum-takim-klozet-beyaz-p-7783l003-0092</t>
         </is>
       </c>
       <c r="B1159" s="6" t="inlineStr">
@@ -49136,17 +49136,17 @@
       </c>
       <c r="C1159" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Shift T10 Lavabo Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Zentrum Takım Klozet (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1159" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1159" s="6" t="inlineStr">
         <is>
-          <t>kod A43715; liste fiyatı 4.707 TL; sepette 4236,3 TL; stokta; en düşük liste fiyatı 2.989 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 7783L003-0092; liste fiyatı 8.813 TL; sepette 7931,7 TL; stokta yok; en düşük liste fiyatı 8.813 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1159" s="7" t="inlineStr">
@@ -49168,7 +49168,7 @@
     <row r="1160" ht="43.5" customHeight="1">
       <c r="A1160" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/tek-armatur-delikli-lavabo-bataryalari/solid-s-lavabo-bataryasi-krom-p-a42484</t>
+          <t>https://www.vitra.com.tr/tek-armatur-delikli-lavabo-bataryalari/flow-round-lavabo-bataryasi-krom-p-a42923</t>
         </is>
       </c>
       <c r="B1160" s="6" t="inlineStr">
@@ -49178,17 +49178,17 @@
       </c>
       <c r="C1160" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: Solid S Lavabo Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Flow Round Lavabo Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1160" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1160" s="6" t="inlineStr">
         <is>
-          <t>kod A42484; liste fiyatı 5.016 TL; sepette 4514,4 TL; stokta yok; en düşük liste fiyatı 3821,3 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A42923; liste fiyatı 4.707 TL; sepette 4000,9 TL; stokta yok; en düşük liste fiyatı 2.999 TL (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1160" s="7" t="inlineStr">
@@ -49210,7 +49210,7 @@
     <row r="1161" ht="43.5" customHeight="1">
       <c r="A1161" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/termostatik-bataryalar/aquaheat-termostatik-dus-bataryasi-krom-p-a47055exps</t>
+          <t>https://www.vitra.com.tr/tek-armatur-delikli-lavabo-bataryalari/shift-t10-lavabo-bataryasi-krom-p-a43715</t>
         </is>
       </c>
       <c r="B1161" s="6" t="inlineStr">
@@ -49220,17 +49220,17 @@
       </c>
       <c r="C1161" s="6" t="inlineStr">
         <is>
-          <t>VitrA ürün sayfası: AquaHeat Termostatik Duş Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+          <t>VitrA ürün sayfası: Shift T10 Lavabo Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
       <c r="D1161" s="6" t="inlineStr">
         <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="E1161" s="6" t="inlineStr">
         <is>
-          <t>kod A47055EXPS; liste fiyatı 13.892 TL; sepette 12502,8 TL; stokta; en düşük liste fiyatı 9.390 TL (HB buybox (uygunyapimarket)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A43715; liste fiyatı 4.707 TL; sepette 4236,3 TL; stokta; en düşük liste fiyatı 2.989 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1161" s="7" t="inlineStr">
@@ -49252,133 +49252,133 @@
     <row r="1162" ht="43.5" customHeight="1">
       <c r="A1162" s="5" t="inlineStr">
         <is>
+          <t>https://www.vitra.com.tr/tek-armatur-delikli-lavabo-bataryalari/solid-s-lavabo-bataryasi-krom-p-a42484</t>
+        </is>
+      </c>
+      <c r="B1162" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr</t>
+        </is>
+      </c>
+      <c r="C1162" s="6" t="inlineStr">
+        <is>
+          <t>VitrA ürün sayfası: Solid S Lavabo Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+        </is>
+      </c>
+      <c r="D1162" s="6" t="inlineStr">
+        <is>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="E1162" s="6" t="inlineStr">
+        <is>
+          <t>kod A42484; liste fiyatı 5.016 TL; sepette 4514,4 TL; stokta yok; en düşük liste fiyatı 3821,3 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+        </is>
+      </c>
+      <c r="F1162" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1162" s="6" t="inlineStr">
+        <is>
+          <t>curl · tarayıcı (Playwright)</t>
+        </is>
+      </c>
+      <c r="H1162" s="7" t="inlineStr">
+        <is>
+          <t>D26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163" ht="43.5" customHeight="1">
+      <c r="A1163" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vitra.com.tr/termostatik-bataryalar/aquaheat-termostatik-dus-bataryasi-krom-p-a47055exps</t>
+        </is>
+      </c>
+      <c r="B1163" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr</t>
+        </is>
+      </c>
+      <c r="C1163" s="6" t="inlineStr">
+        <is>
+          <t>VitrA ürün sayfası: AquaHeat Termostatik Duş Bataryası (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
+        </is>
+      </c>
+      <c r="D1163" s="6" t="inlineStr">
+        <is>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="E1163" s="6" t="inlineStr">
+        <is>
+          <t>kod A47055EXPS; liste fiyatı 13.892 TL; sepette 12502,8 TL; stokta; en düşük liste fiyatı 9.390 TL (HB buybox (uygunyapimarket)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+        </is>
+      </c>
+      <c r="F1163" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1163" s="6" t="inlineStr">
+        <is>
+          <t>curl · tarayıcı (Playwright)</t>
+        </is>
+      </c>
+      <c r="H1163" s="7" t="inlineStr">
+        <is>
+          <t>D26</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164" ht="43.5" customHeight="1">
+      <c r="A1164" s="5" t="inlineStr">
+        <is>
           <t>https://www.vitra.com.tr/tezgahalti-lavabolar/s20-tezgahalti-lavabo-beyaz-p-5473b003-0618</t>
         </is>
       </c>
-      <c r="B1162" s="6" t="inlineStr">
+      <c r="B1164" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C1162" s="6" t="inlineStr">
+      <c r="C1164" s="6" t="inlineStr">
         <is>
           <t>VitrA ürün sayfası: S20 Tezgahaltı Lavabo (kanal fiyat karşılaştırması için vitra.com.tr liste ve sepet fiyatı, stok)</t>
         </is>
       </c>
-      <c r="D1162" s="6" t="inlineStr">
-        <is>
-          <t>18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
-        </is>
-      </c>
-      <c r="E1162" s="6" t="inlineStr">
+      <c r="D1164" s="6" t="inlineStr">
+        <is>
+          <t>19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="E1164" s="6" t="inlineStr">
         <is>
           <t>kod 5473B003-0618; liste fiyatı 4.913 TL; sepette 4176,1 TL; stokta yok; en düşük liste fiyatı 4.555 TL (HB buybox (Seçkin Banyo)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
-      <c r="F1162" s="7" t="inlineStr">
+      <c r="F1164" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1162" s="6" t="inlineStr">
+      <c r="G1164" s="6" t="inlineStr">
         <is>
           <t>curl · tarayıcı (Playwright)</t>
         </is>
       </c>
-      <c r="H1162" s="7" t="inlineStr">
+      <c r="H1164" s="7" t="inlineStr">
         <is>
           <t>D26</t>
-        </is>
-      </c>
-    </row>
-    <row r="1163" ht="30" customHeight="1">
-      <c r="A1163" s="5" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com.tr/gp/help/customer/display.html?nodeId=GE66DNRRQVDZAR5E</t>
-        </is>
-      </c>
-      <c r="B1163" s="6" t="inlineStr">
-        <is>
-          <t>amazon.com.tr</t>
-        </is>
-      </c>
-      <c r="C1163" s="6" t="inlineStr">
-        <is>
-          <t>Amazon TR kargo ve iade yardım sayfası</t>
-        </is>
-      </c>
-      <c r="D1163" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1163" s="6" t="inlineStr">
-        <is>
-          <t>Sayfa 403 döndü; arama sonucu özetinden alındı</t>
-        </is>
-      </c>
-      <c r="F1163" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1163" s="6" t="inlineStr">
-        <is>
-          <t>arama sonucu özeti (sayfa açılamadı)</t>
-        </is>
-      </c>
-      <c r="H1163" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1164" ht="30" customHeight="1">
-      <c r="A1164" s="5" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com.tr/gp/help/customer/display.html?nodeId=GKM69DUUYKQWKWX7</t>
-        </is>
-      </c>
-      <c r="B1164" s="6" t="inlineStr">
-        <is>
-          <t>amazon.com.tr</t>
-        </is>
-      </c>
-      <c r="C1164" s="6" t="inlineStr">
-        <is>
-          <t>Amazon TR iade koşulları</t>
-        </is>
-      </c>
-      <c r="D1164" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1164" s="6" t="inlineStr">
-        <is>
-          <t>İade süresi teslimden itibaren kategoriye göre 14 veya 30 gün; büyük üründe iade yöntemi değişebilir, evden alım sunulmayabilir</t>
-        </is>
-      </c>
-      <c r="F1164" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1164" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1164" s="7" t="inlineStr">
-        <is>
-          <t>D23 · D28</t>
         </is>
       </c>
     </row>
     <row r="1165" ht="30" customHeight="1">
       <c r="A1165" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.tr/gp/help/customer/display.html?nodeId=GNWCU626A4NXEEGJ</t>
+          <t>https://www.amazon.com.tr/gp/help/customer/display.html?nodeId=GE66DNRRQVDZAR5E</t>
         </is>
       </c>
       <c r="B1165" s="6" t="inlineStr">
@@ -49388,39 +49388,39 @@
       </c>
       <c r="C1165" s="6" t="inlineStr">
         <is>
-          <t>Amazon TR standart teslimat ve ücretsiz kargo eşiği</t>
+          <t>Amazon TR kargo ve iade yardım sayfası</t>
         </is>
       </c>
       <c r="D1165" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1165" s="6" t="inlineStr">
         <is>
-          <t>500 TL altında teslimat başına 49,90 TL; 500 TL ve üzeri ücretsiz</t>
+          <t>Sayfa 403 döndü; arama sonucu özetinden alındı</t>
         </is>
       </c>
       <c r="F1165" s="7" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="G1165" s="6" t="inlineStr">
         <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+          <t>arama sonucu özeti (sayfa açılamadı)</t>
         </is>
       </c>
       <c r="H1165" s="7" t="inlineStr">
         <is>
-          <t>D23 · D28</t>
+          <t>D23</t>
         </is>
       </c>
     </row>
     <row r="1166" ht="30" customHeight="1">
       <c r="A1166" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.tr/gp/help/customer/display.html?nodeId=GRVPA5TTFNQXJ2GZ</t>
+          <t>https://www.amazon.com.tr/gp/help/customer/display.html?nodeId=GKM69DUUYKQWKWX7</t>
         </is>
       </c>
       <c r="B1166" s="6" t="inlineStr">
@@ -49430,17 +49430,17 @@
       </c>
       <c r="C1166" s="6" t="inlineStr">
         <is>
-          <t>Amazon TR taksit seçenekleri</t>
+          <t>Amazon TR iade koşulları</t>
         </is>
       </c>
       <c r="D1166" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1166" s="6" t="inlineStr">
         <is>
-          <t>Kredi kartıyla ödemede 12 aya varan taksit</t>
+          <t>İade süresi teslimden itibaren kategoriye göre 14 veya 30 gün; büyük üründe iade yöntemi değişebilir, evden alım sunulmayabilir</t>
         </is>
       </c>
       <c r="F1166" s="7" t="inlineStr">
@@ -49462,7 +49462,7 @@
     <row r="1167" ht="30" customHeight="1">
       <c r="A1167" s="5" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.tr/gp/help/customer/display.html?nodeId=TKE3ITKU0oMx19kIos</t>
+          <t>https://www.amazon.com.tr/gp/help/customer/display.html?nodeId=GNWCU626A4NXEEGJ</t>
         </is>
       </c>
       <c r="B1167" s="6" t="inlineStr">
@@ -49472,153 +49472,153 @@
       </c>
       <c r="C1167" s="6" t="inlineStr">
         <is>
-          <t>Amazon TR ödeme yardım sayfası</t>
+          <t>Amazon TR standart teslimat ve ücretsiz kargo eşiği</t>
         </is>
       </c>
       <c r="D1167" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1167" s="6" t="inlineStr">
         <is>
-          <t>Fatura ve ödeme koşulları (ticari vergi mükellefi bilgisiyle fatura); arama sonucu özeti</t>
+          <t>500 TL altında teslimat başına 49,90 TL; 500 TL ve üzeri ücretsiz</t>
         </is>
       </c>
       <c r="F1167" s="7" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="G1167" s="6" t="inlineStr">
         <is>
-          <t>arama sonucu özeti (sayfa açılamadı)</t>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
         </is>
       </c>
       <c r="H1167" s="7" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D23 · D28</t>
         </is>
       </c>
     </row>
     <row r="1168" ht="30" customHeight="1">
       <c r="A1168" s="5" t="inlineStr">
         <is>
+          <t>https://www.amazon.com.tr/gp/help/customer/display.html?nodeId=GRVPA5TTFNQXJ2GZ</t>
+        </is>
+      </c>
+      <c r="B1168" s="6" t="inlineStr">
+        <is>
+          <t>amazon.com.tr</t>
+        </is>
+      </c>
+      <c r="C1168" s="6" t="inlineStr">
+        <is>
+          <t>Amazon TR taksit seçenekleri</t>
+        </is>
+      </c>
+      <c r="D1168" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1168" s="6" t="inlineStr">
+        <is>
+          <t>Kredi kartıyla ödemede 12 aya varan taksit</t>
+        </is>
+      </c>
+      <c r="F1168" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1168" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1168" s="7" t="inlineStr">
+        <is>
+          <t>D23 · D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169" ht="30" customHeight="1">
+      <c r="A1169" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.tr/gp/help/customer/display.html?nodeId=TKE3ITKU0oMx19kIos</t>
+        </is>
+      </c>
+      <c r="B1169" s="6" t="inlineStr">
+        <is>
+          <t>amazon.com.tr</t>
+        </is>
+      </c>
+      <c r="C1169" s="6" t="inlineStr">
+        <is>
+          <t>Amazon TR ödeme yardım sayfası</t>
+        </is>
+      </c>
+      <c r="D1169" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1169" s="6" t="inlineStr">
+        <is>
+          <t>Fatura ve ödeme koşulları (ticari vergi mükellefi bilgisiyle fatura); arama sonucu özeti</t>
+        </is>
+      </c>
+      <c r="F1169" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1169" s="6" t="inlineStr">
+        <is>
+          <t>arama sonucu özeti (sayfa açılamadı)</t>
+        </is>
+      </c>
+      <c r="H1169" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170" ht="30" customHeight="1">
+      <c r="A1170" s="5" t="inlineStr">
+        <is>
           <t>https://apify.com/apify/rag-web-browser</t>
         </is>
       </c>
-      <c r="B1168" s="6" t="inlineStr">
+      <c r="B1170" s="6" t="inlineStr">
         <is>
           <t>apify.com</t>
         </is>
       </c>
-      <c r="C1168" s="6" t="inlineStr">
+      <c r="C1170" s="6" t="inlineStr">
         <is>
           <t>Doğrudan erişimde 403 dönen sayfaların (Koçtaş, Bauhaus ve bazı Hepsiburada sayfaları) metin olarak okunması</t>
         </is>
       </c>
-      <c r="D1168" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1168" s="6" t="inlineStr">
+      <c r="D1170" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1170" s="6" t="inlineStr">
         <is>
           <t>Koçtaş taksit, nakliye ve montaj sayfaları ve ana sayfa; Hepsiburada mobilya ve büyük ürün sayfası; yaklaşık 16 çağrı</t>
         </is>
       </c>
-      <c r="F1168" s="7" t="inlineStr">
+      <c r="F1170" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1168" s="6" t="inlineStr">
+      <c r="G1170" s="6" t="inlineStr">
         <is>
           <t>API (Apify)</t>
-        </is>
-      </c>
-      <c r="H1168" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1169" ht="16.5" customHeight="1">
-      <c r="A1169" s="5" t="inlineStr">
-        <is>
-          <t>https://www.artema.com.tr/garanti-hizmetleri/</t>
-        </is>
-      </c>
-      <c r="B1169" s="6" t="inlineStr">
-        <is>
-          <t>artema.com.tr</t>
-        </is>
-      </c>
-      <c r="C1169" s="6" t="inlineStr">
-        <is>
-          <t>Artema garanti hizmetleri</t>
-        </is>
-      </c>
-      <c r="D1169" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1169" s="6" t="inlineStr">
-        <is>
-          <t>Sayfa mevcut, içerik statik HTML'de görünmüyor (süre okunamadı)</t>
-        </is>
-      </c>
-      <c r="F1169" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1169" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1169" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1170" ht="16.5" customHeight="1">
-      <c r="A1170" s="5" t="inlineStr">
-        <is>
-          <t>https://www.artema.com.tr/servisler-ve-satis-noktalari</t>
-        </is>
-      </c>
-      <c r="B1170" s="6" t="inlineStr">
-        <is>
-          <t>artema.com.tr</t>
-        </is>
-      </c>
-      <c r="C1170" s="6" t="inlineStr">
-        <is>
-          <t>Artema servis ve satış noktaları</t>
-        </is>
-      </c>
-      <c r="D1170" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1170" s="6" t="inlineStr">
-        <is>
-          <t>VitrA ile ortak müşteri hizmetleri ve servis sayfası</t>
-        </is>
-      </c>
-      <c r="F1170" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1170" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
         </is>
       </c>
       <c r="H1170" s="7" t="inlineStr">
@@ -49630,111 +49630,111 @@
     <row r="1171" ht="16.5" customHeight="1">
       <c r="A1171" s="5" t="inlineStr">
         <is>
+          <t>https://www.artema.com.tr/garanti-hizmetleri/</t>
+        </is>
+      </c>
+      <c r="B1171" s="6" t="inlineStr">
+        <is>
+          <t>artema.com.tr</t>
+        </is>
+      </c>
+      <c r="C1171" s="6" t="inlineStr">
+        <is>
+          <t>Artema garanti hizmetleri</t>
+        </is>
+      </c>
+      <c r="D1171" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1171" s="6" t="inlineStr">
+        <is>
+          <t>Sayfa mevcut, içerik statik HTML'de görünmüyor (süre okunamadı)</t>
+        </is>
+      </c>
+      <c r="F1171" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1171" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1171" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172" ht="16.5" customHeight="1">
+      <c r="A1172" s="5" t="inlineStr">
+        <is>
+          <t>https://www.artema.com.tr/servisler-ve-satis-noktalari</t>
+        </is>
+      </c>
+      <c r="B1172" s="6" t="inlineStr">
+        <is>
+          <t>artema.com.tr</t>
+        </is>
+      </c>
+      <c r="C1172" s="6" t="inlineStr">
+        <is>
+          <t>Artema servis ve satış noktaları</t>
+        </is>
+      </c>
+      <c r="D1172" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1172" s="6" t="inlineStr">
+        <is>
+          <t>VitrA ile ortak müşteri hizmetleri ve servis sayfası</t>
+        </is>
+      </c>
+      <c r="F1172" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1172" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1172" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173" ht="16.5" customHeight="1">
+      <c r="A1173" s="5" t="inlineStr">
+        <is>
           <t>https://www.banyoline.com/kampanyalar</t>
         </is>
       </c>
-      <c r="B1171" s="6" t="inlineStr">
+      <c r="B1173" s="6" t="inlineStr">
         <is>
           <t>banyoline.com</t>
         </is>
       </c>
-      <c r="C1171" s="6" t="inlineStr">
+      <c r="C1173" s="6" t="inlineStr">
         <is>
           <t>Banyoline kampanyalar</t>
         </is>
       </c>
-      <c r="D1171" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1171" s="6" t="inlineStr">
+      <c r="D1173" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1173" s="6" t="inlineStr">
         <is>
           <t>Kampanya ve taksit ifadeleri</t>
-        </is>
-      </c>
-      <c r="F1171" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1171" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1171" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1172" ht="30" customHeight="1">
-      <c r="A1172" s="5" t="inlineStr">
-        <is>
-          <t>https://www.banyoline.com/mesafeli-satis-sozlesmesi</t>
-        </is>
-      </c>
-      <c r="B1172" s="6" t="inlineStr">
-        <is>
-          <t>banyoline.com</t>
-        </is>
-      </c>
-      <c r="C1172" s="6" t="inlineStr">
-        <is>
-          <t>Banyoline mesafeli satış sözleşmesi</t>
-        </is>
-      </c>
-      <c r="D1172" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1172" s="6" t="inlineStr">
-        <is>
-          <t>İptal ve iade talebi formu; teslim süresi bölgeye bağlı (yasal 30 günü aşmaz); teslim alırken kontrol alıcıda</t>
-        </is>
-      </c>
-      <c r="F1172" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1172" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1172" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1173" ht="57" customHeight="1">
-      <c r="A1173" s="5" t="inlineStr">
-        <is>
-          <t>https://www.banyoline.com/montaj-hizmeti</t>
-        </is>
-      </c>
-      <c r="B1173" s="6" t="inlineStr">
-        <is>
-          <t>banyoline.com</t>
-        </is>
-      </c>
-      <c r="C1173" s="6" t="inlineStr">
-        <is>
-          <t>Banyoline montaj hizmeti</t>
-        </is>
-      </c>
-      <c r="D1173" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1173" s="6" t="inlineStr">
-        <is>
-          <t>Yalnızca İstanbul'da ücretsiz montaj: Orka seçili dolaplar ve VitrA Metropole Edge, Valarte, Nest Trendy, Sento, Root modelleri; batarya ve ara musluk montajı ve ölçü alma yok; ücretsiz montajda ön hazırlık yönergesine uyulmazsa iade ve ikinci montaj yok</t>
         </is>
       </c>
       <c r="F1173" s="7" t="inlineStr">
@@ -49756,153 +49756,153 @@
     <row r="1174" ht="30" customHeight="1">
       <c r="A1174" s="5" t="inlineStr">
         <is>
+          <t>https://www.banyoline.com/mesafeli-satis-sozlesmesi</t>
+        </is>
+      </c>
+      <c r="B1174" s="6" t="inlineStr">
+        <is>
+          <t>banyoline.com</t>
+        </is>
+      </c>
+      <c r="C1174" s="6" t="inlineStr">
+        <is>
+          <t>Banyoline mesafeli satış sözleşmesi</t>
+        </is>
+      </c>
+      <c r="D1174" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1174" s="6" t="inlineStr">
+        <is>
+          <t>İptal ve iade talebi formu; teslim süresi bölgeye bağlı (yasal 30 günü aşmaz); teslim alırken kontrol alıcıda</t>
+        </is>
+      </c>
+      <c r="F1174" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1174" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1174" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175" ht="57" customHeight="1">
+      <c r="A1175" s="5" t="inlineStr">
+        <is>
+          <t>https://www.banyoline.com/montaj-hizmeti</t>
+        </is>
+      </c>
+      <c r="B1175" s="6" t="inlineStr">
+        <is>
+          <t>banyoline.com</t>
+        </is>
+      </c>
+      <c r="C1175" s="6" t="inlineStr">
+        <is>
+          <t>Banyoline montaj hizmeti</t>
+        </is>
+      </c>
+      <c r="D1175" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1175" s="6" t="inlineStr">
+        <is>
+          <t>Yalnızca İstanbul'da ücretsiz montaj: Orka seçili dolaplar ve VitrA Metropole Edge, Valarte, Nest Trendy, Sento, Root modelleri; batarya ve ara musluk montajı ve ölçü alma yok; ücretsiz montajda ön hazırlık yönergesine uyulmazsa iade ve ikinci montaj yok</t>
+        </is>
+      </c>
+      <c r="F1175" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1175" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1175" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176" ht="30" customHeight="1">
+      <c r="A1176" s="5" t="inlineStr">
+        <is>
           <t>https://www.banyomarka.com/garanti-ve-iade-kosullari.shtm</t>
         </is>
       </c>
-      <c r="B1174" s="6" t="inlineStr">
+      <c r="B1176" s="6" t="inlineStr">
         <is>
           <t>banyomarka.com</t>
         </is>
       </c>
-      <c r="C1174" s="6" t="inlineStr">
+      <c r="C1176" s="6" t="inlineStr">
         <is>
           <t>Banyomarka garanti ve iade koşulları</t>
         </is>
       </c>
-      <c r="D1174" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1174" s="6" t="inlineStr">
+      <c r="D1176" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1176" s="6" t="inlineStr">
         <is>
           <t>Ürün kartında 30 gün iade; ürün kusuru durumunda 15 gün içinde bildirim; kullanılmış üründe iade ve değişim yok</t>
         </is>
       </c>
-      <c r="F1174" s="7" t="inlineStr">
+      <c r="F1176" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1174" s="6" t="inlineStr">
+      <c r="G1176" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1174" s="7" t="inlineStr">
+      <c r="H1176" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1175" ht="16.5" customHeight="1">
-      <c r="A1175" s="5" t="inlineStr">
+    <row r="1177" ht="16.5" customHeight="1">
+      <c r="A1177" s="5" t="inlineStr">
         <is>
           <t>https://www.banyomarka.com/musteri-hizmetleri.xhtml</t>
         </is>
       </c>
-      <c r="B1175" s="6" t="inlineStr">
+      <c r="B1177" s="6" t="inlineStr">
         <is>
           <t>banyomarka.com</t>
         </is>
       </c>
-      <c r="C1175" s="6" t="inlineStr">
+      <c r="C1177" s="6" t="inlineStr">
         <is>
           <t>Banyomarka müşteri hizmetleri</t>
         </is>
       </c>
-      <c r="D1175" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1175" s="6" t="inlineStr">
+      <c r="D1177" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1177" s="6" t="inlineStr">
         <is>
           <t>İstanbul içi kapıda nakit ödeme; WhatsApp destek; iletişim kanalları</t>
-        </is>
-      </c>
-      <c r="F1175" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1175" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1175" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1176" ht="16.5" customHeight="1">
-      <c r="A1176" s="5" t="inlineStr">
-        <is>
-          <t>https://www.banyomarka.com/satis-sozlesmesi.shtm</t>
-        </is>
-      </c>
-      <c r="B1176" s="6" t="inlineStr">
-        <is>
-          <t>banyomarka.com</t>
-        </is>
-      </c>
-      <c r="C1176" s="6" t="inlineStr">
-        <is>
-          <t>Banyomarka satış sözleşmesi</t>
-        </is>
-      </c>
-      <c r="D1176" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1176" s="6" t="inlineStr">
-        <is>
-          <t>Ödeme, havale/EFT ve teslimat maddeleri</t>
-        </is>
-      </c>
-      <c r="F1176" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1176" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1176" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1177" ht="30" customHeight="1">
-      <c r="A1177" s="5" t="inlineStr">
-        <is>
-          <t>https://www.banyomarka.com/teslimat-kosullari.shtm</t>
-        </is>
-      </c>
-      <c r="B1177" s="6" t="inlineStr">
-        <is>
-          <t>banyomarka.com</t>
-        </is>
-      </c>
-      <c r="C1177" s="6" t="inlineStr">
-        <is>
-          <t>Banyomarka teslimat koşulları</t>
-        </is>
-      </c>
-      <c r="D1177" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1177" s="6" t="inlineStr">
-        <is>
-          <t>3 iş günü içinde kargoya, kargo 1-3 gün; stokta yoksa 4-30 gün; ücretsiz kargo seçili ürünlerde (banner'da İstanbul içi 250 TL, güncelliği belirsiz)</t>
         </is>
       </c>
       <c r="F1177" s="7" t="inlineStr">
@@ -49924,27 +49924,27 @@
     <row r="1178" ht="16.5" customHeight="1">
       <c r="A1178" s="5" t="inlineStr">
         <is>
-          <t>https://www.bauhaus.com.tr/iade</t>
+          <t>https://www.banyomarka.com/satis-sozlesmesi.shtm</t>
         </is>
       </c>
       <c r="B1178" s="6" t="inlineStr">
         <is>
-          <t>bauhaus.com.tr</t>
+          <t>banyomarka.com</t>
         </is>
       </c>
       <c r="C1178" s="6" t="inlineStr">
         <is>
-          <t>Bauhaus TR iade koşulları</t>
+          <t>Banyomarka satış sözleşmesi</t>
         </is>
       </c>
       <c r="D1178" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1178" s="6" t="inlineStr">
         <is>
-          <t>14 gün iade; iade kodu 7 gün içinde kargoya verilmeli</t>
+          <t>Ödeme, havale/EFT ve teslimat maddeleri</t>
         </is>
       </c>
       <c r="F1178" s="7" t="inlineStr">
@@ -49966,69 +49966,69 @@
     <row r="1179" ht="30" customHeight="1">
       <c r="A1179" s="5" t="inlineStr">
         <is>
-          <t>https://www.bauhaus.com.tr/servisler</t>
+          <t>https://www.banyomarka.com/teslimat-kosullari.shtm</t>
         </is>
       </c>
       <c r="B1179" s="6" t="inlineStr">
         <is>
+          <t>banyomarka.com</t>
+        </is>
+      </c>
+      <c r="C1179" s="6" t="inlineStr">
+        <is>
+          <t>Banyomarka teslimat koşulları</t>
+        </is>
+      </c>
+      <c r="D1179" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1179" s="6" t="inlineStr">
+        <is>
+          <t>3 iş günü içinde kargoya, kargo 1-3 gün; stokta yoksa 4-30 gün; ücretsiz kargo seçili ürünlerde (banner'da İstanbul içi 250 TL, güncelliği belirsiz)</t>
+        </is>
+      </c>
+      <c r="F1179" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1179" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1179" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180" ht="16.5" customHeight="1">
+      <c r="A1180" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bauhaus.com.tr/iade</t>
+        </is>
+      </c>
+      <c r="B1180" s="6" t="inlineStr">
+        <is>
           <t>bauhaus.com.tr</t>
         </is>
       </c>
-      <c r="C1179" s="6" t="inlineStr">
-        <is>
-          <t>Bauhaus TR servisler: montaj ve hasar bildirimi</t>
-        </is>
-      </c>
-      <c r="D1179" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1179" s="6" t="inlineStr">
-        <is>
-          <t>Usta temini müşteri hizmetleri üzerinden, fiyat bulunamadı; hasar tespit tutanağı zorunlu (tutanak yoksa kargo kaynaklı olduğu ispatlanamıyor)</t>
-        </is>
-      </c>
-      <c r="F1179" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1179" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1179" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1180" ht="30" customHeight="1">
-      <c r="A1180" s="5" t="inlineStr">
-        <is>
-          <t>https://www.bauhaus.com.tr/sss</t>
-        </is>
-      </c>
-      <c r="B1180" s="6" t="inlineStr">
-        <is>
-          <t>bauhaus.com.tr</t>
-        </is>
-      </c>
       <c r="C1180" s="6" t="inlineStr">
         <is>
-          <t>Bauhaus TR SSS: ödeme yöntemleri, iade ve kargo</t>
+          <t>Bauhaus TR iade koşulları</t>
         </is>
       </c>
       <c r="D1180" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1180" s="6" t="inlineStr">
         <is>
-          <t>Havale/EFT ile ödeme (sipariş numarası açıklamada); kapıda ödeme yok; kurumsal müşteri servisi ve Bauhaus Kurumsal Kart</t>
+          <t>14 gün iade; iade kodu 7 gün içinde kargoya verilmeli</t>
         </is>
       </c>
       <c r="F1180" s="7" t="inlineStr">
@@ -50050,699 +50050,699 @@
     <row r="1181" ht="30" customHeight="1">
       <c r="A1181" s="5" t="inlineStr">
         <is>
+          <t>https://www.bauhaus.com.tr/servisler</t>
+        </is>
+      </c>
+      <c r="B1181" s="6" t="inlineStr">
+        <is>
+          <t>bauhaus.com.tr</t>
+        </is>
+      </c>
+      <c r="C1181" s="6" t="inlineStr">
+        <is>
+          <t>Bauhaus TR servisler: montaj ve hasar bildirimi</t>
+        </is>
+      </c>
+      <c r="D1181" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1181" s="6" t="inlineStr">
+        <is>
+          <t>Usta temini müşteri hizmetleri üzerinden, fiyat bulunamadı; hasar tespit tutanağı zorunlu (tutanak yoksa kargo kaynaklı olduğu ispatlanamıyor)</t>
+        </is>
+      </c>
+      <c r="F1181" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1181" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1181" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182" ht="30" customHeight="1">
+      <c r="A1182" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bauhaus.com.tr/sss</t>
+        </is>
+      </c>
+      <c r="B1182" s="6" t="inlineStr">
+        <is>
+          <t>bauhaus.com.tr</t>
+        </is>
+      </c>
+      <c r="C1182" s="6" t="inlineStr">
+        <is>
+          <t>Bauhaus TR SSS: ödeme yöntemleri, iade ve kargo</t>
+        </is>
+      </c>
+      <c r="D1182" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1182" s="6" t="inlineStr">
+        <is>
+          <t>Havale/EFT ile ödeme (sipariş numarası açıklamada); kapıda ödeme yok; kurumsal müşteri servisi ve Bauhaus Kurumsal Kart</t>
+        </is>
+      </c>
+      <c r="F1182" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1182" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1182" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183" ht="30" customHeight="1">
+      <c r="A1183" s="5" t="inlineStr">
+        <is>
           <t>https://www.bauhaus.com.tr/taksit-secenekleri</t>
         </is>
       </c>
-      <c r="B1181" s="6" t="inlineStr">
+      <c r="B1183" s="6" t="inlineStr">
         <is>
           <t>bauhaus.com.tr</t>
         </is>
       </c>
-      <c r="C1181" s="6" t="inlineStr">
+      <c r="C1183" s="6" t="inlineStr">
         <is>
           <t>Bauhaus TR taksit koşulları</t>
         </is>
       </c>
-      <c r="D1181" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1181" s="6" t="inlineStr">
+      <c r="D1183" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1183" s="6" t="inlineStr">
         <is>
           <t>2.500 TL ve üzeri alışverişte anlaşmalı banka kartlarıyla vade farksız (online ve şubeler); azami taksit yazmıyor</t>
         </is>
       </c>
-      <c r="F1181" s="7" t="inlineStr">
+      <c r="F1183" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1181" s="6" t="inlineStr">
+      <c r="G1183" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1181" s="7" t="inlineStr">
+      <c r="H1183" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1182" ht="43.5" customHeight="1">
-      <c r="A1182" s="5" t="inlineStr">
+    <row r="1184" ht="43.5" customHeight="1">
+      <c r="A1184" s="5" t="inlineStr">
         <is>
           <t>https://www.bauhaus.com.tr/ucretsiz-kargo</t>
         </is>
       </c>
-      <c r="B1182" s="6" t="inlineStr">
+      <c r="B1184" s="6" t="inlineStr">
         <is>
           <t>bauhaus.com.tr</t>
         </is>
       </c>
-      <c r="C1182" s="6" t="inlineStr">
+      <c r="C1184" s="6" t="inlineStr">
         <is>
           <t>Bauhaus TR ücretsiz kargo ve büyük ürün teslimatı</t>
         </is>
       </c>
-      <c r="D1182" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1182" s="6" t="inlineStr">
+      <c r="D1184" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1184" s="6" t="inlineStr">
         <is>
           <t>1.000 TL ve üzeri (belirlenen ürünlerde) ücretsiz kargo; şubelerden 40.000 TL ve üzeri şehir içi 30 km'ye kadar ücretsiz nakliye; 30 desi altı Yurtiçi/KolayGelsin, üstü Horoz/Arvato</t>
         </is>
       </c>
-      <c r="F1182" s="7" t="inlineStr">
+      <c r="F1184" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1182" s="6" t="inlineStr">
+      <c r="G1184" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1182" s="7" t="inlineStr">
+      <c r="H1184" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1183" ht="16.5" customHeight="1">
-      <c r="A1183" s="5" t="inlineStr">
+    <row r="1185" ht="16.5" customHeight="1">
+      <c r="A1185" s="5" t="inlineStr">
         <is>
           <t>https://www.bauhaus.com.tr/urun-garantisi</t>
         </is>
       </c>
-      <c r="B1183" s="6" t="inlineStr">
+      <c r="B1185" s="6" t="inlineStr">
         <is>
           <t>bauhaus.com.tr</t>
         </is>
       </c>
-      <c r="C1183" s="6" t="inlineStr">
+      <c r="C1185" s="6" t="inlineStr">
         <is>
           <t>Bauhaus TR ürün garantisi bilgisi</t>
         </is>
       </c>
-      <c r="D1183" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1183" s="6" t="inlineStr">
+      <c r="D1185" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1185" s="6" t="inlineStr">
         <is>
           <t>Ürün garantisi koşulları (garanti başlığı için taranan sayfa)</t>
         </is>
       </c>
-      <c r="F1183" s="7" t="inlineStr">
+      <c r="F1185" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1183" s="6" t="inlineStr">
+      <c r="G1185" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1183" s="7" t="inlineStr">
+      <c r="H1185" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1184" ht="30" customHeight="1">
-      <c r="A1184" s="5" t="inlineStr">
+    <row r="1186" ht="30" customHeight="1">
+      <c r="A1186" s="5" t="inlineStr">
         <is>
           <t>https://www.bauhaus.com.tr/urun-iade-garantisi</t>
         </is>
       </c>
-      <c r="B1184" s="6" t="inlineStr">
+      <c r="B1186" s="6" t="inlineStr">
         <is>
           <t>bauhaus.com.tr</t>
         </is>
       </c>
-      <c r="C1184" s="6" t="inlineStr">
+      <c r="C1186" s="6" t="inlineStr">
         <is>
           <t>Bauhaus TR ürün iade garantisi koşulları</t>
         </is>
       </c>
-      <c r="D1184" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1184" s="6" t="inlineStr">
+      <c r="D1186" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1186" s="6" t="inlineStr">
         <is>
           <t>Demonte üründe kurulumdan sonra iade yok; klozet takımı ve kapağında ambalajı açılmamış ve denenmemiş şartı</t>
         </is>
       </c>
-      <c r="F1184" s="7" t="inlineStr">
+      <c r="F1186" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1184" s="6" t="inlineStr">
+      <c r="G1186" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1184" s="7" t="inlineStr">
+      <c r="H1186" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1185" ht="30" customHeight="1">
-      <c r="A1185" s="5" t="inlineStr">
+    <row r="1187" ht="30" customHeight="1">
+      <c r="A1187" s="5" t="inlineStr">
         <is>
           <t>https://shop.creavit.com.tr</t>
         </is>
       </c>
-      <c r="B1185" s="6" t="inlineStr">
+      <c r="B1187" s="6" t="inlineStr">
         <is>
           <t>creavit.com.tr</t>
         </is>
       </c>
-      <c r="C1185" s="6" t="inlineStr">
+      <c r="C1187" s="6" t="inlineStr">
         <is>
           <t>Creavit e-mağaza ana sayfa: taksit ve iade mesajları</t>
         </is>
       </c>
-      <c r="D1185" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1185" s="6" t="inlineStr">
+      <c r="D1187" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1187" s="6" t="inlineStr">
         <is>
           <t>Peşin fiyatına 6 ve 9 taksit ifadeleri birlikte görünüyor (banner 9, alt metin 6); 30 gün ücretsiz iade ve değişim; 3.000 TL üzeri ücretsiz kargo</t>
         </is>
       </c>
-      <c r="F1185" s="7" t="inlineStr">
+      <c r="F1187" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1185" s="6" t="inlineStr">
+      <c r="G1187" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1185" s="7" t="inlineStr">
+      <c r="H1187" s="7" t="inlineStr">
         <is>
           <t>D23 · D29</t>
         </is>
       </c>
     </row>
-    <row r="1186" ht="43.5" customHeight="1">
-      <c r="A1186" s="5" t="inlineStr">
+    <row r="1188" ht="43.5" customHeight="1">
+      <c r="A1188" s="5" t="inlineStr">
         <is>
           <t>https://shop.creavit.com.tr/collections/montaj-hizmeti</t>
         </is>
       </c>
-      <c r="B1186" s="6" t="inlineStr">
+      <c r="B1188" s="6" t="inlineStr">
         <is>
           <t>creavit.com.tr</t>
         </is>
       </c>
-      <c r="C1186" s="6" t="inlineStr">
+      <c r="C1188" s="6" t="inlineStr">
         <is>
           <t>Creavit e-mağaza montaj hizmeti kalemleri ve fiyatları</t>
         </is>
       </c>
-      <c r="D1186" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1186" s="6" t="inlineStr">
+      <c r="D1188" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1188" s="6" t="inlineStr">
         <is>
           <t>11 kalem: asma ve takım klozet 2.450 TL, rezervuar ve iç takım 1.750, armatür ve duş 1.750, lavabo 2.450, banyo mobilyası alt modül 2.450, boy dolabı 1.400, demonte takım 3.900 TL (söküm hariç)</t>
         </is>
       </c>
-      <c r="F1186" s="7" t="inlineStr">
+      <c r="F1188" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1186" s="6" t="inlineStr">
+      <c r="G1188" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1186" s="7" t="inlineStr">
+      <c r="H1188" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1187" ht="16.5" customHeight="1">
-      <c r="A1187" s="5" t="inlineStr">
+    <row r="1189" ht="16.5" customHeight="1">
+      <c r="A1189" s="5" t="inlineStr">
         <is>
           <t>https://shop.creavit.com.tr/pages/contact</t>
         </is>
       </c>
-      <c r="B1187" s="6" t="inlineStr">
+      <c r="B1189" s="6" t="inlineStr">
         <is>
           <t>creavit.com.tr</t>
         </is>
       </c>
-      <c r="C1187" s="6" t="inlineStr">
+      <c r="C1189" s="6" t="inlineStr">
         <is>
           <t>Creavit e-mağaza iletişim</t>
         </is>
       </c>
-      <c r="D1187" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1187" s="6" t="inlineStr">
+      <c r="D1189" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1189" s="6" t="inlineStr">
         <is>
           <t>E-mağaza hattı (Pzt-Cuma 08:30-17:30)</t>
         </is>
       </c>
-      <c r="F1187" s="7" t="inlineStr">
+      <c r="F1189" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1187" s="6" t="inlineStr">
+      <c r="G1189" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1187" s="7" t="inlineStr">
+      <c r="H1189" s="7" t="inlineStr">
         <is>
           <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1188" ht="30" customHeight="1">
-      <c r="A1188" s="5" t="inlineStr">
-        <is>
-          <t>https://shop.creavit.com.tr/pages/teslimat-kosullari</t>
-        </is>
-      </c>
-      <c r="B1188" s="6" t="inlineStr">
-        <is>
-          <t>creavit.com.tr</t>
-        </is>
-      </c>
-      <c r="C1188" s="6" t="inlineStr">
-        <is>
-          <t>Creavit e-mağaza teslimat koşulları</t>
-        </is>
-      </c>
-      <c r="D1188" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1188" s="6" t="inlineStr">
-        <is>
-          <t>Banka onayından sonra 5 iş günü içinde kargoya, kargo 1-5 gün; 3.000 TL üzeri ücretsiz kargo; 30 gün ücretsiz iade ve değişim</t>
-        </is>
-      </c>
-      <c r="F1188" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1188" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1188" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1189" ht="43.5" customHeight="1">
-      <c r="A1189" s="5" t="inlineStr">
-        <is>
-          <t>https://www.creavit.com.tr/dokumanlar/</t>
-        </is>
-      </c>
-      <c r="B1189" s="6" t="inlineStr">
-        <is>
-          <t>creavit.com.tr</t>
-        </is>
-      </c>
-      <c r="C1189" s="6" t="inlineStr">
-        <is>
-          <t>Creavit doküman sayfası: garanti süreleri</t>
-        </is>
-      </c>
-      <c r="D1189" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1189" s="6" t="inlineStr">
-        <is>
-          <t>12 yıllık ve 2 yıllık kullanma kılavuzu ve garanti şartları (PDF); seramik 12, gömme rezervuar 10, armatür ve duş 5 yıl (arama özeti, PDF ile kısmen doğrulandı)</t>
-        </is>
-      </c>
-      <c r="F1189" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1189" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1189" s="7" t="inlineStr">
-        <is>
-          <t>D23 · D28</t>
         </is>
       </c>
     </row>
     <row r="1190" ht="30" customHeight="1">
       <c r="A1190" s="5" t="inlineStr">
         <is>
+          <t>https://shop.creavit.com.tr/pages/teslimat-kosullari</t>
+        </is>
+      </c>
+      <c r="B1190" s="6" t="inlineStr">
+        <is>
+          <t>creavit.com.tr</t>
+        </is>
+      </c>
+      <c r="C1190" s="6" t="inlineStr">
+        <is>
+          <t>Creavit e-mağaza teslimat koşulları</t>
+        </is>
+      </c>
+      <c r="D1190" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1190" s="6" t="inlineStr">
+        <is>
+          <t>Banka onayından sonra 5 iş günü içinde kargoya, kargo 1-5 gün; 3.000 TL üzeri ücretsiz kargo; 30 gün ücretsiz iade ve değişim</t>
+        </is>
+      </c>
+      <c r="F1190" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1190" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1190" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191" ht="43.5" customHeight="1">
+      <c r="A1191" s="5" t="inlineStr">
+        <is>
+          <t>https://www.creavit.com.tr/dokumanlar/</t>
+        </is>
+      </c>
+      <c r="B1191" s="6" t="inlineStr">
+        <is>
+          <t>creavit.com.tr</t>
+        </is>
+      </c>
+      <c r="C1191" s="6" t="inlineStr">
+        <is>
+          <t>Creavit doküman sayfası: garanti süreleri</t>
+        </is>
+      </c>
+      <c r="D1191" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1191" s="6" t="inlineStr">
+        <is>
+          <t>12 yıllık ve 2 yıllık kullanma kılavuzu ve garanti şartları (PDF); seramik 12, gömme rezervuar 10, armatür ve duş 5 yıl (arama özeti, PDF ile kısmen doğrulandı)</t>
+        </is>
+      </c>
+      <c r="F1191" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1191" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1191" s="7" t="inlineStr">
+        <is>
+          <t>D23 · D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192" ht="30" customHeight="1">
+      <c r="A1192" s="5" t="inlineStr">
+        <is>
           <t>https://www.creavit.com.tr/dokumanlar/kataloglar/</t>
         </is>
       </c>
-      <c r="B1190" s="6" t="inlineStr">
+      <c r="B1192" s="6" t="inlineStr">
         <is>
           <t>creavit.com.tr</t>
         </is>
       </c>
-      <c r="C1190" s="6" t="inlineStr">
+      <c r="C1192" s="6" t="inlineStr">
         <is>
           <t>Creavit kataloglar sayfası: yedek parça listesi kontrolü</t>
         </is>
       </c>
-      <c r="D1190" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1190" s="6" t="inlineStr">
+      <c r="D1192" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1192" s="6" t="inlineStr">
         <is>
           <t>15 PDF listeleniyor; hiçbirinin adında yedek parça yok, sayfada 'yedek' ifadesi geçmiyor</t>
         </is>
       </c>
-      <c r="F1190" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1190" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1190" s="7" t="inlineStr">
+      <c r="F1192" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1192" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1192" s="7" t="inlineStr">
         <is>
           <t>D28</t>
-        </is>
-      </c>
-    </row>
-    <row r="1191" ht="30" customHeight="1">
-      <c r="A1191" s="5" t="inlineStr">
-        <is>
-          <t>https://www.creavit.com.tr/tr/iletisim/servisler/yetkili-servisler-P27</t>
-        </is>
-      </c>
-      <c r="B1191" s="6" t="inlineStr">
-        <is>
-          <t>creavit.com.tr</t>
-        </is>
-      </c>
-      <c r="C1191" s="6" t="inlineStr">
-        <is>
-          <t>Creavit yetkili servisler</t>
-        </is>
-      </c>
-      <c r="D1191" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1191" s="6" t="inlineStr">
-        <is>
-          <t>Yetkili servisler sayfası ve servis randevu akışı</t>
-        </is>
-      </c>
-      <c r="F1191" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1191" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1191" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1192" ht="43.5" customHeight="1">
-      <c r="A1192" s="5" t="inlineStr">
-        <is>
-          <t>https://api.dataforseo.com/v3/serp/google/maps/live/advanced</t>
-        </is>
-      </c>
-      <c r="B1192" s="6" t="inlineStr">
-        <is>
-          <t>dataforseo.com</t>
-        </is>
-      </c>
-      <c r="C1192" s="6" t="inlineStr">
-        <is>
-          <t>Google Maps sonuçları: VitrA etiketli profillerin puanı, yorum sayısı ve il dağılımı</t>
-        </is>
-      </c>
-      <c r="D1192" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1192" s="6" t="inlineStr">
-        <is>
-          <t>103 sorgu, Türkiye, Türkçe, depth 20; kayıtlar cid ile tekilleştirildi; İstanbul 64, Ankara ve İzmir 16'şar, Muğla ve Mersin 11'er satış noktası profili</t>
-        </is>
-      </c>
-      <c r="F1192" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1192" s="6" t="inlineStr">
-        <is>
-          <t>API (DataForSEO)</t>
-        </is>
-      </c>
-      <c r="H1192" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
         </is>
       </c>
     </row>
     <row r="1193" ht="30" customHeight="1">
       <c r="A1193" s="5" t="inlineStr">
         <is>
+          <t>https://www.creavit.com.tr/tr/iletisim/servisler/yetkili-servisler-P27</t>
+        </is>
+      </c>
+      <c r="B1193" s="6" t="inlineStr">
+        <is>
+          <t>creavit.com.tr</t>
+        </is>
+      </c>
+      <c r="C1193" s="6" t="inlineStr">
+        <is>
+          <t>Creavit yetkili servisler</t>
+        </is>
+      </c>
+      <c r="D1193" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1193" s="6" t="inlineStr">
+        <is>
+          <t>Yetkili servisler sayfası ve servis randevu akışı</t>
+        </is>
+      </c>
+      <c r="F1193" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1193" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1193" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194" ht="43.5" customHeight="1">
+      <c r="A1194" s="5" t="inlineStr">
+        <is>
+          <t>https://api.dataforseo.com/v3/serp/google/maps/live/advanced</t>
+        </is>
+      </c>
+      <c r="B1194" s="6" t="inlineStr">
+        <is>
+          <t>dataforseo.com</t>
+        </is>
+      </c>
+      <c r="C1194" s="6" t="inlineStr">
+        <is>
+          <t>Google Maps sonuçları: VitrA etiketli profillerin puanı, yorum sayısı ve il dağılımı</t>
+        </is>
+      </c>
+      <c r="D1194" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1194" s="6" t="inlineStr">
+        <is>
+          <t>103 sorgu, Türkiye, Türkçe, depth 20; kayıtlar cid ile tekilleştirildi; İstanbul 64, Ankara ve İzmir 16'şar, Muğla ve Mersin 11'er satış noktası profili</t>
+        </is>
+      </c>
+      <c r="F1194" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1194" s="6" t="inlineStr">
+        <is>
+          <t>API (DataForSEO)</t>
+        </is>
+      </c>
+      <c r="H1194" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195" ht="30" customHeight="1">
+      <c r="A1195" s="5" t="inlineStr">
+        <is>
           <t>https://www.duravit.com.tr/servis_hizmeti/faqs.tr-tr.html</t>
         </is>
       </c>
-      <c r="B1193" s="6" t="inlineStr">
+      <c r="B1195" s="6" t="inlineStr">
         <is>
           <t>duravit.com.tr</t>
         </is>
       </c>
-      <c r="C1193" s="6" t="inlineStr">
+      <c r="C1195" s="6" t="inlineStr">
         <is>
           <t>Duravit Türkiye SSS: garanti</t>
         </is>
       </c>
-      <c r="D1193" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1193" s="6" t="inlineStr">
+      <c r="D1195" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1195" s="6" t="inlineStr">
         <is>
           <t>Ürüne bağlı gönüllü üretici garantisi; süre belirtilmemiş</t>
         </is>
       </c>
-      <c r="F1193" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1193" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1193" s="7" t="inlineStr">
+      <c r="F1195" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1195" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1195" s="7" t="inlineStr">
         <is>
           <t>D28</t>
         </is>
       </c>
     </row>
-    <row r="1194" ht="30" customHeight="1">
-      <c r="A1194" s="5" t="inlineStr">
+    <row r="1196" ht="30" customHeight="1">
+      <c r="A1196" s="5" t="inlineStr">
         <is>
           <t>https://www.duravit.com.tr/servis_hizmeti/teknik_servisler.tr-tr.html</t>
         </is>
       </c>
-      <c r="B1194" s="6" t="inlineStr">
+      <c r="B1196" s="6" t="inlineStr">
         <is>
           <t>duravit.com.tr</t>
         </is>
       </c>
-      <c r="C1194" s="6" t="inlineStr">
+      <c r="C1196" s="6" t="inlineStr">
         <is>
           <t>Duravit Türkiye teknik servisler</t>
         </is>
       </c>
-      <c r="D1194" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1194" s="6" t="inlineStr">
+      <c r="D1196" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1196" s="6" t="inlineStr">
         <is>
           <t>İl bazlı teknik servis listesi; tüm Türkiye'ye yayılan servis ağı</t>
         </is>
       </c>
-      <c r="F1194" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1194" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1194" s="7" t="inlineStr">
+      <c r="F1196" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1196" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1196" s="7" t="inlineStr">
         <is>
           <t>D23 · D28</t>
         </is>
       </c>
     </row>
-    <row r="1195" ht="16.5" customHeight="1">
-      <c r="A1195" s="5" t="inlineStr">
+    <row r="1197" ht="16.5" customHeight="1">
+      <c r="A1197" s="5" t="inlineStr">
         <is>
           <t>https://eca.com.tr/iletisim-bilgileri</t>
         </is>
       </c>
-      <c r="B1195" s="6" t="inlineStr">
+      <c r="B1197" s="6" t="inlineStr">
         <is>
           <t>eca.com.tr</t>
         </is>
       </c>
-      <c r="C1195" s="6" t="inlineStr">
+      <c r="C1197" s="6" t="inlineStr">
         <is>
           <t>E.C.A. iletişim ve WhatsApp</t>
         </is>
       </c>
-      <c r="D1195" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1195" s="6" t="inlineStr">
+      <c r="D1197" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1197" s="6" t="inlineStr">
         <is>
           <t>Servis hatları ve WhatsApp bağlantısı</t>
-        </is>
-      </c>
-      <c r="F1195" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1195" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1195" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1196" ht="16.5" customHeight="1">
-      <c r="A1196" s="5" t="inlineStr">
-        <is>
-          <t>https://eca.com.tr/servisler</t>
-        </is>
-      </c>
-      <c r="B1196" s="6" t="inlineStr">
-        <is>
-          <t>eca.com.tr</t>
-        </is>
-      </c>
-      <c r="C1196" s="6" t="inlineStr">
-        <is>
-          <t>E.C.A. yetkili servis haritası</t>
-        </is>
-      </c>
-      <c r="D1196" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1196" s="6" t="inlineStr">
-        <is>
-          <t>Yetkili servis haritası ve il bazlı servis listesi</t>
-        </is>
-      </c>
-      <c r="F1196" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1196" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1196" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1197" ht="30" customHeight="1">
-      <c r="A1197" s="5" t="inlineStr">
-        <is>
-          <t>https://eca.com.tr/urun/life-lavabo-bataryasi</t>
-        </is>
-      </c>
-      <c r="B1197" s="6" t="inlineStr">
-        <is>
-          <t>eca.com.tr</t>
-        </is>
-      </c>
-      <c r="C1197" s="6" t="inlineStr">
-        <is>
-          <t>E.C.A. ürün sayfası örneği: garanti süresi ve yedek parça bölümü</t>
-        </is>
-      </c>
-      <c r="D1197" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1197" s="6" t="inlineStr">
-        <is>
-          <t>Life lavabo bataryasında 'Garanti Süresi: 20 Yıl' ve 'Yedek Parça Resmi' bölümü</t>
         </is>
       </c>
       <c r="F1197" s="7" t="inlineStr">
@@ -50764,27 +50764,27 @@
     <row r="1198" ht="16.5" customHeight="1">
       <c r="A1198" s="5" t="inlineStr">
         <is>
-          <t>https://www.geberit.com.tr/anasayfa/</t>
+          <t>https://eca.com.tr/servisler</t>
         </is>
       </c>
       <c r="B1198" s="6" t="inlineStr">
         <is>
-          <t>geberit.com.tr</t>
+          <t>eca.com.tr</t>
         </is>
       </c>
       <c r="C1198" s="6" t="inlineStr">
         <is>
-          <t>Geberit Türkiye ana sayfa</t>
+          <t>E.C.A. yetkili servis haritası</t>
         </is>
       </c>
       <c r="D1198" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1198" s="6" t="inlineStr">
         <is>
-          <t>Marka sitesi menüsü; hizmet ve destek girişi</t>
+          <t>Yetkili servis haritası ve il bazlı servis listesi</t>
         </is>
       </c>
       <c r="F1198" s="7" t="inlineStr">
@@ -50806,49 +50806,49 @@
     <row r="1199" ht="30" customHeight="1">
       <c r="A1199" s="5" t="inlineStr">
         <is>
-          <t>https://www.geberit.com.tr/banyo-urunleri/ilham-alin/bayiler-yetkili-servisler/</t>
+          <t>https://eca.com.tr/urun/life-lavabo-bataryasi</t>
         </is>
       </c>
       <c r="B1199" s="6" t="inlineStr">
         <is>
-          <t>geberit.com.tr</t>
+          <t>eca.com.tr</t>
         </is>
       </c>
       <c r="C1199" s="6" t="inlineStr">
         <is>
-          <t>Geberit Türkiye bayi ve yetkili servisler</t>
+          <t>E.C.A. ürün sayfası örneği: garanti süresi ve yedek parça bölümü</t>
         </is>
       </c>
       <c r="D1199" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1199" s="6" t="inlineStr">
         <is>
-          <t>Ürün, yedek parça ve teknik destek için bayi ve yetkili servis listesi</t>
+          <t>Life lavabo bataryasında 'Garanti Süresi: 20 Yıl' ve 'Yedek Parça Resmi' bölümü</t>
         </is>
       </c>
       <c r="F1199" s="7" t="inlineStr">
         <is>
-          <t>29.09.2026 · 30.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="G1199" s="6" t="inlineStr">
         <is>
-          <t>curl · tarayıcı (Chrome, kullanıcı oturumu)</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="H1199" s="7" t="inlineStr">
         <is>
-          <t>D23 · D28</t>
+          <t>D23</t>
         </is>
       </c>
     </row>
     <row r="1200" ht="16.5" customHeight="1">
       <c r="A1200" s="5" t="inlineStr">
         <is>
-          <t>https://www.geberit.com.tr/hizmet-ve-destek/iletisim/</t>
+          <t>https://www.geberit.com.tr/anasayfa/</t>
         </is>
       </c>
       <c r="B1200" s="6" t="inlineStr">
@@ -50858,17 +50858,17 @@
       </c>
       <c r="C1200" s="6" t="inlineStr">
         <is>
-          <t>Geberit Türkiye iletişim</t>
+          <t>Geberit Türkiye ana sayfa</t>
         </is>
       </c>
       <c r="D1200" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1200" s="6" t="inlineStr">
         <is>
-          <t>Müşteri hattı ve iletişim bilgileri</t>
+          <t>Marka sitesi menüsü; hizmet ve destek girişi</t>
         </is>
       </c>
       <c r="F1200" s="7" t="inlineStr">
@@ -50890,343 +50890,343 @@
     <row r="1201" ht="30" customHeight="1">
       <c r="A1201" s="5" t="inlineStr">
         <is>
+          <t>https://www.geberit.com.tr/banyo-urunleri/ilham-alin/bayiler-yetkili-servisler/</t>
+        </is>
+      </c>
+      <c r="B1201" s="6" t="inlineStr">
+        <is>
+          <t>geberit.com.tr</t>
+        </is>
+      </c>
+      <c r="C1201" s="6" t="inlineStr">
+        <is>
+          <t>Geberit Türkiye bayi ve yetkili servisler</t>
+        </is>
+      </c>
+      <c r="D1201" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1201" s="6" t="inlineStr">
+        <is>
+          <t>Ürün, yedek parça ve teknik destek için bayi ve yetkili servis listesi</t>
+        </is>
+      </c>
+      <c r="F1201" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026 · 30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1201" s="6" t="inlineStr">
+        <is>
+          <t>curl · tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1201" s="7" t="inlineStr">
+        <is>
+          <t>D23 · D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202" ht="16.5" customHeight="1">
+      <c r="A1202" s="5" t="inlineStr">
+        <is>
+          <t>https://www.geberit.com.tr/hizmet-ve-destek/iletisim/</t>
+        </is>
+      </c>
+      <c r="B1202" s="6" t="inlineStr">
+        <is>
+          <t>geberit.com.tr</t>
+        </is>
+      </c>
+      <c r="C1202" s="6" t="inlineStr">
+        <is>
+          <t>Geberit Türkiye iletişim</t>
+        </is>
+      </c>
+      <c r="D1202" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1202" s="6" t="inlineStr">
+        <is>
+          <t>Müşteri hattı ve iletişim bilgileri</t>
+        </is>
+      </c>
+      <c r="F1202" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1202" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1202" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203" ht="30" customHeight="1">
+      <c r="A1203" s="5" t="inlineStr">
+        <is>
           <t>https://www.geberit.com.tr/hizmet-ve-destek/medya-merkezi/</t>
         </is>
       </c>
-      <c r="B1201" s="6" t="inlineStr">
+      <c r="B1203" s="6" t="inlineStr">
         <is>
           <t>geberit.com.tr</t>
         </is>
       </c>
-      <c r="C1201" s="6" t="inlineStr">
+      <c r="C1203" s="6" t="inlineStr">
         <is>
           <t>Geberit Türkiye medya merkezi: garanti koşulları PDF'i</t>
         </is>
       </c>
-      <c r="D1201" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1201" s="6" t="inlineStr">
+      <c r="D1203" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1203" s="6" t="inlineStr">
         <is>
           <t>Geberit Banyo Ürünleri ve Serileri Garanti Koşulları (PDF); süre sayfada yazmıyor</t>
         </is>
       </c>
-      <c r="F1201" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1201" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1201" s="7" t="inlineStr">
+      <c r="F1203" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1203" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1203" s="7" t="inlineStr">
         <is>
           <t>D28</t>
         </is>
       </c>
     </row>
-    <row r="1202" ht="43.5" customHeight="1">
-      <c r="A1202" s="5" t="inlineStr">
+    <row r="1204" ht="43.5" customHeight="1">
+      <c r="A1204" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/vitra+banyo+mağazası+{il}</t>
         </is>
       </c>
-      <c r="B1202" s="6" t="inlineStr">
+      <c r="B1204" s="6" t="inlineStr">
         <is>
           <t>google.com</t>
         </is>
       </c>
-      <c r="C1202" s="6" t="inlineStr">
+      <c r="C1204" s="6" t="inlineStr">
         <is>
           <t>VitrA etiketli satış noktası ve servis profillerinin Google Maps görünürlüğü ve puanı</t>
         </is>
       </c>
-      <c r="D1202" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1202" s="6" t="inlineStr">
+      <c r="D1204" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1204" s="6" t="inlineStr">
         <is>
           <t>103 sorgu (81 il + 22 İstanbul ilçesi), sorgu başına ilk 20 sonuç; 262 VitrA etiketli satış noktası profili (8.451 yorum, ortalama 4,48) ve 76 servis profili (2.007 yorum); resmi mağaza bulucuda 161 satış + 76 servis noktası</t>
         </is>
       </c>
-      <c r="F1202" s="7" t="inlineStr">
+      <c r="F1204" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1202" s="6" t="inlineStr">
+      <c r="G1204" s="6" t="inlineStr">
         <is>
           <t>API (DataForSEO Maps)</t>
         </is>
       </c>
-      <c r="H1202" s="7" t="inlineStr">
+      <c r="H1204" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1203" ht="57" customHeight="1">
-      <c r="A1203" s="5" t="inlineStr">
+    <row r="1205" ht="57" customHeight="1">
+      <c r="A1205" s="5" t="inlineStr">
         <is>
           <t>https://www.google.com.tr/search?q=site:pinterest.com+{banyo+teması}</t>
         </is>
       </c>
-      <c r="B1203" s="6" t="inlineStr">
+      <c r="B1205" s="6" t="inlineStr">
         <is>
           <t>google.com.tr</t>
         </is>
       </c>
-      <c r="C1203" s="6" t="inlineStr">
+      <c r="C1205" s="6" t="inlineStr">
         <is>
           <t>Pinterest'te banyo temalı markasız görünürlük ve VitrA/Artema pin sayısı</t>
         </is>
       </c>
-      <c r="D1203" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1203" s="6" t="inlineStr">
+      <c r="D1205" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1205" s="6" t="inlineStr">
         <is>
           <t>9 sorgu (8'i site:pinterest.com, 1'i doğal arama; "vitra banyo pinterest"); sonuç başlığı ve açıklamasında marka adı geçen pin sayıları: VitrA marka adlı dört sorguda 37, Artema 6 pin; markasız 5 sorguda yalnızca Ideal Standard 1</t>
         </is>
       </c>
-      <c r="F1203" s="7" t="inlineStr">
+      <c r="F1205" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1203" s="6" t="inlineStr">
+      <c r="G1205" s="6" t="inlineStr">
         <is>
           <t>API (DataForSEO SERP)</t>
         </is>
       </c>
-      <c r="H1203" s="7" t="inlineStr">
+      <c r="H1205" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1204" ht="16.5" customHeight="1">
-      <c r="A1204" s="5" t="inlineStr">
+    <row r="1206" ht="16.5" customHeight="1">
+      <c r="A1206" s="5" t="inlineStr">
         <is>
           <t>https://www.grohe.com/tr-TR</t>
         </is>
       </c>
-      <c r="B1204" s="6" t="inlineStr">
+      <c r="B1206" s="6" t="inlineStr">
         <is>
           <t>grohe.com</t>
         </is>
       </c>
-      <c r="C1204" s="6" t="inlineStr">
+      <c r="C1206" s="6" t="inlineStr">
         <is>
           <t>Grohe Türkiye ana sayfa</t>
         </is>
       </c>
-      <c r="D1204" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1204" s="6" t="inlineStr">
+      <c r="D1206" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1206" s="6" t="inlineStr">
         <is>
           <t>Marka sitesi menüsü; servis ve destek girişi</t>
         </is>
       </c>
-      <c r="F1204" s="7" t="inlineStr">
+      <c r="F1206" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1204" s="6" t="inlineStr">
+      <c r="G1206" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1204" s="7" t="inlineStr">
+      <c r="H1206" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1205" ht="16.5" customHeight="1">
-      <c r="A1205" s="5" t="inlineStr">
+    <row r="1207" ht="16.5" customHeight="1">
+      <c r="A1207" s="5" t="inlineStr">
         <is>
           <t>https://www.grohe.com/tr-TR/servis-destek/bayi-bulucu</t>
         </is>
       </c>
-      <c r="B1205" s="6" t="inlineStr">
+      <c r="B1207" s="6" t="inlineStr">
         <is>
           <t>grohe.com</t>
         </is>
       </c>
-      <c r="C1205" s="6" t="inlineStr">
+      <c r="C1207" s="6" t="inlineStr">
         <is>
           <t>Grohe Türkiye bayi bulucu ve servis talebi</t>
         </is>
       </c>
-      <c r="D1205" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1205" s="6" t="inlineStr">
+      <c r="D1207" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1207" s="6" t="inlineStr">
         <is>
           <t>Servis talebi formu ve bayi bulucu; yedek parça bulucu</t>
         </is>
       </c>
-      <c r="F1205" s="7" t="inlineStr">
+      <c r="F1207" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1205" s="6" t="inlineStr">
+      <c r="G1207" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1205" s="7" t="inlineStr">
+      <c r="H1207" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1206" ht="30" customHeight="1">
-      <c r="A1206" s="5" t="inlineStr">
+    <row r="1208" ht="30" customHeight="1">
+      <c r="A1208" s="5" t="inlineStr">
         <is>
           <t>https://www.grohe.com/tr-TR/servis-destek/garanti</t>
         </is>
       </c>
-      <c r="B1206" s="6" t="inlineStr">
+      <c r="B1208" s="6" t="inlineStr">
         <is>
           <t>grohe.com</t>
         </is>
       </c>
-      <c r="C1206" s="6" t="inlineStr">
+      <c r="C1208" s="6" t="inlineStr">
         <is>
           <t>Grohe Türkiye garanti sayfası</t>
         </is>
       </c>
-      <c r="D1206" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1206" s="6" t="inlineStr">
+      <c r="D1208" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1208" s="6" t="inlineStr">
         <is>
           <t>Seçili ürünlerde 10 yıla kadar; 2 yıl (çevrim içi kayıtla +1 yıl) ve 5 yıl; garanti kapsamında yedek parça 48 saatte teslim</t>
         </is>
       </c>
-      <c r="F1206" s="7" t="inlineStr">
+      <c r="F1208" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1206" s="6" t="inlineStr">
+      <c r="G1208" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1206" s="7" t="inlineStr">
+      <c r="H1208" s="7" t="inlineStr">
         <is>
           <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1207" ht="30" customHeight="1">
-      <c r="A1207" s="5" t="inlineStr">
-        <is>
-          <t>https://www.hepsiburada.com/odeme-secenekleri</t>
-        </is>
-      </c>
-      <c r="B1207" s="6" t="inlineStr">
-        <is>
-          <t>hepsiburada.com</t>
-        </is>
-      </c>
-      <c r="C1207" s="6" t="inlineStr">
-        <is>
-          <t>Hepsiburada ödeme seçenekleri</t>
-        </is>
-      </c>
-      <c r="D1207" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1207" s="6" t="inlineStr">
-        <is>
-          <t>12 aya varan taksit (Hepsiburada limiti); uygun ürünlerde kapıda nakit ödeme, üst limit 7.000 TL; alışveriş kredisi; kurumsal fatura (arama özeti)</t>
-        </is>
-      </c>
-      <c r="F1207" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1207" s="6" t="inlineStr">
-        <is>
-          <t>arama sonucu özeti (sayfa açılamadı)</t>
-        </is>
-      </c>
-      <c r="H1207" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1208" ht="43.5" customHeight="1">
-      <c r="A1208" s="5" t="inlineStr">
-        <is>
-          <t>https://www.hepsiburada.com/staticpage/397066447924442</t>
-        </is>
-      </c>
-      <c r="B1208" s="6" t="inlineStr">
-        <is>
-          <t>hepsiburada.com</t>
-        </is>
-      </c>
-      <c r="C1208" s="6" t="inlineStr">
-        <is>
-          <t>Hepsiburada mobilya ve büyük ürün teslimat, iade ve kurulum sayfası</t>
-        </is>
-      </c>
-      <c r="D1208" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1208" s="6" t="inlineStr">
-        <is>
-          <t>Mobilya birden fazla pakette ve farklı günlerde gelebilir (HepsiJET XL); adresten önceden seçilen tarihte alınır; 14 gün ücretsiz iade (demonte ve orijinal kutuyla); 69 ilde montaj (uzman ekiplerden mobilya montaj hizmeti)</t>
-        </is>
-      </c>
-      <c r="F1208" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026 · 30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1208" s="6" t="inlineStr">
-        <is>
-          <t>API (Apify rag-web-browser) · tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1208" s="7" t="inlineStr">
-        <is>
-          <t>D23 · D28</t>
         </is>
       </c>
     </row>
     <row r="1209" ht="30" customHeight="1">
       <c r="A1209" s="5" t="inlineStr">
         <is>
-          <t>https://www.hepsiburada.com/staticpage/416030025820088</t>
+          <t>https://www.hepsiburada.com/odeme-secenekleri</t>
         </is>
       </c>
       <c r="B1209" s="6" t="inlineStr">
@@ -51236,17 +51236,17 @@
       </c>
       <c r="C1209" s="6" t="inlineStr">
         <is>
-          <t>Hepsiburada ödeme ve kredi bilgi sayfası</t>
+          <t>Hepsiburada ödeme seçenekleri</t>
         </is>
       </c>
       <c r="D1209" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1209" s="6" t="inlineStr">
         <is>
-          <t>Alışveriş kredisi ve taksit başlıkları; sayfa açılamadı, arama sonucu özetinden alındı</t>
+          <t>12 aya varan taksit (Hepsiburada limiti); uygun ürünlerde kapıda nakit ödeme, üst limit 7.000 TL; alışveriş kredisi; kurumsal fatura (arama özeti)</t>
         </is>
       </c>
       <c r="F1209" s="7" t="inlineStr">
@@ -51265,10 +51265,10 @@
         </is>
       </c>
     </row>
-    <row r="1210" ht="30" customHeight="1">
+    <row r="1210" ht="43.5" customHeight="1">
       <c r="A1210" s="5" t="inlineStr">
         <is>
-          <t>https://www.hepsiburada.com/teslimat</t>
+          <t>https://www.hepsiburada.com/staticpage/397066447924442</t>
         </is>
       </c>
       <c r="B1210" s="6" t="inlineStr">
@@ -51278,59 +51278,59 @@
       </c>
       <c r="C1210" s="6" t="inlineStr">
         <is>
-          <t>Hepsiburada teslimat sayfası: ücretsiz kargo eşiği kontrolü</t>
+          <t>Hepsiburada mobilya ve büyük ürün teslimat, iade ve kurulum sayfası</t>
         </is>
       </c>
       <c r="D1210" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1210" s="6" t="inlineStr">
         <is>
-          <t>Yarın Kapında: sepet kargo bedavaya uygunsa ek ücret alınmıyor; eşik tutarı herkese açık sayfada bulunamadı</t>
+          <t>Mobilya birden fazla pakette ve farklı günlerde gelebilir (HepsiJET XL); adresten önceden seçilen tarihte alınır; 14 gün ücretsiz iade (demonte ve orijinal kutuyla); 69 ilde montaj (uzman ekiplerden mobilya montaj hizmeti)</t>
         </is>
       </c>
       <c r="F1210" s="7" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>29.09.2026 · 30.09.2026</t>
         </is>
       </c>
       <c r="G1210" s="6" t="inlineStr">
         <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+          <t>API (Apify rag-web-browser) · tarayıcı (Chrome, kullanıcı oturumu)</t>
         </is>
       </c>
       <c r="H1210" s="7" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D23 · D28</t>
         </is>
       </c>
     </row>
     <row r="1211" ht="30" customHeight="1">
       <c r="A1211" s="5" t="inlineStr">
         <is>
-          <t>https://www.ikea.com.tr/iade-politikasi</t>
+          <t>https://www.hepsiburada.com/staticpage/416030025820088</t>
         </is>
       </c>
       <c r="B1211" s="6" t="inlineStr">
         <is>
-          <t>ikea.com.tr</t>
+          <t>hepsiburada.com</t>
         </is>
       </c>
       <c r="C1211" s="6" t="inlineStr">
         <is>
-          <t>IKEA TR iade politikası</t>
+          <t>Hepsiburada ödeme ve kredi bilgi sayfası</t>
         </is>
       </c>
       <c r="D1211" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1211" s="6" t="inlineStr">
         <is>
-          <t>İnternet siparişlerinde 14 gün ücretsiz iade, mağazada 30 gün; ambalajı açılmamış orijinal kutu şartı; özel kesim ürünler iade dışı</t>
+          <t>Alışveriş kredisi ve taksit başlıkları; sayfa açılamadı, arama sonucu özetinden alındı</t>
         </is>
       </c>
       <c r="F1211" s="7" t="inlineStr">
@@ -51340,7 +51340,7 @@
       </c>
       <c r="G1211" s="6" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>arama sonucu özeti (sayfa açılamadı)</t>
         </is>
       </c>
       <c r="H1211" s="7" t="inlineStr">
@@ -51349,52 +51349,52 @@
         </is>
       </c>
     </row>
-    <row r="1212" ht="16.5" customHeight="1">
+    <row r="1212" ht="30" customHeight="1">
       <c r="A1212" s="5" t="inlineStr">
         <is>
-          <t>https://www.ikea.com.tr/ikea-kurumsal</t>
+          <t>https://www.hepsiburada.com/teslimat</t>
         </is>
       </c>
       <c r="B1212" s="6" t="inlineStr">
         <is>
-          <t>ikea.com.tr</t>
+          <t>hepsiburada.com</t>
         </is>
       </c>
       <c r="C1212" s="6" t="inlineStr">
         <is>
-          <t>IKEA TR kurumsal sayfası</t>
+          <t>Hepsiburada teslimat sayfası: ücretsiz kargo eşiği kontrolü</t>
         </is>
       </c>
       <c r="D1212" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1212" s="6" t="inlineStr">
         <is>
-          <t>IKEA Kurumsal Kart bilgisi (kurumsal fatura seçeneği)</t>
+          <t>Yarın Kapında: sepet kargo bedavaya uygunsa ek ücret alınmıyor; eşik tutarı herkese açık sayfada bulunamadı</t>
         </is>
       </c>
       <c r="F1212" s="7" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="G1212" s="6" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
         </is>
       </c>
       <c r="H1212" s="7" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D28</t>
         </is>
       </c>
     </row>
     <row r="1213" ht="30" customHeight="1">
       <c r="A1213" s="5" t="inlineStr">
         <is>
-          <t>https://www.ikea.com.tr/ikea-onemli-bilgilendirme</t>
+          <t>https://www.ikea.com.tr/iade-politikasi</t>
         </is>
       </c>
       <c r="B1213" s="6" t="inlineStr">
@@ -51404,17 +51404,17 @@
       </c>
       <c r="C1213" s="6" t="inlineStr">
         <is>
-          <t>IKEA TR önemli bilgilendirme sayfası</t>
+          <t>IKEA TR iade politikası</t>
         </is>
       </c>
       <c r="D1213" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1213" s="6" t="inlineStr">
         <is>
-          <t>Önemli bilgilendirme sayfası; teslimat ve ödeme başlıkları için taranan sayfalar arasında yer aldı</t>
+          <t>İnternet siparişlerinde 14 gün ücretsiz iade, mağazada 30 gün; ambalajı açılmamış orijinal kutu şartı; özel kesim ürünler iade dışı</t>
         </is>
       </c>
       <c r="F1213" s="7" t="inlineStr">
@@ -51436,7 +51436,7 @@
     <row r="1214" ht="16.5" customHeight="1">
       <c r="A1214" s="5" t="inlineStr">
         <is>
-          <t>https://www.ikea.com.tr/musteri-hizmetleri/garanti-kosullari</t>
+          <t>https://www.ikea.com.tr/ikea-kurumsal</t>
         </is>
       </c>
       <c r="B1214" s="6" t="inlineStr">
@@ -51446,17 +51446,17 @@
       </c>
       <c r="C1214" s="6" t="inlineStr">
         <is>
-          <t>IKEA TR garanti koşulları</t>
+          <t>IKEA TR kurumsal sayfası</t>
         </is>
       </c>
       <c r="D1214" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1214" s="6" t="inlineStr">
         <is>
-          <t>Garanti koşulları sayfası (garanti başlığı için taranan sayfa)</t>
+          <t>IKEA Kurumsal Kart bilgisi (kurumsal fatura seçeneği)</t>
         </is>
       </c>
       <c r="F1214" s="7" t="inlineStr">
@@ -51478,205 +51478,205 @@
     <row r="1215" ht="30" customHeight="1">
       <c r="A1215" s="5" t="inlineStr">
         <is>
+          <t>https://www.ikea.com.tr/ikea-onemli-bilgilendirme</t>
+        </is>
+      </c>
+      <c r="B1215" s="6" t="inlineStr">
+        <is>
+          <t>ikea.com.tr</t>
+        </is>
+      </c>
+      <c r="C1215" s="6" t="inlineStr">
+        <is>
+          <t>IKEA TR önemli bilgilendirme sayfası</t>
+        </is>
+      </c>
+      <c r="D1215" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1215" s="6" t="inlineStr">
+        <is>
+          <t>Önemli bilgilendirme sayfası; teslimat ve ödeme başlıkları için taranan sayfalar arasında yer aldı</t>
+        </is>
+      </c>
+      <c r="F1215" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1215" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1215" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216" ht="16.5" customHeight="1">
+      <c r="A1216" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ikea.com.tr/musteri-hizmetleri/garanti-kosullari</t>
+        </is>
+      </c>
+      <c r="B1216" s="6" t="inlineStr">
+        <is>
+          <t>ikea.com.tr</t>
+        </is>
+      </c>
+      <c r="C1216" s="6" t="inlineStr">
+        <is>
+          <t>IKEA TR garanti koşulları</t>
+        </is>
+      </c>
+      <c r="D1216" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1216" s="6" t="inlineStr">
+        <is>
+          <t>Garanti koşulları sayfası (garanti başlığı için taranan sayfa)</t>
+        </is>
+      </c>
+      <c r="F1216" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1216" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1216" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217" ht="30" customHeight="1">
+      <c r="A1217" s="5" t="inlineStr">
+        <is>
           <t>https://www.ikea.com.tr/musteri-hizmetleri/sikca-sorulan-sorular</t>
         </is>
       </c>
-      <c r="B1215" s="6" t="inlineStr">
+      <c r="B1217" s="6" t="inlineStr">
         <is>
           <t>ikea.com.tr</t>
         </is>
       </c>
-      <c r="C1215" s="6" t="inlineStr">
+      <c r="C1217" s="6" t="inlineStr">
         <is>
           <t>IKEA TR SSS</t>
         </is>
       </c>
-      <c r="D1215" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1215" s="6" t="inlineStr">
+      <c r="D1217" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1217" s="6" t="inlineStr">
         <is>
           <t>SSS sayfası; hasar politikası bilgisi statik HTML'de görünmedi</t>
         </is>
       </c>
-      <c r="F1215" s="7" t="inlineStr">
+      <c r="F1217" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1215" s="6" t="inlineStr">
+      <c r="G1217" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1215" s="7" t="inlineStr">
+      <c r="H1217" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1216" ht="43.5" customHeight="1">
-      <c r="A1216" s="5" t="inlineStr">
+    <row r="1218" ht="43.5" customHeight="1">
+      <c r="A1218" s="5" t="inlineStr">
         <is>
           <t>https://www.ikea.com.tr/nakliye-hizmeti</t>
         </is>
       </c>
-      <c r="B1216" s="6" t="inlineStr">
+      <c r="B1218" s="6" t="inlineStr">
         <is>
           <t>ikea.com.tr</t>
         </is>
       </c>
-      <c r="C1216" s="6" t="inlineStr">
+      <c r="C1218" s="6" t="inlineStr">
         <is>
           <t>IKEA TR nakliye hizmeti</t>
         </is>
       </c>
-      <c r="D1216" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1216" s="6" t="inlineStr">
+      <c r="D1218" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1218" s="6" t="inlineStr">
         <is>
           <t>Arvato, Horoz, HepsiJET, Yurtiçi, KolayGelsin; şehir içi ayrı nakliye hizmeti; daire kapısına kadar teslim; minimum sipariş 500 TL, kargo 299 TL (1.500 TL'ye kadar) ve 799 TL (7.500 TL'ye kadar), üstünde %11</t>
         </is>
       </c>
-      <c r="F1216" s="7" t="inlineStr">
+      <c r="F1218" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1216" s="6" t="inlineStr">
+      <c r="G1218" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1216" s="7" t="inlineStr">
+      <c r="H1218" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1217" ht="43.5" customHeight="1">
-      <c r="A1217" s="5" t="inlineStr">
+    <row r="1219" ht="43.5" customHeight="1">
+      <c r="A1219" s="5" t="inlineStr">
         <is>
           <t>https://www.ikea.com.tr/odeme-secenekleri</t>
         </is>
       </c>
-      <c r="B1217" s="6" t="inlineStr">
+      <c r="B1219" s="6" t="inlineStr">
         <is>
           <t>ikea.com.tr</t>
         </is>
       </c>
-      <c r="C1217" s="6" t="inlineStr">
+      <c r="C1219" s="6" t="inlineStr">
         <is>
           <t>IKEA TR ödeme ve taksit koşulları</t>
         </is>
       </c>
-      <c r="D1217" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1217" s="6" t="inlineStr">
+      <c r="D1219" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1219" s="6" t="inlineStr">
         <is>
           <t>1.500 TL üzeri 3 taksit; IKEA Aile üyelerine 7.500 TL üzeri 6 ve 20.000 TL üzeri 9 taksit (belirli kartlar); 5 Ocak 2026 - 3 Ocak 2027 arası geçerli; kapıda ödeme yok (Full 3D kart)</t>
         </is>
       </c>
-      <c r="F1217" s="7" t="inlineStr">
+      <c r="F1219" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1217" s="6" t="inlineStr">
+      <c r="G1219" s="6" t="inlineStr">
         <is>
           <t>curl</t>
-        </is>
-      </c>
-      <c r="H1217" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1218" ht="30" customHeight="1">
-      <c r="A1218" s="5" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/artematurkiye/</t>
-        </is>
-      </c>
-      <c r="B1218" s="6" t="inlineStr">
-        <is>
-          <t>instagram.com</t>
-        </is>
-      </c>
-      <c r="C1218" s="6" t="inlineStr">
-        <is>
-          <t>Artema Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
-        </is>
-      </c>
-      <c r="D1218" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1218" s="6" t="inlineStr">
-        <is>
-          <t>~20K takipçi, 579 gönderi (SERP'ten, yaklaşık)</t>
-        </is>
-      </c>
-      <c r="F1218" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1218" s="6" t="inlineStr">
-        <is>
-          <t>API (DataForSEO SERP snippet)</t>
-        </is>
-      </c>
-      <c r="H1218" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1219" ht="30" customHeight="1">
-      <c r="A1219" s="5" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/canakkaleseramik/</t>
-        </is>
-      </c>
-      <c r="B1219" s="6" t="inlineStr">
-        <is>
-          <t>instagram.com</t>
-        </is>
-      </c>
-      <c r="C1219" s="6" t="inlineStr">
-        <is>
-          <t>Kale Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
-        </is>
-      </c>
-      <c r="D1219" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1219" s="6" t="inlineStr">
-        <is>
-          <t>Sayı SERP'te görünmedi, alınamadı</t>
-        </is>
-      </c>
-      <c r="F1219" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1219" s="6" t="inlineStr">
-        <is>
-          <t>API (DataForSEO SERP snippet)</t>
         </is>
       </c>
       <c r="H1219" s="7" t="inlineStr">
@@ -51688,7 +51688,7 @@
     <row r="1220" ht="30" customHeight="1">
       <c r="A1220" s="5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/creavitturkiye/</t>
+          <t>https://www.instagram.com/artematurkiye/</t>
         </is>
       </c>
       <c r="B1220" s="6" t="inlineStr">
@@ -51698,17 +51698,17 @@
       </c>
       <c r="C1220" s="6" t="inlineStr">
         <is>
-          <t>Creavit Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
+          <t>Artema Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
         </is>
       </c>
       <c r="D1220" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1220" s="6" t="inlineStr">
         <is>
-          <t>Sayı SERP'te görünmedi, alınamadı</t>
+          <t>~20K takipçi, 579 gönderi (SERP'ten, yaklaşık)</t>
         </is>
       </c>
       <c r="F1220" s="7" t="inlineStr">
@@ -51730,7 +51730,7 @@
     <row r="1221" ht="30" customHeight="1">
       <c r="A1221" s="5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/elginkaneca/</t>
+          <t>https://www.instagram.com/canakkaleseramik/</t>
         </is>
       </c>
       <c r="B1221" s="6" t="inlineStr">
@@ -51740,17 +51740,17 @@
       </c>
       <c r="C1221" s="6" t="inlineStr">
         <is>
-          <t>E.C.A. (Elginkan) Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
+          <t>Kale Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
         </is>
       </c>
       <c r="D1221" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1221" s="6" t="inlineStr">
         <is>
-          <t>~24K takipçi, 1694 gönderi (SERP'ten, yaklaşık)</t>
+          <t>Sayı SERP'te görünmedi, alınamadı</t>
         </is>
       </c>
       <c r="F1221" s="7" t="inlineStr">
@@ -51772,7 +51772,7 @@
     <row r="1222" ht="30" customHeight="1">
       <c r="A1222" s="5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/geberit.tr/</t>
+          <t>https://www.instagram.com/creavitturkiye/</t>
         </is>
       </c>
       <c r="B1222" s="6" t="inlineStr">
@@ -51782,17 +51782,17 @@
       </c>
       <c r="C1222" s="6" t="inlineStr">
         <is>
-          <t>Geberit Türkiye Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
+          <t>Creavit Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
         </is>
       </c>
       <c r="D1222" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1222" s="6" t="inlineStr">
         <is>
-          <t>~39K takipçi, 806 gönderi (SERP'ten, yaklaşık)</t>
+          <t>Sayı SERP'te görünmedi, alınamadı</t>
         </is>
       </c>
       <c r="F1222" s="7" t="inlineStr">
@@ -51814,7 +51814,7 @@
     <row r="1223" ht="30" customHeight="1">
       <c r="A1223" s="5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/groheturkiye/</t>
+          <t>https://www.instagram.com/elginkaneca/</t>
         </is>
       </c>
       <c r="B1223" s="6" t="inlineStr">
@@ -51824,17 +51824,17 @@
       </c>
       <c r="C1223" s="6" t="inlineStr">
         <is>
-          <t>Grohe Türkiye Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
+          <t>E.C.A. (Elginkan) Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
         </is>
       </c>
       <c r="D1223" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1223" s="6" t="inlineStr">
         <is>
-          <t>Sayı SERP'te görünmedi, alınamadı</t>
+          <t>~24K takipçi, 1694 gönderi (SERP'ten, yaklaşık)</t>
         </is>
       </c>
       <c r="F1223" s="7" t="inlineStr">
@@ -51856,511 +51856,511 @@
     <row r="1224" ht="30" customHeight="1">
       <c r="A1224" s="5" t="inlineStr">
         <is>
+          <t>https://www.instagram.com/geberit.tr/</t>
+        </is>
+      </c>
+      <c r="B1224" s="6" t="inlineStr">
+        <is>
+          <t>instagram.com</t>
+        </is>
+      </c>
+      <c r="C1224" s="6" t="inlineStr">
+        <is>
+          <t>Geberit Türkiye Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
+        </is>
+      </c>
+      <c r="D1224" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1224" s="6" t="inlineStr">
+        <is>
+          <t>~39K takipçi, 806 gönderi (SERP'ten, yaklaşık)</t>
+        </is>
+      </c>
+      <c r="F1224" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1224" s="6" t="inlineStr">
+        <is>
+          <t>API (DataForSEO SERP snippet)</t>
+        </is>
+      </c>
+      <c r="H1224" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225" ht="30" customHeight="1">
+      <c r="A1225" s="5" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/groheturkiye/</t>
+        </is>
+      </c>
+      <c r="B1225" s="6" t="inlineStr">
+        <is>
+          <t>instagram.com</t>
+        </is>
+      </c>
+      <c r="C1225" s="6" t="inlineStr">
+        <is>
+          <t>Grohe Türkiye Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
+        </is>
+      </c>
+      <c r="D1225" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1225" s="6" t="inlineStr">
+        <is>
+          <t>Sayı SERP'te görünmedi, alınamadı</t>
+        </is>
+      </c>
+      <c r="F1225" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1225" s="6" t="inlineStr">
+        <is>
+          <t>API (DataForSEO SERP snippet)</t>
+        </is>
+      </c>
+      <c r="H1225" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226" ht="30" customHeight="1">
+      <c r="A1226" s="5" t="inlineStr">
+        <is>
           <t>https://www.instagram.com/vitraturkiye/</t>
         </is>
       </c>
-      <c r="B1224" s="6" t="inlineStr">
+      <c r="B1226" s="6" t="inlineStr">
         <is>
           <t>instagram.com</t>
         </is>
       </c>
-      <c r="C1224" s="6" t="inlineStr">
+      <c r="C1226" s="6" t="inlineStr">
         <is>
           <t>VitrA Türkiye Instagram profil sayısı (giriş gerektirdiğinden sayfa açılmadı)</t>
         </is>
       </c>
-      <c r="D1224" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1224" s="6" t="inlineStr">
+      <c r="D1226" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1226" s="6" t="inlineStr">
         <is>
           <t>~144K takipçi, 1.8K+ gönderi (Google SERP snippet'inden, yaklaşık)</t>
         </is>
       </c>
-      <c r="F1224" s="7" t="inlineStr">
+      <c r="F1226" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1224" s="6" t="inlineStr">
+      <c r="G1226" s="6" t="inlineStr">
         <is>
           <t>API (DataForSEO SERP snippet)</t>
         </is>
       </c>
-      <c r="H1224" s="7" t="inlineStr">
+      <c r="H1226" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1225" ht="16.5" customHeight="1">
-      <c r="A1225" s="5" t="inlineStr">
+    <row r="1227" ht="16.5" customHeight="1">
+      <c r="A1227" s="5" t="inlineStr">
         <is>
           <t>https://www.kale.com.tr/iletisim</t>
         </is>
       </c>
-      <c r="B1225" s="6" t="inlineStr">
+      <c r="B1227" s="6" t="inlineStr">
         <is>
           <t>kale.com.tr</t>
         </is>
       </c>
-      <c r="C1225" s="6" t="inlineStr">
+      <c r="C1227" s="6" t="inlineStr">
         <is>
           <t>Kale iletişim sayfası</t>
         </is>
       </c>
-      <c r="D1225" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1225" s="6" t="inlineStr">
+      <c r="D1227" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1227" s="6" t="inlineStr">
         <is>
           <t>İletişim kanalları ve destek hattı</t>
         </is>
       </c>
-      <c r="F1225" s="7" t="inlineStr">
+      <c r="F1227" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1225" s="6" t="inlineStr">
+      <c r="G1227" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1225" s="7" t="inlineStr">
+      <c r="H1227" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1226" ht="16.5" customHeight="1">
-      <c r="A1226" s="5" t="inlineStr">
+    <row r="1228" ht="16.5" customHeight="1">
+      <c r="A1228" s="5" t="inlineStr">
         <is>
           <t>https://www.kale.com.tr/magazalar-ve-satis-noktalari</t>
         </is>
       </c>
-      <c r="B1226" s="6" t="inlineStr">
+      <c r="B1228" s="6" t="inlineStr">
         <is>
           <t>kale.com.tr</t>
         </is>
       </c>
-      <c r="C1226" s="6" t="inlineStr">
+      <c r="C1228" s="6" t="inlineStr">
         <is>
           <t>Kale mağaza ve satış noktaları</t>
         </is>
       </c>
-      <c r="D1226" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1226" s="6" t="inlineStr">
+      <c r="D1228" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1228" s="6" t="inlineStr">
         <is>
           <t>Online satışın olmadığı, satış noktalarına yönlendirme yapıldığı</t>
         </is>
       </c>
-      <c r="F1226" s="7" t="inlineStr">
+      <c r="F1228" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1226" s="6" t="inlineStr">
+      <c r="G1228" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1226" s="7" t="inlineStr">
+      <c r="H1228" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1227" ht="43.5" customHeight="1">
-      <c r="A1227" s="5" t="inlineStr">
+    <row r="1229" ht="43.5" customHeight="1">
+      <c r="A1229" s="5" t="inlineStr">
         <is>
           <t>https://www.kale.com.tr/sikca-sorulan-sorular</t>
         </is>
       </c>
-      <c r="B1227" s="6" t="inlineStr">
+      <c r="B1229" s="6" t="inlineStr">
         <is>
           <t>kale.com.tr</t>
         </is>
       </c>
-      <c r="C1227" s="6" t="inlineStr">
+      <c r="C1229" s="6" t="inlineStr">
         <is>
           <t>Kale garanti, teslimat ve iade SSS</t>
         </is>
       </c>
-      <c r="D1227" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1227" s="6" t="inlineStr">
+      <c r="D1229" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1229" s="6" t="inlineStr">
         <is>
           <t>Seramik sağlık gereçleri ve armatürler 10 ve 5 yıl, musluk 2 yıl, duş sistemleri ve gömme rezervuar 5 yıl garanti; servis işçiliği 1 yıl; ayrı yedek parça sayfası bulunamadı</t>
         </is>
       </c>
-      <c r="F1227" s="7" t="inlineStr">
+      <c r="F1229" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1227" s="6" t="inlineStr">
+      <c r="G1229" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1227" s="7" t="inlineStr">
+      <c r="H1229" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1228" ht="30" customHeight="1">
-      <c r="A1228" s="5" t="inlineStr">
+    <row r="1230" ht="30" customHeight="1">
+      <c r="A1230" s="5" t="inlineStr">
         <is>
           <t>https://www.kale.com.tr/yetkili-servisler-ve-hizmetler</t>
         </is>
       </c>
-      <c r="B1228" s="6" t="inlineStr">
+      <c r="B1230" s="6" t="inlineStr">
         <is>
           <t>kale.com.tr</t>
         </is>
       </c>
-      <c r="C1228" s="6" t="inlineStr">
+      <c r="C1230" s="6" t="inlineStr">
         <is>
           <t>Kale yetkili servis ve servis talebi</t>
         </is>
       </c>
-      <c r="D1228" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1228" s="6" t="inlineStr">
+      <c r="D1230" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1230" s="6" t="inlineStr">
         <is>
           <t>Yetkili servisler sayfasından servis talebi; servis hattı; WhatsApp destek hattı</t>
         </is>
       </c>
-      <c r="F1228" s="7" t="inlineStr">
+      <c r="F1230" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1228" s="6" t="inlineStr">
+      <c r="G1230" s="6" t="inlineStr">
         <is>
           <t>curl</t>
         </is>
       </c>
-      <c r="H1228" s="7" t="inlineStr">
+      <c r="H1230" s="7" t="inlineStr">
         <is>
           <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1229" ht="30" customHeight="1">
-      <c r="A1229" s="5" t="inlineStr">
-        <is>
-          <t>https://www.koctas.com.tr/hizmetlerimiz/montaj-hizmeti</t>
-        </is>
-      </c>
-      <c r="B1229" s="6" t="inlineStr">
-        <is>
-          <t>koctas.com.tr</t>
-        </is>
-      </c>
-      <c r="C1229" s="6" t="inlineStr">
-        <is>
-          <t>Koçtaş montaj hizmeti sayfası</t>
-        </is>
-      </c>
-      <c r="D1229" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1229" s="6" t="inlineStr">
-        <is>
-          <t>Montaj hizmetleri ücretli; montaj kaleminin sepete ayrıca eklenmesi gerekir; sayfada fiyat ve il sayısı yok</t>
-        </is>
-      </c>
-      <c r="F1229" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1229" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1229" s="7" t="inlineStr">
-        <is>
-          <t>D28</t>
-        </is>
-      </c>
-    </row>
-    <row r="1230" ht="70.5" customHeight="1">
-      <c r="A1230" s="5" t="inlineStr">
-        <is>
-          <t>https://www.koctas.com.tr/myaccount/faq</t>
-        </is>
-      </c>
-      <c r="B1230" s="6" t="inlineStr">
-        <is>
-          <t>koctas.com.tr</t>
-        </is>
-      </c>
-      <c r="C1230" s="6" t="inlineStr">
-        <is>
-          <t>Koçtaş yardım sayfası: kargo, teslimat, iade, hasar ve ödeme koşullarının doğrulanması</t>
-        </is>
-      </c>
-      <c r="D1230" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1230" s="6" t="inlineStr">
-        <is>
-          <t>Ücretsiz kargo eşiği yalnız 300 TL (altı 49,90 TL); 30 desi üstü lojistikle kata teslim; iade 14 gün, iade kodu 7 gün; demonte üründe montaj yapıldıysa iade yok; klozet takımı ve kapağında ambalajı açılmamış şartı; hasar için Durum Tespit Tutanağı; kapıda ödeme yok; taksit eşiği bu sayfada 10.000 TL (/taksitler sayfasında 5.000 TL, tutarsız)</t>
-        </is>
-      </c>
-      <c r="F1230" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1230" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1230" s="7" t="inlineStr">
-        <is>
-          <t>D23 · D28</t>
         </is>
       </c>
     </row>
     <row r="1231" ht="30" customHeight="1">
       <c r="A1231" s="5" t="inlineStr">
         <is>
+          <t>https://www.koctas.com.tr/hizmetlerimiz/montaj-hizmeti</t>
+        </is>
+      </c>
+      <c r="B1231" s="6" t="inlineStr">
+        <is>
+          <t>koctas.com.tr</t>
+        </is>
+      </c>
+      <c r="C1231" s="6" t="inlineStr">
+        <is>
+          <t>Koçtaş montaj hizmeti sayfası</t>
+        </is>
+      </c>
+      <c r="D1231" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1231" s="6" t="inlineStr">
+        <is>
+          <t>Montaj hizmetleri ücretli; montaj kaleminin sepete ayrıca eklenmesi gerekir; sayfada fiyat ve il sayısı yok</t>
+        </is>
+      </c>
+      <c r="F1231" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1231" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1231" s="7" t="inlineStr">
+        <is>
+          <t>D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232" ht="70.5" customHeight="1">
+      <c r="A1232" s="5" t="inlineStr">
+        <is>
+          <t>https://www.koctas.com.tr/myaccount/faq</t>
+        </is>
+      </c>
+      <c r="B1232" s="6" t="inlineStr">
+        <is>
+          <t>koctas.com.tr</t>
+        </is>
+      </c>
+      <c r="C1232" s="6" t="inlineStr">
+        <is>
+          <t>Koçtaş yardım sayfası: kargo, teslimat, iade, hasar ve ödeme koşullarının doğrulanması</t>
+        </is>
+      </c>
+      <c r="D1232" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1232" s="6" t="inlineStr">
+        <is>
+          <t>Ücretsiz kargo eşiği yalnız 300 TL (altı 49,90 TL); 30 desi üstü lojistikle kata teslim; iade 14 gün, iade kodu 7 gün; demonte üründe montaj yapıldıysa iade yok; klozet takımı ve kapağında ambalajı açılmamış şartı; hasar için Durum Tespit Tutanağı; kapıda ödeme yok; taksit eşiği bu sayfada 10.000 TL (/taksitler sayfasında 5.000 TL, tutarsız)</t>
+        </is>
+      </c>
+      <c r="F1232" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1232" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1232" s="7" t="inlineStr">
+        <is>
+          <t>D23 · D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233" ht="30" customHeight="1">
+      <c r="A1233" s="5" t="inlineStr">
+        <is>
           <t>https://www.koctas.com.tr/nakliye-ve-montaj-hizmetleri</t>
         </is>
       </c>
-      <c r="B1231" s="6" t="inlineStr">
+      <c r="B1233" s="6" t="inlineStr">
         <is>
           <t>koctas.com.tr</t>
         </is>
       </c>
-      <c r="C1231" s="6" t="inlineStr">
+      <c r="C1233" s="6" t="inlineStr">
         <is>
           <t>Koçtaş nakliye ve montaj hizmetleri</t>
         </is>
       </c>
-      <c r="D1231" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1231" s="6" t="inlineStr">
+      <c r="D1233" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1233" s="6" t="inlineStr">
         <is>
           <t>20 ilde montaj (İstanbul, Ankara, İzmir başta); seçili aydınlatma ve mobilyada ücretsiz montaj; Ustabilir hizmeti</t>
         </is>
       </c>
-      <c r="F1231" s="7" t="inlineStr">
+      <c r="F1233" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1231" s="6" t="inlineStr">
+      <c r="G1233" s="6" t="inlineStr">
         <is>
           <t>API (Apify rag-web-browser)</t>
         </is>
       </c>
-      <c r="H1231" s="7" t="inlineStr">
+      <c r="H1233" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1232" ht="43.5" customHeight="1">
-      <c r="A1232" s="5" t="inlineStr">
+    <row r="1234" ht="43.5" customHeight="1">
+      <c r="A1234" s="5" t="inlineStr">
         <is>
           <t>https://www.koctas.com.tr/taksitler</t>
         </is>
       </c>
-      <c r="B1232" s="6" t="inlineStr">
+      <c r="B1234" s="6" t="inlineStr">
         <is>
           <t>koctas.com.tr</t>
         </is>
       </c>
-      <c r="C1232" s="6" t="inlineStr">
+      <c r="C1234" s="6" t="inlineStr">
         <is>
           <t>Koçtaş taksit ve vade farksız koşulları</t>
         </is>
       </c>
-      <c r="D1232" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1232" s="6" t="inlineStr">
+      <c r="D1234" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1234" s="6" t="inlineStr">
         <is>
           <t>Online 5.000 TL üzeri 7 taksite kadar vade farksız (mağazada 10.000 TL üzeri); vade farklı 9 taksite kadar; Flexi kart, aidatsız kart ve TEB Worldcard kapsam dışı; alışveriş kredisi bulunamadı</t>
         </is>
       </c>
-      <c r="F1232" s="7" t="inlineStr">
+      <c r="F1234" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1232" s="6" t="inlineStr">
+      <c r="G1234" s="6" t="inlineStr">
         <is>
           <t>API (Apify rag-web-browser)</t>
         </is>
       </c>
-      <c r="H1232" s="7" t="inlineStr">
+      <c r="H1234" s="7" t="inlineStr">
         <is>
           <t>D23</t>
         </is>
       </c>
     </row>
-    <row r="1233" ht="43.5" customHeight="1">
-      <c r="A1233" s="5" t="inlineStr">
+    <row r="1235" ht="43.5" customHeight="1">
+      <c r="A1235" s="5" t="inlineStr">
         <is>
           <t>https://www.n11.com/destek-merkezi</t>
         </is>
       </c>
-      <c r="B1233" s="6" t="inlineStr">
+      <c r="B1235" s="6" t="inlineStr">
         <is>
           <t>n11.com</t>
         </is>
       </c>
-      <c r="C1233" s="6" t="inlineStr">
+      <c r="C1235" s="6" t="inlineStr">
         <is>
           <t>n11 destek merkezi: kargo, iade, kapıda ödeme ve kredi koşullarının doğrulanması</t>
         </is>
       </c>
-      <c r="D1233" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1233" s="6" t="inlineStr">
+      <c r="D1235" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1235" s="6" t="inlineStr">
         <is>
           <t>Kargo için 3 seçenek (alıcı öder, mağaza öder, şartlı kargo); 14 gün cayma hakkı; kapıda ödeme yok; Garanti Alışveriş Kredisi 750-15.000 TL, 48 aya varan vade; garanti satıcı sorumluluğunda</t>
         </is>
       </c>
-      <c r="F1233" s="7" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="G1233" s="6" t="inlineStr">
-        <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
-        </is>
-      </c>
-      <c r="H1233" s="7" t="inlineStr">
+      <c r="F1235" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1235" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1235" s="7" t="inlineStr">
         <is>
           <t>D23 · D28</t>
-        </is>
-      </c>
-    </row>
-    <row r="1234" ht="30" customHeight="1">
-      <c r="A1234" s="5" t="inlineStr">
-        <is>
-          <t>https://www.n11.com/destek-merkezi/iptal-iade-degisim/iade</t>
-        </is>
-      </c>
-      <c r="B1234" s="6" t="inlineStr">
-        <is>
-          <t>n11.com</t>
-        </is>
-      </c>
-      <c r="C1234" s="6" t="inlineStr">
-        <is>
-          <t>n11 iade koşulları</t>
-        </is>
-      </c>
-      <c r="D1234" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1234" s="6" t="inlineStr">
-        <is>
-          <t>14 gün cayma hakkı; arama sonucu özeti</t>
-        </is>
-      </c>
-      <c r="F1234" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1234" s="6" t="inlineStr">
-        <is>
-          <t>arama sonucu özeti (sayfa açılamadı)</t>
-        </is>
-      </c>
-      <c r="H1234" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1235" ht="30" customHeight="1">
-      <c r="A1235" s="5" t="inlineStr">
-        <is>
-          <t>https://www.n11.com/destek-merkezi/kargo-teslimat/kargo-gonderim-sureci</t>
-        </is>
-      </c>
-      <c r="B1235" s="6" t="inlineStr">
-        <is>
-          <t>n11.com</t>
-        </is>
-      </c>
-      <c r="C1235" s="6" t="inlineStr">
-        <is>
-          <t>n11 kargo ve gönderim süreci</t>
-        </is>
-      </c>
-      <c r="D1235" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1235" s="6" t="inlineStr">
-        <is>
-          <t>Mağaza bazlı 300 TL şartlı kargo ifadesi (Chrome ile sayfada bulunamadı); arama sonucu özeti</t>
-        </is>
-      </c>
-      <c r="F1235" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1235" s="6" t="inlineStr">
-        <is>
-          <t>arama sonucu özeti (sayfa açılamadı)</t>
-        </is>
-      </c>
-      <c r="H1235" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
         </is>
       </c>
     </row>
     <row r="1236" ht="30" customHeight="1">
       <c r="A1236" s="5" t="inlineStr">
         <is>
-          <t>https://www.n11.com/destek-merkezi/odeme/odeme-secenekleri</t>
+          <t>https://www.n11.com/destek-merkezi/iptal-iade-degisim/iade</t>
         </is>
       </c>
       <c r="B1236" s="6" t="inlineStr">
@@ -52370,17 +52370,17 @@
       </c>
       <c r="C1236" s="6" t="inlineStr">
         <is>
-          <t>n11 ödeme seçenekleri</t>
+          <t>n11 iade koşulları</t>
         </is>
       </c>
       <c r="D1236" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1236" s="6" t="inlineStr">
         <is>
-          <t>Banka bazlı taksit; alışveriş kredisiyle 48 aya kadar; sayfa 403 döndü, arama sonucu özetinden alındı</t>
+          <t>14 gün cayma hakkı; arama sonucu özeti</t>
         </is>
       </c>
       <c r="F1236" s="7" t="inlineStr">
@@ -52402,7 +52402,7 @@
     <row r="1237" ht="30" customHeight="1">
       <c r="A1237" s="5" t="inlineStr">
         <is>
-          <t>https://www.n11.com/kampanyalar/kredim-alisveris-kredisi-kampanyasi</t>
+          <t>https://www.n11.com/destek-merkezi/kargo-teslimat/kargo-gonderim-sureci</t>
         </is>
       </c>
       <c r="B1237" s="6" t="inlineStr">
@@ -52412,17 +52412,17 @@
       </c>
       <c r="C1237" s="6" t="inlineStr">
         <is>
-          <t>n11 alışveriş kredisi kampanyası</t>
+          <t>n11 kargo ve gönderim süreci</t>
         </is>
       </c>
       <c r="D1237" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1237" s="6" t="inlineStr">
         <is>
-          <t>Kredim 6 taksit ve İş Bankası alışveriş kredisi; arama sonucu özeti</t>
+          <t>Mağaza bazlı 300 TL şartlı kargo ifadesi (Chrome ile sayfada bulunamadı); arama sonucu özeti</t>
         </is>
       </c>
       <c r="F1237" s="7" t="inlineStr">
@@ -52444,27 +52444,27 @@
     <row r="1238" ht="30" customHeight="1">
       <c r="A1238" s="5" t="inlineStr">
         <is>
-          <t>http://www.pinterest.com/canakkalesrmk/</t>
+          <t>https://www.n11.com/destek-merkezi/odeme/odeme-secenekleri</t>
         </is>
       </c>
       <c r="B1238" s="6" t="inlineStr">
         <is>
-          <t>pinterest.com</t>
+          <t>n11.com</t>
         </is>
       </c>
       <c r="C1238" s="6" t="inlineStr">
         <is>
-          <t>Kale Pinterest hesabı: takipçi sayısı (sosyal kanal karşılaştırması)</t>
+          <t>n11 ödeme seçenekleri</t>
         </is>
       </c>
       <c r="D1238" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1238" s="6" t="inlineStr">
         <is>
-          <t>943 takipçi</t>
+          <t>Banka bazlı taksit; alışveriş kredisiyle 48 aya kadar; sayfa 403 döndü, arama sonucu özetinden alındı</t>
         </is>
       </c>
       <c r="F1238" s="7" t="inlineStr">
@@ -52474,7 +52474,7 @@
       </c>
       <c r="G1238" s="6" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>arama sonucu özeti (sayfa açılamadı)</t>
         </is>
       </c>
       <c r="H1238" s="7" t="inlineStr">
@@ -52483,30 +52483,30 @@
         </is>
       </c>
     </row>
-    <row r="1239" ht="43.5" customHeight="1">
+    <row r="1239" ht="30" customHeight="1">
       <c r="A1239" s="5" t="inlineStr">
         <is>
-          <t>https://tr.pinterest.com/DesignStudioVitrA/</t>
+          <t>https://www.n11.com/kampanyalar/kredim-alisveris-kredisi-kampanyasi</t>
         </is>
       </c>
       <c r="B1239" s="6" t="inlineStr">
         <is>
-          <t>pinterest.com</t>
+          <t>n11.com</t>
         </is>
       </c>
       <c r="C1239" s="6" t="inlineStr">
         <is>
-          <t>Design Studio VitrA Pinterest hesabı (Artema sayfası bu hesaba bağlanıyor): takipçi sayısı (sosyal kanal karşılaştırması)</t>
+          <t>n11 alışveriş kredisi kampanyası</t>
         </is>
       </c>
       <c r="D1239" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1239" s="6" t="inlineStr">
         <is>
-          <t>3.825 takipçi</t>
+          <t>Kredim 6 taksit ve İş Bankası alışveriş kredisi; arama sonucu özeti</t>
         </is>
       </c>
       <c r="F1239" s="7" t="inlineStr">
@@ -52516,7 +52516,7 @@
       </c>
       <c r="G1239" s="6" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>arama sonucu özeti (sayfa açılamadı)</t>
         </is>
       </c>
       <c r="H1239" s="7" t="inlineStr">
@@ -52528,7 +52528,7 @@
     <row r="1240" ht="30" customHeight="1">
       <c r="A1240" s="5" t="inlineStr">
         <is>
-          <t>https://tr.pinterest.com/creavitturkiye/</t>
+          <t>http://www.pinterest.com/canakkalesrmk/</t>
         </is>
       </c>
       <c r="B1240" s="6" t="inlineStr">
@@ -52538,17 +52538,17 @@
       </c>
       <c r="C1240" s="6" t="inlineStr">
         <is>
-          <t>Creavit Pinterest hesabı: takipçi sayısı (sosyal kanal karşılaştırması)</t>
+          <t>Kale Pinterest hesabı: takipçi sayısı (sosyal kanal karşılaştırması)</t>
         </is>
       </c>
       <c r="D1240" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1240" s="6" t="inlineStr">
         <is>
-          <t>187 takipçi</t>
+          <t>943 takipçi</t>
         </is>
       </c>
       <c r="F1240" s="7" t="inlineStr">
@@ -52567,10 +52567,10 @@
         </is>
       </c>
     </row>
-    <row r="1241" ht="30" customHeight="1">
+    <row r="1241" ht="43.5" customHeight="1">
       <c r="A1241" s="5" t="inlineStr">
         <is>
-          <t>https://tr.pinterest.com/vitrabathrooms/</t>
+          <t>https://tr.pinterest.com/DesignStudioVitrA/</t>
         </is>
       </c>
       <c r="B1241" s="6" t="inlineStr">
@@ -52580,17 +52580,17 @@
       </c>
       <c r="C1241" s="6" t="inlineStr">
         <is>
-          <t>VitrA Bathrooms Pinterest hesabı: takipçi sayısı (sosyal kanal karşılaştırması)</t>
+          <t>Design Studio VitrA Pinterest hesabı (Artema sayfası bu hesaba bağlanıyor): takipçi sayısı (sosyal kanal karşılaştırması)</t>
         </is>
       </c>
       <c r="D1241" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1241" s="6" t="inlineStr">
         <is>
-          <t>1.478 takipçi</t>
+          <t>3.825 takipçi</t>
         </is>
       </c>
       <c r="F1241" s="7" t="inlineStr">
@@ -52612,7 +52612,7 @@
     <row r="1242" ht="30" customHeight="1">
       <c r="A1242" s="5" t="inlineStr">
         <is>
-          <t>https://www.pinterest.com/grohe/</t>
+          <t>https://tr.pinterest.com/creavitturkiye/</t>
         </is>
       </c>
       <c r="B1242" s="6" t="inlineStr">
@@ -52622,17 +52622,17 @@
       </c>
       <c r="C1242" s="6" t="inlineStr">
         <is>
-          <t>Grohe Pinterest hesabı: takipçi sayısı (sosyal kanal karşılaştırması)</t>
+          <t>Creavit Pinterest hesabı: takipçi sayısı (sosyal kanal karşılaştırması)</t>
         </is>
       </c>
       <c r="D1242" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1242" s="6" t="inlineStr">
         <is>
-          <t>10.325 takipçi</t>
+          <t>187 takipçi</t>
         </is>
       </c>
       <c r="F1242" s="7" t="inlineStr">
@@ -52654,27 +52654,27 @@
     <row r="1243" ht="30" customHeight="1">
       <c r="A1243" s="5" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@banyobutarafta</t>
+          <t>https://tr.pinterest.com/vitrabathrooms/</t>
         </is>
       </c>
       <c r="B1243" s="6" t="inlineStr">
         <is>
-          <t>tiktok.com</t>
+          <t>pinterest.com</t>
         </is>
       </c>
       <c r="C1243" s="6" t="inlineStr">
         <is>
-          <t>Creavit TikTok hesabı (VitrA ve Artema için resmi hesap bulunamadı)</t>
+          <t>VitrA Bathrooms Pinterest hesabı: takipçi sayısı (sosyal kanal karşılaştırması)</t>
         </is>
       </c>
       <c r="D1243" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1243" s="6" t="inlineStr">
         <is>
-          <t>~118 takipçi (SERP'ten, yaklaşık)</t>
+          <t>1.478 takipçi</t>
         </is>
       </c>
       <c r="F1243" s="7" t="inlineStr">
@@ -52684,7 +52684,7 @@
       </c>
       <c r="G1243" s="6" t="inlineStr">
         <is>
-          <t>API (DataForSEO SERP snippet)</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="H1243" s="7" t="inlineStr">
@@ -52696,27 +52696,27 @@
     <row r="1244" ht="30" customHeight="1">
       <c r="A1244" s="5" t="inlineStr">
         <is>
-          <t>https://akademi.trendyol.com/satici-bilgi-merkezi/detay/275</t>
+          <t>https://www.pinterest.com/grohe/</t>
         </is>
       </c>
       <c r="B1244" s="6" t="inlineStr">
         <is>
-          <t>trendyol.com</t>
+          <t>pinterest.com</t>
         </is>
       </c>
       <c r="C1244" s="6" t="inlineStr">
         <is>
-          <t>Trendyol satıcı bilgi merkezi: taksit ve ödeme</t>
+          <t>Grohe Pinterest hesabı: takipçi sayısı (sosyal kanal karşılaştırması)</t>
         </is>
       </c>
       <c r="D1244" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1244" s="6" t="inlineStr">
         <is>
-          <t>Satıcı tarafı taksit ve ödeme kuralları; arama sonucu özeti</t>
+          <t>10.325 takipçi</t>
         </is>
       </c>
       <c r="F1244" s="7" t="inlineStr">
@@ -52726,7 +52726,7 @@
       </c>
       <c r="G1244" s="6" t="inlineStr">
         <is>
-          <t>arama sonucu özeti (sayfa açılamadı)</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="H1244" s="7" t="inlineStr">
@@ -52738,27 +52738,27 @@
     <row r="1245" ht="30" customHeight="1">
       <c r="A1245" s="5" t="inlineStr">
         <is>
-          <t>https://akademi.trendyol.com/satici-bilgi-merkezi/detay/kargo-baremi-uygulamasi</t>
+          <t>https://www.tiktok.com/@banyobutarafta</t>
         </is>
       </c>
       <c r="B1245" s="6" t="inlineStr">
         <is>
-          <t>trendyol.com</t>
+          <t>tiktok.com</t>
         </is>
       </c>
       <c r="C1245" s="6" t="inlineStr">
         <is>
-          <t>Trendyol satıcı bilgi merkezi: kargo baremi</t>
+          <t>Creavit TikTok hesabı (VitrA ve Artema için resmi hesap bulunamadı)</t>
         </is>
       </c>
       <c r="D1245" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1245" s="6" t="inlineStr">
         <is>
-          <t>Satıcı bareminin 350 TL olduğu ifadesi (alıcı eşiği doğrulanamadı); arama sonucu özeti</t>
+          <t>~118 takipçi (SERP'ten, yaklaşık)</t>
         </is>
       </c>
       <c r="F1245" s="7" t="inlineStr">
@@ -52768,7 +52768,7 @@
       </c>
       <c r="G1245" s="6" t="inlineStr">
         <is>
-          <t>arama sonucu özeti (sayfa açılamadı)</t>
+          <t>API (DataForSEO SERP snippet)</t>
         </is>
       </c>
       <c r="H1245" s="7" t="inlineStr">
@@ -52780,7 +52780,7 @@
     <row r="1246" ht="30" customHeight="1">
       <c r="A1246" s="5" t="inlineStr">
         <is>
-          <t>https://www.trendyol.com/s/mobilya-alisverisi-hakkinda-sik-sorulan-sorular</t>
+          <t>https://akademi.trendyol.com/satici-bilgi-merkezi/detay/275</t>
         </is>
       </c>
       <c r="B1246" s="6" t="inlineStr">
@@ -52790,39 +52790,39 @@
       </c>
       <c r="C1246" s="6" t="inlineStr">
         <is>
-          <t>Trendyol mobilya alışverişi SSS: montajlı ürün iadesi</t>
+          <t>Trendyol satıcı bilgi merkezi: taksit ve ödeme</t>
         </is>
       </c>
       <c r="D1246" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1246" s="6" t="inlineStr">
         <is>
-          <t>Montajlı ürünün iadesi, paketin adresten alınması ve ücretsiz yapılması adımları</t>
+          <t>Satıcı tarafı taksit ve ödeme kuralları; arama sonucu özeti</t>
         </is>
       </c>
       <c r="F1246" s="7" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="G1246" s="6" t="inlineStr">
         <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+          <t>arama sonucu özeti (sayfa açılamadı)</t>
         </is>
       </c>
       <c r="H1246" s="7" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D23</t>
         </is>
       </c>
     </row>
     <row r="1247" ht="30" customHeight="1">
       <c r="A1247" s="5" t="inlineStr">
         <is>
-          <t>https://www.trendyol.com/s/montajix-montaj-hizmeti</t>
+          <t>https://akademi.trendyol.com/satici-bilgi-merkezi/detay/kargo-baremi-uygulamasi</t>
         </is>
       </c>
       <c r="B1247" s="6" t="inlineStr">
@@ -52832,17 +52832,17 @@
       </c>
       <c r="C1247" s="6" t="inlineStr">
         <is>
-          <t>Trendyol ürün sayfasında ek montaj hizmeti</t>
+          <t>Trendyol satıcı bilgi merkezi: kargo baremi</t>
         </is>
       </c>
       <c r="D1247" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1247" s="6" t="inlineStr">
         <is>
-          <t>30 gün içinde randevu; tamamlanan montaj iade edilemez; sayfa açılamadı, arama sonucu özetinden alındı</t>
+          <t>Satıcı bareminin 350 TL olduğu ifadesi (alıcı eşiği doğrulanamadı); arama sonucu özeti</t>
         </is>
       </c>
       <c r="F1247" s="7" t="inlineStr">
@@ -52864,7 +52864,7 @@
     <row r="1248" ht="30" customHeight="1">
       <c r="A1248" s="5" t="inlineStr">
         <is>
-          <t>https://www.trendyol.com/yardim/iade</t>
+          <t>https://www.trendyol.com/s/mobilya-alisverisi-hakkinda-sik-sorulan-sorular</t>
         </is>
       </c>
       <c r="B1248" s="6" t="inlineStr">
@@ -52874,17 +52874,17 @@
       </c>
       <c r="C1248" s="6" t="inlineStr">
         <is>
-          <t>Trendyol iade süresi, taksit ve kapıda ödeme kuralları</t>
+          <t>Trendyol mobilya alışverişi SSS: montajlı ürün iadesi</t>
         </is>
       </c>
       <c r="D1248" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1248" s="6" t="inlineStr">
         <is>
-          <t>İade süresi teslimden itibaren 15 gün; taksit yalnızca taksit yapılabilen ürünlerde; kapıda ödeme ve havale seçeneği yok</t>
+          <t>Montajlı ürünün iadesi, paketin adresten alınması ve ücretsiz yapılması adımları</t>
         </is>
       </c>
       <c r="F1248" s="7" t="inlineStr">
@@ -52899,14 +52899,14 @@
       </c>
       <c r="H1248" s="7" t="inlineStr">
         <is>
-          <t>D23 · D28</t>
+          <t>D28</t>
         </is>
       </c>
     </row>
     <row r="1249" ht="30" customHeight="1">
       <c r="A1249" s="5" t="inlineStr">
         <is>
-          <t>https://www.trendyol.com/yardim/kargo-ve-teslimat</t>
+          <t>https://www.trendyol.com/s/montajix-montaj-hizmeti</t>
         </is>
       </c>
       <c r="B1249" s="6" t="inlineStr">
@@ -52916,153 +52916,153 @@
       </c>
       <c r="C1249" s="6" t="inlineStr">
         <is>
-          <t>Trendyol kargo ücreti ve teslimat</t>
+          <t>Trendyol ürün sayfasında ek montaj hizmeti</t>
         </is>
       </c>
       <c r="D1249" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1249" s="6" t="inlineStr">
         <is>
-          <t>Standart kargo ücreti 59,99 TL; 'kargo bedava' kampanyalı ürünlerde ücretsiz; genel alıcı eşiği yok</t>
+          <t>30 gün içinde randevu; tamamlanan montaj iade edilemez; sayfa açılamadı, arama sonucu özetinden alındı</t>
         </is>
       </c>
       <c r="F1249" s="7" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="G1249" s="6" t="inlineStr">
         <is>
-          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+          <t>arama sonucu özeti (sayfa açılamadı)</t>
         </is>
       </c>
       <c r="H1249" s="7" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>D23</t>
         </is>
       </c>
     </row>
     <row r="1250" ht="30" customHeight="1">
       <c r="A1250" s="5" t="inlineStr">
         <is>
+          <t>https://www.trendyol.com/yardim/iade</t>
+        </is>
+      </c>
+      <c r="B1250" s="6" t="inlineStr">
+        <is>
+          <t>trendyol.com</t>
+        </is>
+      </c>
+      <c r="C1250" s="6" t="inlineStr">
+        <is>
+          <t>Trendyol iade süresi, taksit ve kapıda ödeme kuralları</t>
+        </is>
+      </c>
+      <c r="D1250" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1250" s="6" t="inlineStr">
+        <is>
+          <t>İade süresi teslimden itibaren 15 gün; taksit yalnızca taksit yapılabilen ürünlerde; kapıda ödeme ve havale seçeneği yok</t>
+        </is>
+      </c>
+      <c r="F1250" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1250" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1250" s="7" t="inlineStr">
+        <is>
+          <t>D23 · D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251" ht="30" customHeight="1">
+      <c r="A1251" s="5" t="inlineStr">
+        <is>
+          <t>https://www.trendyol.com/yardim/kargo-ve-teslimat</t>
+        </is>
+      </c>
+      <c r="B1251" s="6" t="inlineStr">
+        <is>
+          <t>trendyol.com</t>
+        </is>
+      </c>
+      <c r="C1251" s="6" t="inlineStr">
+        <is>
+          <t>Trendyol kargo ücreti ve teslimat</t>
+        </is>
+      </c>
+      <c r="D1251" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1251" s="6" t="inlineStr">
+        <is>
+          <t>Standart kargo ücreti 59,99 TL; 'kargo bedava' kampanyalı ürünlerde ücretsiz; genel alıcı eşiği yok</t>
+        </is>
+      </c>
+      <c r="F1251" s="7" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="G1251" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı (Chrome, kullanıcı oturumu)</t>
+        </is>
+      </c>
+      <c r="H1251" s="7" t="inlineStr">
+        <is>
+          <t>D28</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252" ht="30" customHeight="1">
+      <c r="A1252" s="5" t="inlineStr">
+        <is>
           <t>https://www.trendyol.com/yardim/sorular/3?grup=1</t>
         </is>
       </c>
-      <c r="B1250" s="6" t="inlineStr">
+      <c r="B1252" s="6" t="inlineStr">
         <is>
           <t>trendyol.com</t>
         </is>
       </c>
-      <c r="C1250" s="6" t="inlineStr">
+      <c r="C1252" s="6" t="inlineStr">
         <is>
           <t>Trendyol yardım soruları (ödeme ve taksit)</t>
         </is>
       </c>
-      <c r="D1250" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1250" s="6" t="inlineStr">
+      <c r="D1252" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1252" s="6" t="inlineStr">
         <is>
           <t>Taksit ve ödeme yöntemleri özeti; Trendyol Kredi Pazaryeri; sayfa açılamadı, arama sonucu özetinden alındı</t>
         </is>
       </c>
-      <c r="F1250" s="7" t="inlineStr">
+      <c r="F1252" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1250" s="6" t="inlineStr">
+      <c r="G1252" s="6" t="inlineStr">
         <is>
           <t>arama sonucu özeti (sayfa açılamadı)</t>
-        </is>
-      </c>
-      <c r="H1250" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1251" ht="43.5" customHeight="1">
-      <c r="A1251" s="5" t="inlineStr">
-        <is>
-          <t>https://www.vitra.com.tr/degisim-iade-rehberi</t>
-        </is>
-      </c>
-      <c r="B1251" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr</t>
-        </is>
-      </c>
-      <c r="C1251" s="6" t="inlineStr">
-        <is>
-          <t>VitrA değişim ve iade koşulları</t>
-        </is>
-      </c>
-      <c r="D1251" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1251" s="6" t="inlineStr">
-        <is>
-          <t>Rehberde iade gün sayısı yazmıyor (süre yalnızca ürün sayfasında, 30 güne kadar ücretsiz iade); büyük paket adresten lojistik firmasıyla alınır; klozete özel iade koşulu bulunamadı</t>
-        </is>
-      </c>
-      <c r="F1251" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1251" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1251" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1252" ht="43.5" customHeight="1">
-      <c r="A1252" s="5" t="inlineStr">
-        <is>
-          <t>https://www.vitra.com.tr/dusakabin/universal-surgulu-on-panel-mat-siyah-p-65650002270</t>
-        </is>
-      </c>
-      <c r="B1252" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr</t>
-        </is>
-      </c>
-      <c r="C1252" s="6" t="inlineStr">
-        <is>
-          <t>VitrA ürün sayfası örneği (duşakabin): taksit tablosu, kargo tarihi, montaj seçeneği ve iade ifadesi</t>
-        </is>
-      </c>
-      <c r="D1252" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1252" s="6" t="inlineStr">
-        <is>
-          <t>Ürün tablosunda 12 taksite kadar seçenek (8, 9 ve 12 taksit çoğu kartta vade farklı, 2-3-4-6 taksit eşit tutar); tahmini kargoya teslim tarihi; 30 güne kadar ücretsiz iade ifadesi; montaj hizmeti seçeneği (+5.300 TL)</t>
-        </is>
-      </c>
-      <c r="F1252" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1252" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
         </is>
       </c>
       <c r="H1252" s="7" t="inlineStr">
@@ -53074,111 +53074,111 @@
     <row r="1253" ht="43.5" customHeight="1">
       <c r="A1253" s="5" t="inlineStr">
         <is>
+          <t>https://www.vitra.com.tr/degisim-iade-rehberi</t>
+        </is>
+      </c>
+      <c r="B1253" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr</t>
+        </is>
+      </c>
+      <c r="C1253" s="6" t="inlineStr">
+        <is>
+          <t>VitrA değişim ve iade koşulları</t>
+        </is>
+      </c>
+      <c r="D1253" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1253" s="6" t="inlineStr">
+        <is>
+          <t>Rehberde iade gün sayısı yazmıyor (süre yalnızca ürün sayfasında, 30 güne kadar ücretsiz iade); büyük paket adresten lojistik firmasıyla alınır; klozete özel iade koşulu bulunamadı</t>
+        </is>
+      </c>
+      <c r="F1253" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1253" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1253" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254" ht="43.5" customHeight="1">
+      <c r="A1254" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vitra.com.tr/dusakabin/universal-surgulu-on-panel-mat-siyah-p-65650002270</t>
+        </is>
+      </c>
+      <c r="B1254" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr</t>
+        </is>
+      </c>
+      <c r="C1254" s="6" t="inlineStr">
+        <is>
+          <t>VitrA ürün sayfası örneği (duşakabin): taksit tablosu, kargo tarihi, montaj seçeneği ve iade ifadesi</t>
+        </is>
+      </c>
+      <c r="D1254" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1254" s="6" t="inlineStr">
+        <is>
+          <t>Ürün tablosunda 12 taksite kadar seçenek (8, 9 ve 12 taksit çoğu kartta vade farklı, 2-3-4-6 taksit eşit tutar); tahmini kargoya teslim tarihi; 30 güne kadar ücretsiz iade ifadesi; montaj hizmeti seçeneği (+5.300 TL)</t>
+        </is>
+      </c>
+      <c r="F1254" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1254" s="6" t="inlineStr">
+        <is>
+          <t>curl</t>
+        </is>
+      </c>
+      <c r="H1254" s="7" t="inlineStr">
+        <is>
+          <t>D23</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255" ht="43.5" customHeight="1">
+      <c r="A1255" s="5" t="inlineStr">
+        <is>
           <t>https://www.vitra.com.tr/garanti-hizmetleri</t>
         </is>
       </c>
-      <c r="B1253" s="6" t="inlineStr">
+      <c r="B1255" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C1253" s="6" t="inlineStr">
+      <c r="C1255" s="6" t="inlineStr">
         <is>
           <t>VitrA garanti bilgisi (süre, kapsam, ek garanti paketi)</t>
         </is>
       </c>
-      <c r="D1253" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1253" s="6" t="inlineStr">
+      <c r="D1255" s="6" t="inlineStr">
+        <is>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
+        </is>
+      </c>
+      <c r="E1255" s="6" t="inlineStr">
         <is>
           <t>Ürün sayfalarında garanti süresi yazmıyor; V-Care akıllı klozette 2 yıl (ek garanti paketiyle 4 yıl ve yıllık periyodik bakım); '+2 yıl ek garanti ve periyodik bakım paketi' sayfası</t>
-        </is>
-      </c>
-      <c r="F1253" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1253" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1253" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1254" ht="30" customHeight="1">
-      <c r="A1254" s="5" t="inlineStr">
-        <is>
-          <t>https://www.vitra.com.tr/garanti-talep-formu</t>
-        </is>
-      </c>
-      <c r="B1254" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr</t>
-        </is>
-      </c>
-      <c r="C1254" s="6" t="inlineStr">
-        <is>
-          <t>VitrA online garanti talep formu</t>
-        </is>
-      </c>
-      <c r="D1254" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1254" s="6" t="inlineStr">
-        <is>
-          <t>Garanti talebinin fatura kaydıyla online iletilmesi; servis randevu akışıyla bağlantı</t>
-        </is>
-      </c>
-      <c r="F1254" s="7" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="G1254" s="6" t="inlineStr">
-        <is>
-          <t>curl</t>
-        </is>
-      </c>
-      <c r="H1254" s="7" t="inlineStr">
-        <is>
-          <t>D23</t>
-        </is>
-      </c>
-    </row>
-    <row r="1255" ht="30" customHeight="1">
-      <c r="A1255" s="5" t="inlineStr">
-        <is>
-          <t>https://www.vitra.com.tr/kampanyalar</t>
-        </is>
-      </c>
-      <c r="B1255" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr</t>
-        </is>
-      </c>
-      <c r="C1255" s="6" t="inlineStr">
-        <is>
-          <t>VitrA kampanya ve taksit koşulları</t>
-        </is>
-      </c>
-      <c r="D1255" s="6" t="inlineStr">
-        <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
-        </is>
-      </c>
-      <c r="E1255" s="6" t="inlineStr">
-        <is>
-          <t>21 Eylül - 30 Kasım 2026: seçili renkli ürünlerde %40 indirim, 9 aya varan taksit, 40.000 TL ve üzeri alışverişte ücretsiz montaj</t>
         </is>
       </c>
       <c r="F1255" s="7" t="inlineStr">
@@ -53200,7 +53200,7 @@
     <row r="1256" ht="30" customHeight="1">
       <c r="A1256" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/musteri-hizmetleri</t>
+          <t>https://www.vitra.com.tr/garanti-talep-formu</t>
         </is>
       </c>
       <c r="B1256" s="6" t="inlineStr">
@@ -53210,17 +53210,17 @@
       </c>
       <c r="C1256" s="6" t="inlineStr">
         <is>
-          <t>VitrA müşteri hizmetleri ve iletişim kanalları</t>
+          <t>VitrA online garanti talep formu</t>
         </is>
       </c>
       <c r="D1256" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1256" s="6" t="inlineStr">
         <is>
-          <t>Müşteri hizmetleri hattı (Pzt-Cts 09:00-18:00); online servis randevusu; WhatsApp hattı bulunamadı; ayrı yedek parça sayfası bulunamadı</t>
+          <t>Garanti talebinin fatura kaydıyla online iletilmesi; servis randevu akışıyla bağlantı</t>
         </is>
       </c>
       <c r="F1256" s="7" t="inlineStr">
@@ -53239,10 +53239,10 @@
         </is>
       </c>
     </row>
-    <row r="1257" ht="43.5" customHeight="1">
+    <row r="1257" ht="30" customHeight="1">
       <c r="A1257" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/odeme-rehberi</t>
+          <t>https://www.vitra.com.tr/kampanyalar</t>
         </is>
       </c>
       <c r="B1257" s="6" t="inlineStr">
@@ -53252,17 +53252,17 @@
       </c>
       <c r="C1257" s="6" t="inlineStr">
         <is>
-          <t>VitrA ödeme yöntemleri ve taksit koşulları</t>
+          <t>VitrA kampanya ve taksit koşulları</t>
         </is>
       </c>
       <c r="D1257" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1257" s="6" t="inlineStr">
         <is>
-          <t>Yalnızca kredi kartı (iyzico altyapısı, 3D Secure); kapıda ödeme yok; havale/EFT rehberde geçmiyor; sepette kurumsal fatura bilgisi eklenebiliyor; Banyo ve Karo ürünleri taşıma koşulları nedeniyle ayrı sepette</t>
+          <t>21 Eylül - 30 Kasım 2026: seçili renkli ürünlerde %40 indirim, 9 aya varan taksit, 40.000 TL ve üzeri alışverişte ücretsiz montaj</t>
         </is>
       </c>
       <c r="F1257" s="7" t="inlineStr">
@@ -53284,7 +53284,7 @@
     <row r="1258" ht="30" customHeight="1">
       <c r="A1258" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/support/faq</t>
+          <t>https://www.vitra.com.tr/musteri-hizmetleri</t>
         </is>
       </c>
       <c r="B1258" s="6" t="inlineStr">
@@ -53294,17 +53294,17 @@
       </c>
       <c r="C1258" s="6" t="inlineStr">
         <is>
-          <t>VitrA destek SSS sayfası</t>
+          <t>VitrA müşteri hizmetleri ve iletişim kanalları</t>
         </is>
       </c>
       <c r="D1258" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1258" s="6" t="inlineStr">
         <is>
-          <t>Destek SSS sayfası; ödeme, teslimat ve iade başlıkları için taranan sayfalar arasında yer aldı</t>
+          <t>Müşteri hizmetleri hattı (Pzt-Cts 09:00-18:00); online servis randevusu; WhatsApp hattı bulunamadı; ayrı yedek parça sayfası bulunamadı</t>
         </is>
       </c>
       <c r="F1258" s="7" t="inlineStr">
@@ -53323,10 +53323,10 @@
         </is>
       </c>
     </row>
-    <row r="1259" ht="57" customHeight="1">
+    <row r="1259" ht="43.5" customHeight="1">
       <c r="A1259" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/teslimat-rehberi</t>
+          <t>https://www.vitra.com.tr/odeme-rehberi</t>
         </is>
       </c>
       <c r="B1259" s="6" t="inlineStr">
@@ -53336,17 +53336,17 @@
       </c>
       <c r="C1259" s="6" t="inlineStr">
         <is>
-          <t>VitrA teslimat koşulları (kargo, büyük ürün, kat teslimi)</t>
+          <t>VitrA ödeme yöntemleri ve taksit koşulları</t>
         </is>
       </c>
       <c r="D1259" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1259" s="6" t="inlineStr">
         <is>
-          <t>Sipariş en fazla 3 iş günü içinde paket boyutu ve adrese göre kargo veya lojistik firmasına teslim edilir; ürün sayfasında tahmini kargoya teslim tarihi; 'kapınıza kadar' teslim, kat teslimi belirtilmemiş; ücretsiz kargo eşiksiz</t>
+          <t>Yalnızca kredi kartı (iyzico altyapısı, 3D Secure); kapıda ödeme yok; havale/EFT rehberde geçmiyor; sepette kurumsal fatura bilgisi eklenebiliyor; Banyo ve Karo ürünleri taşıma koşulları nedeniyle ayrı sepette</t>
         </is>
       </c>
       <c r="F1259" s="7" t="inlineStr">
@@ -53368,27 +53368,27 @@
     <row r="1260" ht="30" customHeight="1">
       <c r="A1260" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/grohe/about</t>
+          <t>https://www.vitra.com.tr/support/faq</t>
         </is>
       </c>
       <c r="B1260" s="6" t="inlineStr">
         <is>
-          <t>youtube.com</t>
+          <t>vitra.com.tr</t>
         </is>
       </c>
       <c r="C1260" s="6" t="inlineStr">
         <is>
-          <t>Grohe Türkiye YouTube kanalı: abone, video ve görüntüleme sayıları (sosyal kanal karşılaştırması)</t>
+          <t>VitrA destek SSS sayfası</t>
         </is>
       </c>
       <c r="D1260" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1260" s="6" t="inlineStr">
         <is>
-          <t>75,1 B abone, 627 video, 21.947.546 görüntüleme; 2 Mar 2007'de katılım</t>
+          <t>Destek SSS sayfası; ödeme, teslimat ve iade başlıkları için taranan sayfalar arasında yer aldı</t>
         </is>
       </c>
       <c r="F1260" s="7" t="inlineStr">
@@ -53407,30 +53407,30 @@
         </is>
       </c>
     </row>
-    <row r="1261" ht="30" customHeight="1">
+    <row r="1261" ht="57" customHeight="1">
       <c r="A1261" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/user/ArtemATurkiye/about</t>
+          <t>https://www.vitra.com.tr/teslimat-rehberi</t>
         </is>
       </c>
       <c r="B1261" s="6" t="inlineStr">
         <is>
-          <t>youtube.com</t>
+          <t>vitra.com.tr</t>
         </is>
       </c>
       <c r="C1261" s="6" t="inlineStr">
         <is>
-          <t>Artema YouTube kanalı: abone, video ve görüntüleme sayıları (sosyal kanal karşılaştırması)</t>
+          <t>VitrA teslimat koşulları (kargo, büyük ürün, kat teslimi)</t>
         </is>
       </c>
       <c r="D1261" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1261" s="6" t="inlineStr">
         <is>
-          <t>4,75 B abone, 33 video, 19.702.538 görüntüleme; 3 Eki 2012'de katılım</t>
+          <t>Sipariş en fazla 3 iş günü içinde paket boyutu ve adrese göre kargo veya lojistik firmasına teslim edilir; ürün sayfasında tahmini kargoya teslim tarihi; 'kapınıza kadar' teslim, kat teslimi belirtilmemiş; ücretsiz kargo eşiksiz</t>
         </is>
       </c>
       <c r="F1261" s="7" t="inlineStr">
@@ -53452,7 +53452,7 @@
     <row r="1262" ht="30" customHeight="1">
       <c r="A1262" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/user/CanakkaleSrmk/about</t>
+          <t>https://www.youtube.com/grohe/about</t>
         </is>
       </c>
       <c r="B1262" s="6" t="inlineStr">
@@ -53462,17 +53462,17 @@
       </c>
       <c r="C1262" s="6" t="inlineStr">
         <is>
-          <t>Kale (Çanakkale Seramik) YouTube kanalı: abone, video ve görüntüleme sayıları (sosyal kanal karşılaştırması)</t>
+          <t>Grohe Türkiye YouTube kanalı: abone, video ve görüntüleme sayıları (sosyal kanal karşılaştırması)</t>
         </is>
       </c>
       <c r="D1262" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1262" s="6" t="inlineStr">
         <is>
-          <t>948 abone, 577 video, 1.405.640 görüntüleme; 2 Mar 2012'de katılım</t>
+          <t>75,1 B abone, 627 video, 21.947.546 görüntüleme; 2 Mar 2007'de katılım</t>
         </is>
       </c>
       <c r="F1262" s="7" t="inlineStr">
@@ -53494,7 +53494,7 @@
     <row r="1263" ht="30" customHeight="1">
       <c r="A1263" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/user/VitrAglobal/about</t>
+          <t>https://www.youtube.com/user/ArtemATurkiye/about</t>
         </is>
       </c>
       <c r="B1263" s="6" t="inlineStr">
@@ -53504,17 +53504,17 @@
       </c>
       <c r="C1263" s="6" t="inlineStr">
         <is>
-          <t>VitrA Türkiye YouTube kanalı: abone, video ve görüntüleme sayıları (sosyal kanal karşılaştırması)</t>
+          <t>Artema YouTube kanalı: abone, video ve görüntüleme sayıları (sosyal kanal karşılaştırması)</t>
         </is>
       </c>
       <c r="D1263" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1263" s="6" t="inlineStr">
         <is>
-          <t>1,58 Mn abone, 402 video, 55.846.765 görüntüleme; 18 Ağu 2011'de katılım</t>
+          <t>4,75 B abone, 33 video, 19.702.538 görüntüleme; 3 Eki 2012'de katılım</t>
         </is>
       </c>
       <c r="F1263" s="7" t="inlineStr">
@@ -53536,7 +53536,7 @@
     <row r="1264" ht="30" customHeight="1">
       <c r="A1264" s="5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/user/creavitturkiye/about</t>
+          <t>https://www.youtube.com/user/CanakkaleSrmk/about</t>
         </is>
       </c>
       <c r="B1264" s="6" t="inlineStr">
@@ -53546,17 +53546,17 @@
       </c>
       <c r="C1264" s="6" t="inlineStr">
         <is>
-          <t>Creavit YouTube kanalı: abone, video ve görüntüleme sayıları (sosyal kanal karşılaştırması)</t>
+          <t>Kale (Çanakkale Seramik) YouTube kanalı: abone, video ve görüntüleme sayıları (sosyal kanal karşılaştırması)</t>
         </is>
       </c>
       <c r="D1264" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1264" s="6" t="inlineStr">
         <is>
-          <t>2,17 B abone, 227 video, 7.055.522 görüntüleme; 22 Mar 2013'te katılım</t>
+          <t>948 abone, 577 video, 1.405.640 görüntüleme; 2 Mar 2012'de katılım</t>
         </is>
       </c>
       <c r="F1264" s="7" t="inlineStr">
@@ -53578,27 +53578,27 @@
     <row r="1265" ht="30" customHeight="1">
       <c r="A1265" s="5" t="inlineStr">
         <is>
-          <t>https://www.duravit.com/en-us/service/bathroom-planner/</t>
+          <t>https://www.youtube.com/user/VitrAglobal/about</t>
         </is>
       </c>
       <c r="B1265" s="6" t="inlineStr">
         <is>
-          <t>duravit.com</t>
+          <t>youtube.com</t>
         </is>
       </c>
       <c r="C1265" s="6" t="inlineStr">
         <is>
-          <t>Duravit banyo planlayıcı (dijital deneyim aracı)</t>
+          <t>VitrA Türkiye YouTube kanalı: abone, video ve görüntüleme sayıları (sosyal kanal karşılaştırması)</t>
         </is>
       </c>
       <c r="D1265" s="6" t="inlineStr">
         <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1265" s="6" t="inlineStr">
         <is>
-          <t>Banyo ölçüsüne göre ürün yerleştirme ve plan çıktısı</t>
+          <t>1,58 Mn abone, 402 video, 55.846.765 görüntüleme; 18 Ağu 2011'de katılım</t>
         </is>
       </c>
       <c r="F1265" s="7" t="inlineStr">
@@ -53608,39 +53608,39 @@
       </c>
       <c r="G1265" s="6" t="inlineStr">
         <is>
-          <t>tarayıcı</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="H1265" s="7" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>D23</t>
         </is>
       </c>
     </row>
     <row r="1266" ht="30" customHeight="1">
       <c r="A1266" s="5" t="inlineStr">
         <is>
-          <t>https://www.geberit.de/badezimmerprodukte/wcs-urinale/dusch-wcs-geberit-aquaclean/testen/</t>
+          <t>https://www.youtube.com/user/creavitturkiye/about</t>
         </is>
       </c>
       <c r="B1266" s="6" t="inlineStr">
         <is>
-          <t>geberit.de</t>
+          <t>youtube.com</t>
         </is>
       </c>
       <c r="C1266" s="6" t="inlineStr">
         <is>
-          <t>Geberit AquaClean evde deneme programı (Almanya)</t>
+          <t>Creavit YouTube kanalı: abone, video ve görüntüleme sayıları (sosyal kanal karşılaştırması)</t>
         </is>
       </c>
       <c r="D1266" s="6" t="inlineStr">
         <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E1266" s="6" t="inlineStr">
         <is>
-          <t>Dusch-WC'nin 4 hafta ücretsiz evde denenmesi, kurulum videosu ile</t>
+          <t>2,17 B abone, 227 video, 7.055.522 görüntüleme; 22 Mar 2013'te katılım</t>
         </is>
       </c>
       <c r="F1266" s="7" t="inlineStr">
@@ -53650,39 +53650,39 @@
       </c>
       <c r="G1266" s="6" t="inlineStr">
         <is>
-          <t>tarayıcı</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="H1266" s="7" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>D23</t>
         </is>
       </c>
     </row>
     <row r="1267" ht="30" customHeight="1">
       <c r="A1267" s="5" t="inlineStr">
         <is>
-          <t>https://www.grohe.com/en-GB/service-support/spare-parts-finder</t>
+          <t>https://www.duravit.com/en-us/service/bathroom-planner/</t>
         </is>
       </c>
       <c r="B1267" s="6" t="inlineStr">
         <is>
-          <t>grohe.com</t>
+          <t>duravit.com</t>
         </is>
       </c>
       <c r="C1267" s="6" t="inlineStr">
         <is>
-          <t>GROHE Spare Parts Finder (yedek parça bulucu örneği)</t>
+          <t>Duravit banyo planlayıcı (dijital deneyim aracı)</t>
         </is>
       </c>
       <c r="D1267" s="6" t="inlineStr">
         <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E1267" s="6" t="inlineStr">
         <is>
-          <t>Patlatılmış çizim, parça numarası, montaj videosu; kamera ile ürün tanıma; üretimden kalkan ürünlerde 10 yıl parça güvencesi</t>
+          <t>Banyo ölçüsüne göre ürün yerleştirme ve plan çıktısı</t>
         </is>
       </c>
       <c r="F1267" s="7" t="inlineStr">
@@ -53697,34 +53697,34 @@
       </c>
       <c r="H1267" s="7" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>B10</t>
         </is>
       </c>
     </row>
     <row r="1268" ht="30" customHeight="1">
       <c r="A1268" s="5" t="inlineStr">
         <is>
-          <t>https://www.hansgrohe-usa.com/service/spare-parts-search</t>
+          <t>https://www.geberit.de/badezimmerprodukte/wcs-urinale/dusch-wcs-geberit-aquaclean/testen/</t>
         </is>
       </c>
       <c r="B1268" s="6" t="inlineStr">
         <is>
-          <t>hansgrohe-usa.com</t>
+          <t>geberit.de</t>
         </is>
       </c>
       <c r="C1268" s="6" t="inlineStr">
         <is>
-          <t>hansgrohe yedek parça arama (yedek parça bulucu örneği)</t>
+          <t>Geberit AquaClean evde deneme programı (Almanya)</t>
         </is>
       </c>
       <c r="D1268" s="6" t="inlineStr">
         <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E1268" s="6" t="inlineStr">
         <is>
-          <t>Patlatılmış çizim, parça numarası ve montaj videosu ile yedek parça bulma; uyumluluk bilgisi</t>
+          <t>Dusch-WC'nin 4 hafta ücretsiz evde denenmesi, kurulum videosu ile</t>
         </is>
       </c>
       <c r="F1268" s="7" t="inlineStr">
@@ -53739,34 +53739,34 @@
       </c>
       <c r="H1268" s="7" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>B13</t>
         </is>
       </c>
     </row>
     <row r="1269" ht="30" customHeight="1">
       <c r="A1269" s="5" t="inlineStr">
         <is>
-          <t>https://www.victorianplumbing.co.uk/help-and-customer-service/bathroom-finance</t>
+          <t>https://www.grohe.com/en-GB/service-support/spare-parts-finder</t>
         </is>
       </c>
       <c r="B1269" s="6" t="inlineStr">
         <is>
-          <t>victorianplumbing.co.uk</t>
+          <t>grohe.com</t>
         </is>
       </c>
       <c r="C1269" s="6" t="inlineStr">
         <is>
-          <t>Victorian Plumbing banyo finansmanı</t>
+          <t>GROHE Spare Parts Finder (yedek parça bulucu örneği)</t>
         </is>
       </c>
       <c r="D1269" s="6" t="inlineStr">
         <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E1269" s="6" t="inlineStr">
         <is>
-          <t>250 GBP üzeri siparişte %0 faizli finansman; sepet tutarına bağlı finansman modeli</t>
+          <t>Patlatılmış çizim, parça numarası, montaj videosu; kamera ile ürün tanıma; üretimden kalkan ürünlerde 10 yıl parça güvencesi</t>
         </is>
       </c>
       <c r="F1269" s="7" t="inlineStr">
@@ -53781,34 +53781,34 @@
       </c>
       <c r="H1269" s="7" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B12</t>
         </is>
       </c>
     </row>
     <row r="1270" ht="30" customHeight="1">
       <c r="A1270" s="5" t="inlineStr">
         <is>
-          <t>https://www.villeroy-boch.co.uk/r/bathroom-ideas/planning/bathroom-planner-online/</t>
+          <t>https://www.hansgrohe-usa.com/service/spare-parts-search</t>
         </is>
       </c>
       <c r="B1270" s="6" t="inlineStr">
         <is>
-          <t>villeroy-boch.co.uk</t>
+          <t>hansgrohe-usa.com</t>
         </is>
       </c>
       <c r="C1270" s="6" t="inlineStr">
         <is>
-          <t>Villeroy &amp; Boch 3D online banyo planlayıcı (dijital deneyim aracı)</t>
+          <t>hansgrohe yedek parça arama (yedek parça bulucu örneği)</t>
         </is>
       </c>
       <c r="D1270" s="6" t="inlineStr">
         <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E1270" s="6" t="inlineStr">
         <is>
-          <t>Banyo ölçüsüne göre ürün yerleştirme, planın PDF olarak bayiye iletilmesi</t>
+          <t>Patlatılmış çizim, parça numarası ve montaj videosu ile yedek parça bulma; uyumluluk bilgisi</t>
         </is>
       </c>
       <c r="F1270" s="7" t="inlineStr">
@@ -53823,54 +53823,138 @@
       </c>
       <c r="H1270" s="7" t="inlineStr">
         <is>
-          <t>B9</t>
+          <t>B11</t>
         </is>
       </c>
     </row>
     <row r="1271" ht="30" customHeight="1">
       <c r="A1271" s="5" t="inlineStr">
         <is>
+          <t>https://www.victorianplumbing.co.uk/help-and-customer-service/bathroom-finance</t>
+        </is>
+      </c>
+      <c r="B1271" s="6" t="inlineStr">
+        <is>
+          <t>victorianplumbing.co.uk</t>
+        </is>
+      </c>
+      <c r="C1271" s="6" t="inlineStr">
+        <is>
+          <t>Victorian Plumbing banyo finansmanı</t>
+        </is>
+      </c>
+      <c r="D1271" s="6" t="inlineStr">
+        <is>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+        </is>
+      </c>
+      <c r="E1271" s="6" t="inlineStr">
+        <is>
+          <t>250 GBP üzeri siparişte %0 faizli finansman; sepet tutarına bağlı finansman modeli</t>
+        </is>
+      </c>
+      <c r="F1271" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1271" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı</t>
+        </is>
+      </c>
+      <c r="H1271" s="7" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272" ht="30" customHeight="1">
+      <c r="A1272" s="5" t="inlineStr">
+        <is>
+          <t>https://www.villeroy-boch.co.uk/r/bathroom-ideas/planning/bathroom-planner-online/</t>
+        </is>
+      </c>
+      <c r="B1272" s="6" t="inlineStr">
+        <is>
+          <t>villeroy-boch.co.uk</t>
+        </is>
+      </c>
+      <c r="C1272" s="6" t="inlineStr">
+        <is>
+          <t>Villeroy &amp; Boch 3D online banyo planlayıcı (dijital deneyim aracı)</t>
+        </is>
+      </c>
+      <c r="D1272" s="6" t="inlineStr">
+        <is>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+        </is>
+      </c>
+      <c r="E1272" s="6" t="inlineStr">
+        <is>
+          <t>Banyo ölçüsüne göre ürün yerleştirme, planın PDF olarak bayiye iletilmesi</t>
+        </is>
+      </c>
+      <c r="F1272" s="7" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="G1272" s="6" t="inlineStr">
+        <is>
+          <t>tarayıcı</t>
+        </is>
+      </c>
+      <c r="H1272" s="7" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273" ht="30" customHeight="1">
+      <c r="A1273" s="5" t="inlineStr">
+        <is>
           <t>https://www.vitra.com.tr/banyonu-tasarla</t>
         </is>
       </c>
-      <c r="B1271" s="6" t="inlineStr">
+      <c r="B1273" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C1271" s="6" t="inlineStr">
+      <c r="C1273" s="6" t="inlineStr">
         <is>
           <t>VitrA V-Design (banyoyu tasarla) adresi: 3D planlayıcı durumu</t>
         </is>
       </c>
-      <c r="D1271" s="6" t="inlineStr">
-        <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 22 Sonraki Adımlar</t>
-        </is>
-      </c>
-      <c r="E1271" s="6" t="inlineStr">
+      <c r="D1273" s="6" t="inlineStr">
+        <is>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Sonraki Adımlar</t>
+        </is>
+      </c>
+      <c r="E1273" s="6" t="inlineStr">
         <is>
           <t>V-Design (2018) 750 banyo ve 300 karo ürünüyle tanıtılmıştı; adres bugün ana sayfaya yönleniyor</t>
         </is>
       </c>
-      <c r="F1271" s="7" t="inlineStr">
+      <c r="F1273" s="7" t="inlineStr">
         <is>
           <t>29.09.2026</t>
         </is>
       </c>
-      <c r="G1271" s="6" t="inlineStr">
+      <c r="G1273" s="6" t="inlineStr">
         <is>
           <t>tarayıcı</t>
         </is>
       </c>
-      <c r="H1271" s="7" t="inlineStr">
+      <c r="H1273" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H1271"/>
+  <autoFilter ref="A4:H1273"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
@@ -55141,6 +55225,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1269" r:id="rId1264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1270" r:id="rId1265"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1271" r:id="rId1266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1272" r:id="rId1267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1273" r:id="rId1268"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55309,11 +55395,11 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>04 · 11 · 12 · 14 · 16 · 17 · 18 · 19 · 21 · 22</t>
+          <t>04 · 11 · 12 · 14 · 16 · 17 · 18 · 19 · 20 · 22 · 23</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -55334,11 +55420,11 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>10 · 13 · 14 · 16 · 17 · 18 · 19 · 20 · 22</t>
+          <t>10 · 13 · 14 · 16 · 17 · 18 · 19 · 20 · 21 · 23</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -55363,7 +55449,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>07 · 08 · 10 · 15 · 18 · 19 · 21 · 22</t>
+          <t>07 · 08 · 10 · 15 · 19 · 20 · 22 · 23</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -55388,7 +55474,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 19 Kanal Politikaları ve Keşif Kanalları · 22 Sonraki Adımlar</t>
+          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 20 Kanal Politikaları ve Keşif Kanalları · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -55413,7 +55499,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -55438,7 +55524,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -55463,7 +55549,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>06 · 11 · 12 · 13 · 14 · 15 · 17 · 18 · 19 · 20 · 21 · 22</t>
+          <t>06 · 11 · 12 · 13 · 14 · 15 · 17 · 19 · 20 · 21 · 22 · 23</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -55488,7 +55574,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>03 · 04 · 05 · 06 · 07 · 08 · 09 · 11 · 12 · 13 · 18 · 19 · 21 · 22</t>
+          <t>03 · 04 · 05 · 06 · 07 · 08 · 09 · 11 · 12 · 13 · 19 · 20 · 22 · 23</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -55513,7 +55599,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>12 · 13 · 14 · 16 · 17 · 18 · 19 · 20</t>
+          <t>12 · 13 · 14 · 16 · 17 · 19 · 20 · 21</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -55538,7 +55624,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -55563,7 +55649,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Kanal Politikaları ve Keşif Kanalları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 20 Kanal Politikaları ve Keşif Kanalları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -55588,7 +55674,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 19 Kanal Politikaları ve Keşif Kanalları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 20 Kanal Politikaları ve Keşif Kanalları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -55613,7 +55699,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Sonraki Adımlar</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -55638,7 +55724,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>12 · 13 · 14 · 15 · 17 · 19 · 20</t>
+          <t>12 · 13 · 14 · 15 · 17 · 20 · 21</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -55688,7 +55774,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>03 · 04 · 05 · 06 · 07 · 08 · 09 · 10 · 11 · 12 · 13 · 15 · 18 · 19 · 21 · 22</t>
+          <t>03 · 04 · 05 · 06 · 07 · 08 · 09 · 10 · 11 · 12 · 13 · 15 · 19 · 20 · 22 · 23</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -55713,7 +55799,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>04 SSG ve BM: Derin Talep İncelemesi · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 18 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>04 SSG ve BM: Derin Talep İncelemesi · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 19 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -55738,7 +55824,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Kanal Politikaları ve Keşif Kanalları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 20 Kanal Politikaları ve Keşif Kanalları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -55763,7 +55849,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>02 Makro Ortam ve Ödeme Gücü · 22 Sonraki Adımlar</t>
+          <t>02 Makro Ortam ve Ödeme Gücü · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -55788,7 +55874,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -55813,7 +55899,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -55838,7 +55924,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -55863,7 +55949,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -55888,7 +55974,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -55913,7 +55999,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -55938,7 +56024,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -55963,7 +56049,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -55988,7 +56074,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -56013,7 +56099,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -56038,7 +56124,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -56063,7 +56149,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -56138,7 +56224,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -56213,7 +56299,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -56313,7 +56399,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -56338,7 +56424,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -56363,7 +56449,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 12 Yeni Kategori ve Segment Fırsatları · 22 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 12 Yeni Kategori ve Segment Fırsatları · 23 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -56413,7 +56499,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -56463,7 +56549,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -56588,7 +56674,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -56688,7 +56774,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>19 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>20 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -56763,7 +56849,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>20 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>21 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -56981,7 +57067,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Kapsam: Bu döküm, rapor HTML'indeki 44 kaynakça girdisinin tüm adreslerini, rapordaki bağlantıları, alt ajan araştırmalarında (veri/ham/derin) okunan sayfaları ve API kaynaklarını içerir; 1267 satır, 65 alan adı. Toplu okunan sayfalar kalıp adres ve adet olarak tek satırdadır.</t>
+          <t>Kapsam: Bu döküm, rapor HTML'indeki 44 kaynakça girdisinin tüm adreslerini, rapordaki bağlantıları, alt ajan araştırmalarında (veri/ham/derin) okunan sayfaları ve API kaynaklarını içerir; 1269 satır, 65 alan adı. Toplu okunan sayfalar kalıp adres ve adet olarak tek satırdadır.</t>
         </is>
       </c>
     </row>

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Yöntem" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 Kaynaklar'!$A$4:$H$1303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 Kaynaklar'!$A$4:$H$1305</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02 Alan adı özeti'!$A$4:$E$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03 Yöntem'!$A$4:$A$23</definedName>
   </definedNames>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1303"/>
+  <dimension ref="A1:H1305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -507,7 +507,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VitrA e-ticaret büyüme fırsatları · kaynak siteler ve sayfalar (1299 satır, 77 alan adı)</t>
+          <t>VitrA e-ticaret büyüme fırsatları · kaynak siteler ve sayfalar (1301 satır, 77 alan adı)</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>02 Ekonomik Ortam: Harcama, Güven ve Konut Piyasası · 25 Sonraki Adımlar</t>
+          <t>02 Ekonomik Ortam: Harcama, Güven ve Konut Piyasası · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 23 Kanal Rolleri ve Etkileşim Modeli · 25 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 24 Kanal Rolleri ve Etkileşim Modeli · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 12 Yeni Kategori ve Segment Fırsatları · 25 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 12 Yeni Kategori ve Segment Fırsatları · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 08 Google Arama Sonuçları ve AI Overview · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 23 Kanal Rolleri ve Etkileşim Modeli · 25 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 08 Google Arama Sonuçları ve AI Overview · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 24 Kanal Rolleri ve Etkileşim Modeli · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>04 SSG ve BM: Derin Talep İncelemesi · 08 Google Arama Sonuçları ve AI Overview · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 25 Sonraki Adımlar</t>
+          <t>04 SSG ve BM: Derin Talep İncelemesi · 08 Google Arama Sonuçları ve AI Overview · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>04 SSG ve BM: Derin Talep İncelemesi · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 20 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Rolleri ve Etkileşim Modeli · 25 Sonraki Adımlar</t>
+          <t>04 SSG ve BM: Derin Talep İncelemesi · 11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 20 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 24 Kanal Rolleri ve Etkileşim Modeli · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 07 Marka Aramaları ve Autocomplete · 08 Google Arama Sonuçları ve AI Overview · 09 YouTube: Montaj, Tamir ve Karar Videoları · 11 Katalog ve Talep Eşleşmesi · 13 Set, Komple Banyo ve Ürün + Hizmet · 23 Kanal Rolleri ve Etkileşim Modeli · 25 Sonraki Adımlar</t>
+          <t>05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 07 Marka Aramaları ve Autocomplete · 08 Google Arama Sonuçları ve AI Overview · 09 YouTube: Montaj, Tamir ve Karar Videoları · 11 Katalog ve Talep Eşleşmesi · 13 Set, Komple Banyo ve Ürün + Hizmet · 24 Kanal Rolleri ve Etkileşim Modeli · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 21 Kanal Politikaları ve Keşif Kanalları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>06 Organik Kanal Performansı · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 21 Kanal Politikaları ve Keşif Kanalları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>07 Marka Aramaları ve Autocomplete · 23 Kanal Rolleri ve Etkileşim Modeli · 25 Sonraki Adımlar</t>
+          <t>07 Marka Aramaları ve Autocomplete · 24 Kanal Rolleri ve Etkileşim Modeli · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>07 Marka Aramaları ve Autocomplete · 08 Google Arama Sonuçları ve AI Overview · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 21 Kanal Politikaları ve Keşif Kanalları · 23 Kanal Rolleri ve Etkileşim Modeli · 24 AI Arama ve GEO Fırsatları · 25 Sonraki Adımlar</t>
+          <t>07 Marka Aramaları ve Autocomplete · 08 Google Arama Sonuçları ve AI Overview · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 21 Kanal Politikaları ve Keşif Kanalları · 24 Kanal Rolleri ve Etkileşim Modeli · 25 AI Arama ve GEO Fırsatları · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>API (DataForSEO SERP) · yapay zeka yanıt takibi (günlük ve haftalık koşu)</t>
+          <t>API (DataForSEO SERP) · yapay zeka yanıt takibi (tekrarlı koşu)</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 24 AI Arama ve GEO Fırsatları · 25 Sonraki Adımlar</t>
+          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 25 AI Arama ve GEO Fırsatları · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 24 AI Arama ve GEO Fırsatları · 25 Sonraki Adımlar</t>
+          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 25 AI Arama ve GEO Fırsatları · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>10 Şikayetvar: Satış Sonrası Deneyim · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 20 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 21 Kanal Politikaları ve Keşif Kanalları · 25 Sonraki Adımlar</t>
+          <t>10 Şikayetvar: Satış Sonrası Deneyim · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 20 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 21 Kanal Politikaları ve Keşif Kanalları · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 23 Kanal Rolleri ve Etkileşim Modeli · 25 Sonraki Adımlar</t>
+          <t>11 Katalog ve Talep Eşleşmesi · 12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 24 Kanal Rolleri ve Etkileşim Modeli · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 21 Kanal Politikaları ve Keşif Kanalları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 21 Kanal Politikaları ve Keşif Kanalları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E156" s="6" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Kanal Politikaları ve Keşif Kanalları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Kanal Politikaları ve Keşif Kanalları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E168" s="6" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Kanal Politikaları ve Keşif Kanalları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Kanal Politikaları ve Keşif Kanalları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Kanal Politikaları ve Keşif Kanalları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 21 Kanal Politikaları ve Keşif Kanalları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 23 Kanal Rolleri ve Etkileşim Modeli</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 24 Kanal Rolleri ve Etkileşim Modeli</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 25 Sonraki Adımlar</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
@@ -48133,7 +48133,7 @@
       </c>
       <c r="D1135" s="6" t="inlineStr">
         <is>
-          <t>20 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 24 AI Arama ve GEO Fırsatları · 25 Sonraki Adımlar</t>
+          <t>20 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 25 AI Arama ve GEO Fırsatları · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E1135" s="6" t="inlineStr">
@@ -54544,111 +54544,111 @@
     <row r="1288" ht="30" customHeight="1">
       <c r="A1288" s="5" t="inlineStr">
         <is>
-          <t>https://www.duravit.com/en-us/service/bathroom-planner/</t>
+          <t>https://www.vitra.com.tr/search?q=klozet+kapa%C4%9F%C4%B1</t>
         </is>
       </c>
       <c r="B1288" s="6" t="inlineStr">
         <is>
-          <t>duravit.com</t>
+          <t>vitra.com.tr</t>
         </is>
       </c>
       <c r="C1288" s="6" t="inlineStr">
         <is>
-          <t>Duravit banyo planlayıcı (dijital deneyim aracı)</t>
+          <t>vitra.com.tr site içi arama testi (38 arama)</t>
         </is>
       </c>
       <c r="D1288" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>22 vitra.com.tr Satın Alma Yolculuğu: Site İçi Arama, Sepet ve Ödeme</t>
         </is>
       </c>
       <c r="E1288" s="6" t="inlineStr">
         <is>
-          <t>Banyo ölçüsüne göre ürün yerleştirme ve plan çıktısı</t>
+          <t>Sonuç sayısı, ilk 20 ürün kartı; 6 aramada sonuç yok; ilk kartlarda montaj hizmeti</t>
         </is>
       </c>
       <c r="F1288" s="7" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>04.10.2026</t>
         </is>
       </c>
       <c r="G1288" s="6" t="inlineStr">
         <is>
-          <t>tarayıcı</t>
+          <t>curl (herkese açık arama sayfası, istekler arası 2 sn)</t>
         </is>
       </c>
       <c r="H1288" s="7" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>D40</t>
         </is>
       </c>
     </row>
     <row r="1289" ht="30" customHeight="1">
       <c r="A1289" s="5" t="inlineStr">
         <is>
-          <t>https://www.geberit.de/badezimmerprodukte/wcs-urinale/dusch-wcs-geberit-aquaclean/testen/</t>
+          <t>https://www.vitra.com.tr/sepetim</t>
         </is>
       </c>
       <c r="B1289" s="6" t="inlineStr">
         <is>
-          <t>geberit.de</t>
+          <t>vitra.com.tr</t>
         </is>
       </c>
       <c r="C1289" s="6" t="inlineStr">
         <is>
-          <t>Geberit AquaClean evde deneme programı (Almanya)</t>
+          <t>vitra.com.tr sepet, giriş ve üyeliksiz alışveriş ekranları</t>
         </is>
       </c>
       <c r="D1289" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>22 vitra.com.tr Satın Alma Yolculuğu: Site İçi Arama, Sepet ve Ödeme</t>
         </is>
       </c>
       <c r="E1289" s="6" t="inlineStr">
         <is>
-          <t>Dusch-WC'nin 4 hafta ücretsiz evde denenmesi, kurulum videosu ile</t>
+          <t>Sepeti Onayla → giriş paneli → e-posta ekranı → adres; montaj ve öneri karuselleri sepetin altında</t>
         </is>
       </c>
       <c r="F1289" s="7" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>04.10.2026</t>
         </is>
       </c>
       <c r="G1289" s="6" t="inlineStr">
         <is>
-          <t>tarayıcı</t>
+          <t>ekran görüntüsü (kullanıcı tarafından iletildi)</t>
         </is>
       </c>
       <c r="H1289" s="7" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>D41</t>
         </is>
       </c>
     </row>
     <row r="1290" ht="30" customHeight="1">
       <c r="A1290" s="5" t="inlineStr">
         <is>
-          <t>https://www.grohe.com/en-GB/service-support/spare-parts-finder</t>
+          <t>https://www.duravit.com/en-us/service/bathroom-planner/</t>
         </is>
       </c>
       <c r="B1290" s="6" t="inlineStr">
         <is>
-          <t>grohe.com</t>
+          <t>duravit.com</t>
         </is>
       </c>
       <c r="C1290" s="6" t="inlineStr">
         <is>
-          <t>GROHE Spare Parts Finder (yedek parça bulucu örneği)</t>
+          <t>Duravit banyo planlayıcı (dijital deneyim aracı)</t>
         </is>
       </c>
       <c r="D1290" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E1290" s="6" t="inlineStr">
         <is>
-          <t>Patlatılmış çizim, parça numarası, montaj videosu; kamera ile ürün tanıma; üretimden kalkan ürünlerde 10 yıl parça güvencesi</t>
+          <t>Banyo ölçüsüne göre ürün yerleştirme ve plan çıktısı</t>
         </is>
       </c>
       <c r="F1290" s="7" t="inlineStr">
@@ -54663,34 +54663,34 @@
       </c>
       <c r="H1290" s="7" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>B10</t>
         </is>
       </c>
     </row>
     <row r="1291" ht="30" customHeight="1">
       <c r="A1291" s="5" t="inlineStr">
         <is>
-          <t>https://www.hansgrohe-usa.com/service/spare-parts-search</t>
+          <t>https://www.geberit.de/badezimmerprodukte/wcs-urinale/dusch-wcs-geberit-aquaclean/testen/</t>
         </is>
       </c>
       <c r="B1291" s="6" t="inlineStr">
         <is>
-          <t>hansgrohe-usa.com</t>
+          <t>geberit.de</t>
         </is>
       </c>
       <c r="C1291" s="6" t="inlineStr">
         <is>
-          <t>hansgrohe yedek parça arama (yedek parça bulucu örneği)</t>
+          <t>Geberit AquaClean evde deneme programı (Almanya)</t>
         </is>
       </c>
       <c r="D1291" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E1291" s="6" t="inlineStr">
         <is>
-          <t>Patlatılmış çizim, parça numarası ve montaj videosu ile yedek parça bulma; uyumluluk bilgisi</t>
+          <t>Dusch-WC'nin 4 hafta ücretsiz evde denenmesi, kurulum videosu ile</t>
         </is>
       </c>
       <c r="F1291" s="7" t="inlineStr">
@@ -54705,34 +54705,34 @@
       </c>
       <c r="H1291" s="7" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>B13</t>
         </is>
       </c>
     </row>
     <row r="1292" ht="30" customHeight="1">
       <c r="A1292" s="5" t="inlineStr">
         <is>
-          <t>https://www.victorianplumbing.co.uk/help-and-customer-service/bathroom-finance</t>
+          <t>https://www.grohe.com/en-GB/service-support/spare-parts-finder</t>
         </is>
       </c>
       <c r="B1292" s="6" t="inlineStr">
         <is>
-          <t>victorianplumbing.co.uk</t>
+          <t>grohe.com</t>
         </is>
       </c>
       <c r="C1292" s="6" t="inlineStr">
         <is>
-          <t>Victorian Plumbing banyo finansmanı</t>
+          <t>GROHE Spare Parts Finder (yedek parça bulucu örneği)</t>
         </is>
       </c>
       <c r="D1292" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E1292" s="6" t="inlineStr">
         <is>
-          <t>250 GBP üzeri siparişte %0 faizli finansman; sepet tutarına bağlı finansman modeli</t>
+          <t>Patlatılmış çizim, parça numarası, montaj videosu; kamera ile ürün tanıma; üretimden kalkan ürünlerde 10 yıl parça güvencesi</t>
         </is>
       </c>
       <c r="F1292" s="7" t="inlineStr">
@@ -54747,34 +54747,34 @@
       </c>
       <c r="H1292" s="7" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B12</t>
         </is>
       </c>
     </row>
     <row r="1293" ht="30" customHeight="1">
       <c r="A1293" s="5" t="inlineStr">
         <is>
-          <t>https://www.villeroy-boch.co.uk/r/bathroom-ideas/planning/bathroom-planner-online/</t>
+          <t>https://www.hansgrohe-usa.com/service/spare-parts-search</t>
         </is>
       </c>
       <c r="B1293" s="6" t="inlineStr">
         <is>
-          <t>villeroy-boch.co.uk</t>
+          <t>hansgrohe-usa.com</t>
         </is>
       </c>
       <c r="C1293" s="6" t="inlineStr">
         <is>
-          <t>Villeroy &amp; Boch 3D online banyo planlayıcı (dijital deneyim aracı)</t>
+          <t>hansgrohe yedek parça arama (yedek parça bulucu örneği)</t>
         </is>
       </c>
       <c r="D1293" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E1293" s="6" t="inlineStr">
         <is>
-          <t>Banyo ölçüsüne göre ürün yerleştirme, planın PDF olarak bayiye iletilmesi</t>
+          <t>Patlatılmış çizim, parça numarası ve montaj videosu ile yedek parça bulma; uyumluluk bilgisi</t>
         </is>
       </c>
       <c r="F1293" s="7" t="inlineStr">
@@ -54789,34 +54789,34 @@
       </c>
       <c r="H1293" s="7" t="inlineStr">
         <is>
-          <t>B9</t>
+          <t>B11</t>
         </is>
       </c>
     </row>
     <row r="1294" ht="30" customHeight="1">
       <c r="A1294" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/banyonu-tasarla</t>
+          <t>https://www.victorianplumbing.co.uk/help-and-customer-service/bathroom-finance</t>
         </is>
       </c>
       <c r="B1294" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr</t>
+          <t>victorianplumbing.co.uk</t>
         </is>
       </c>
       <c r="C1294" s="6" t="inlineStr">
         <is>
-          <t>VitrA V-Design (banyoyu tasarla) adresi: 3D planlayıcı durumu</t>
+          <t>Victorian Plumbing banyo finansmanı</t>
         </is>
       </c>
       <c r="D1294" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 25 Sonraki Adımlar</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E1294" s="6" t="inlineStr">
         <is>
-          <t>V-Design (2018) 750 banyo ve 300 karo ürünüyle tanıtılmıştı; adres bugün ana sayfaya yönleniyor</t>
+          <t>250 GBP üzeri siparişte %0 faizli finansman; sepet tutarına bağlı finansman modeli</t>
         </is>
       </c>
       <c r="F1294" s="7" t="inlineStr">
@@ -54831,182 +54831,182 @@
       </c>
       <c r="H1294" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>B14</t>
         </is>
       </c>
     </row>
     <row r="1295" ht="30" customHeight="1">
       <c r="A1295" s="5" t="inlineStr">
         <is>
-          <t>https://chatgpt.com#ai-yanit</t>
+          <t>https://www.villeroy-boch.co.uk/r/bathroom-ideas/planning/bathroom-planner-online/</t>
         </is>
       </c>
       <c r="B1295" s="6" t="inlineStr">
         <is>
-          <t>chatgpt.com</t>
+          <t>villeroy-boch.co.uk</t>
         </is>
       </c>
       <c r="C1295" s="6" t="inlineStr">
         <is>
-          <t>ChatGPT yanıtları: 125 soruda VitrA ve rakip markaların adı geçme oranı, kaynak gösterilen alan adları</t>
+          <t>Villeroy &amp; Boch 3D online banyo planlayıcı (dijital deneyim aracı)</t>
         </is>
       </c>
       <c r="D1295" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E1295" s="6" t="inlineStr">
         <is>
-          <t>111 markasız ve 14 markalı soru; e-ticaret (20 soru) ve montaj (9 soru) grupları 28.09.2026'dan itibaren; 4 Eyl - 3 Eki 2026</t>
+          <t>Banyo ölçüsüne göre ürün yerleştirme, planın PDF olarak bayiye iletilmesi</t>
         </is>
       </c>
       <c r="F1295" s="7" t="inlineStr">
         <is>
-          <t>04.10.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="G1295" s="6" t="inlineStr">
         <is>
-          <t>yapay zeka yanıt takibi (günlük ve haftalık koşu)</t>
+          <t>tarayıcı</t>
         </is>
       </c>
       <c r="H1295" s="7" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>B9</t>
         </is>
       </c>
     </row>
     <row r="1296" ht="30" customHeight="1">
       <c r="A1296" s="5" t="inlineStr">
         <is>
-          <t>https://gemini.google.com#ai-yanit</t>
+          <t>https://www.vitra.com.tr/banyonu-tasarla</t>
         </is>
       </c>
       <c r="B1296" s="6" t="inlineStr">
         <is>
-          <t>google.com</t>
+          <t>vitra.com.tr</t>
         </is>
       </c>
       <c r="C1296" s="6" t="inlineStr">
         <is>
-          <t>Gemini yanıtları: 125 soruda VitrA ve rakip markaların adı geçme oranı, kaynak gösterilen alan adları</t>
+          <t>VitrA V-Design (banyoyu tasarla) adresi: 3D planlayıcı durumu</t>
         </is>
       </c>
       <c r="D1296" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E1296" s="6" t="inlineStr">
         <is>
-          <t>111 markasız ve 14 markalı soru; e-ticaret (20 soru) ve montaj (9 soru) grupları 28.09.2026'dan itibaren; 4 Eyl - 3 Eki 2026</t>
+          <t>V-Design (2018) 750 banyo ve 300 karo ürünüyle tanıtılmıştı; adres bugün ana sayfaya yönleniyor</t>
         </is>
       </c>
       <c r="F1296" s="7" t="inlineStr">
         <is>
-          <t>04.10.2026</t>
+          <t>29.09.2026</t>
         </is>
       </c>
       <c r="G1296" s="6" t="inlineStr">
         <is>
-          <t>yapay zeka yanıt takibi (günlük ve haftalık koşu)</t>
+          <t>tarayıcı</t>
         </is>
       </c>
       <c r="H1296" s="7" t="inlineStr">
         <is>
-          <t>D39</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="1297" ht="30" customHeight="1">
       <c r="A1297" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/llms.txt</t>
+          <t>https://chatgpt.com#ai-yanit</t>
         </is>
       </c>
       <c r="B1297" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr</t>
+          <t>chatgpt.com</t>
         </is>
       </c>
       <c r="C1297" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr llms.txt</t>
+          <t>ChatGPT yanıtları: 125 soruda VitrA ve rakip markaların adı geçme oranı, kaynak gösterilen alan adları</t>
         </is>
       </c>
       <c r="D1297" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>25 AI Arama ve GEO Fırsatları</t>
         </is>
       </c>
       <c r="E1297" s="6" t="inlineStr">
         <is>
-          <t>Dosyadaki bölüm ve bağlantılar; destek ve rehber içeriğinin kapsamı</t>
+          <t>111 markasız ve 14 markalı soru; e-ticaret (20 soru) ve montaj (9 soru) grupları 28.09.2026'dan itibaren; 4 Eyl - 3 Eki 2026</t>
         </is>
       </c>
       <c r="F1297" s="7" t="inlineStr">
         <is>
-          <t>02.10.2026</t>
+          <t>04.10.2026</t>
         </is>
       </c>
       <c r="G1297" s="6" t="inlineStr">
         <is>
-          <t>web araştırması (sayfa okuma)</t>
+          <t>yapay zeka yanıt takibi (tekrarlı koşu)</t>
         </is>
       </c>
       <c r="H1297" s="7" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D39</t>
         </is>
       </c>
     </row>
     <row r="1298" ht="30" customHeight="1">
       <c r="A1298" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/sitemaps/sitemap-ilham.xml</t>
+          <t>https://gemini.google.com#ai-yanit</t>
         </is>
       </c>
       <c r="B1298" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr</t>
+          <t>google.com</t>
         </is>
       </c>
       <c r="C1298" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr ilham site haritası</t>
+          <t>Gemini yanıtları: 125 soruda VitrA ve rakip markaların adı geçme oranı, kaynak gösterilen alan adları</t>
         </is>
       </c>
       <c r="D1298" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>25 AI Arama ve GEO Fırsatları</t>
         </is>
       </c>
       <c r="E1298" s="6" t="inlineStr">
         <is>
-          <t>Rehber ve ilham sayfalarının listesi</t>
+          <t>111 markasız ve 14 markalı soru; e-ticaret (20 soru) ve montaj (9 soru) grupları 28.09.2026'dan itibaren; 4 Eyl - 3 Eki 2026</t>
         </is>
       </c>
       <c r="F1298" s="7" t="inlineStr">
         <is>
-          <t>02.10.2026</t>
+          <t>04.10.2026</t>
         </is>
       </c>
       <c r="G1298" s="6" t="inlineStr">
         <is>
-          <t>web araştırması (sayfa okuma)</t>
+          <t>yapay zeka yanıt takibi (tekrarlı koşu)</t>
         </is>
       </c>
       <c r="H1298" s="7" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D39</t>
         </is>
       </c>
     </row>
     <row r="1299" ht="30" customHeight="1">
       <c r="A1299" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/sitemaps/sitemap-support.xml</t>
+          <t>https://www.vitra.com.tr/llms.txt</t>
         </is>
       </c>
       <c r="B1299" s="6" t="inlineStr">
@@ -55016,17 +55016,17 @@
       </c>
       <c r="C1299" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr destek site haritası</t>
+          <t>vitra.com.tr llms.txt</t>
         </is>
       </c>
       <c r="D1299" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>25 AI Arama ve GEO Fırsatları</t>
         </is>
       </c>
       <c r="E1299" s="6" t="inlineStr">
         <is>
-          <t>Destek bölümündeki sayfa sayısı (5)</t>
+          <t>Dosyadaki bölüm ve bağlantılar; destek ve rehber içeriğinin kapsamı</t>
         </is>
       </c>
       <c r="F1299" s="7" t="inlineStr">
@@ -55048,27 +55048,27 @@
     <row r="1300" ht="30" customHeight="1">
       <c r="A1300" s="5" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q127325081</t>
+          <t>https://www.vitra.com.tr/sitemaps/sitemap-ilham.xml</t>
         </is>
       </c>
       <c r="B1300" s="6" t="inlineStr">
         <is>
-          <t>wikidata.org</t>
+          <t>vitra.com.tr</t>
         </is>
       </c>
       <c r="C1300" s="6" t="inlineStr">
         <is>
-          <t>Wikidata ikinci VitrA kaydı</t>
+          <t>vitra.com.tr ilham site haritası</t>
         </is>
       </c>
       <c r="D1300" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>25 AI Arama ve GEO Fırsatları</t>
         </is>
       </c>
       <c r="E1300" s="6" t="inlineStr">
         <is>
-          <t>Aynı marka için ayrı kayıt; alanlar ve bağlantılar</t>
+          <t>Rehber ve ilham sayfalarının listesi</t>
         </is>
       </c>
       <c r="F1300" s="7" t="inlineStr">
@@ -55083,34 +55083,34 @@
       </c>
       <c r="H1300" s="7" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D35</t>
         </is>
       </c>
     </row>
     <row r="1301" ht="30" customHeight="1">
       <c r="A1301" s="5" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q7937213</t>
+          <t>https://www.vitra.com.tr/sitemaps/sitemap-support.xml</t>
         </is>
       </c>
       <c r="B1301" s="6" t="inlineStr">
         <is>
-          <t>wikidata.org</t>
+          <t>vitra.com.tr</t>
         </is>
       </c>
       <c r="C1301" s="6" t="inlineStr">
         <is>
-          <t>Wikidata VitrA kaydı (marka ve entity tutarlılığı)</t>
+          <t>vitra.com.tr destek site haritası</t>
         </is>
       </c>
       <c r="D1301" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>25 AI Arama ve GEO Fırsatları</t>
         </is>
       </c>
       <c r="E1301" s="6" t="inlineStr">
         <is>
-          <t>Kuruluş tarihi, üst kuruluş, web sitesi ve ürün grubu alanları</t>
+          <t>Destek bölümündeki sayfa sayısı (5)</t>
         </is>
       </c>
       <c r="F1301" s="7" t="inlineStr">
@@ -55125,34 +55125,34 @@
       </c>
       <c r="H1301" s="7" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D35</t>
         </is>
       </c>
     </row>
     <row r="1302" ht="30" customHeight="1">
       <c r="A1302" s="5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/VitrA_(sanitaryware)</t>
+          <t>https://www.wikidata.org/wiki/Q127325081</t>
         </is>
       </c>
       <c r="B1302" s="6" t="inlineStr">
         <is>
-          <t>wikipedia.org</t>
+          <t>wikidata.org</t>
         </is>
       </c>
       <c r="C1302" s="6" t="inlineStr">
         <is>
-          <t>İngilizce Wikipedia VitrA maddesi</t>
+          <t>Wikidata ikinci VitrA kaydı</t>
         </is>
       </c>
       <c r="D1302" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>25 AI Arama ve GEO Fırsatları</t>
         </is>
       </c>
       <c r="E1302" s="6" t="inlineStr">
         <is>
-          <t>Kuruluş tarihi, üst kuruluş</t>
+          <t>Aynı marka için ayrı kayıt; alanlar ve bağlantılar</t>
         </is>
       </c>
       <c r="F1302" s="7" t="inlineStr">
@@ -55174,47 +55174,131 @@
     <row r="1303" ht="30" customHeight="1">
       <c r="A1303" s="5" t="inlineStr">
         <is>
+          <t>https://www.wikidata.org/wiki/Q7937213</t>
+        </is>
+      </c>
+      <c r="B1303" s="6" t="inlineStr">
+        <is>
+          <t>wikidata.org</t>
+        </is>
+      </c>
+      <c r="C1303" s="6" t="inlineStr">
+        <is>
+          <t>Wikidata VitrA kaydı (marka ve entity tutarlılığı)</t>
+        </is>
+      </c>
+      <c r="D1303" s="6" t="inlineStr">
+        <is>
+          <t>25 AI Arama ve GEO Fırsatları</t>
+        </is>
+      </c>
+      <c r="E1303" s="6" t="inlineStr">
+        <is>
+          <t>Kuruluş tarihi, üst kuruluş, web sitesi ve ürün grubu alanları</t>
+        </is>
+      </c>
+      <c r="F1303" s="7" t="inlineStr">
+        <is>
+          <t>02.10.2026</t>
+        </is>
+      </c>
+      <c r="G1303" s="6" t="inlineStr">
+        <is>
+          <t>web araştırması (sayfa okuma)</t>
+        </is>
+      </c>
+      <c r="H1303" s="7" t="inlineStr">
+        <is>
+          <t>D34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304" ht="30" customHeight="1">
+      <c r="A1304" s="5" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/VitrA_(sanitaryware)</t>
+        </is>
+      </c>
+      <c r="B1304" s="6" t="inlineStr">
+        <is>
+          <t>wikipedia.org</t>
+        </is>
+      </c>
+      <c r="C1304" s="6" t="inlineStr">
+        <is>
+          <t>İngilizce Wikipedia VitrA maddesi</t>
+        </is>
+      </c>
+      <c r="D1304" s="6" t="inlineStr">
+        <is>
+          <t>25 AI Arama ve GEO Fırsatları</t>
+        </is>
+      </c>
+      <c r="E1304" s="6" t="inlineStr">
+        <is>
+          <t>Kuruluş tarihi, üst kuruluş</t>
+        </is>
+      </c>
+      <c r="F1304" s="7" t="inlineStr">
+        <is>
+          <t>02.10.2026</t>
+        </is>
+      </c>
+      <c r="G1304" s="6" t="inlineStr">
+        <is>
+          <t>web araştırması (sayfa okuma)</t>
+        </is>
+      </c>
+      <c r="H1304" s="7" t="inlineStr">
+        <is>
+          <t>D34</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305" ht="30" customHeight="1">
+      <c r="A1305" s="5" t="inlineStr">
+        <is>
           <t>https://tr.wikipedia.org/wiki/VitrA</t>
         </is>
       </c>
-      <c r="B1303" s="6" t="inlineStr">
+      <c r="B1305" s="6" t="inlineStr">
         <is>
           <t>wikipedia.org</t>
         </is>
       </c>
-      <c r="C1303" s="6" t="inlineStr">
+      <c r="C1305" s="6" t="inlineStr">
         <is>
           <t>Türkçe Wikipedia VitrA maddesi</t>
         </is>
       </c>
-      <c r="D1303" s="6" t="inlineStr">
-        <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
-        </is>
-      </c>
-      <c r="E1303" s="6" t="inlineStr">
+      <c r="D1305" s="6" t="inlineStr">
+        <is>
+          <t>25 AI Arama ve GEO Fırsatları</t>
+        </is>
+      </c>
+      <c r="E1305" s="6" t="inlineStr">
         <is>
           <t>Kuruluş tarihi, Artema ilişkisi</t>
         </is>
       </c>
-      <c r="F1303" s="7" t="inlineStr">
+      <c r="F1305" s="7" t="inlineStr">
         <is>
           <t>02.10.2026</t>
         </is>
       </c>
-      <c r="G1303" s="6" t="inlineStr">
+      <c r="G1305" s="6" t="inlineStr">
         <is>
           <t>web araştırması (sayfa okuma)</t>
         </is>
       </c>
-      <c r="H1303" s="7" t="inlineStr">
+      <c r="H1305" s="7" t="inlineStr">
         <is>
           <t>D34</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H1303"/>
+  <autoFilter ref="A4:H1305"/>
   <mergeCells count="1">
     <mergeCell ref="A2:H2"/>
   </mergeCells>
@@ -56517,6 +56601,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1301" r:id="rId1296"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1302" r:id="rId1297"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1303" r:id="rId1298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1304" r:id="rId1299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1305" r:id="rId1300"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56689,7 +56775,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>04 · 11 · 12 · 14 · 16 · 17 · 18 · 20 · 21 · 23 · 25</t>
+          <t>04 · 11 · 12 · 14 · 16 · 17 · 18 · 20 · 21 · 24 · 26</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -56714,7 +56800,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>10 · 13 · 14 · 16 · 17 · 18 · 20 · 21 · 22 · 25</t>
+          <t>10 · 13 · 14 · 16 · 17 · 18 · 20 · 21 · 23 · 26</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -56739,7 +56825,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>07 · 08 · 10 · 15 · 20 · 21 · 23 · 24 · 25</t>
+          <t>07 · 08 · 10 · 15 · 20 · 21 · 24 · 25 · 26</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -56753,103 +56839,103 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="43.5" customHeight="1">
+    <row r="9" ht="70.5" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>vitra.com.tr</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>171</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>06 · 11 · 12 · 13 · 14 · 15 · 17 · 20 · 21 · 22 · 23 · 24 · 25 · 26</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>marka sitesi</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Yöntem: curl, tarayıcı, MCP (Ahrefs), API (Search Console), tarayıcı (Chrome, kullanıcı oturumu), tarayıcı (Playwright), curl (herkese açık arama sayfası, istekler arası 2 sn), ekran görüntüsü (kullanıcı tarafından iletildi), web araştırması (sayfa okuma); erişim 27.09.2026, 28.09.2026, 29.09.2026, 30.09.2026, 02.10.2026, 04.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="43.5" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>youtube.com</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B10" s="8" t="n">
         <v>167</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 21 Kanal Politikaları ve Keşif Kanalları · 24 AI Arama ve GEO Fırsatları · 25 Sonraki Adımlar</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>09 YouTube: Montaj, Tamir ve Karar Videoları · 21 Kanal Politikaları ve Keşif Kanalları · 25 AI Arama ve GEO Fırsatları · 26 Sonraki Adımlar</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>sosyal</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Yöntem: API (DataForSEO YouTube), curl; erişim 28.09.2026, 29.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="57" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>cimri.com</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>137</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 20 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>fiyat karşılaştırma</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Arama sayfası doğrulama katmanı nedeniyle açılamadı; kategori, marka ve ürün sayfaları Chrome ile okundu; 10 SKU eşleşmedi</t>
         </is>
       </c>
     </row>
     <row r="11" ht="57" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>cimri.com</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>137</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 20 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>fiyat karşılaştırma</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Arama sayfası doğrulama katmanı nedeniyle açılamadı; kategori, marka ve ürün sayfaları Chrome ile okundu; 10 SKU eşleşmedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="57" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>akakce.com</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B12" s="8" t="n">
         <v>135</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 20 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>fiyat karşılaştırma</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Doğrudan erişim yaklaşık 15 istekten sonra doğrulama sayfası verdi (29.09.2026); 30.09.2026'da Chrome ile 24 ürün ve 12 kategori sayfası okundu</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="43.5" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>132</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>06 · 11 · 12 · 13 · 14 · 15 · 17 · 20 · 21 · 22 · 23 · 24 · 25</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>marka sitesi</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Yöntem: curl, tarayıcı, MCP (Ahrefs), API (Search Console), tarayıcı (Chrome, kullanıcı oturumu), tarayıcı (Playwright), web araştırması (sayfa okuma); erişim 27.09.2026, 28.09.2026, 29.09.2026, 30.09.2026, 02.10.2026</t>
         </is>
       </c>
     </row>
@@ -56864,7 +56950,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>03 · 04 · 05 · 06 · 07 · 08 · 09 · 11 · 12 · 13 · 20 · 21 · 23 · 24 · 25</t>
+          <t>03 · 04 · 05 · 06 · 07 · 08 · 09 · 11 · 12 · 13 · 20 · 21 · 24 · 25 · 26</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -56889,7 +56975,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>12 · 13 · 14 · 16 · 17 · 20 · 21 · 22</t>
+          <t>12 · 13 · 14 · 16 · 17 · 20 · 21 · 23</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -56939,7 +57025,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 21 Kanal Politikaları ve Keşif Kanalları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 21 Kanal Politikaları ve Keşif Kanalları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -56964,7 +57050,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 21 Kanal Politikaları ve Keşif Kanalları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 21 Kanal Politikaları ve Keşif Kanalları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -56989,7 +57075,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 25 Sonraki Adımlar</t>
+          <t>14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -57014,7 +57100,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>12 · 13 · 14 · 15 · 17 · 21 · 22</t>
+          <t>12 · 13 · 14 · 15 · 17 · 21 · 23</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -57064,7 +57150,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>03 · 04 · 05 · 06 · 07 · 08 · 09 · 10 · 11 · 12 · 13 · 15 · 20 · 21 · 23 · 24 · 25</t>
+          <t>03 · 04 · 05 · 06 · 07 · 08 · 09 · 10 · 11 · 12 · 13 · 15 · 20 · 21 · 24 · 25 · 26</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -57114,7 +57200,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 21 Kanal Politikaları ve Keşif Kanalları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 21 Kanal Politikaları ve Keşif Kanalları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -57139,7 +57225,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>02 Ekonomik Ortam: Harcama, Güven ve Konut Piyasası · 25 Sonraki Adımlar</t>
+          <t>02 Ekonomik Ortam: Harcama, Güven ve Konut Piyasası · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -57164,7 +57250,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 21 Kanal Politikaları ve Keşif Kanalları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 13 Set, Komple Banyo ve Ürün + Hizmet · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 15 Marka ve Uzman Sitelerde Kategori Trafiği · 21 Kanal Politikaları ve Keşif Kanalları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -57339,7 +57425,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>21 Kanal Politikaları ve Keşif Kanalları · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>21 Kanal Politikaları ve Keşif Kanalları · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -57439,7 +57525,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -57464,7 +57550,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -57489,7 +57575,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>25 AI Arama ve GEO Fırsatları</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -57514,7 +57600,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>25 AI Arama ve GEO Fırsatları</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -57614,7 +57700,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -57678,7 +57764,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46" ht="16.5" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
           <t>chatgpt.com</t>
@@ -57689,7 +57775,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>24 AI Arama ve GEO Fırsatları</t>
+          <t>25 AI Arama ve GEO Fırsatları</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -57699,7 +57785,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Yöntem: yapay zeka yanıt takibi (günlük ve haftalık koşu); erişim 04.10.2026</t>
+          <t>Yöntem: yapay zeka yanıt takibi (tekrarlı koşu); erişim 04.10.2026</t>
         </is>
       </c>
     </row>
@@ -57714,7 +57800,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -57839,7 +57925,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>12 Yeni Kategori ve Segment Fırsatları · 14 Rakip Görünürlüğü ve Kanal Ölçeği · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -57864,7 +57950,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -57889,7 +57975,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 12 Yeni Kategori ve Segment Fırsatları · 25 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 12 Yeni Kategori ve Segment Fırsatları · 26 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -57939,7 +58025,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -57989,7 +58075,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -58114,7 +58200,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>13 Set, Komple Banyo ve Ürün + Hizmet · 23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -58439,7 +58525,7 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>22 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>23 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -58657,7 +58743,7 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Kapsam: Bu döküm, rapor HTML'indeki 44 kaynakça girdisinin tüm adreslerini, rapordaki bağlantıları, alt ajan araştırmalarında (veri/ham/derin) okunan sayfaları ve API kaynaklarını içerir; 1299 satır, 77 alan adı. Toplu okunan sayfalar kalıp adres ve adet olarak tek satırdadır.</t>
+          <t>Kapsam: Bu döküm, rapor HTML'indeki 44 kaynakça girdisinin tüm adreslerini, rapordaki bağlantıları, alt ajan araştırmalarında (veri/ham/derin) okunan sayfaları ve API kaynaklarını içerir; 1301 satır, 77 alan adı. Toplu okunan sayfalar kalıp adres ve adet olarak tek satırdadır.</t>
         </is>
       </c>
     </row>

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -1499,84 +1499,84 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="124.5" customHeight="1">
+    <row r="28" ht="97.5" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t>https://ahrefs.com/site-explorer</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>ahrefs.com</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Organik rakipler, alan adı metrikleri, marka ve uzman sitelerin ve pazaryerlerinin kategori sayfası trafiği</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>06 Organik Kanal Performansı · 07 Google Yapay Zeka Özellikleri ve Organik Tık · 15 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 25 Kanal Rolleri ve Etkileşim Modeli · 27 Sonraki Adımlar</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr'nin organik rakipleri (ilk 20) ve Batch Analysis (25 alan adı: DR, organik kelime, ilk 3, organik ve paid trafik; 27.09.2026); marka ve uzman siteler için top pages (26 hedef); pazaryeri ve yapı market için top pages ve organic keywords (10 site, Trendyol ve Hepsiburada 300'er kelime); Türkiye, 28.09.2026</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>27.09.2026 · 28.09.2026</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>33 · 36 · 35 · 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="124.5" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
           <t>https://www.vitra.com.tr</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>VitrA ana sayfa: şerit mesajları ve Banyo Asistanı akışı (taksit, kargo ve hizmet mesajı) | Rakip görünürlüğü ve kanal ölçeği: vitra.com.tr alan adı metrikleri (Ahrefs, Türkiye) | Marka ve uzman sitelerde kategori trafiği: vitra.com.tr tema × trafik matrisi (Ahrefs, Türkiye) | vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (ana sayfa)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı · 14 Set, Komple Banyo ve Ürün + Hizmet · 15 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Marka ve Uzman Sitelerde Kategori Trafiği · 22 Kanal Politikaları ve Keşif Kanalları · 24 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>Şeritte 'tüm ürünlerde vade farksız 6 ay taksit' ve 'tüm ürünlerde ücretsiz kargo'; Banyo Asistanı (Banyomu Yenilemek İstiyorum) 4 adımlı lead akışı: telefon, mağaza veya görüntülü görüşme seçimi, slot, WhatsApp teyidi; %40'a varan indirim, 9 taksit, ücretsiz mimari projelendirme | Batch Analysis: DR 66, 7.428 organik kelime, ilk 3'te 4.127 kelime, 330.499 organik ve 50.286 paid trafik (Ahrefs tahmini, 27.09.2026) | Ahrefs site toplamı: DR 66, 7.428 organik kelime, 330.499 aylık organik trafik; top pages: 138 sayfa 40'tan fazla temaya eşlendi (28.09.2026) | 1 Eki 2025 - 30 Eyl 2026: 134.587 tıklama, 4.500.313 gösterim, ortalama sıra 10</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>27.09.2026 · 28.09.2026 · 29.09.2026</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>11 · 33 · 22 · 35 · 47</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>https://www.vitra.com.tr/c-banyo-dolaplari</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-banyo-dolaplari)</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>06 Organik Kanal Performansı</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 24.731 tıklama, 721.659 gösterim, ortalama sıra 6</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-banyo-karo-seramikleri</t>
+          <t>https://www.vitra.com.tr/c-banyo-dolaplari</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-banyo-karo-seramikleri)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-banyo-dolaplari)</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 32.464 tıklama, 1.193.310 gösterim, ortalama sıra 6</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 24.731 tıklama, 721.659 gösterim, ortalama sıra 6</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1613,7 +1613,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-banyo-mobilyalari</t>
+          <t>https://www.vitra.com.tr/c-banyo-karo-seramikleri</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-banyo-mobilyalari)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-banyo-karo-seramikleri)</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 39.036 tıklama, 1.297.491 gösterim, ortalama sıra 5,5</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 32.464 tıklama, 1.193.310 gösterim, ortalama sıra 6</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1650,7 +1650,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-dus-setleri</t>
+          <t>https://www.vitra.com.tr/c-banyo-mobilyalari</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-dus-setleri)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-banyo-mobilyalari)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 18.435 tıklama, 647.203 gösterim, ortalama sıra 5,6</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 39.036 tıklama, 1.297.491 gösterim, ortalama sıra 5,5</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-dus-tekneleri</t>
+          <t>https://www.vitra.com.tr/c-dus-setleri</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-dus-tekneleri)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-dus-setleri)</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 18.923 tıklama, 432.258 gösterim, ortalama sıra 5,1</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 18.435 tıklama, 647.203 gösterim, ortalama sıra 5,6</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -1724,7 +1724,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-dusakabin</t>
+          <t>https://www.vitra.com.tr/c-dus-tekneleri</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-dusakabin)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-dus-tekneleri)</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 47.218 tıklama, 1.578.979 gösterim, ortalama sıra 6,6</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 18.923 tıklama, 432.258 gösterim, ortalama sıra 5,1</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-ev-ici-zemin-karo-seramikleri</t>
+          <t>https://www.vitra.com.tr/c-dusakabin</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-ev-ici-zemin-karo-seramikleri)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-dusakabin)</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 19.416 tıklama, 878.622 gösterim, ortalama sıra 6,4</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 47.218 tıklama, 1.578.979 gösterim, ortalama sıra 6,6</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -1798,7 +1798,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-eviye-bataryalari</t>
+          <t>https://www.vitra.com.tr/c-ev-ici-zemin-karo-seramikleri</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-eviye-bataryalari)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-ev-ici-zemin-karo-seramikleri)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 27.192 tıklama, 874.023 gösterim, ortalama sıra 5,5</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 19.416 tıklama, 878.622 gösterim, ortalama sıra 6,4</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-gomme-rezervuarlar</t>
+          <t>https://www.vitra.com.tr/c-eviye-bataryalari</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-gomme-rezervuarlar)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-eviye-bataryalari)</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 24.686 tıklama, 709.966 gösterim, ortalama sıra 4,9</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 27.192 tıklama, 874.023 gösterim, ortalama sıra 5,5</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -1872,7 +1872,7 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-karo-seramik-urunleri</t>
+          <t>https://www.vitra.com.tr/c-gomme-rezervuarlar</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-karo-seramik-urunleri)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-gomme-rezervuarlar)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 29.900 tıklama, 1.032.767 gösterim, ortalama sıra 6,3</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 24.686 tıklama, 709.966 gösterim, ortalama sıra 4,9</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-klozetler</t>
+          <t>https://www.vitra.com.tr/c-karo-seramik-urunleri</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-klozetler)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-karo-seramik-urunleri)</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 60.921 tıklama, 2.302.714 gösterim, ortalama sıra 5,2</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 29.900 tıklama, 1.032.767 gösterim, ortalama sıra 6,3</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/c-lavabo-dolaplari</t>
+          <t>https://www.vitra.com.tr/c-klozetler</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-lavabo-dolaplari)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-klozetler)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 21.562 tıklama, 740.877 gösterim, ortalama sıra 5,9</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 60.921 tıklama, 2.302.714 gösterim, ortalama sıra 5,2</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -1983,101 +1983,101 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
+          <t>https://www.vitra.com.tr/c-lavabo-dolaplari</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-lavabo-dolaplari)</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>06 Organik Kanal Performansı</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>1 Eki 2025 - 30 Eyl 2026: 21.562 tıklama, 740.877 gösterim, ortalama sıra 5,9</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
           <t>https://www.vitra.com.tr/c-lavabolar</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/c-lavabolar)</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>1 Eki 2025 - 30 Eyl 2026: 45.640 tıklama, 1.777.097 gösterim, ortalama sıra 6,6</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="43.5" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="43" ht="43.5" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/ilham-veren-fikirler/ahsap-gorunumlu-seramik-modelleri/</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/ahsap-gorunumlu-seramik-modelleri)</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>1 Eki 2025 - 30 Eyl 2026: 5.839 tıklama, 183.660 gösterim, ortalama sıra 6</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>https://www.vitra.com.tr/ilham-veren-fikirler/banyo-temizligi-nasil-yapilir/</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/banyo-temizligi-nasil-yapilir)</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>06 Organik Kanal Performansı</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 1.618 tıklama, 239.581 gösterim, ortalama sıra 5,3</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2094,7 +2094,7 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/ilham-veren-fikirler/bide-nedir/</t>
+          <t>https://www.vitra.com.tr/ilham-veren-fikirler/banyo-temizligi-nasil-yapilir/</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/bide-nedir)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/banyo-temizligi-nasil-yapilir)</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 3.226 tıklama, 386.711 gösterim, ortalama sıra 5</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 1.618 tıklama, 239.581 gösterim, ortalama sıra 5,3</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2131,212 +2131,212 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>https://www.vitra.com.tr/ilham-veren-fikirler/bide-nedir/</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/bide-nedir)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>06 Organik Kanal Performansı</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>1 Eki 2025 - 30 Eyl 2026: 3.226 tıklama, 386.711 gösterim, ortalama sıra 5</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>https://www.vitra.com.tr/ilham-veren-fikirler/dusakabin-montaji-nasil-yapilir/</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/dusakabin-montaji-nasil-yapilir)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>1 Eki 2025 - 30 Eyl 2026: 2.236 tıklama, 192.047 gösterim, ortalama sıra 5,3</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="43.5" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="47" ht="43.5" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/ilham-veren-fikirler/dusakabin-temizligi-nasil-yapilir/</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/dusakabin-temizligi-nasil-yapilir)</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>1 Eki 2025 - 30 Eyl 2026: 8.681 tıklama, 564.677 gösterim, ortalama sıra 4</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/ilham-veren-fikirler/en-kullanisli-evye-hangisi/</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/en-kullanisli-evye-hangisi)</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>1 Eki 2025 - 30 Eyl 2026: 12.879 tıklama, 621.735 gösterim, ortalama sıra 7</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="43.5" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="49" ht="43.5" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/ilham-veren-fikirler/gomme-rezervuar-montaji-nasil-yapilir/</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/gomme-rezervuar-montaji-nasil-yapilir)</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>1 Eki 2025 - 30 Eyl 2026: 2.535 tıklama, 298.519 gösterim, ortalama sıra 6,2</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/ilham-veren-fikirler/gomme-rezervuar-tamiri/</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/gomme-rezervuar-tamiri)</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>1 Eki 2025 - 30 Eyl 2026: 6.752 tıklama, 623.040 gösterim, ortalama sıra 5,7</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="43.5" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>https://www.vitra.com.tr/ilham-veren-fikirler/kanalsiz-klozet-nedir-ve-nasil-calisir/</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/kanalsiz-klozet-nedir-ve-nasil-calisir)</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>06 Organik Kanal Performansı</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 1.821 tıklama, 83.454 gösterim, ortalama sıra 4,5</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2353,7 +2353,7 @@
     <row r="51" ht="43.5" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/ilham-veren-fikirler/klozet-kapagi-montaji-nasil-yapilir/</t>
+          <t>https://www.vitra.com.tr/ilham-veren-fikirler/kanalsiz-klozet-nedir-ve-nasil-calisir/</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/klozet-kapagi-montaji-nasil-yapilir)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/kanalsiz-klozet-nedir-ve-nasil-calisir)</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 2.468 tıklama, 351.426 gösterim, ortalama sıra 5,8</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 1.821 tıklama, 83.454 gösterim, ortalama sıra 4,5</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="52" ht="43.5" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/ilham-veren-fikirler/klozet-secim-rehberi-ve-tavsiyeler/</t>
+          <t>https://www.vitra.com.tr/ilham-veren-fikirler/klozet-kapagi-montaji-nasil-yapilir/</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/klozet-secim-rehberi-ve-tavsiyeler)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/klozet-kapagi-montaji-nasil-yapilir)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 3.472 tıklama, 275.927 gösterim, ortalama sıra 5,5</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 2.468 tıklama, 351.426 gösterim, ortalama sıra 5,8</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2427,7 +2427,7 @@
     <row r="53" ht="43.5" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>https://www.vitra.com.tr/ilham-veren-fikirler/kucuk-banyolar-icin-karo-secimi-nasil-olmali/</t>
+          <t>https://www.vitra.com.tr/ilham-veren-fikirler/klozet-secim-rehberi-ve-tavsiyeler/</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/kucuk-banyolar-icin-karo-secimi-nasil-olmali)</t>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/klozet-secim-rehberi-ve-tavsiyeler)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 1.731 tıklama, 104.802 gösterim, ortalama sıra 6,6</t>
+          <t>1 Eki 2025 - 30 Eyl 2026: 3.472 tıklama, 275.927 gösterim, ortalama sıra 5,5</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -2464,64 +2464,64 @@
     <row r="54" ht="43.5" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
+          <t>https://www.vitra.com.tr/ilham-veren-fikirler/kucuk-banyolar-icin-karo-secimi-nasil-olmali/</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/kucuk-banyolar-icin-karo-secimi-nasil-olmali)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>06 Organik Kanal Performansı</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>1 Eki 2025 - 30 Eyl 2026: 1.731 tıklama, 104.802 gösterim, ortalama sıra 6,6</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="43.5" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
           <t>https://www.vitra.com.tr/ilham-veren-fikirler/lavabo-secim-rehberi-ve-tavsiyeler/</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/lavabo-secim-rehberi-ve-tavsiyeler)</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>1 Eki 2025 - 30 Eyl 2026: 1.467 tıklama, 167.001 gösterim, ortalama sıra 6,6</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>https://www.vitra.com.tr/ilham-veren-fikirler/mutfak-dekorasyonu-nasil-yapilir/</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/mutfak-dekorasyonu-nasil-yapilir)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>06 Organik Kanal Performansı</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>1 Eki 2025 - 30 Eyl 2026: 2.865 tıklama, 466.233 gösterim, ortalama sıra 2,5</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -2538,111 +2538,111 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
+          <t>https://www.vitra.com.tr/ilham-veren-fikirler/mutfak-dekorasyonu-nasil-yapilir/</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/mutfak-dekorasyonu-nasil-yapilir)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>06 Organik Kanal Performansı</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>1 Eki 2025 - 30 Eyl 2026: 2.865 tıklama, 466.233 gösterim, ortalama sıra 2,5</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
           <t>https://www.vitra.com.tr/ilham-veren-fikirler/vitrifiye-urun-gruplari-nelerdir/</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/vitrifiye-urun-gruplari-nelerdir)</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>1 Eki 2025 - 30 Eyl 2026: 1.617 tıklama, 118.742 gösterim, ortalama sıra 5,1</t>
         </is>
       </c>
-      <c r="F56" s="7" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>28.09.2026</t>
         </is>
       </c>
-      <c r="G56" s="7" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="43.5" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="58" ht="43.5" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/servisler-ve-satis-noktalari</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>VitrA resmi satış ve servis noktası bulucusu | vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (/servisler-ve-satis-noktalari)</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>06 Organik Kanal Performansı · 22 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>161 satış noktası ve 76 servis noktası (toplam 237); Google Maps profilleriyle karşılaştırma için resmi sayı | 1 Eki 2025 - 30 Eyl 2026: 25.760 tıklama, 1.300.640 gösterim, ortalama sıra 5,1</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>28.09.2026 · 29.09.2026</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>11 · 47</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="84" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>https://ahrefs.com/site-explorer</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>ahrefs.com</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Organik rakipler, alan adı metrikleri, marka ve uzman sitelerin ve pazaryerlerinin kategori sayfası trafiği</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>07 Google Yapay Zeka Özellikleri ve Organik Tık · 15 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 25 Kanal Rolleri ve Etkileşim Modeli · 27 Sonraki Adımlar</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>vitra.com.tr'nin organik rakipleri (ilk 20) ve Batch Analysis (25 alan adı: DR, organik kelime, ilk 3, organik ve paid trafik; 27.09.2026); marka ve uzman siteler için top pages (26 hedef); pazaryeri ve yapı market için top pages ve organic keywords (10 site, Trendyol ve Hepsiburada 300'er kelime); Türkiye, 28.09.2026</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>27.09.2026 · 28.09.2026</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>33 · 36 · 35 · 12</t>
         </is>
       </c>
     </row>
@@ -50776,7 +50776,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="57" customHeight="1">
+    <row r="18" ht="16.5" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>ahrefs.com</t>
@@ -50787,7 +50787,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>07 Google Yapay Zeka Özellikleri ve Organik Tık · 15 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 25 Kanal Rolleri ve Etkileşim Modeli · 27 Sonraki Adımlar</t>
+          <t>06 · 07 · 15 · 16 · 17 · 25 · 27</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 08 Marka Aramaları ve Autocomplete · 09 Google Arama Sonuçları ve AI Overview · 12 Katalog ve Talep Eşleşmesi · 13 Yeni Kategori ve Segment Fırsatları · 14 Set, Komple Banyo ve Ürün + Hizmet · 25 Kanal Rolleri ve Etkileşim Modeli · 27 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 GSC - Organik Kanal · 08 Marka Aramaları ve Autocomplete · 09 Google Arama Sonuçları ve AI Overview · 12 Katalog ve Talep Eşleşmesi · 13 Yeni Kategori ve Segment Fırsatları · 14 Set, Komple Banyo ve Ürün + Hizmet · 25 Kanal Rolleri ve Etkileşim Modeli · 27 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 Organik Kanal Performansı · 07 Google Yapay Zeka Özellikleri ve Organik Tık · 08 Marka Aramaları ve Autocomplete · 09 Google Arama Sonuçları ve AI Overview · 10 YouTube: Montaj, Tamir ve Karar Videoları · 12 Katalog ve Talep Eşleşmesi · 14 Set, Komple Banyo ve Ürün + Hizmet · 25 Kanal Rolleri ve Etkileşim Modeli · 26 AI Arama ve GEO Fırsatları · 27 Sonraki Adımlar</t>
+          <t>05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Tık · 08 Marka Aramaları ve Autocomplete · 09 Google Arama Sonuçları ve AI Overview · 10 YouTube: Montaj, Tamir ve Karar Videoları · 12 Katalog ve Talep Eşleşmesi · 14 Set, Komple Banyo ve Ürün + Hizmet · 25 Kanal Rolleri ve Etkileşim Modeli · 26 AI Arama ve GEO Fırsatları · 27 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı · 07 Google Yapay Zeka Özellikleri ve Organik Tık · 15 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 25 Kanal Rolleri ve Etkileşim Modeli · 27 Sonraki Adımlar</t>
+          <t>06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Tık · 15 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Marka ve Uzman Sitelerde Kategori Trafiği · 17 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 25 Kanal Rolleri ve Etkileşim Modeli · 27 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı · 14 Set, Komple Banyo ve Ürün + Hizmet · 15 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Marka ve Uzman Sitelerde Kategori Trafiği · 22 Kanal Politikaları ve Keşif Kanalları · 24 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>06 GSC - Organik Kanal · 14 Set, Komple Banyo ve Ürün + Hizmet · 15 Rakip Görünürlüğü ve Kanal Ölçeği · 16 Marka ve Uzman Sitelerde Kategori Trafiği · 22 Kanal Politikaları ve Keşif Kanalları · 24 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı</t>
+          <t>06 GSC - Organik Kanal</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>06 Organik Kanal Performansı · 22 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>06 GSC - Organik Kanal · 22 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -52471,7 +52471,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="57" customHeight="1">
+    <row r="8" ht="70.5" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Google Analytics 4</t>
@@ -52479,7 +52479,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr mülkü, VitrA ekibi dışa aktarımı (05.10.2026) · genel bakış Oca 2025 - Eyl 2026 · kanal Oca - Eyl 2025 ve 2026 · site içi arama 1 Nis - 5 Eki 2026 · ödeme, teslimat, talep olayları, sayfa ve promosyon 1 Eyl 2025 - 30 Eyl 2026</t>
+          <t>vitra.com.tr mülkü, VitrA ekibi dışa aktarımı (05.10.2026) · genel bakış Oca 2025 - Eyl 2026 · kanal Oca - Eyl 2025 ve 2026 · site içi arama 1 May - 30 Eyl 2026 · ödeme, teslimat, servis düğmesi tıklaması, sayfa ve promosyon 1 Eyl 2025 - 30 Eyl 2026 · giriş sayfası Oca 2025 - 5 Eki 2026</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -52489,7 +52489,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Site içi arama keşif raporu örneklenmiştir; landing page dışa aktarımı süzgeç belirsizliği nedeniyle kullanılmamıştır</t>
+          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Giriş sayfası raporunda bir oturum birden fazla giriş sayfasında sayılabildiği için oturum pay olarak verilmiştir; gelir genel bakışla birebir aynıdır. Anahtar olay (key event) sütunları tüm olayları kapsadığından kullanılmamıştır</t>
         </is>
       </c>
     </row>

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -52489,7 +52489,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Giriş sayfası raporunda bir oturum birden fazla giriş sayfasında sayılabildiği için oturum pay olarak verilmiştir; gelir genel bakışla birebir aynıdır. Anahtar olay (key event) sütunları tüm olayları kapsadığından kullanılmamıştır</t>
+          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Giriş sayfası raporunda bir oturum birden fazla giriş sayfasında sayılabildiği için oturum pay olarak verilmiştir; gelir genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır</t>
         </is>
       </c>
     </row>

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -52471,7 +52471,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="70.5" customHeight="1">
+    <row r="8" ht="97.5" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Google Analytics 4</t>
@@ -52489,7 +52489,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Giriş sayfası raporunda bir oturum birden fazla giriş sayfasında sayılabildiği için oturum pay olarak verilmiştir; gelir genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır</t>
+          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Giriş sayfası raporunda bir oturum birden fazla giriş sayfasında sayılabildiği için oturum pay olarak verilmiştir; gelir genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır. Ürün raporunda sepete eklenen ürün (Items added to cart) bazı aylarda geçersiz değer taşıdığından kullanılmamış; ürün geliri genel bakıştaki gelirden farklı hesaplandığı için pay olarak verilmiştir</t>
         </is>
       </c>
     </row>

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -52471,7 +52471,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="97.5" customHeight="1">
+    <row r="8" ht="138" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Google Analytics 4</t>
@@ -52479,7 +52479,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr mülkü, VitrA ekibi dışa aktarımı (05.10.2026) · genel bakış Oca 2025 - Eyl 2026 · kanal Oca - Eyl 2025 ve 2026 · site içi arama 1 May - 30 Eyl 2026 · ödeme, teslimat, servis düğmesi tıklaması, sayfa ve promosyon 1 Eyl 2025 - 30 Eyl 2026 · giriş sayfası Oca 2025 - 5 Eki 2026</t>
+          <t>vitra.com.tr mülkü, VitrA ekibi dışa aktarımı (05.10.2026) · genel bakış Oca 2025 - Eyl 2026 · kanal Oca - Eyl 2025 ve 2026 · site içi arama 1 May - 30 Eyl 2026 · ödeme, teslimat, servis düğmesi ve promosyon 1 Eki 2025 - 30 Eyl 2026 · blog ve koleksiyon sayfaları 1 Ara 2025 - 30 Eyl 2026 · giriş sayfası Oca 2025 - 5 Eki 2026 · huni ve ürün Oca 2025 - Eyl 2026</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -52489,7 +52489,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Giriş sayfası raporunda bir oturum birden fazla giriş sayfasında sayılabildiği için oturum pay olarak verilmiştir; gelir genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır. Ürün raporunda sepete eklenen ürün (Items added to cart) bazı aylarda geçersiz değer taşıdığından kullanılmamış; ürün geliri genel bakıştaki gelirden farklı hesaplandığı için pay olarak verilmiştir</t>
+          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Giriş sayfası raporunda bir oturum birden fazla giriş sayfasında sayılabildiği için oturum pay olarak verilmiştir; gelir genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır. Ürün raporunda sepete eklenen ürün (Items added to cart) beş ürün kodunda hatalı adet taşıdığı için bu kodlar, sepete ekleme olayının hatalı tetiklendiği Eylül 2026 ile birlikte oran hesabına katılmamış; ürün geliri genel bakıştaki gelirden farklı hesaplandığı için pay olarak verilmiştir. Sepet sayfasında oturum ve kullanıcı çerezi yenilendiği için kullanıcı düzeyindeki kırılımlar (yeni ve geri dönen kullanıcı, ilk kez satın alan) kullanılmamıştır. www.vitra.com.tr sayfaları (blog, koleksiyon, servis) bu mülkte Aralık 2025'ten itibaren ölçülmektedir</t>
         </is>
       </c>
     </row>

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -52471,7 +52471,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="138" customHeight="1">
+    <row r="8" ht="165" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Google Analytics 4</t>
@@ -52479,7 +52479,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>vitra.com.tr mülkü, VitrA ekibi dışa aktarımı (05.10.2026) · genel bakış Oca 2025 - Eyl 2026 · kanal Oca - Eyl 2025 ve 2026 · site içi arama 1 May - 30 Eyl 2026 · ödeme, teslimat, servis düğmesi ve promosyon 1 Eki 2025 - 30 Eyl 2026 · blog ve koleksiyon sayfaları 1 Ara 2025 - 30 Eyl 2026 · giriş sayfası Oca 2025 - 5 Eki 2026 · huni ve ürün Oca 2025 - Eyl 2026</t>
+          <t>vitra.com.tr mülkü, VitrA ekibi dışa aktarımı (05.10.2026) · genel bakış Oca 2025 - Eyl 2026 · kanal Oca - Eyl 2025 ve 2026 · site içi arama 1 May - 30 Eyl 2026 · ödeme, teslimat, servis düğmesi ve promosyon 1 Eki 2025 - 30 Eyl 2026 · blog ve koleksiyon sayfaları 1 Ara 2025 - 30 Eyl 2026 · giriş sayfası Oca 2025 - 5 Eki 2026 · sipariş onay sayfası 1 Eki 2025 - 30 Eyl 2026 · huni ve ürün Oca 2025 - Eyl 2026</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -52489,7 +52489,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Giriş sayfası raporunda bir oturum birden fazla giriş sayfasında sayılabildiği için oturum pay olarak verilmiştir; gelir genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır. Ürün raporunda sepete eklenen ürün (Items added to cart) beş ürün kodunda hatalı adet taşıdığı için bu kodlar, sepete ekleme olayının hatalı tetiklendiği Eylül 2026 ile birlikte oran hesabına katılmamış; ürün geliri genel bakıştaki gelirden farklı hesaplandığı için pay olarak verilmiştir. Sepet sayfasında oturum ve kullanıcı çerezi yenilendiği için kullanıcı düzeyindeki kırılımlar (yeni ve geri dönen kullanıcı, ilk kez satın alan) kullanılmamıştır. www.vitra.com.tr sayfaları (blog, koleksiyon, servis) bu mülkte Aralık 2025'ten itibaren ölçülmektedir</t>
+          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Giriş sayfası raporunda bir oturum birden fazla giriş sayfasında sayılabildiği için oturum pay olarak verilmiştir; gelir genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır. Ürün raporunda sepete eklenen ürün (Items added to cart) beş ürün kodunda hatalı adet taşıdığı için bu kodlar, sepete ekleme olayının hatalı tetiklendiği Eylül 2026 ile birlikte oran hesabına katılmamış; ürün geliri genel bakıştaki gelirden farklı hesaplandığı için pay olarak verilmiştir. Sepet sayfasında oturum ve kullanıcı çerezi yenilendiği için kullanıcı düzeyindeki kırılımlar (yeni ve geri dönen kullanıcı, ilk kez satın alan) kullanılmamıştır. www.vitra.com.tr sayfaları (blog, koleksiyon, servis) bu mülkte Aralık 2025'ten itibaren ölçülmektedir. Sipariş onay sayfası keşiflerinde (1 Eki 2025 - 30 Eyl 2026) bazı aylar örneklendiği için yalnız paylar kullanılmış; satın almanın kaynak / ortamı GA4 atama modeline göre, oturum kanalı ise oturum kanal grubuna göre verilmiştir</t>
         </is>
       </c>
     </row>

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Tık · 08 GA4 - Site ve E-Ticaret Performansı · 09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 11 YouTube: Montaj, Tamir ve Karar Videoları · 13 Katalog ve Talep Eşleşmesi · 15 Set, Komple Banyo ve Ürün + Hizmet · 26 Kanal Rolleri ve Etkileşim Modeli · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Click · 08 GA4 - Site ve E-Ticaret Performansı · 09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 11 YouTube: Montaj, Tamir ve Karar Videoları · 13 Katalog ve Talep Eşleşmesi · 15 Set, Komple Banyo ve Ürün + Hizmet · 26 Kanal Rolleri ve Etkileşim Modeli · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Tık · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar</t>
+          <t>06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Click · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>06 GSC - Organik Kanal · 15 Set, Komple Banyo ve Ürün + Hizmet · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>06 GSC - Organik Kanal · 15 Set, Komple Banyo ve Ürün + Hizmet · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları · 26 Kanal Rolleri ve Etkileşim Modeli · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları · 26 Kanal Rolleri ve Etkileşim Modeli · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -6568,7 +6568,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="97.5" customHeight="1">
+    <row r="165" ht="111" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
         <is>
           <t>https://www.banyoline.com</t>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>14 Yeni Kategori ve Segment Fırsatları · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>14 Yeni Kategori ve Segment Fırsatları · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="D227" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği · 28 Sonraki Adımlar</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
@@ -50712,7 +50712,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>12 Şikayetvar: Satış Sonrası Deneyim · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>12 Şikayetvar: Satış Sonrası Deneyim · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -50837,7 +50837,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -50937,7 +50937,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -51037,7 +51037,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -51087,7 +51087,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -51162,7 +51162,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -51187,7 +51187,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>12 Şikayetvar: Satış Sonrası Deneyim · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>12 Şikayetvar: Satış Sonrası Deneyim · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -51312,7 +51312,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -51412,7 +51412,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -51437,7 +51437,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -51512,7 +51512,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -51562,7 +51562,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -51587,7 +51587,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -51687,7 +51687,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -51737,7 +51737,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -51787,7 +51787,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -51812,7 +51812,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -51837,7 +51837,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -51912,7 +51912,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -51987,7 +51987,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -52037,7 +52037,7 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -52062,7 +52062,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -52137,7 +52137,7 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -52162,7 +52162,7 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -52262,7 +52262,7 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -52287,7 +52287,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -52312,7 +52312,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -52413,7 +52413,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>2.299 tekil kelime · Türkiye, Türkçe · aylık hacim Eyl 2022 - Ağu 2026 (talep grafiğinde Oca 2023 - Ağu 2026)</t>
+          <t>2.299 tekil kelime · Türkiye, Türkçe · aylık search volume Eyl 2022 - Ağu 2026 (talep grafiğinde Oca 2023 - Ağu 2026)</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -52423,7 +52423,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Google Ads yakın yazım varyantlarına (çoğul, yazım farkı) aynı aylık seriyi döndürür; aynı seriye sahip kelimeler tek kelime olarak sayılmıştır (2.437 satırdan 2.349 tekil kelime); birleşen varyantlarda Türkçe ve yaygın yazım gösterilir (banyo batarya yerine banyo bataryası). Sezonsallık listesinde bulunmayan 19 kategori baş kelimesi (duşakabin, klozet fiyatları, tuvalet fırçası, musluk başlığı vb.) 04.10.2026 tarihinde eklenmiştir. Banyo Tezgahları altında yer alan ve banyo ya da lavabo içermeyen 21 mutfak ve genel tezgah araması (porselen tezgah, mermer tezgah, mutfak mermeri vb.) banyo mobilyası talebini yansıtmadığı için çıkarılmıştır. Kaynak listede banyo alt kategorisine eşlenmiş, ancak Google sonuçlarında banyo dışı ürünlere yönelen 25 genel ifade de (dolap kulpu ve salon konsolu, banyo ifadesi içermeyen çöp kovası, masa peçeteliği, elektronik panel, doğal taş traverten; 04.10.2026 kontrolü) ile marka adı geçen 4 arama evrenden çıkarılmıştır; marka aramaları Bölüm 09'da ayrıca ele alınmaktadır. Evren bu düzenlemelerle 2.299 kelimeye inmiştir. "lavabo" kelimesinde Keyword Planner Haziran 2025 - Mayıs 2026 arasında önceki ve sonraki aylardan 2-4 kat yüksek hacim göstermektedir; aynı dönemde Google Trends yalnızca yaklaşık %30'luk bir artış gösterdiği için bu aylar Trends seyrine göre yeniden ölçeklenmiştir. "wc" kelimesinin Haziran-Temmuz 2026 değerleri Dünya Kupası aramalarıyla karıştığı için 2025'in aynı aylarıyla değiştirilmiştir</t>
+          <t>Google Ads yakın yazım varyantlarına (çoğul, yazım farkı) aynı aylık seriyi döndürür; aynı seriye sahip kelimeler tek kelime olarak sayılmıştır (2.437 satırdan 2.349 tekil kelime); birleşen varyantlarda Türkçe ve yaygın yazım gösterilir (banyo batarya yerine banyo bataryası). Sezonsallık listesinde bulunmayan 19 kategori baş kelimesi (duşakabin, klozet fiyatları, tuvalet fırçası, musluk başlığı vb.) 04.10.2026 tarihinde eklenmiştir. Banyo Tezgahları altında yer alan ve banyo ya da lavabo içermeyen 21 mutfak ve genel tezgah araması (porselen tezgah, mermer tezgah, mutfak mermeri vb.) banyo mobilyası talebini yansıtmadığı için çıkarılmıştır. Kaynak listede banyo alt kategorisine eşlenmiş, ancak Google sonuçlarında banyo dışı ürünlere yönelen 25 genel ifade de (dolap kulpu ve salon konsolu, banyo ifadesi içermeyen çöp kovası, masa peçeteliği, elektronik panel, doğal taş traverten; 04.10.2026 kontrolü) ile marka adı geçen 4 arama evrenden çıkarılmıştır; marka aramaları Bölüm 09'da ayrıca ele alınmaktadır. Evren bu düzenlemelerle 2.299 kelimeye inmiştir. "lavabo" kelimesinde Keyword Planner Haziran 2025 - Mayıs 2026 arasında önceki ve sonraki aylardan 2-4 kat yüksek search volume göstermektedir; aynı dönemde Google Trends yalnızca yaklaşık %30'luk bir artış gösterdiği için bu aylar Trends seyrine göre yeniden ölçeklenmiştir. "wc" kelimesinin Haziran-Temmuz 2026 değerleri Dünya Kupası aramalarıyla karıştığı için 2025'in aynı aylarıyla değiştirilmiştir</t>
         </is>
       </c>
     </row>
@@ -52435,7 +52435,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>26 üretici marka ve 10 perakendeci · yalın marka adı ve marka + kategori aramaları · Türkiye, Türkçe · aylık hacim Eyl 2022 - Ağu 2026 · 04.10.2026</t>
+          <t>26 üretici marka ve 10 perakendeci · yalın marka adı ve marka + kategori aramaları · Türkiye, Türkçe · aylık search volume Eyl 2022 - Ağu 2026 · 04.10.2026</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -52445,7 +52445,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>"vitra" için kelime evrenindeki ifadelerin markalı biçimleri (2.227 ifade), rakipler için bunlardan VitrA'da hacmi olan 637 kategori ifadesi kullanılmıştır; yakın yazım varyantları marka ve kategori içinde tek sayılmış, " seramik" şirket adı araması olduğu için kategori hesabına alınmamıştır. "kale" kelimesi marka dışı anlamlar da taşır. Ahrefs'te rakip marka sitelerinin ve Trendyol, Hepsiburada, Koçtaş'ın sıralandığı marka ifadeleri (hacmi 10 ve üzeri, 04.10.2026) eklenmiştir; pazaryerlerinden yalnız banyo kategorisine eşlenen ifadeler, marka sitelerinden ayrıca servis, yedek parça ve satış noktası ifadeleri alınmış, ısıtma, kilit ve borsa gibi banyo dışı konular çıkarılmıştır. E.C.A. servis aramaları kombi servisinden ayrıştırılamadığı için alınmamıştır.</t>
+          <t>"vitra" için kelime evrenindeki ifadelerin markalı biçimleri (2.227 ifade), rakipler için bunlardan VitrA'da search volume olan 637 kategori ifadesi kullanılmıştır; yakın yazım varyantları marka ve kategori içinde tek sayılmış, " seramik" şirket adı araması olduğu için kategori hesabına alınmamıştır. "kale" kelimesi marka dışı anlamlar da taşır. Ahrefs'te rakip marka sitelerinin ve Trendyol, Hepsiburada, Koçtaş'ın sıralandığı marka ifadeleri (search volume 10 ve üzeri, 04.10.2026) eklenmiştir; pazaryerlerinden yalnız banyo kategorisine eşlenen ifadeler, marka sitelerinden ayrıca servis, yedek parça ve satış noktası ifadeleri alınmış, ısıtma, kilit ve borsa gibi banyo dışı konular çıkarılmıştır. E.C.A. servis aramaları kombi servisinden ayrıştırılamadığı için alınmamıştır.</t>
         </is>
       </c>
     </row>
@@ -52471,7 +52471,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="165" customHeight="1">
+    <row r="8" ht="178.5" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Google Analytics 4</t>
@@ -52489,7 +52489,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için oturum ve dönüşüm oranı Aralık öncesi ve sonrası kıyaslanmaz; gelir ve satın alma kıyaslanabilir. Giriş sayfası raporunda bir oturum birden fazla giriş sayfasında sayılabildiği için oturum pay olarak verilmiştir; gelir genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır. Ürün raporunda sepete eklenen ürün (Items added to cart) beş ürün kodunda hatalı adet taşıdığı için bu kodlar, sepete ekleme olayının hatalı tetiklendiği Eylül 2026 ile birlikte oran hesabına katılmamış; ürün geliri genel bakıştaki gelirden farklı hesaplandığı için pay olarak verilmiştir. Sepet sayfasında oturum ve kullanıcı çerezi yenilendiği için kullanıcı düzeyindeki kırılımlar (yeni ve geri dönen kullanıcı, ilk kez satın alan) kullanılmamıştır. www.vitra.com.tr sayfaları (blog, koleksiyon, servis) bu mülkte Aralık 2025'ten itibaren ölçülmektedir. Sipariş onay sayfası keşiflerinde (1 Eki 2025 - 30 Eyl 2026) bazı aylar örneklendiği için yalnız paylar kullanılmış; satın almanın kaynak / ortamı GA4 atama modeline göre, oturum kanalı ise oturum kanal grubuna göre verilmiştir</t>
+          <t>Aralık 2025'te www.vitra.com.tr traffic'i aynı mülke katıldığı için session ve conversion rate Aralık öncesi ve sonrası kıyaslanmaz; revenue ve purchase kıyaslanabilir. Giriş sayfası raporunda bir session birden fazla giriş sayfasında sayılabildiği için session pay olarak verilmiştir; revenue genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır. Ürün raporunda sepete eklenen ürün (Items added to cart) beş ürün kodunda hatalı adet taşıdığı için bu kodlar, sepete ekleme olayının hatalı tetiklendiği Eylül 2026 ile birlikte oran hesabına katılmamış; ürün revenue'su genel bakıştaki revenue'dan farklı hesaplandığı için pay olarak verilmiştir. Sepet sayfasında session ve kullanıcı çerezi yenilendiği için kullanıcı düzeyindeki kırılımlar (yeni ve geri dönen kullanıcı, ilk kez satın alan) kullanılmamıştır. www.vitra.com.tr sayfaları (blog, koleksiyon, servis) bu mülkte Aralık 2025'ten itibaren ölçülmektedir. Sipariş onay sayfası keşiflerinde (1 Eki 2025 - 30 Eyl 2026) bazı aylar örneklendiği için yalnız paylar kullanılmış; purchase'ın kaynak / ortamı GA4 atama modeline göre, session kanalı ise session kanal grubuna göre verilmiştir</t>
         </is>
       </c>
     </row>
@@ -52555,7 +52555,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Organik ve paid trafik değerleri Ahrefs tahminidir; gerçek ziyaret sayısı değildir</t>
+          <t>Organik ve paid traffic değerleri Ahrefs tahminidir; gerçek visit sayısı değildir</t>
         </is>
       </c>
     </row>
@@ -52691,7 +52691,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="57" customHeight="1">
+    <row r="18" ht="70.5" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Google arama sonuçları</t>
@@ -52699,7 +52699,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>322 kelime: A · VitrA gamı 159 (her alt kategoriden en az bir baş kelime), B · yakın kategori fırsatları 83, C · marka ve karşılaştırma 80; Keyword Planner'da hacmi olan · Türkiye, Türkçe, mobil · ilk 20 organik sonuç, AI Overview, PAA · 04.10.2026</t>
+          <t>322 kelime: A · VitrA gamı 159 (her alt kategoriden en az bir baş kelime), B · yakın kategori fırsatları 83, C · marka ve karşılaştırma 80; Keyword Planner'da search volume olan · Türkiye, Türkçe, mobil · ilk 20 organik sonuç, AI Overview, PAA · 04.10.2026</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -52731,7 +52731,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Yanıtlar kişiselleştirilmemiş oturumlardan alınmıştır ve aynı soruya gün içinde farklı yanıt verilebilir; oranlar yön göstericidir</t>
+          <t>Yanıtlar kişiselleştirilmemiş session'lardan alınmıştır ve aynı soruya gün içinde farklı yanıt verilebilir; oranlar yön göstericidir</t>
         </is>
       </c>
     </row>
@@ -52765,7 +52765,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>24 marka ve uzman site top pages ve 69 baş kelimenin sıralama verisi · Türkiye · 28.09.2026; bu bölümdeki arama hacimleri Google Keyword Planner (Eyl 2024 - Ağu 2026)</t>
+          <t>24 marka ve uzman site top pages ve 69 baş kelimenin sıralama verisi · Türkiye · 28.09.2026; bu bölümdeki search volume'ları Google Keyword Planner (Eyl 2024 - Ağu 2026)</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Kategori trafiği listelenen sayfalarla sınırlıdır ve alt sınır olarak okunmalıdır</t>
+          <t>Kategori traffic'i listelenen sayfalarla sınırlıdır ve alt sınır olarak okunmalıdır</t>
         </is>
       </c>
     </row>
@@ -52941,7 +52941,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Trendyol satıcı paneli: satış ve sipariş dağılımı (2025 Q4 - 2026 Q3), favori-görüntüleme (2025, 2026), 1.023 ürün ve 149 satıcı değerlendirmesi, 352 ürün sorusu, 44 Enleri listesi · Hepsiburada: hak ediş, görüntülenme, iptal, değerlendirme · 30.09.2026; ürün bazlı satış raporu, son 12 ay · 02.10.2026</t>
+          <t>Trendyol satıcı paneli: satış ve sipariş dağılımı (2025 Q4 - 2026 Q3), favori-görüntüleme (2025, 2026), 1.023 ürün ve 149 satıcı değerlendirmesi, 352 ürün sorusu, 44 Enleri listesi · Hepsiburada: hak ediş, view, iptal, değerlendirme · 30.09.2026; ürün bazlı satış raporu, son 12 ay · 02.10.2026</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -52951,7 +52951,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Yalnız resmi mağaza; ciro tutarı verilmez, pay ve oran kullanılır; temalar anahtar kelimeyle; Enleri ekran görüntüsünden okunmuştur</t>
+          <t>Yalnız resmi mağaza; revenue tutarı verilmez, pay ve oran kullanılır; temalar anahtar kelimeyle; Enleri ekran görüntüsünden okunmuştur</t>
         </is>
       </c>
     </row>
@@ -52973,7 +52973,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Rehber sayfaları adres yapısına göre konu gruplarına ayrılmıştır; en az 5 tık alan 93 sayfa değerlendirilmiştir</t>
+          <t>Rehber sayfaları adres yapısına göre konu gruplarına ayrılmıştır; en az 5 click alan 93 sayfa değerlendirilmiştir</t>
         </is>
       </c>
     </row>
@@ -53024,12 +53024,12 @@
     <row r="33" ht="43.5" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Similarweb site trafiği</t>
+          <t>Similarweb site traffic'i</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>31 alan adı: marka, uzman, yapı market, pazaryeri ve fiyat karşılaştırma siteleri; aylık ziyaret, kanal kırılımı, etkileşim · Haz - Ağu 2026 · 03.10.2026</t>
+          <t>31 alan adı: marka, uzman, yapı market, pazaryeri ve fiyat karşılaştırma siteleri; aylık visit, kanal kırılımı, etkileşim · Haz - Ağu 2026 · 03.10.2026</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -53039,7 +53039,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>Ziyaretler tüm ülkeleri kapsayan tahminlerdir; aylık ziyareti ~35 binin altındaki 9 sitede kanal dağılımı modellendiği için gösterilmemiştir</t>
+          <t>Visit'ler tüm ülkeleri kapsayan tahminlerdir; aylık visit'i ~35 binin altındaki 9 sitede kanal dağılımı modellendiği için gösterilmemiştir</t>
         </is>
       </c>
     </row>
@@ -53083,7 +53083,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>Click payı SEOmonitor'ün sıra ve hacimden türettiği tahmindir</t>
+          <t>Click payı SEOmonitor'ün sıra ve search volume'dan türettiği tahmindir</t>
         </is>
       </c>
     </row>

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -5185,7 +5185,7 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>500 TL altında teslimat başına 49,90 TL; 500 TL ve üzeri ücretsiz</t>
+          <t>₺500 altında teslimat başına ₺49,90; ₺500 ve üzeri ücretsiz</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>Batch Analysis: DR 87, 955.958 organik kelime, ilk 3'te 359.188 kelime, 14.743.911 organik ve 391.829 paid trafik (Ahrefs tahmini, 27.09.2026) | Top pages sorgusu 300 satır (alt sınır, pencere tabanı 162 aylık ziyaret); banyo çekirdeği 106.822, banyo-bitişik 54.435 aylık tahmini organik ziyaret; banyo çekirdeğinde 178 sayfa | Organic keywords sorgusu: 300 kelime (hacim, en iyi sıra, tahmini trafik) | Ev, Yaşam, Kırtasiye, Ofis &gt; Banyo &amp; Mutfak (10.000+ ürün) ağacı; marka filtreli toplamlar (VitrA 3.191, Artema 1.938, Kale 1.376, Creavit 1.975 ürün); 13 arama kökü için arama önerisi servisi; yaklaşık 65 sayfa yüklemesi (47'si ham veriye kaydedildi); VitrA buybox payı: %19 VitrA mağazası, %13 Hepsiburada, %69 3. taraf satıcı; giriş, form ve sepet işlemi yapılmadı | Kategori ağacı ve marka filtreli toplamlar, 14 kategori × 36 ürün çok satan listeleri, 29 VitrA ve Artema SKU'sunun buybox ve satıcı listesi, Mr Usta montaj hizmet ürünleri (klozet montajı 2.730 TL)</t>
+          <t>Batch Analysis: DR 87, 955.958 organik kelime, ilk 3'te 359.188 kelime, 14.743.911 organik ve 391.829 paid trafik (Ahrefs tahmini, 27.09.2026) | Top pages sorgusu 300 satır (alt sınır, pencere tabanı 162 aylık ziyaret); banyo çekirdeği 106.822, banyo-bitişik 54.435 aylık tahmini organik ziyaret; banyo çekirdeğinde 178 sayfa | Organic keywords sorgusu: 300 kelime (hacim, en iyi sıra, tahmini trafik) | Ev, Yaşam, Kırtasiye, Ofis &gt; Banyo &amp; Mutfak (10.000+ ürün) ağacı; marka filtreli toplamlar (VitrA 3.191, Artema 1.938, Kale 1.376, Creavit 1.975 ürün); 13 arama kökü için arama önerisi servisi; yaklaşık 65 sayfa yüklemesi (47'si ham veriye kaydedildi); VitrA buybox payı: %19 VitrA mağazası, %13 Hepsiburada, %69 3. taraf satıcı; giriş, form ve sepet işlemi yapılmadı | Kategori ağacı ve marka filtreli toplamlar, 14 kategori × 36 ürün çok satan listeleri, 29 VitrA ve Artema SKU'sunun buybox ve satıcı listesi, Mr Usta montaj hizmet ürünleri (klozet montajı ₺2.730)</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Ücretsiz kargo eşiği yalnız 300 TL (altı 49,90 TL); 30 desi üstü lojistikle kata teslim; iade 14 gün, iade kodu 7 gün; demonte üründe montaj yapıldıysa iade yok; klozet takımı ve kapağında ambalajı açılmamış şartı; hasar için Durum Tespit Tutanağı; kapıda ödeme yok; taksit eşiği bu sayfada 10.000 TL (/taksitler sayfasında 5.000 TL, tutarsız)</t>
+          <t>Ücretsiz kargo eşiği yalnız ₺300 (altı ₺49,90); 30 desi üstü lojistikle kata teslim; iade 14 gün, iade kodu 7 gün; demonte üründe montaj yapıldıysa iade yok; klozet takımı ve kapağında ambalajı açılmamış şartı; hasar için Durum Tespit Tutanağı; kapıda ödeme yok; taksit eşiği bu sayfada ₺10.000 (/taksitler sayfasında ₺5.000, tutarsız)</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>Kargo için 3 seçenek (alıcı öder, mağaza öder, şartlı kargo); 14 gün cayma hakkı; kapıda ödeme yok; Garanti Alışveriş Kredisi 750-15.000 TL, 48 aya varan vade; garanti satıcı sorumluluğunda</t>
+          <t>Kargo için 3 seçenek (alıcı öder, mağaza öder, şartlı kargo); 14 gün cayma hakkı; kapıda ödeme yok; Garanti Alışveriş Kredisi ₺750-15.000, 48 aya varan vade; garanti satıcı sorumluluğunda</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>11 montaj kalemi ve fiyatı: klozet 2.750 TL, gömme rezervuar 3.900, banyo mobilyası seti 4.000, lavabo 2.299, armatür ve duş 2.350, büyük 5.300 TL; 1 yıl servis garantisi; 40.000 TL üzeri kampanyada ücretsiz montaj</t>
+          <t>11 montaj kalemi ve fiyatı: klozet ₺2.750, gömme rezervuar 3.900, banyo mobilyası seti 4.000, lavabo 2.299, armatür ve duş 2.350, büyük ₺5.300; 1 yıl servis garantisi; ₺40.000 üzeri kampanyada ücretsiz montaj</t>
         </is>
       </c>
       <c r="F161" s="7" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>Keşif hizmeti 1.400 TL (2 banyo, rölöve ve kırım hariç); kapsam ve koşul metni | Hizmet kapsamı ve koşul maddeleri; fiyat 1.400 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Keşif hizmeti ₺1.400 (2 banyo, rölöve ve kırım hariç); kapsam ve koşul metni | Hizmet kapsamı ve koşul maddeleri; fiyat ₺1.400; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F162" s="7" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>Taksit kampanyası (30 Eylül 2026'ya kadar), '3 AL 2 ÖDE' ve 1.500 TL üzeri ek 250 TL indirim başlıkları; Koçtaş Kart menüde | Organik rakipler raporu: vitra.com.tr ile 4.645 ortak kelime, rakibin 99.325 kelimesi, 2.413.380 aylık organik trafik, DR 72; Batch Analysis: DR 72, 103.539 organik kelime, ilk 3'te 29.860 kelime, 2.626.864 organik ve 213.866 paid trafik (Ahrefs tahmini, 27.09.2026) | Top pages sorgusu 150 satır (alt sınır, pencere tabanı 177 aylık ziyaret); banyo çekirdeği 204.086, banyo-bitişik 83.006 aylık tahmini organik ziyaret; banyo çekirdeğinde 110 sayfa | Kategori yapısı kategori sayfalarından okundu; 16 VitrA ve Artema ürün sayfasının liste ve sepet fiyatı; Koçtaş, VitrA kelimelerinin %63'ünde sıralanıyor ve organik trafiği VitrA'nın yaklaşık 8x'i</t>
+          <t>Taksit kampanyası (30 Eylül 2026'ya kadar), '3 AL 2 ÖDE' ve ₺1.500 üzeri ek ₺250 indirim başlıkları; Koçtaş Kart menüde | Organik rakipler raporu: vitra.com.tr ile 4.645 ortak kelime, rakibin 99.325 kelimesi, 2.413.380 aylık organik trafik, DR 72; Batch Analysis: DR 72, 103.539 organik kelime, ilk 3'te 29.860 kelime, 2.626.864 organik ve 213.866 paid trafik (Ahrefs tahmini, 27.09.2026) | Top pages sorgusu 150 satır (alt sınır, pencere tabanı 177 aylık ziyaret); banyo çekirdeği 204.086, banyo-bitişik 83.006 aylık tahmini organik ziyaret; banyo çekirdeğinde 110 sayfa | Kategori yapısı kategori sayfalarından okundu; 16 VitrA ve Artema ürün sayfasının liste ve sepet fiyatı; Koçtaş, VitrA kelimelerinin %63'ünde sıralanıyor ve organik trafiği VitrA'nın yaklaşık 8x'i</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 2.212 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺2.212; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
@@ -7405,7 +7405,7 @@
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 937 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺937; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 2.350 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺2.350; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 4.000 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺4.000; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 5.300 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺5.300; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 2.000 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺2.000; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 3.900 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺3.900; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 2.750 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺2.750; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 1.150 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺1.150; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 2.300 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺2.300; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>Hizmet kapsamı ve koşul maddeleri; fiyat 2.200 TL; 1 yıl servis garantisi ve servis formu koşulu</t>
+          <t>Hizmet kapsamı ve koşul maddeleri; fiyat ₺2.200; 1 yıl servis garantisi ve servis formu koşulu</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="E244" s="6" t="inlineStr">
         <is>
-          <t>Aylık 3.959 tahmini organik ziyaret (banyo çekirdeğinin en büyük sayfası) | 24 ürün okundu; medyan 7.777 TL; VitrA/Artema 1 ürün; marka dağılımı: Fly:13/5, Karen Banyo:9/51, (markasız):1/0, VitrA:1/0</t>
+          <t>Aylık 3.959 tahmini organik ziyaret (banyo çekirdeğinin en büyük sayfası) | 24 ürün okundu; medyan ₺7.777; VitrA/Artema 1 ürün; marka dağılımı: Fly:13/5, Karen Banyo:9/51, (markasız):1/0, VitrA:1/0</t>
         </is>
       </c>
       <c r="F244" s="7" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E246" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 1.613; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 4.764 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 1654; medyan 2.700 TL; toplam değerlendirme 4252; platform satış payı %0.0; VitrA/Artema 1 ürün</t>
+          <t>sonuç sayısı 1.613; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺4.764; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 1654; medyan ₺2.700; toplam değerlendirme 4252; platform satış payı %0.0; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F246" s="7" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 934; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 4.315 TL</t>
+          <t>Sonuç sayısı 934; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺4.315</t>
         </is>
       </c>
       <c r="F247" s="7" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="E248" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 645 TL</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺645</t>
         </is>
       </c>
       <c r="F248" s="7" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 2.432 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan 1.149 TL; toplam değerlendirme 7926; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺2.432; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan ₺1.149; toplam değerlendirme 7926; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F249" s="7" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 263 TL</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺263</t>
         </is>
       </c>
       <c r="F250" s="7" t="inlineStr">
@@ -9773,7 +9773,7 @@
       </c>
       <c r="E251" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 629; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 8.845 TL</t>
+          <t>Sonuç sayısı 629; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺8.845</t>
         </is>
       </c>
       <c r="F251" s="7" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="E252" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 4; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 1.595 TL</t>
+          <t>Sonuç sayısı 4; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺1.595</t>
         </is>
       </c>
       <c r="F252" s="7" t="inlineStr">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="E253" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 3.456; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 8.671 TL | 36 ürün okundu, kategori toplamı 3294; medyan 5.720 TL; toplam değerlendirme 1676; platform satış payı %0.0; VitrA/Artema 3 ürün</t>
+          <t>Sonuç sayısı 3.456; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺8.671 | 36 ürün okundu, kategori toplamı 3294; medyan ₺5.720; toplam değerlendirme 1676; platform satış payı %0.0; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F253" s="7" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="E254" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 4.466; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 399 TL | 72 ürün okundu, kategori toplamı 4304; medyan 357 TL; toplam değerlendirme 4501; platform satış payı %5.6; VitrA/Artema 4 ürün</t>
+          <t>Sonuç sayısı 4.466; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺399 | 72 ürün okundu, kategori toplamı 4304; medyan ₺357; toplam değerlendirme 4501; platform satış payı %5.6; VitrA/Artema 4 ürün</t>
         </is>
       </c>
       <c r="F254" s="7" t="inlineStr">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="E255" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 2; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 1.061 TL</t>
+          <t>Sonuç sayısı 2; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺1.061</t>
         </is>
       </c>
       <c r="F255" s="7" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="E256" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 458 TL</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺458</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="E257" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 2.943; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 637 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 2880; medyan 520 TL; toplam değerlendirme 3527; platform satış payı %0.0; VitrA/Artema 3 ürün</t>
+          <t>sonuç sayısı 2.943; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺637; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 2880; medyan ₺520; toplam değerlendirme 3527; platform satış payı %0.0; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="E258" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 1.938; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 3.670 TL</t>
+          <t>Sonuç sayısı 1.938; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺3.670</t>
         </is>
       </c>
       <c r="F258" s="7" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="E259" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 1.223; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 3.613 TL</t>
+          <t>Sonuç sayısı 1.223; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺3.613</t>
         </is>
       </c>
       <c r="F259" s="7" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="E260" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 934 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan 699 TL; toplam değerlendirme 5024; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺934; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan ₺699; toplam değerlendirme 5024; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F260" s="7" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="E261" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 372 TL</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺372</t>
         </is>
       </c>
       <c r="F261" s="7" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="E262" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 1.891 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan 1.949 TL; toplam değerlendirme 571; platform satış payı %0.0; VitrA/Artema 2 ürün</t>
+          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺1.891; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan ₺1.949; toplam değerlendirme 571; platform satış payı %0.0; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F262" s="7" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E263" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 4.118 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan 3.080 TL; toplam değerlendirme 5604; platform satış payı %16.7; VitrA/Artema 8 ürün</t>
+          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺4.118; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan ₺3.080; toplam değerlendirme 5604; platform satış payı %16.7; VitrA/Artema 8 ürün</t>
         </is>
       </c>
       <c r="F263" s="7" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="E266" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 2.305 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan 1.450 TL; toplam değerlendirme 9554; platform satış payı %19.4; VitrA/Artema 11 ürün</t>
+          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺2.305; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan ₺1.450; toplam değerlendirme 9554; platform satış payı %19.4; VitrA/Artema 11 ürün</t>
         </is>
       </c>
       <c r="F266" s="7" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E268" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 3.535 TL</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺3.535</t>
         </is>
       </c>
       <c r="F268" s="7" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="E269" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 1.092 TL</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺1.092</t>
         </is>
       </c>
       <c r="F269" s="7" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="E270" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 628 TL</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺628</t>
         </is>
       </c>
       <c r="F270" s="7" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="E271" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 1.500 TL</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺1.500</t>
         </is>
       </c>
       <c r="F271" s="7" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="E272" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 1.975; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 4.754 TL</t>
+          <t>Sonuç sayısı 1.975; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺4.754</t>
         </is>
       </c>
       <c r="F272" s="7" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="E273" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 259; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 10.880 TL</t>
+          <t>Sonuç sayısı 259; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺10.880</t>
         </is>
       </c>
       <c r="F273" s="7" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="E274" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 369 TL | 72 ürün okundu, kategori toplamı 10000; medyan 328 TL; toplam değerlendirme 15545; platform satış payı %0.0; VitrA/Artema 5 ürün</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺369 | 72 ürün okundu, kategori toplamı 10000; medyan ₺328; toplam değerlendirme 15545; platform satış payı %0.0; VitrA/Artema 5 ürün</t>
         </is>
       </c>
       <c r="F274" s="7" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="E275" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 1.298 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan 452 TL; toplam değerlendirme 11423; platform satış payı %15.3; VitrA/Artema 4 ürün</t>
+          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺1.298; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan ₺452; toplam değerlendirme 11423; platform satış payı %15.3; VitrA/Artema 4 ürün</t>
         </is>
       </c>
       <c r="F275" s="7" t="inlineStr">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="E276" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 694 TL</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺694</t>
         </is>
       </c>
       <c r="F276" s="7" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="E277" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 2.375; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 8.431 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 2383; medyan 6.709 TL; toplam değerlendirme 3428; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>sonuç sayısı 2.375; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺8.431; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 2383; medyan ₺6.709; toplam değerlendirme 3428; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F277" s="7" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="E278" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 4.768 TL | 72 ürün okundu, kategori toplamı 10000; medyan 2.680 TL; toplam değerlendirme 2472; platform satış payı %11.1; VitrA/Artema 0 ürün</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺4.768 | 72 ürün okundu, kategori toplamı 10000; medyan ₺2.680; toplam değerlendirme 2472; platform satış payı %11.1; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F278" s="7" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="E279" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 3.787; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 1.553 TL | 72 ürün okundu, kategori toplamı 3638; medyan 1.331 TL; toplam değerlendirme 1584; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>Sonuç sayısı 3.787; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺1.553 | 72 ürün okundu, kategori toplamı 3638; medyan ₺1.331; toplam değerlendirme 1584; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F279" s="7" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="E280" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 1.376; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 1.322 TL</t>
+          <t>Sonuç sayısı 1.376; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺1.322</t>
         </is>
       </c>
       <c r="F280" s="7" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="E281" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 72; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 10.585 TL</t>
+          <t>Sonuç sayısı 72; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺10.585</t>
         </is>
       </c>
       <c r="F281" s="7" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="E282" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 865 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan 699 TL; toplam değerlendirme 12887; platform satış payı %12.5; VitrA/Artema 12 ürün</t>
+          <t>sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺865; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 10000; medyan ₺699; toplam değerlendirme 12887; platform satış payı %12.5; VitrA/Artema 12 ürün</t>
         </is>
       </c>
       <c r="F282" s="7" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="E283" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 4.095; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 8.536 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 3655; medyan 7.518 TL; toplam değerlendirme 2152; platform satış payı %45.8; VitrA/Artema 17 ürün</t>
+          <t>sonuç sayısı 4.095; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺8.536; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 3655; medyan ₺7.518; toplam değerlendirme 2152; platform satış payı %45.8; VitrA/Artema 17 ürün</t>
         </is>
       </c>
       <c r="F283" s="7" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="E286" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 8.956; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 1.669 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 8708; medyan 2.340 TL; toplam değerlendirme 2747; platform satış payı %59.7; VitrA/Artema 1 ürün</t>
+          <t>sonuç sayısı 8.956; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺1.669; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 8708; medyan ₺2.340; toplam değerlendirme 2747; platform satış payı %59.7; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F286" s="7" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="E289" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 2.660 TL | 72 ürün okundu, kategori toplamı 10000; medyan 2.175 TL; toplam değerlendirme 15384; platform satış payı %18.1; VitrA/Artema 13 ürün</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺2.660 | 72 ürün okundu, kategori toplamı 10000; medyan ₺2.175; toplam değerlendirme 15384; platform satış payı %18.1; VitrA/Artema 13 ürün</t>
         </is>
       </c>
       <c r="F289" s="7" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="E290" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 412; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 8.854 TL | 72 ürün okundu, kategori toplamı 389; medyan 6.178 TL; toplam değerlendirme 34; platform satış payı %11.1; VitrA/Artema 7 ürün</t>
+          <t>Sonuç sayısı 412; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺8.854 | 72 ürün okundu, kategori toplamı 389; medyan ₺6.178; toplam değerlendirme 34; platform satış payı %11.1; VitrA/Artema 7 ürün</t>
         </is>
       </c>
       <c r="F290" s="7" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="E291" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 3.956; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 907 TL; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 3990; medyan 602 TL; toplam değerlendirme 7666; platform satış payı %4.2; VitrA/Artema 20 ürün</t>
+          <t>sonuç sayısı 3.956; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺907; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 3990; medyan ₺602; toplam değerlendirme 7666; platform satış payı %4.2; VitrA/Artema 20 ürün</t>
         </is>
       </c>
       <c r="F291" s="7" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="E292" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 1.606; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 8.612 TL | 72 ürün okundu, kategori toplamı 1611; medyan 4.149 TL; toplam değerlendirme 8399; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>Sonuç sayısı 1.606; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺8.612 | 72 ürün okundu, kategori toplamı 1611; medyan ₺4.149; toplam değerlendirme 8399; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F292" s="7" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="E293" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 263; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 15.260 TL</t>
+          <t>Sonuç sayısı 263; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺15.260</t>
         </is>
       </c>
       <c r="F293" s="7" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="E294" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 3.191; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 2.821 TL</t>
+          <t>Sonuç sayısı 3.191; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺2.821</t>
         </is>
       </c>
       <c r="F294" s="7" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="E295" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 800; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 5.076 TL</t>
+          <t>Sonuç sayısı 800; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺5.076</t>
         </is>
       </c>
       <c r="F295" s="7" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="E296" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 143; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 2.127 TL</t>
+          <t>Sonuç sayısı 143; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺2.127</t>
         </is>
       </c>
       <c r="F296" s="7" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="E298" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 302; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 13.164 TL</t>
+          <t>Sonuç sayısı 302; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺13.164</t>
         </is>
       </c>
       <c r="F298" s="7" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="E299" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 313; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 7.758 TL</t>
+          <t>Sonuç sayısı 313; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺7.758</t>
         </is>
       </c>
       <c r="F299" s="7" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="E300" s="6" t="inlineStr">
         <is>
-          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı 1.563 TL</t>
+          <t>Sonuç sayısı 10.000+; ilk 36 ürünün çok satan sıralaması; ortalama liste fiyatı ₺1.563</t>
         </is>
       </c>
       <c r="F300" s="7" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="E314" s="6" t="inlineStr">
         <is>
-          <t>Markanın Trendyol'daki listeleme sayısı 1.659; ilk 36 ürünün medyan fiyatı 1.458 TL, toplam değerlendirme sayısı 2.942; satıcı ve kategori dağılımı</t>
+          <t>Markanın Trendyol'daki listeleme sayısı 1.659; ilk 36 ürünün medyan fiyatı ₺1.458, toplam değerlendirme sayısı 2.942; satıcı ve kategori dağılımı</t>
         </is>
       </c>
       <c r="F314" s="7" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="E315" s="6" t="inlineStr">
         <is>
-          <t>Markanın Trendyol'daki listeleme sayısı 2.781; ilk 36 ürünün medyan fiyatı 854 TL, toplam değerlendirme sayısı 2.286; satıcı ve kategori dağılımı</t>
+          <t>Markanın Trendyol'daki listeleme sayısı 2.781; ilk 36 ürünün medyan fiyatı ₺854, toplam değerlendirme sayısı 2.286; satıcı ve kategori dağılımı</t>
         </is>
       </c>
       <c r="F315" s="7" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="E316" s="6" t="inlineStr">
         <is>
-          <t>Markanın Trendyol'daki listeleme sayısı 1.645; ilk 36 ürünün medyan fiyatı 2.656 TL, toplam değerlendirme sayısı 1.943; satıcı ve kategori dağılımı</t>
+          <t>Markanın Trendyol'daki listeleme sayısı 1.645; ilk 36 ürünün medyan fiyatı ₺2.656, toplam değerlendirme sayısı 1.943; satıcı ve kategori dağılımı</t>
         </is>
       </c>
       <c r="F316" s="7" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="E317" s="6" t="inlineStr">
         <is>
-          <t>Markanın Trendyol'daki listeleme sayısı 6.537; ilk 36 ürünün medyan fiyatı 1.400 TL, toplam değerlendirme sayısı 10.153; satıcı ve kategori dağılımı</t>
+          <t>Markanın Trendyol'daki listeleme sayısı 6.537; ilk 36 ürünün medyan fiyatı ₺1.400, toplam değerlendirme sayısı 10.153; satıcı ve kategori dağılımı</t>
         </is>
       </c>
       <c r="F317" s="7" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="E318" s="6" t="inlineStr">
         <is>
-          <t>Kategori sonuç sayısı 63.531; ilk 36 ürünün medyan fiyatı 169 TL, toplam değerlendirme sayısı 113.236</t>
+          <t>Kategori sonuç sayısı 63.531; ilk 36 ürünün medyan fiyatı ₺169, toplam değerlendirme sayısı 113.236</t>
         </is>
       </c>
       <c r="F318" s="7" t="inlineStr">
@@ -12289,7 +12289,7 @@
       </c>
       <c r="E319" s="6" t="inlineStr">
         <is>
-          <t>Kategori sonuç sayısı 24.480; ilk 36 ürünün medyan fiyatı 2.828 TL, toplam değerlendirme sayısı 33.368</t>
+          <t>Kategori sonuç sayısı 24.480; ilk 36 ürünün medyan fiyatı ₺2.828, toplam değerlendirme sayısı 33.368</t>
         </is>
       </c>
       <c r="F319" s="7" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="E320" s="6" t="inlineStr">
         <is>
-          <t>Kategori sonuç sayısı 41.057; ilk 36 ürünün medyan fiyatı 397 TL, toplam değerlendirme sayısı 37.644</t>
+          <t>Kategori sonuç sayısı 41.057; ilk 36 ürünün medyan fiyatı ₺397, toplam değerlendirme sayısı 37.644</t>
         </is>
       </c>
       <c r="F320" s="7" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="E321" s="6" t="inlineStr">
         <is>
-          <t>Kategori sonuç sayısı 23.892; ilk 36 ürünün medyan fiyatı 71 TL, toplam değerlendirme sayısı 14.187</t>
+          <t>Kategori sonuç sayısı 23.892; ilk 36 ürünün medyan fiyatı ₺71, toplam değerlendirme sayısı 14.187</t>
         </is>
       </c>
       <c r="F321" s="7" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="E322" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 23.213; ilk 36 ürünün medyan fiyatı 349 TL, toplam değerlendirme sayısı 47.702ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 21717; medyan 338 TL; toplam değerlendirme 67579; 25 marka; VitrA/Artema 0 ürün</t>
+          <t>K; ategori sonuç sayısı 23.213; ilk 36 ürünün medyan fiyatı ₺349, toplam değerlendirme sayısı 47.702ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 21717; medyan ₺338; toplam değerlendirme 67579; 25 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F322" s="7" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="E323" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 3.404; ilk 36 ürünün medyan fiyatı 700 TL, toplam değerlendirme sayısı 9.790ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 36 ürün okundu, kategori toplamı 3392; medyan 689 TL; toplam değerlendirme 9495; 22 marka; VitrA/Artema 0 ürün</t>
+          <t>K; ategori sonuç sayısı 3.404; ilk 36 ürünün medyan fiyatı ₺700, toplam değerlendirme sayısı 9.790ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 36 ürün okundu, kategori toplamı 3392; medyan ₺689; toplam değerlendirme 9495; 22 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F323" s="7" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="E324" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 1.458; ilk 36 ürünün medyan fiyatı 7.500 TL, toplam değerlendirme sayısı 1.053ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 1477; medyan 7.682 TL; toplam değerlendirme 1479; 30 marka; VitrA/Artema 9 ürün</t>
+          <t>K; ategori sonuç sayısı 1.458; ilk 36 ürünün medyan fiyatı ₺7.500, toplam değerlendirme sayısı 1.053ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 1477; medyan ₺7.682; toplam değerlendirme 1479; 30 marka; VitrA/Artema 9 ürün</t>
         </is>
       </c>
       <c r="F324" s="7" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="E325" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 5.806; ilk 36 ürünün medyan fiyatı 2.930 TL, toplam değerlendirme sayısı 3.365ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 5816; medyan 2.690 TL; toplam değerlendirme 4194; 31 marka; VitrA/Artema 1 ürün</t>
+          <t>K; ategori sonuç sayısı 5.806; ilk 36 ürünün medyan fiyatı ₺2.930, toplam değerlendirme sayısı 3.365ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 5816; medyan ₺2.690; toplam değerlendirme 4194; 31 marka; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F325" s="7" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="E326" s="6" t="inlineStr">
         <is>
-          <t>Kategori sonuç sayısı 3.252; ilk 36 ürünün medyan fiyatı 5.349 TL, toplam değerlendirme sayısı 2.005 | 72 ürün okundu, kategori toplamı 3289; medyan 5.092 TL; toplam değerlendirme 2562; 35 marka; VitrA/Artema 0 ürün</t>
+          <t>Kategori sonuç sayısı 3.252; ilk 36 ürünün medyan fiyatı ₺5.349, toplam değerlendirme sayısı 2.005 | 72 ürün okundu, kategori toplamı 3289; medyan ₺5.092; toplam değerlendirme 2562; 35 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F326" s="7" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="E327" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 4.384; ilk 36 ürünün medyan fiyatı 619 TL, toplam değerlendirme sayısı 17.897ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 4273; medyan 640 TL; toplam değerlendirme 20317; 42 marka; VitrA/Artema 6 ürün</t>
+          <t>K; ategori sonuç sayısı 4.384; ilk 36 ürünün medyan fiyatı ₺619, toplam değerlendirme sayısı 17.897ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 4273; medyan ₺640; toplam değerlendirme 20317; 42 marka; VitrA/Artema 6 ürün</t>
         </is>
       </c>
       <c r="F327" s="7" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="E328" s="6" t="inlineStr">
         <is>
-          <t>Kategori sonuç sayısı 260; ilk 36 ürünün medyan fiyatı 630 TL, toplam değerlendirme sayısı 425 | 72 ürün okundu, kategori toplamı 239; medyan 1.505 TL; toplam değerlendirme 465; 34 marka; VitrA/Artema 9 ürün</t>
+          <t>Kategori sonuç sayısı 260; ilk 36 ürünün medyan fiyatı ₺630, toplam değerlendirme sayısı 425 | 72 ürün okundu, kategori toplamı 239; medyan ₺1.505; toplam değerlendirme 465; 34 marka; VitrA/Artema 9 ürün</t>
         </is>
       </c>
       <c r="F328" s="7" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="E329" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 1.982; ilk 36 ürünün medyan fiyatı 6.799 TL, toplam değerlendirme sayısı 4.059ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 1563; medyan 5.821 TL; toplam değerlendirme 5191; 16 marka; VitrA/Artema 0 ürün</t>
+          <t>K; ategori sonuç sayısı 1.982; ilk 36 ürünün medyan fiyatı ₺6.799, toplam değerlendirme sayısı 4.059ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 1563; medyan ₺5.821; toplam değerlendirme 5191; 16 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F329" s="7" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="E330" s="6" t="inlineStr">
         <is>
-          <t>Kategori sonuç sayısı 1.273; ilk 36 ürünün medyan fiyatı 6.325 TL, toplam değerlendirme sayısı 70 | 72 ürün okundu, kategori toplamı 1257; medyan 5.840 TL; toplam değerlendirme 110; 24 marka; VitrA/Artema 1 ürün</t>
+          <t>Kategori sonuç sayısı 1.273; ilk 36 ürünün medyan fiyatı ₺6.325, toplam değerlendirme sayısı 70 | 72 ürün okundu, kategori toplamı 1257; medyan ₺5.840; toplam değerlendirme 110; 24 marka; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F330" s="7" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="E331" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 4.316; ilk 36 ürünün medyan fiyatı 350 TL, toplam değerlendirme sayısı 6.746ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi</t>
+          <t>K; ategori sonuç sayısı 4.316; ilk 36 ürünün medyan fiyatı ₺350, toplam değerlendirme sayısı 6.746ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi</t>
         </is>
       </c>
       <c r="F331" s="7" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="E332" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 6.895; ilk 36 ürünün medyan fiyatı 2.100 TL, toplam değerlendirme sayısı 7.451ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi</t>
+          <t>K; ategori sonuç sayısı 6.895; ilk 36 ürünün medyan fiyatı ₺2.100, toplam değerlendirme sayısı 7.451ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi</t>
         </is>
       </c>
       <c r="F332" s="7" t="inlineStr">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="E333" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 10.080; ilk 36 ürünün medyan fiyatı 1.019 TL, toplam değerlendirme sayısı 12.861ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi</t>
+          <t>K; ategori sonuç sayısı 10.080; ilk 36 ürünün medyan fiyatı ₺1.019, toplam değerlendirme sayısı 12.861ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi</t>
         </is>
       </c>
       <c r="F333" s="7" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="E334" s="6" t="inlineStr">
         <is>
-          <t>Kategori sonuç sayısı 169; ilk 36 ürünün medyan fiyatı 1.498 TL, toplam değerlendirme sayısı 1.553</t>
+          <t>Kategori sonuç sayısı 169; ilk 36 ürünün medyan fiyatı ₺1.498, toplam değerlendirme sayısı 1.553</t>
         </is>
       </c>
       <c r="F334" s="7" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="E335" s="6" t="inlineStr">
         <is>
-          <t>Kategori sonuç sayısı 9.561; ilk 36 ürünün medyan fiyatı 1.100 TL, toplam değerlendirme sayısı 22.452</t>
+          <t>Kategori sonuç sayısı 9.561; ilk 36 ürünün medyan fiyatı ₺1.100, toplam değerlendirme sayısı 22.452</t>
         </is>
       </c>
       <c r="F335" s="7" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="E336" s="6" t="inlineStr">
         <is>
-          <t>Kategori sonuç sayısı 515; ilk 36 ürünün medyan fiyatı 18.420 TL, toplam değerlendirme sayısı 19 | 72 ürün okundu, kategori toplamı 518; medyan 21.400 TL; toplam değerlendirme 23; 21 marka; VitrA/Artema 0 ürün</t>
+          <t>Kategori sonuç sayısı 515; ilk 36 ürünün medyan fiyatı ₺18.420, toplam değerlendirme sayısı 19 | 72 ürün okundu, kategori toplamı 518; medyan ₺21.400; toplam değerlendirme 23; 21 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F336" s="7" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="E337" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 4.149; ilk 36 ürünün medyan fiyatı 281 TL, toplam değerlendirme sayısı 3.228ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi</t>
+          <t>K; ategori sonuç sayısı 4.149; ilk 36 ürünün medyan fiyatı ₺281, toplam değerlendirme sayısı 3.228ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi</t>
         </is>
       </c>
       <c r="F337" s="7" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="E338" s="6" t="inlineStr">
         <is>
-          <t>K; ategori sonuç sayısı 25.973; ilk 36 ürünün medyan fiyatı 6.400 TL, toplam değerlendirme sayısı 8.091ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 12244; medyan 6.924 TL; toplam değerlendirme 12564; 22 marka; VitrA/Artema 1 ürün</t>
+          <t>K; ategori sonuç sayısı 25.973; ilk 36 ürünün medyan fiyatı ₺6.400, toplam değerlendirme sayısı 8.091ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 12244; medyan ₺6.924; toplam değerlendirme 12564; 22 marka; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F338" s="7" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="E340" s="6" t="inlineStr">
         <is>
-          <t>22 ürün okundu, 22 eşleşen; medyan 3.184 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>22 ürün okundu, 22 eşleşen; medyan ₺3.184; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F340" s="7" t="inlineStr">
@@ -13103,7 +13103,7 @@
       </c>
       <c r="E341" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 11.952 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺11.952; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F341" s="7" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="E342" s="6" t="inlineStr">
         <is>
-          <t>15 ürün okundu, 15 eşleşen; medyan 828 TL; satıcı sayısı medyanı 1; VitrA/Artema 2 ürün</t>
+          <t>15 ürün okundu, 15 eşleşen; medyan ₺828; satıcı sayısı medyanı 1; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F342" s="7" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="E343" s="6" t="inlineStr">
         <is>
-          <t>9 ürün okundu, 9 eşleşen; medyan 830 TL; satıcı sayısı medyanı 1; VitrA/Artema 3 ürün</t>
+          <t>9 ürün okundu, 9 eşleşen; medyan ₺830; satıcı sayısı medyanı 1; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F343" s="7" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="E344" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 819 TL; satıcı sayısı medyanı 6.0; VitrA/Artema 22 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺819; satıcı sayısı medyanı 6.0; VitrA/Artema 22 ürün</t>
         </is>
       </c>
       <c r="F344" s="7" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="E345" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 6.750 TL; satıcı sayısı medyanı 26; VitrA/Artema 3 ürün</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺6.750; satıcı sayısı medyanı 26; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F345" s="7" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="E346" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 31 eşleşen; medyan 8.926 TL; satıcı sayısı medyanı 1; VitrA/Artema 5 ürün</t>
+          <t>32 ürün okundu, 31 eşleşen; medyan ₺8.926; satıcı sayısı medyanı 1; VitrA/Artema 5 ürün</t>
         </is>
       </c>
       <c r="F346" s="7" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="E347" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 6.014 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 1 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺6.014; satıcı sayısı medyanı 1.0; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F347" s="7" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="E348" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 101.595 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺101.595; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F348" s="7" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="E349" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 1 eşleşen; medyan 1.519 TL; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
+          <t>5 ürün okundu, 1 eşleşen; medyan ₺1.519; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F349" s="7" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="E350" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 69 TL; satıcı sayısı medyanı 4.0; VitrA/Artema 0 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺69; satıcı sayısı medyanı 4.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F350" s="7" t="inlineStr">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="E351" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 2.999 TL; satıcı sayısı medyanı 29; VitrA/Artema 0 ürün</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺2.999; satıcı sayısı medyanı 29; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F351" s="7" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="E352" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 390 TL; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺390; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F352" s="7" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="E353" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 1.499 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺1.499; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F353" s="7" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="E354" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 571 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺571; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F354" s="7" t="inlineStr">
@@ -13621,7 +13621,7 @@
       </c>
       <c r="E355" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 1.965 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺1.965; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F355" s="7" t="inlineStr">
@@ -13658,7 +13658,7 @@
       </c>
       <c r="E356" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 23.962 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 4 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺23.962; satıcı sayısı medyanı 1.0; VitrA/Artema 4 ürün</t>
         </is>
       </c>
       <c r="F356" s="7" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="E357" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 687 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 4 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺687; satıcı sayısı medyanı 2.0; VitrA/Artema 4 ürün</t>
         </is>
       </c>
       <c r="F357" s="7" t="inlineStr">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="E358" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 5.178 TL; satıcı sayısı medyanı 6; VitrA/Artema 4 ürün</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺5.178; satıcı sayısı medyanı 6; VitrA/Artema 4 ürün</t>
         </is>
       </c>
       <c r="F358" s="7" t="inlineStr">
@@ -13769,7 +13769,7 @@
       </c>
       <c r="E359" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 671 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 7 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺671; satıcı sayısı medyanı 2.0; VitrA/Artema 7 ürün</t>
         </is>
       </c>
       <c r="F359" s="7" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="E360" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 7.015 TL; satıcı sayısı medyanı 6.0; VitrA/Artema 12 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺7.015; satıcı sayısı medyanı 6.0; VitrA/Artema 12 ürün</t>
         </is>
       </c>
       <c r="F360" s="7" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="E361" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; medyan 8.459 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>6 ürün okundu, 6 eşleşen; medyan ₺8.459; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F361" s="7" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="E362" s="6" t="inlineStr">
         <is>
-          <t>11 ürün okundu, 11 eşleşen; medyan 7.500 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
+          <t>11 ürün okundu, 11 eşleşen; medyan ₺7.500; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F362" s="7" t="inlineStr">
@@ -13917,7 +13917,7 @@
       </c>
       <c r="E363" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 2.883 TL; satıcı sayısı medyanı 6.0; VitrA/Artema 27 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺2.883; satıcı sayısı medyanı 6.0; VitrA/Artema 27 ürün</t>
         </is>
       </c>
       <c r="F363" s="7" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="E364" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 2.275 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺2.275; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F364" s="7" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="E365" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 32.999 TL; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺32.999; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F365" s="7" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="E366" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 1.628 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺1.628; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F366" s="7" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="E367" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 59.878 TL; satıcı sayısı medyanı 3.5; VitrA/Artema 4 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺59.878; satıcı sayısı medyanı 3.5; VitrA/Artema 4 ürün</t>
         </is>
       </c>
       <c r="F367" s="7" t="inlineStr">
@@ -14102,7 +14102,7 @@
       </c>
       <c r="E368" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 439 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺439; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F368" s="7" t="inlineStr">
@@ -14139,7 +14139,7 @@
       </c>
       <c r="E369" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; medyan 654 TL; satıcı sayısı medyanı 8.0; VitrA/Artema 0 ürün</t>
+          <t>6 ürün okundu, 6 eşleşen; medyan ₺654; satıcı sayısı medyanı 8.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F369" s="7" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="E370" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 1.155 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺1.155; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F370" s="7" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="E371" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 1 eşleşen; medyan 1.979 TL; satıcı sayısı medyanı 2; VitrA/Artema 1 ürün</t>
+          <t>5 ürün okundu, 1 eşleşen; medyan ₺1.979; satıcı sayısı medyanı 2; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F371" s="7" t="inlineStr">
@@ -14250,7 +14250,7 @@
       </c>
       <c r="E372" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 422 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 1 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺422; satıcı sayısı medyanı 1.0; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F372" s="7" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="E373" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 11.861 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 9 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺11.861; satıcı sayısı medyanı 1.0; VitrA/Artema 9 ürün</t>
         </is>
       </c>
       <c r="F373" s="7" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="E374" s="6" t="inlineStr">
         <is>
-          <t>7 ürün okundu, 7 eşleşen; medyan 1.500 TL; satıcı sayısı medyanı 2; VitrA/Artema 3 ürün</t>
+          <t>7 ürün okundu, 7 eşleşen; medyan ₺1.500; satıcı sayısı medyanı 2; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F374" s="7" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="E375" s="6" t="inlineStr">
         <is>
-          <t>11 ürün okundu, 11 eşleşen; medyan 3.229 TL; satıcı sayısı medyanı 3; VitrA/Artema 0 ürün</t>
+          <t>11 ürün okundu, 11 eşleşen; medyan ₺3.229; satıcı sayısı medyanı 3; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F375" s="7" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="E376" s="6" t="inlineStr">
         <is>
-          <t>31 ürün okundu, 31 eşleşen; medyan 10.656 TL; satıcı sayısı medyanı 1; VitrA/Artema 5 ürün</t>
+          <t>31 ürün okundu, 31 eşleşen; medyan ₺10.656; satıcı sayısı medyanı 1; VitrA/Artema 5 ürün</t>
         </is>
       </c>
       <c r="F376" s="7" t="inlineStr">
@@ -14435,7 +14435,7 @@
       </c>
       <c r="E377" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 3.695 TL; satıcı sayısı medyanı 4.5; VitrA/Artema 25 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺3.695; satıcı sayısı medyanı 4.5; VitrA/Artema 25 ürün</t>
         </is>
       </c>
       <c r="F377" s="7" t="inlineStr">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="E378" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 3.293 TL; satıcı sayısı medyanı 5.5; VitrA/Artema 13 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺3.293; satıcı sayısı medyanı 5.5; VitrA/Artema 13 ürün</t>
         </is>
       </c>
       <c r="F378" s="7" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="E379" s="6" t="inlineStr">
         <is>
-          <t>7 ürün okundu, 7 eşleşen; medyan 10.482 TL; satıcı sayısı medyanı 3; VitrA/Artema 6 ürün</t>
+          <t>7 ürün okundu, 7 eşleşen; medyan ₺10.482; satıcı sayısı medyanı 3; VitrA/Artema 6 ürün</t>
         </is>
       </c>
       <c r="F379" s="7" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="E380" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 17.120 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺17.120; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F380" s="7" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="E381" s="6" t="inlineStr">
         <is>
-          <t>7 ürün okundu, 7 eşleşen; medyan 3.000 TL; satıcı sayısı medyanı 1; VitrA/Artema 1 ürün</t>
+          <t>7 ürün okundu, 7 eşleşen; medyan ₺3.000; satıcı sayısı medyanı 1; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F381" s="7" t="inlineStr">
@@ -14620,7 +14620,7 @@
       </c>
       <c r="E382" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 4.350 TL; satıcı sayısı medyanı 4.0; VitrA/Artema 6 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺4.350; satıcı sayısı medyanı 4.0; VitrA/Artema 6 ürün</t>
         </is>
       </c>
       <c r="F382" s="7" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="E383" s="6" t="inlineStr">
         <is>
-          <t>11 ürün okundu, 11 eşleşen; medyan 5.500 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
+          <t>11 ürün okundu, 11 eşleşen; medyan ₺5.500; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F383" s="7" t="inlineStr">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="E384" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 896; medyan 1.867 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 896; medyan ₺1.867; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F384" s="7" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="E385" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 551 TL; satıcı sayısı medyanı 7.5; VitrA/Artema 10 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺551; satıcı sayısı medyanı 7.5; VitrA/Artema 10 ürün</t>
         </is>
       </c>
       <c r="F385" s="7" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="E386" s="6" t="inlineStr">
         <is>
-          <t>ilk 32 ürünün fiyatı en düşük 389, medyan 2.111, en yüksek 15.200 TL; VitrA ilk 32 ürünün 1'inde; markalar: Creavit:5, Nuun:4, Özlider:4, Lider:4, Altıntepe:2 | 64 ürün okundu, kategori toplamı 594; medyan 4.899 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 7 ürün; marka filtresi ilk 15</t>
+          <t>ilk 32 ürünün fiyatı en düşük 389, medyan 2.111, en yüksek ₺15.200; VitrA ilk 32 ürünün 1'inde; markalar: Creavit:5, Nuun:4, Özlider:4, Lider:4, Altıntepe:2 | 64 ürün okundu, kategori toplamı 594; medyan ₺4.899; satıcı sayısı medyanı 1.0; VitrA/Artema 7 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F386" s="7" t="inlineStr">
@@ -14805,7 +14805,7 @@
       </c>
       <c r="E387" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, kategori toplamı 6; medyan 6.404 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>6 ürün okundu, kategori toplamı 6; medyan ₺6.404; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F387" s="7" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="E388" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 6.105 ürün; ilk 32 ürünün fiyatı en düşük 777, medyan 3.995, en yüksek 9.562 TL; VitrA ilk 32 ürünün 10'inde; markalar: Artema:10, E.C.A.:8, Creavit:4, Grohe:3, GPD:3 | 64 ürün okundu, kategori toplamı 6103; medyan 3.934 TL; satıcı sayısı medyanı 26.5; VitrA/Artema 18 ürün; marka filtresi ilk 15</t>
+          <t>Kategoride 6.105 ürün; ilk 32 ürünün fiyatı en düşük 777, medyan 3.995, en yüksek ₺9.562; VitrA ilk 32 ürünün 10'unda; markalar: Artema:10, E.C.A.:8, Creavit:4, Grohe:3, GPD:3 | 64 ürün okundu, kategori toplamı 6103; medyan ₺3.934; satıcı sayısı medyanı 26.5; VitrA/Artema 18 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F388" s="7" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="E389" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 1246; medyan 4.000 TL; satıcı sayısı medyanı 6.0; VitrA/Artema 26 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 1246; medyan ₺4.000; satıcı sayısı medyanı 6.0; VitrA/Artema 26 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F389" s="7" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="E390" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 1.027 TL; satıcı sayısı medyanı 6.0; VitrA/Artema 3 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺1.027; satıcı sayısı medyanı 6.0; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F390" s="7" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="E391" s="6" t="inlineStr">
         <is>
-          <t>ilk 32 ürünün fiyatı en düşük 650, medyan 4.680, en yüksek 18.189 TL; VitrA ilk 32 ürünün 1'inde; markalar: Karen:9, Teta:5, Kenzlife:3, Bofigo:2, Orka:2 | 64 ürün okundu, kategori toplamı 7777; medyan 4.900 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 1 ürün; marka filtresi ilk 15</t>
+          <t>ilk 32 ürünün fiyatı en düşük 650, medyan 4.680, en yüksek ₺18.189; VitrA ilk 32 ürünün 1'inde; markalar: Karen:9, Teta:5, Kenzlife:3, Bofigo:2, Orka:2 | 64 ürün okundu, kategori toplamı 7777; medyan ₺4.900; satıcı sayısı medyanı 3.0; VitrA/Artema 1 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F391" s="7" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="E392" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 7.200 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 1 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺7.200; satıcı sayısı medyanı 3.0; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F392" s="7" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="E393" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 1459; medyan 6.966 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 1459; medyan ₺6.966; satıcı sayısı medyanı 3.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F393" s="7" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="E394" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 22030; medyan 634 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 22030; medyan ₺634; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F394" s="7" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="E395" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 1560; medyan 826 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 5 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 1560; medyan ₺826; satıcı sayısı medyanı 2.0; VitrA/Artema 5 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F395" s="7" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="E396" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 1246; medyan 1.152 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 1246; medyan ₺1.152; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F396" s="7" t="inlineStr">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="E397" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 6.025 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 8 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺6.025; satıcı sayısı medyanı 2.0; VitrA/Artema 8 ürün</t>
         </is>
       </c>
       <c r="F397" s="7" t="inlineStr">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="E398" s="6" t="inlineStr">
         <is>
-          <t>49 ürün okundu, kategori toplamı 49; medyan 10.000 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>49 ürün okundu, kategori toplamı 49; medyan ₺10.000; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F398" s="7" t="inlineStr">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="E399" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 261; medyan 3.299 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 261; medyan ₺3.299; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F399" s="7" t="inlineStr">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="E400" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 10123; medyan 2.250 TL; satıcı sayısı medyanı 8.0; VitrA/Artema 17 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 10123; medyan ₺2.250; satıcı sayısı medyanı 8.0; VitrA/Artema 17 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F400" s="7" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="E401" s="6" t="inlineStr">
         <is>
-          <t>ilk 32 ürünün fiyatı en düşük 693, medyan 3.316, en yüksek 15.999 TL; VitrA ilk 32 ürünün 7'inde; markalar: Artema:7, E.C.A.:6, Creavit:3, Tema:3, GPD:3 | 64 ürün okundu, kategori toplamı 9709; medyan 3.505 TL; satıcı sayısı medyanı 12.5; VitrA/Artema 18 ürün; marka filtresi ilk 15</t>
+          <t>ilk 32 ürünün fiyatı en düşük 693, medyan 3.316, en yüksek ₺15.999; VitrA ilk 32 ürünün 7'sinde; markalar: Artema:7, E.C.A.:6, Creavit:3, Tema:3, GPD:3 | 64 ürün okundu, kategori toplamı 9709; medyan ₺3.505; satıcı sayısı medyanı 12.5; VitrA/Artema 18 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F401" s="7" t="inlineStr">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="E402" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 1366; medyan 7.104 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 1 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 1366; medyan ₺7.104; satıcı sayısı medyanı 1.0; VitrA/Artema 1 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F402" s="7" t="inlineStr">
@@ -15397,7 +15397,7 @@
       </c>
       <c r="E403" s="6" t="inlineStr">
         <is>
-          <t>ilk 32 ürünün fiyatı en düşük 4.658, medyan 7.066, en yüksek 28.461 TL; VitrA ilk 32 ürünün 0'inde; markalar: Durul:12, Monaqua:5, Teknesiz:3, Giray:2 | 64 ürün okundu, kategori toplamı 28232; medyan 6.901 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>ilk 32 ürünün fiyatı en düşük 4.658, medyan 7.066, en yüksek ₺28.461; VitrA ilk 32 ürünün 0'ında; markalar: Durul:12, Monaqua:5, Teknesiz:3, Giray:2 | 64 ürün okundu, kategori toplamı 28232; medyan ₺6.901; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F403" s="7" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="E404" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 3782; medyan 8.463 TL; satıcı sayısı medyanı 18.5; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 3782; medyan ₺8.463; satıcı sayısı medyanı 18.5; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F404" s="7" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="E405" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 3010; medyan 798 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 16 ürün; marka filtresi ilk 15 | 32 ürün okundu, 32 eşleşen; medyan 1.177 TL; satıcı sayısı medyanı 5.5; VitrA/Artema 11 ürün</t>
+          <t>64 ürün okundu, kategori toplamı 3010; medyan ₺798; satıcı sayısı medyanı 2.0; VitrA/Artema 16 ürün; marka filtresi ilk 15 | 32 ürün okundu, 32 eşleşen; medyan ₺1.177; satıcı sayısı medyanı 5.5; VitrA/Artema 11 ürün</t>
         </is>
       </c>
       <c r="F405" s="7" t="inlineStr">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="E406" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 9767; medyan 2.561 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 9767; medyan ₺2.561; satıcı sayısı medyanı 3.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F406" s="7" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="E407" s="6" t="inlineStr">
         <is>
-          <t>ilk 32 ürünün fiyatı en düşük 370, medyan 1.012, en yüksek 15.902 TL; VitrA ilk 32 ürünün 7'inde; markalar: VitrA:7, Nkp:7, Visam:6, Serel:3, Kale:3 | 64 ürün okundu, kategori toplamı 3437; medyan 1.009 TL; satıcı sayısı medyanı 7.0; VitrA/Artema 11 ürün; marka filtresi ilk 15</t>
+          <t>ilk 32 ürünün fiyatı en düşük 370, medyan 1.012, en yüksek ₺15.902; VitrA ilk 32 ürünün 7'sinde; markalar: VitrA:7, Nkp:7, Visam:6, Serel:3, Kale:3 | 64 ürün okundu, kategori toplamı 3437; medyan ₺1.009; satıcı sayısı medyanı 7.0; VitrA/Artema 11 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F407" s="7" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="E408" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 1.747 ürün; ilk 32 ürünün fiyatı en düşük 3.505, medyan 7.308, en yüksek 13.999 TL; VitrA ilk 32 ürünün 6'inde; markalar: Creavit:11, VitrA:5, Bocchi:5, Turkuaz:4, Seramiksan:1 | 63 ürün okundu, kategori toplamı 1736; medyan 7.999 TL; satıcı sayısı medyanı 3; VitrA/Artema 11 ürün; marka filtresi ilk 15</t>
+          <t>Kategoride 1.747 ürün; ilk 32 ürünün fiyatı en düşük 3.505, medyan 7.308, en yüksek ₺13.999; VitrA ilk 32 ürünün 6'sında; markalar: Creavit:11, VitrA:5, Bocchi:5, Turkuaz:4, Seramiksan:1 | 63 ürün okundu, kategori toplamı 1736; medyan ₺7.999; satıcı sayısı medyanı 3; VitrA/Artema 11 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F408" s="7" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="E409" s="6" t="inlineStr">
         <is>
-          <t>22 ürün okundu, kategori toplamı 22; medyan 97.400 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 5 ürün; marka filtresi ilk 15</t>
+          <t>22 ürün okundu, kategori toplamı 22; medyan ₺97.400; satıcı sayısı medyanı 1.0; VitrA/Artema 5 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F409" s="7" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="E410" s="6" t="inlineStr">
         <is>
-          <t>60 ürün okundu, kategori toplamı 60; medyan 11.713 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 13 ürün; marka filtresi ilk 15</t>
+          <t>60 ürün okundu, kategori toplamı 60; medyan ₺11.713; satıcı sayısı medyanı 2.0; VitrA/Artema 13 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F410" s="7" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="E411" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 1382; medyan 7.292 TL; satıcı sayısı medyanı 4.5; VitrA/Artema 17 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 1382; medyan ₺7.292; satıcı sayısı medyanı 4.5; VitrA/Artema 17 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F411" s="7" t="inlineStr">
@@ -15730,7 +15730,7 @@
       </c>
       <c r="E412" s="6" t="inlineStr">
         <is>
-          <t>10 ürün okundu, 10 eşleşen; medyan 15.564 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 0 ürün</t>
+          <t>10 ürün okundu, 10 eşleşen; medyan ₺15.564; satıcı sayısı medyanı 3.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F412" s="7" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="E413" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 130; medyan 12.860 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 8 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 130; medyan ₺12.860; satıcı sayısı medyanı 1.0; VitrA/Artema 8 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F413" s="7" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="E414" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 265; medyan 20.681 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 265; medyan ₺20.681; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F414" s="7" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="E415" s="6" t="inlineStr">
         <is>
-          <t>ilk 32 ürünün fiyatı en düşük 557, medyan 3.725, en yüksek 8.075 TL; VitrA ilk 32 ürünün 13'inde; markalar: Artema:12, E.C.A.:11, Grohe:3, GPD:2, Creavit:1 | 64 ürün okundu, kategori toplamı 9865; medyan 3.715 TL; satıcı sayısı medyanı 26.0; VitrA/Artema 27 ürün; marka filtresi ilk 15</t>
+          <t>ilk 32 ürünün fiyatı en düşük 557, medyan 3.725, en yüksek ₺8.075; VitrA ilk 32 ürünün 13'ünde; markalar: Artema:12, E.C.A.:11, Grohe:3, GPD:2, Creavit:1 | 64 ürün okundu, kategori toplamı 9865; medyan ₺3.715; satıcı sayısı medyanı 26.0; VitrA/Artema 27 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F415" s="7" t="inlineStr">
@@ -15878,7 +15878,7 @@
       </c>
       <c r="E416" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 7.703 TL; satıcı sayısı medyanı 7.0; VitrA/Artema 2 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺7.703; satıcı sayısı medyanı 7.0; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F416" s="7" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="E417" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 1137; medyan 418 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 8 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 1137; medyan ₺418; satıcı sayısı medyanı 2.0; VitrA/Artema 8 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F417" s="7" t="inlineStr">
@@ -15952,7 +15952,7 @@
       </c>
       <c r="E418" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 4.943 ürün; ilk 32 ürünün fiyatı en düşük 1.334, medyan 5.190, en yüksek 59.999 TL; VitrA ilk 32 ürünün 3'inde; markalar: Turkuaz:11, İsvea:8, Bocchi:7, VitrA:3, Karen:2 | 64 ürün okundu, kategori toplamı 4942; medyan 3.811 TL; satıcı sayısı medyanı 4.0; VitrA/Artema 6 ürün; marka filtresi ilk 15</t>
+          <t>Kategoride 4.943 ürün; ilk 32 ürünün fiyatı en düşük 1.334, medyan 5.190, en yüksek ₺59.999; VitrA ilk 32 ürünün 3'ünde; markalar: Turkuaz:11, İsvea:8, Bocchi:7, VitrA:3, Karen:2 | 64 ürün okundu, kategori toplamı 4942; medyan ₺3.811; satıcı sayısı medyanı 4.0; VitrA/Artema 6 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F418" s="7" t="inlineStr">
@@ -15989,7 +15989,7 @@
       </c>
       <c r="E419" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 1722; medyan 3.911 TL; satıcı sayısı medyanı 4.0; VitrA/Artema 9 ürün; marka filtresi ilk 15 | 32 ürün okundu, 32 eşleşen; medyan 4.396 TL; satıcı sayısı medyanı 4.0; VitrA/Artema 5 ürün</t>
+          <t>64 ürün okundu, kategori toplamı 1722; medyan ₺3.911; satıcı sayısı medyanı 4.0; VitrA/Artema 9 ürün; marka filtresi ilk 15 | 32 ürün okundu, 32 eşleşen; medyan ₺4.396; satıcı sayısı medyanı 4.0; VitrA/Artema 5 ürün</t>
         </is>
       </c>
       <c r="F419" s="7" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="E420" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 3.253 TL; satıcı sayısı medyanı 4.0; VitrA/Artema 1 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺3.253; satıcı sayısı medyanı 4.0; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F420" s="7" t="inlineStr">
@@ -16063,7 +16063,7 @@
       </c>
       <c r="E421" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 100; medyan 35.999 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün; marka filtresi ilk 15 | 32 ürün okundu, 32 eşleşen; medyan 30.888 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 0 ürün</t>
+          <t>64 ürün okundu, kategori toplamı 100; medyan ₺35.999; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün; marka filtresi ilk 15 | 32 ürün okundu, 32 eşleşen; medyan ₺30.888; satıcı sayısı medyanı 3.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F421" s="7" t="inlineStr">
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E422" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 167; medyan 3.784 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 13 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 167; medyan ₺3.784; satıcı sayısı medyanı 3.0; VitrA/Artema 13 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F422" s="7" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="E423" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 593 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺593; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F423" s="7" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="E424" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 4.011 ürün; ilk 32 ürünün fiyatı en düşük 270, medyan 825, en yüksek 2.435 TL; VitrA ilk 32 ürünün 9'inde; markalar: GPD:8, E.C.A.:7, VitrA:5, Artema:4, Fause:3 | 64 ürün okundu, kategori toplamı 4012; medyan 819 TL; satıcı sayısı medyanı 18.5; VitrA/Artema 23 ürün; marka filtresi ilk 15</t>
+          <t>Kategoride 4.011 ürün; ilk 32 ürünün fiyatı en düşük 270, medyan 825, en yüksek ₺2.435; VitrA ilk 32 ürünün 9'unda; markalar: GPD:8, E.C.A.:7, VitrA:5, Artema:4, Fause:3 | 64 ürün okundu, kategori toplamı 4012; medyan ₺819; satıcı sayısı medyanı 18.5; VitrA/Artema 23 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F424" s="7" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="E425" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 837; medyan 776 TL; satıcı sayısı medyanı 9.0; VitrA/Artema 15 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 837; medyan ₺776; satıcı sayısı medyanı 9.0; VitrA/Artema 15 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F425" s="7" t="inlineStr">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="E426" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 1057; medyan 690 TL; satıcı sayısı medyanı 8.5; VitrA/Artema 13 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 1057; medyan ₺690; satıcı sayısı medyanı 8.5; VitrA/Artema 13 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F426" s="7" t="inlineStr">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="E427" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 11702; medyan 4.589 TL; satıcı sayısı medyanı 29.0; VitrA/Artema 13 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 11702; medyan ₺4.589; satıcı sayısı medyanı 29.0; VitrA/Artema 13 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F427" s="7" t="inlineStr">
@@ -16322,7 +16322,7 @@
       </c>
       <c r="E428" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 96; medyan 21.880 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 10 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 96; medyan ₺21.880; satıcı sayısı medyanı 1.0; VitrA/Artema 10 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F428" s="7" t="inlineStr">
@@ -16359,7 +16359,7 @@
       </c>
       <c r="E429" s="6" t="inlineStr">
         <is>
-          <t>ilk 32 ürünün fiyatı en düşük 127, medyan 789, en yüksek 6.406 TL; VitrA ilk 32 ürünün 11'inde; markalar: VitrA:10, Visam:5, Serel:5, Creavit:3, Siamp:2 | 64 ürün okundu, kategori toplamı 2884; medyan 787 TL; satıcı sayısı medyanı 6.0; VitrA/Artema 18 ürün; marka filtresi ilk 15</t>
+          <t>ilk 32 ürünün fiyatı en düşük 127, medyan 789, en yüksek ₺6.406; VitrA ilk 32 ürünün 11'inde; markalar: VitrA:10, Visam:5, Serel:5, Creavit:3, Siamp:2 | 64 ürün okundu, kategori toplamı 2884; medyan ₺787; satıcı sayısı medyanı 6.0; VitrA/Artema 18 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F429" s="7" t="inlineStr">
@@ -16373,7 +16373,7 @@
         </is>
       </c>
     </row>
-    <row r="430" ht="70.5" customHeight="1">
+    <row r="430" ht="57" customHeight="1">
       <c r="A430" s="5" t="inlineStr">
         <is>
           <t>https://www.akakce.com/rezervuar.html</t>
@@ -16396,7 +16396,7 @@
       </c>
       <c r="E430" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 347 ürün; ilk 32 ürünün fiyatı en düşük 499, medyan 4.250, en yüksek 9.516 TL; VitrA ilk 32 ürünün 9'inde; markalar: VitrA:8, Visam:6, Geberit:4, Serel:3, Creavit:3 | 64 ürün okundu, kategori toplamı 345; medyan 4.662 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 18 ürün; marka filtresi ilk 15</t>
+          <t>Kategoride 347 ürün; ilk 32 ürünün fiyatı en düşük 499, medyan 4.250, en yüksek ₺9.516; VitrA ilk 32 ürünün 9'unda; markalar: VitrA:8, Visam:6, Geberit:4, Serel:3, Creavit:3 | 64 ürün okundu, kategori toplamı 345; medyan ₺4.662; satıcı sayısı medyanı 2.0; VitrA/Artema 18 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F430" s="7" t="inlineStr">
@@ -16433,7 +16433,7 @@
       </c>
       <c r="E431" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 516; medyan 9.251 TL; satıcı sayısı medyanı 14.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 516; medyan ₺9.251; satıcı sayısı medyanı 14.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F431" s="7" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="E432" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 2061; medyan 6.999 TL; satıcı sayısı medyanı 5.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 2061; medyan ₺6.999; satıcı sayısı medyanı 5.0; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F432" s="7" t="inlineStr">
@@ -16507,7 +16507,7 @@
       </c>
       <c r="E433" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 168; medyan 12.554 TL; satıcı sayısı medyanı 11.5; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
+          <t>64 ürün okundu, kategori toplamı 168; medyan ₺12.554; satıcı sayısı medyanı 11.5; VitrA/Artema 0 ürün; marka filtresi ilk 15</t>
         </is>
       </c>
       <c r="F433" s="7" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="E434" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 770 TL; satıcı sayısı medyanı 3.5; VitrA/Artema 10 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺770; satıcı sayısı medyanı 3.5; VitrA/Artema 10 ürün</t>
         </is>
       </c>
       <c r="F434" s="7" t="inlineStr">
@@ -16581,7 +16581,7 @@
       </c>
       <c r="E435" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 1.733 TL; satıcı sayısı medyanı 7.5; VitrA/Artema 9 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺1.733; satıcı sayısı medyanı 7.5; VitrA/Artema 9 ürün</t>
         </is>
       </c>
       <c r="F435" s="7" t="inlineStr">
@@ -16655,7 +16655,7 @@
       </c>
       <c r="E437" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 12 eşleşen; medyan 3.293 TL; VitrA/Artema 1 ürün; marka dağılımı: Turkuaz Seramik:8, Diğer:2, VitrA:1, Creavit:1</t>
+          <t>24 ürün okundu, 12 eşleşen; medyan ₺3.293; VitrA/Artema 1 ürün; marka dağılımı: Turkuaz Seramik:8, Diğer:2, VitrA:1, Creavit:1</t>
         </is>
       </c>
       <c r="F437" s="7" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="E438" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 819 TL; VitrA/Artema 0 ürün; marka dağılımı: NKP:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺819; VitrA/Artema 0 ürün; marka dağılımı: NKP:1</t>
         </is>
       </c>
       <c r="F438" s="7" t="inlineStr">
@@ -16729,7 +16729,7 @@
       </c>
       <c r="E439" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 5 eşleşen; medyan 3.355 TL; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, NKP:1, Turkuaz Seramik:1</t>
+          <t>24 ürün okundu, 5 eşleşen; medyan ₺3.355; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, NKP:1, Turkuaz Seramik:1</t>
         </is>
       </c>
       <c r="F439" s="7" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="E440" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 5 eşleşen; medyan 2.905 TL; VitrA/Artema 1 ürün; marka dağılımı: NKP:2, Turkuaz Seramik:2, VitrA:1</t>
+          <t>24 ürün okundu, 5 eşleşen; medyan ₺2.905; VitrA/Artema 1 ürün; marka dağılımı: NKP:2, Turkuaz Seramik:2, VitrA:1</t>
         </is>
       </c>
       <c r="F440" s="7" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="E441" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 21 eşleşen; medyan 4.937 TL; VitrA/Artema 15 ürün; marka dağılımı: VitrA:10, Artema:5, GMS:3, Creavit:2, Valtemo:1</t>
+          <t>24 ürün okundu, 21 eşleşen; medyan ₺4.937; VitrA/Artema 15 ürün; marka dağılımı: VitrA:10, Artema:5, GMS:3, Creavit:2, Valtemo:1</t>
         </is>
       </c>
       <c r="F441" s="7" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="E442" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 8 eşleşen; medyan 1.280 TL; VitrA/Artema 3 ürün; marka dağılımı: Monavit:3, VitrA:3, NKP:1, Turkuaz Seramik:1</t>
+          <t>24 ürün okundu, 8 eşleşen; medyan ₺1.280; VitrA/Artema 3 ürün; marka dağılımı: Monavit:3, VitrA:3, NKP:1, Turkuaz Seramik:1</t>
         </is>
       </c>
       <c r="F442" s="7" t="inlineStr">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="E443" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 4 eşleşen; medyan 5.083 TL; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:2, NKP:2</t>
+          <t>24 ürün okundu, 4 eşleşen; medyan ₺5.083; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:2, NKP:2</t>
         </is>
       </c>
       <c r="F443" s="7" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="E444" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 18 eşleşen; medyan 14.425 TL; VitrA/Artema 11 ürün; marka dağılımı: VitrA:11, Turkuaz Seramik:4, NKP:3</t>
+          <t>24 ürün okundu, 18 eşleşen; medyan ₺14.425; VitrA/Artema 11 ürün; marka dağılımı: VitrA:11, Turkuaz Seramik:4, NKP:3</t>
         </is>
       </c>
       <c r="F444" s="7" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="E445" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 1 eşleşen; medyan 950 TL; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:1</t>
+          <t>24 ürün okundu, 1 eşleşen; medyan ₺950; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:1</t>
         </is>
       </c>
       <c r="F445" s="7" t="inlineStr">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="E446" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 21 eşleşen; medyan 7.989 TL; VitrA/Artema 0 ürün; marka dağılımı: Orka:14, Turkuaz Seramik:7</t>
+          <t>24 ürün okundu, 21 eşleşen; medyan ₺7.989; VitrA/Artema 0 ürün; marka dağılımı: Orka:14, Turkuaz Seramik:7</t>
         </is>
       </c>
       <c r="F446" s="7" t="inlineStr">
@@ -17025,7 +17025,7 @@
       </c>
       <c r="E447" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 16.213 TL; VitrA/Artema 0 ürün; marka dağılımı: Orka:24</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺16.213; VitrA/Artema 0 ürün; marka dağılımı: Orka:24</t>
         </is>
       </c>
       <c r="F447" s="7" t="inlineStr">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="E448" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; medyan 418 TL; VitrA/Artema 0 ürün; marka dağılımı: Monavit:5, GMS:1</t>
+          <t>6 ürün okundu, 6 eşleşen; medyan ₺418; VitrA/Artema 0 ürün; marka dağılımı: Monavit:5, GMS:1</t>
         </is>
       </c>
       <c r="F448" s="7" t="inlineStr">
@@ -17173,7 +17173,7 @@
       </c>
       <c r="E451" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 3 eşleşen; medyan 4.992 TL; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:3</t>
+          <t>24 ürün okundu, 3 eşleşen; medyan ₺4.992; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:3</t>
         </is>
       </c>
       <c r="F451" s="7" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="E454" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 30.432 TL; VitrA/Artema 1 ürün; marka dağılımı: Orka:14, Denko:9, VitrA:1</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺30.432; VitrA/Artema 1 ürün; marka dağılımı: Orka:14, Denko:9, VitrA:1</t>
         </is>
       </c>
       <c r="F454" s="7" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="E455" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 19 eşleşen; medyan 12.040 TL; VitrA/Artema 10 ürün; marka dağılımı: VitrA:9, Turkuaz Seramik:4, GMS:3, Artema:1, Valtemo:1, NKP:1</t>
+          <t>24 ürün okundu, 19 eşleşen; medyan ₺12.040; VitrA/Artema 10 ürün; marka dağılımı: VitrA:9, Turkuaz Seramik:4, GMS:3, Artema:1, Valtemo:1, NKP:1</t>
         </is>
       </c>
       <c r="F455" s="7" t="inlineStr">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="E456" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 3 eşleşen; medyan 303 TL; VitrA/Artema 1 ürün; marka dağılımı: Monavit:2, VitrA:1</t>
+          <t>24 ürün okundu, 3 eşleşen; medyan ₺303; VitrA/Artema 1 ürün; marka dağılımı: Monavit:2, VitrA:1</t>
         </is>
       </c>
       <c r="F456" s="7" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="E458" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 7 eşleşen; medyan 10.502 TL; VitrA/Artema 5 ürün; marka dağılımı: Artema:3, VitrA:2, GMS:2</t>
+          <t>24 ürün okundu, 7 eşleşen; medyan ₺10.502; VitrA/Artema 5 ürün; marka dağılımı: Artema:3, VitrA:2, GMS:2</t>
         </is>
       </c>
       <c r="F458" s="7" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="E460" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 3 eşleşen; medyan 1.386 TL; VitrA/Artema 2 ürün; marka dağılımı: VitrA:2, Monavit:1</t>
+          <t>6 ürün okundu, 3 eşleşen; medyan ₺1.386; VitrA/Artema 2 ürün; marka dağılımı: VitrA:2, Monavit:1</t>
         </is>
       </c>
       <c r="F460" s="7" t="inlineStr">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="E461" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 7 eşleşen; medyan 3.650 TL; VitrA/Artema 7 ürün; marka dağılımı: VitrA:4, Artema:3</t>
+          <t>24 ürün okundu, 7 eşleşen; medyan ₺3.650; VitrA/Artema 7 ürün; marka dağılımı: VitrA:4, Artema:3</t>
         </is>
       </c>
       <c r="F461" s="7" t="inlineStr">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="E462" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 15 eşleşen; medyan 1.375 TL; VitrA/Artema 2 ürün; marka dağılımı: Sukar:13, VitrA:2</t>
+          <t>24 ürün okundu, 15 eşleşen; medyan ₺1.375; VitrA/Artema 2 ürün; marka dağılımı: Sukar:13, VitrA:2</t>
         </is>
       </c>
       <c r="F462" s="7" t="inlineStr">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="E463" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 6 eşleşen; medyan 6.131 TL; VitrA/Artema 3 ürün; marka dağılımı: GMS:3, Artema:2, VitrA:1</t>
+          <t>24 ürün okundu, 6 eşleşen; medyan ₺6.131; VitrA/Artema 3 ürün; marka dağılımı: GMS:3, Artema:2, VitrA:1</t>
         </is>
       </c>
       <c r="F463" s="7" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="E464" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 6 eşleşen; medyan 4.011 TL; VitrA/Artema 4 ürün; marka dağılımı: VitrA:4, Turkuaz Seramik:1, NKP:1</t>
+          <t>24 ürün okundu, 6 eşleşen; medyan ₺4.011; VitrA/Artema 4 ürün; marka dağılımı: VitrA:4, Turkuaz Seramik:1, NKP:1</t>
         </is>
       </c>
       <c r="F464" s="7" t="inlineStr">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="E465" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 21 eşleşen; medyan 6.606 TL; VitrA/Artema 8 ürün; marka dağılımı: NKP:8, VitrA:8, Turkuaz Seramik:5</t>
+          <t>24 ürün okundu, 21 eşleşen; medyan ₺6.606; VitrA/Artema 8 ürün; marka dağılımı: NKP:8, VitrA:8, Turkuaz Seramik:5</t>
         </is>
       </c>
       <c r="F465" s="7" t="inlineStr">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="E466" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 16 eşleşen; medyan 2.571 TL; VitrA/Artema 14 ürün; marka dağılımı: Artema:9, VitrA:5, GMS:2</t>
+          <t>24 ürün okundu, 16 eşleşen; medyan ₺2.571; VitrA/Artema 14 ürün; marka dağılımı: Artema:9, VitrA:5, GMS:2</t>
         </is>
       </c>
       <c r="F466" s="7" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="E467" s="6" t="inlineStr">
         <is>
-          <t>7 ürün okundu, 6 eşleşen; medyan 418 TL; VitrA/Artema 0 ürün; marka dağılımı: Monavit:5, Turkuaz Seramik:1</t>
+          <t>7 ürün okundu, 6 eşleşen; medyan ₺418; VitrA/Artema 0 ürün; marka dağılımı: Monavit:5, Turkuaz Seramik:1</t>
         </is>
       </c>
       <c r="F467" s="7" t="inlineStr">
@@ -17802,7 +17802,7 @@
       </c>
       <c r="E468" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 17 eşleşen; medyan 7.468 TL; VitrA/Artema 0 ürün; marka dağılımı: Denko:10, Turkuaz Seramik:6, Creavit:1</t>
+          <t>24 ürün okundu, 17 eşleşen; medyan ₺7.468; VitrA/Artema 0 ürün; marka dağılımı: Denko:10, Turkuaz Seramik:6, Creavit:1</t>
         </is>
       </c>
       <c r="F468" s="7" t="inlineStr">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="E469" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 17 eşleşen; medyan 7.178 TL; VitrA/Artema 0 ürün; marka dağılımı: GMS:17</t>
+          <t>24 ürün okundu, 17 eşleşen; medyan ₺7.178; VitrA/Artema 0 ürün; marka dağılımı: GMS:17</t>
         </is>
       </c>
       <c r="F469" s="7" t="inlineStr">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="E470" s="6" t="inlineStr">
         <is>
-          <t>12 ürün okundu, 12 eşleşen; medyan 1.114 TL; VitrA/Artema 8 ürün; marka dağılımı: VitrA:8, Monavit:3, Denko:1</t>
+          <t>12 ürün okundu, 12 eşleşen; medyan ₺1.114; VitrA/Artema 8 ürün; marka dağılımı: VitrA:8, Monavit:3, Denko:1</t>
         </is>
       </c>
       <c r="F470" s="7" t="inlineStr">
@@ -17913,7 +17913,7 @@
       </c>
       <c r="E471" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; medyan 418 TL; VitrA/Artema 0 ürün; marka dağılımı: Monavit:5, GMS:1</t>
+          <t>6 ürün okundu, 6 eşleşen; medyan ₺418; VitrA/Artema 0 ürün; marka dağılımı: Monavit:5, GMS:1</t>
         </is>
       </c>
       <c r="F471" s="7" t="inlineStr">
@@ -17950,7 +17950,7 @@
       </c>
       <c r="E472" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 11 eşleşen; medyan 1.684 TL; VitrA/Artema 1 ürün; marka dağılımı: Radiva:5, Turkuaz Seramik:2, Orka:2, Monavit:1, VitrA:1</t>
+          <t>24 ürün okundu, 11 eşleşen; medyan ₺1.684; VitrA/Artema 1 ürün; marka dağılımı: Radiva:5, Turkuaz Seramik:2, Orka:2, Monavit:1, VitrA:1</t>
         </is>
       </c>
       <c r="F472" s="7" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="E473" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 14 eşleşen; medyan 4.271 TL; VitrA/Artema 7 ürün; marka dağılımı: GMS:7, VitrA:5, Artema:2</t>
+          <t>24 ürün okundu, 14 eşleşen; medyan ₺4.271; VitrA/Artema 7 ürün; marka dağılımı: GMS:7, VitrA:5, Artema:2</t>
         </is>
       </c>
       <c r="F473" s="7" t="inlineStr">
@@ -18061,7 +18061,7 @@
       </c>
       <c r="E475" s="6" t="inlineStr">
         <is>
-          <t>17 ürün okundu, 11 eşleşen; medyan 3.213 TL; VitrA/Artema 8 ürün; marka dağılımı: VitrA:8, Turkuaz Seramik:1, NKP:1, Creavit:1</t>
+          <t>17 ürün okundu, 11 eşleşen; medyan ₺3.213; VitrA/Artema 8 ürün; marka dağılımı: VitrA:8, Turkuaz Seramik:1, NKP:1, Creavit:1</t>
         </is>
       </c>
       <c r="F475" s="7" t="inlineStr">
@@ -18135,7 +18135,7 @@
       </c>
       <c r="E477" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 3 eşleşen; medyan 4.992 TL; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:3</t>
+          <t>24 ürün okundu, 3 eşleşen; medyan ₺4.992; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:3</t>
         </is>
       </c>
       <c r="F477" s="7" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="E478" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 13 eşleşen; medyan 760 TL; VitrA/Artema 7 ürün; marka dağılımı: VitrA:6, Monavit:5, Artema:1, Sukar:1</t>
+          <t>24 ürün okundu, 13 eşleşen; medyan ₺760; VitrA/Artema 7 ürün; marka dağılımı: VitrA:6, Monavit:5, Artema:1, Sukar:1</t>
         </is>
       </c>
       <c r="F478" s="7" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="E479" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 2 eşleşen; medyan 14.937 TL; VitrA/Artema 2 ürün; marka dağılımı: VitrA:2</t>
+          <t>24 ürün okundu, 2 eşleşen; medyan ₺14.937; VitrA/Artema 2 ürün; marka dağılımı: VitrA:2</t>
         </is>
       </c>
       <c r="F479" s="7" t="inlineStr">
@@ -18246,7 +18246,7 @@
       </c>
       <c r="E480" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 5 eşleşen; medyan 3.355 TL; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, NKP:1, Turkuaz Seramik:1</t>
+          <t>24 ürün okundu, 5 eşleşen; medyan ₺3.355; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, NKP:1, Turkuaz Seramik:1</t>
         </is>
       </c>
       <c r="F480" s="7" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="E482" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 1 eşleşen; medyan 4.345 TL; VitrA/Artema 1 ürün; marka dağılımı: VitrA:1</t>
+          <t>24 ürün okundu, 1 eşleşen; medyan ₺4.345; VitrA/Artema 1 ürün; marka dağılımı: VitrA:1</t>
         </is>
       </c>
       <c r="F482" s="7" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="E483" s="6" t="inlineStr">
         <is>
-          <t>9 ürün okundu, 5 eşleşen; medyan 6.450 TL; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, GMS:1, Turkuaz Seramik:1</t>
+          <t>9 ürün okundu, 5 eşleşen; medyan ₺6.450; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, GMS:1, Turkuaz Seramik:1</t>
         </is>
       </c>
       <c r="F483" s="7" t="inlineStr">
@@ -18394,7 +18394,7 @@
       </c>
       <c r="E484" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 14 eşleşen; medyan 5.600 TL; VitrA/Artema 11 ürün; marka dağılımı: Artema:11, GMS:2, Valtemo:1</t>
+          <t>24 ürün okundu, 14 eşleşen; medyan ₺5.600; VitrA/Artema 11 ürün; marka dağılımı: Artema:11, GMS:2, Valtemo:1</t>
         </is>
       </c>
       <c r="F484" s="7" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="E485" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 10 eşleşen; medyan 3.646 TL; VitrA/Artema 9 ürün; marka dağılımı: Artema:6, VitrA:3, GMS:1</t>
+          <t>24 ürün okundu, 10 eşleşen; medyan ₺3.646; VitrA/Artema 9 ürün; marka dağılımı: Artema:6, VitrA:3, GMS:1</t>
         </is>
       </c>
       <c r="F485" s="7" t="inlineStr">
@@ -18468,7 +18468,7 @@
       </c>
       <c r="E486" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 5 eşleşen; medyan 3.355 TL; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, NKP:1, Turkuaz Seramik:1</t>
+          <t>24 ürün okundu, 5 eşleşen; medyan ₺3.355; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, NKP:1, Turkuaz Seramik:1</t>
         </is>
       </c>
       <c r="F486" s="7" t="inlineStr">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="E487" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 2 eşleşen; medyan 25.627 TL; VitrA/Artema 2 ürün; marka dağılımı: Artema:2</t>
+          <t>24 ürün okundu, 2 eşleşen; medyan ₺25.627; VitrA/Artema 2 ürün; marka dağılımı: Artema:2</t>
         </is>
       </c>
       <c r="F487" s="7" t="inlineStr">
@@ -18542,7 +18542,7 @@
       </c>
       <c r="E488" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 3 eşleşen; medyan 3.895 TL; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3</t>
+          <t>24 ürün okundu, 3 eşleşen; medyan ₺3.895; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3</t>
         </is>
       </c>
       <c r="F488" s="7" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="E489" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 8 eşleşen; medyan 1.721 TL; VitrA/Artema 8 ürün; marka dağılımı: VitrA:8</t>
+          <t>24 ürün okundu, 8 eşleşen; medyan ₺1.721; VitrA/Artema 8 ürün; marka dağılımı: VitrA:8</t>
         </is>
       </c>
       <c r="F489" s="7" t="inlineStr">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="E490" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 3 eşleşen; medyan 2.793 TL; VitrA/Artema 1 ürün; marka dağılımı: NKP:2, VitrA:1</t>
+          <t>24 ürün okundu, 3 eşleşen; medyan ₺2.793; VitrA/Artema 1 ürün; marka dağılımı: NKP:2, VitrA:1</t>
         </is>
       </c>
       <c r="F490" s="7" t="inlineStr">
@@ -18653,7 +18653,7 @@
       </c>
       <c r="E491" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 5.605 TL; VitrA/Artema 10 ürün; marka dağılımı: GMS:10, Artema:8, Orka:4, VitrA:2</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺5.605; VitrA/Artema 10 ürün; marka dağılımı: GMS:10, Artema:8, Orka:4, VitrA:2</t>
         </is>
       </c>
       <c r="F491" s="7" t="inlineStr">
@@ -18690,7 +18690,7 @@
       </c>
       <c r="E492" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 6 eşleşen; medyan 4.295 TL; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:6</t>
+          <t>24 ürün okundu, 6 eşleşen; medyan ₺4.295; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:6</t>
         </is>
       </c>
       <c r="F492" s="7" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="E493" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 11.677 TL; VitrA/Artema 16 ürün; marka dağılımı: Artema:11, VitrA:5, Valtemo:2</t>
+          <t>18 ürün okundu; medyan ₺11.677; VitrA/Artema 16 ürün; marka dağılımı: Artema:11, VitrA:5, Valtemo:2</t>
         </is>
       </c>
       <c r="F493" s="7" t="inlineStr">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="E494" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 8.745 TL; VitrA/Artema 18 ürün; marka dağılımı: VitrA:18, Turkuaz Seramik:5, Bocchi:1</t>
+          <t>24 ürün okundu; medyan ₺8.745; VitrA/Artema 18 ürün; marka dağılımı: VitrA:18, Turkuaz Seramik:5, Bocchi:1</t>
         </is>
       </c>
       <c r="F494" s="7" t="inlineStr">
@@ -18801,7 +18801,7 @@
       </c>
       <c r="E495" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 4.271 TL; VitrA/Artema 14 ürün; marka dağılımı: GMS:10, VitrA:10, Artema:4</t>
+          <t>24 ürün okundu; medyan ₺4.271; VitrA/Artema 14 ürün; marka dağılımı: GMS:10, VitrA:10, Artema:4</t>
         </is>
       </c>
       <c r="F495" s="7" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="E496" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 16.587 TL; VitrA/Artema 0 ürün; marka dağılımı: Denko:13, Orka:11</t>
+          <t>24 ürün okundu; medyan ₺16.587; VitrA/Artema 0 ürün; marka dağılımı: Denko:13, Orka:11</t>
         </is>
       </c>
       <c r="F496" s="7" t="inlineStr">
@@ -18875,7 +18875,7 @@
       </c>
       <c r="E497" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 12.335 TL; VitrA/Artema 0 ürün; marka dağılımı: Orka:17, Denko:7</t>
+          <t>24 ürün okundu; medyan ₺12.335; VitrA/Artema 0 ürün; marka dağılımı: Orka:17, Denko:7</t>
         </is>
       </c>
       <c r="F497" s="7" t="inlineStr">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="E498" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 1.465 TL; VitrA/Artema 9 ürün; marka dağılımı: VitrA:7, GMS:7, Monavit:5, Valtemo:3, Artema:2</t>
+          <t>24 ürün okundu; medyan ₺1.465; VitrA/Artema 9 ürün; marka dağılımı: VitrA:7, GMS:7, Monavit:5, Valtemo:3, Artema:2</t>
         </is>
       </c>
       <c r="F498" s="7" t="inlineStr">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="E499" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 3.402 TL; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:24</t>
+          <t>24 ürün okundu; medyan ₺3.402; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:24</t>
         </is>
       </c>
       <c r="F499" s="7" t="inlineStr">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="E500" s="6" t="inlineStr">
         <is>
-          <t>12 ürün okundu; medyan 3.145 TL; VitrA/Artema 4 ürün; marka dağılımı: NKP:6, VitrA:4, Turkuaz Seramik:1, Creavit:1</t>
+          <t>12 ürün okundu; medyan ₺3.145; VitrA/Artema 4 ürün; marka dağılımı: NKP:6, VitrA:4, Turkuaz Seramik:1, Creavit:1</t>
         </is>
       </c>
       <c r="F500" s="7" t="inlineStr">
@@ -19023,7 +19023,7 @@
       </c>
       <c r="E501" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 8.745 TL; VitrA/Artema 16 ürün; marka dağılımı: VitrA:16, Turkuaz Seramik:7, Bocchi:1</t>
+          <t>24 ürün okundu; medyan ₺8.745; VitrA/Artema 16 ürün; marka dağılımı: VitrA:16, Turkuaz Seramik:7, Bocchi:1</t>
         </is>
       </c>
       <c r="F501" s="7" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="E502" s="6" t="inlineStr">
         <is>
-          <t>19 ürün okundu; medyan 1.480 TL; VitrA/Artema 8 ürün; marka dağılımı: NKP:8, VitrA:8, Turkuaz Seramik:2, Creavit:1</t>
+          <t>19 ürün okundu; medyan ₺1.480; VitrA/Artema 8 ürün; marka dağılımı: NKP:8, VitrA:8, Turkuaz Seramik:2, Creavit:1</t>
         </is>
       </c>
       <c r="F502" s="7" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="E503" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 4.560 TL; VitrA/Artema 8 ürün; marka dağılımı: GMS:16, Artema:4, VitrA:4</t>
+          <t>24 ürün okundu; medyan ₺4.560; VitrA/Artema 8 ürün; marka dağılımı: GMS:16, Artema:4, VitrA:4</t>
         </is>
       </c>
       <c r="F503" s="7" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="E504" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 3.755 TL; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:24</t>
+          <t>24 ürün okundu; medyan ₺3.755; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz Seramik:24</t>
         </is>
       </c>
       <c r="F504" s="7" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="E505" s="6" t="inlineStr">
         <is>
-          <t>4 ürün okundu; medyan 6.987 TL; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, Turkuaz Seramik:1</t>
+          <t>4 ürün okundu; medyan ₺6.987; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, Turkuaz Seramik:1</t>
         </is>
       </c>
       <c r="F505" s="7" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="E506" s="6" t="inlineStr">
         <is>
-          <t>3 ürün okundu; medyan 638 TL; VitrA/Artema 1 ürün; marka dağılımı: NKP:2, VitrA:1</t>
+          <t>3 ürün okundu; medyan ₺638; VitrA/Artema 1 ürün; marka dağılımı: NKP:2, VitrA:1</t>
         </is>
       </c>
       <c r="F506" s="7" t="inlineStr">
@@ -19245,7 +19245,7 @@
       </c>
       <c r="E507" s="6" t="inlineStr">
         <is>
-          <t>11 ürün okundu; medyan 3.873 TL; VitrA/Artema 4 ürün; marka dağılımı: Orka:4, VitrA:3, Denko:2, Artema:1, Monavit:1</t>
+          <t>11 ürün okundu; medyan ₺3.873; VitrA/Artema 4 ürün; marka dağılımı: Orka:4, VitrA:3, Denko:2, Artema:1, Monavit:1</t>
         </is>
       </c>
       <c r="F507" s="7" t="inlineStr">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="E508" s="6" t="inlineStr">
         <is>
-          <t>21 ürün okundu; medyan 605 TL; VitrA/Artema 6 ürün; marka dağılımı: GMS:15, Artema:6</t>
+          <t>21 ürün okundu; medyan ₺605; VitrA/Artema 6 ürün; marka dağılımı: GMS:15, Artema:6</t>
         </is>
       </c>
       <c r="F508" s="7" t="inlineStr">
@@ -19319,7 +19319,7 @@
       </c>
       <c r="E509" s="6" t="inlineStr">
         <is>
-          <t>9 ürün okundu; medyan 2.665 TL; VitrA/Artema 3 ürün; marka dağılımı: Turkuaz Seramik:6, VitrA:3</t>
+          <t>9 ürün okundu; medyan ₺2.665; VitrA/Artema 3 ürün; marka dağılımı: Turkuaz Seramik:6, VitrA:3</t>
         </is>
       </c>
       <c r="F509" s="7" t="inlineStr">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="E510" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 3.626 TL; VitrA/Artema 1 ürün; marka dağılımı: Turkuaz Seramik:22, VitrA:1, Creavit:1</t>
+          <t>24 ürün okundu; medyan ₺3.626; VitrA/Artema 1 ürün; marka dağılımı: Turkuaz Seramik:22, VitrA:1, Creavit:1</t>
         </is>
       </c>
       <c r="F510" s="7" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="E511" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 104.741 TL; VitrA/Artema 10 ürün; marka dağılımı: Geberit:14, VitrA:10, Grohe:3, Duravit:2, Creavit:2, Hansgrohe:1</t>
+          <t>32 ürün okundu; medyan ₺104.741; VitrA/Artema 10 ürün; marka dağılımı: Geberit:14, VitrA:10, Grohe:3, Duravit:2, Creavit:2, Hansgrohe:1</t>
         </is>
       </c>
       <c r="F511" s="7" t="inlineStr">
@@ -19430,7 +19430,7 @@
       </c>
       <c r="E512" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 13.595 TL; VitrA/Artema 9 ürün; marka dağılımı: Duravit:16, VitrA:9, Creavit:5, Ideal Standard:2</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺13.595; VitrA/Artema 9 ürün; marka dağılımı: Duravit:16, VitrA:9, Creavit:5, Ideal Standard:2</t>
         </is>
       </c>
       <c r="F512" s="7" t="inlineStr">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="E513" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 29 eşleşen; medyan 11.425 TL; VitrA/Artema 13 ürün; marka dağılımı: VitrA:13, Serel:12, Creavit:3, Duravit:1</t>
+          <t>32 ürün okundu, 29 eşleşen; medyan ₺11.425; VitrA/Artema 13 ürün; marka dağılımı: VitrA:13, Serel:12, Creavit:3, Duravit:1</t>
         </is>
       </c>
       <c r="F513" s="7" t="inlineStr">
@@ -19578,7 +19578,7 @@
       </c>
       <c r="E516" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 1.800 TL; VitrA/Artema 10 ürün; marka dağılımı: Grohe:14, Artema:7, VitrA:3, Ideal Standard:2, Gpd:2, Geberit:2</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺1.800; VitrA/Artema 10 ürün; marka dağılımı: Grohe:14, Artema:7, VitrA:3, Ideal Standard:2, Gpd:2, Geberit:2</t>
         </is>
       </c>
       <c r="F516" s="7" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="E517" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 5 eşleşen; medyan 3.625 TL; VitrA/Artema 0 ürün; marka dağılımı: Serel:5</t>
+          <t>30 ürün okundu, 5 eşleşen; medyan ₺3.625; VitrA/Artema 0 ürün; marka dağılımı: Serel:5</t>
         </is>
       </c>
       <c r="F517" s="7" t="inlineStr">
@@ -19726,7 +19726,7 @@
       </c>
       <c r="E520" s="6" t="inlineStr">
         <is>
-          <t>23 ürün okundu, 23 eşleşen; medyan 4.100 TL; VitrA/Artema 8 ürün; marka dağılımı: Orka:10, VitrA:8, Hansgrohe:3, Rulopak:2</t>
+          <t>23 ürün okundu, 23 eşleşen; medyan ₺4.100; VitrA/Artema 8 ürün; marka dağılımı: Orka:10, VitrA:8, Hansgrohe:3, Rulopak:2</t>
         </is>
       </c>
       <c r="F520" s="7" t="inlineStr">
@@ -19800,7 +19800,7 @@
       </c>
       <c r="E522" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 31 eşleşen; medyan 2.502 TL; VitrA/Artema 10 ürün; marka dağılımı: Grohe:15, Artema:7, Camero:4, VitrA:3, Duxxa:1, Bocchi:1</t>
+          <t>32 ürün okundu, 31 eşleşen; medyan ₺2.502; VitrA/Artema 10 ürün; marka dağılımı: Grohe:15, Artema:7, Camero:4, VitrA:3, Duxxa:1, Bocchi:1</t>
         </is>
       </c>
       <c r="F522" s="7" t="inlineStr">
@@ -19837,7 +19837,7 @@
       </c>
       <c r="E523" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 29 eşleşen; medyan 32.185 TL; VitrA/Artema 0 ürün; marka dağılımı: Grohe:22, Hansgrohe:4, Duravit:3</t>
+          <t>32 ürün okundu, 29 eşleşen; medyan ₺32.185; VitrA/Artema 0 ürün; marka dağılımı: Grohe:22, Hansgrohe:4, Duravit:3</t>
         </is>
       </c>
       <c r="F523" s="7" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="E524" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 11.385 TL; VitrA/Artema 7 ürün; marka dağılımı: Grohe:17, VitrA:7, Duravit:5, Hansgrohe:3</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺11.385; VitrA/Artema 7 ürün; marka dağılımı: Grohe:17, VitrA:7, Duravit:5, Hansgrohe:3</t>
         </is>
       </c>
       <c r="F524" s="7" t="inlineStr">
@@ -19911,7 +19911,7 @@
       </c>
       <c r="E525" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 2.375 TL; VitrA/Artema 22 ürün; marka dağılımı: Artema:14, VitrA:8, Grohe:8, Duravit:1, Creavit:1</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺2.375; VitrA/Artema 22 ürün; marka dağılımı: Artema:14, VitrA:8, Grohe:8, Duravit:1, Creavit:1</t>
         </is>
       </c>
       <c r="F525" s="7" t="inlineStr">
@@ -19985,7 +19985,7 @@
       </c>
       <c r="E527" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 31 eşleşen; medyan 3.650 TL; VitrA/Artema 0 ürün; marka dağılımı: Sukar:15, Hüppe:11, Geberit:5</t>
+          <t>32 ürün okundu, 31 eşleşen; medyan ₺3.650; VitrA/Artema 0 ürün; marka dağılımı: Sukar:15, Hüppe:11, Geberit:5</t>
         </is>
       </c>
       <c r="F527" s="7" t="inlineStr">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="E528" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 24 eşleşen; medyan 20.075 TL; VitrA/Artema 4 ürün; marka dağılımı: Grohe:13, Artema:4, Duravit:3, E.C.A:2, Duxxa:2</t>
+          <t>32 ürün okundu, 24 eşleşen; medyan ₺20.075; VitrA/Artema 4 ürün; marka dağılımı: Grohe:13, Artema:4, Duravit:3, E.C.A:2, Duxxa:2</t>
         </is>
       </c>
       <c r="F528" s="7" t="inlineStr">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="E529" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 26 eşleşen; medyan 11.678 TL; VitrA/Artema 7 ürün; marka dağılımı: VitrA:7, Creavit:7, Geberit:6, Duravit:5, Serel:1</t>
+          <t>32 ürün okundu, 26 eşleşen; medyan ₺11.678; VitrA/Artema 7 ürün; marka dağılımı: VitrA:7, Creavit:7, Geberit:6, Duravit:5, Serel:1</t>
         </is>
       </c>
       <c r="F529" s="7" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="E530" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 1.950 TL; VitrA/Artema 9 ürün; marka dağılımı: Grohe:16, VitrA:5, E.C.A:5, Artema:4, Ideal Standard:2</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺1.950; VitrA/Artema 9 ürün; marka dağılımı: Grohe:16, VitrA:5, E.C.A:5, Artema:4, Ideal Standard:2</t>
         </is>
       </c>
       <c r="F530" s="7" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="E531" s="6" t="inlineStr">
         <is>
-          <t>29 ürün okundu, 25 eşleşen; medyan 18.372 TL; VitrA/Artema 13 ürün; marka dağılımı: VitrA:13, Ideal Standard:4, Creavit:3, Serel:3, Duravit:1, Kale:1</t>
+          <t>29 ürün okundu, 25 eşleşen; medyan ₺18.372; VitrA/Artema 13 ürün; marka dağılımı: VitrA:13, Ideal Standard:4, Creavit:3, Serel:3, Duravit:1, Kale:1</t>
         </is>
       </c>
       <c r="F531" s="7" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="E532" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 10.850 TL; VitrA/Artema 25 ürün; marka dağılımı: VitrA:25, Duravit:6, Ideal Standard:1</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺10.850; VitrA/Artema 25 ürün; marka dağılımı: VitrA:25, Duravit:6, Ideal Standard:1</t>
         </is>
       </c>
       <c r="F532" s="7" t="inlineStr">
@@ -20207,7 +20207,7 @@
       </c>
       <c r="E533" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 29 eşleşen; medyan 16.450 TL; VitrA/Artema 7 ürün; marka dağılımı: Gpd:8, Grohe:8, VitrA:5, E.C.A:3, Geberit:3, Artema:2</t>
+          <t>32 ürün okundu, 29 eşleşen; medyan ₺16.450; VitrA/Artema 7 ürün; marka dağılımı: Gpd:8, Grohe:8, VitrA:5, E.C.A:3, Geberit:3, Artema:2</t>
         </is>
       </c>
       <c r="F533" s="7" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="E534" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 31 eşleşen; medyan 3.550 TL; VitrA/Artema 6 ürün; marka dağılımı: Camero:15, Grohe:10, VitrA:6</t>
+          <t>32 ürün okundu, 31 eşleşen; medyan ₺3.550; VitrA/Artema 6 ürün; marka dağılımı: Camero:15, Grohe:10, VitrA:6</t>
         </is>
       </c>
       <c r="F534" s="7" t="inlineStr">
@@ -20281,7 +20281,7 @@
       </c>
       <c r="E535" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 31 eşleşen; medyan 254.250 TL; VitrA/Artema 17 ürün; marka dağılımı: VitrA:17, Duravit:8, Artemis:4, (markasız):2</t>
+          <t>32 ürün okundu, 31 eşleşen; medyan ₺254.250; VitrA/Artema 17 ürün; marka dağılımı: VitrA:17, Duravit:8, Artemis:4, (markasız):2</t>
         </is>
       </c>
       <c r="F535" s="7" t="inlineStr">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="E536" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 23 eşleşen; medyan 18.950 TL; VitrA/Artema 19 ürün; marka dağılımı: VitrA:19, Creavit:4</t>
+          <t>32 ürün okundu, 23 eşleşen; medyan ₺18.950; VitrA/Artema 19 ürün; marka dağılımı: VitrA:19, Creavit:4</t>
         </is>
       </c>
       <c r="F536" s="7" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="E537" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 53.875 TL; VitrA/Artema 13 ürün; marka dağılımı: Grohe:15, Artema:11, Gpd:4, VitrA:2</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺53.875; VitrA/Artema 13 ürün; marka dağılımı: Grohe:15, Artema:11, Gpd:4, VitrA:2</t>
         </is>
       </c>
       <c r="F537" s="7" t="inlineStr">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="E538" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 23 eşleşen; medyan 3.100 TL; VitrA/Artema 10 ürün; marka dağılımı: VitrA:9, Creavit:7, Serel:4, Duravit:2, (markasız):1</t>
+          <t>32 ürün okundu, 23 eşleşen; medyan ₺3.100; VitrA/Artema 10 ürün; marka dağılımı: VitrA:9, Creavit:7, Serel:4, Duravit:2, (markasız):1</t>
         </is>
       </c>
       <c r="F538" s="7" t="inlineStr">
@@ -20466,7 +20466,7 @@
       </c>
       <c r="E540" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 6.598 TL; VitrA/Artema 4 ürün; marka dağılımı: Decor Walther:11, Grohe:8, OMG:7, Artema:2, VitrA:2, Duravit:2</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺6.598; VitrA/Artema 4 ürün; marka dağılımı: Decor Walther:11, Grohe:8, OMG:7, Artema:2, VitrA:2, Duravit:2</t>
         </is>
       </c>
       <c r="F540" s="7" t="inlineStr">
@@ -20503,7 +20503,7 @@
       </c>
       <c r="E541" s="6" t="inlineStr">
         <is>
-          <t>16 ürün okundu, 16 eşleşen; medyan 17.311 TL; VitrA/Artema 9 ürün; marka dağılımı: VitrA:9, Gpd:7</t>
+          <t>16 ürün okundu, 16 eşleşen; medyan ₺17.311; VitrA/Artema 9 ürün; marka dağılımı: VitrA:9, Gpd:7</t>
         </is>
       </c>
       <c r="F541" s="7" t="inlineStr">
@@ -20577,7 +20577,7 @@
       </c>
       <c r="E543" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 31 eşleşen; medyan 60.025 TL; VitrA/Artema 11 ürün; marka dağılımı: Isvea:16, VitrA:10, Bocchi:2, Duravit:1, Creavit:1, (markasız):1</t>
+          <t>32 ürün okundu, 31 eşleşen; medyan ₺60.025; VitrA/Artema 11 ürün; marka dağılımı: Isvea:16, VitrA:10, Bocchi:2, Duravit:1, Creavit:1, (markasız):1</t>
         </is>
       </c>
       <c r="F543" s="7" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="E544" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 26 eşleşen; medyan 5.055 TL; VitrA/Artema 10 ürün; marka dağılımı: VitrA:10, Creavit:6, Grohe:3, E.C.A:3, Gpd:2, Geberit:1</t>
+          <t>32 ürün okundu, 26 eşleşen; medyan ₺5.055; VitrA/Artema 10 ürün; marka dağılımı: VitrA:10, Creavit:6, Grohe:3, E.C.A:3, Gpd:2, Geberit:1</t>
         </is>
       </c>
       <c r="F544" s="7" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="E545" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 8.550 TL; VitrA/Artema 32 ürün; marka dağılımı: Artema:26, VitrA:6</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺8.550; VitrA/Artema 32 ürün; marka dağılımı: Artema:26, VitrA:6</t>
         </is>
       </c>
       <c r="F545" s="7" t="inlineStr">
@@ -20688,7 +20688,7 @@
       </c>
       <c r="E546" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 26 eşleşen; medyan 8.575 TL; VitrA/Artema 9 ürün; marka dağılımı: Grohe:13, Artema:6, E.C.A:4, VitrA:3</t>
+          <t>32 ürün okundu, 26 eşleşen; medyan ₺8.575; VitrA/Artema 9 ürün; marka dağılımı: Grohe:13, Artema:6, E.C.A:4, VitrA:3</t>
         </is>
       </c>
       <c r="F546" s="7" t="inlineStr">
@@ -20725,7 +20725,7 @@
       </c>
       <c r="E547" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 26 eşleşen; medyan 31.950 TL; VitrA/Artema 3 ürün; marka dağılımı: Grohe:21, VitrA:2, Ideal Standard:1, Hansgrohe:1, Artema:1</t>
+          <t>32 ürün okundu, 26 eşleşen; medyan ₺31.950; VitrA/Artema 3 ürün; marka dağılımı: Grohe:21, VitrA:2, Ideal Standard:1, Hansgrohe:1, Artema:1</t>
         </is>
       </c>
       <c r="F547" s="7" t="inlineStr">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="E548" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 3.990 TL; VitrA/Artema 0 ürün; marka dağılımı: Hansgrohe:13, Grohe:7, Ideal Standard:5, Camero:4, Duravit:3</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺3.990; VitrA/Artema 0 ürün; marka dağılımı: Hansgrohe:13, Grohe:7, Ideal Standard:5, Camero:4, Duravit:3</t>
         </is>
       </c>
       <c r="F548" s="7" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="E549" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 2.800 TL; VitrA/Artema 10 ürün; marka dağılımı: Grohe:12, Camero:7, Artema:7, VitrA:3, Bocchi:3</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺2.800; VitrA/Artema 10 ürün; marka dağılımı: Grohe:12, Camero:7, Artema:7, VitrA:3, Bocchi:3</t>
         </is>
       </c>
       <c r="F549" s="7" t="inlineStr">
@@ -20873,7 +20873,7 @@
       </c>
       <c r="E551" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 30 eşleşen; medyan 11.150 TL; VitrA/Artema 21 ürün; marka dağılımı: VitrA:21, Duravit:4, Serel:2, Ideal Standard:2, Creavit:1</t>
+          <t>32 ürün okundu, 30 eşleşen; medyan ₺11.150; VitrA/Artema 21 ürün; marka dağılımı: VitrA:21, Duravit:4, Serel:2, Ideal Standard:2, Creavit:1</t>
         </is>
       </c>
       <c r="F551" s="7" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="E552" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 14.112 TL; VitrA/Artema 12 ürün; marka dağılımı: VitrA:12, Creavit:8, Duravit:7, Geberit:3, Ideal Standard:1, Serel:1</t>
+          <t>32 ürün okundu; medyan ₺14.112; VitrA/Artema 12 ürün; marka dağılımı: VitrA:12, Creavit:8, Duravit:7, Geberit:3, Ideal Standard:1, Serel:1</t>
         </is>
       </c>
       <c r="F552" s="7" t="inlineStr">
@@ -20947,7 +20947,7 @@
       </c>
       <c r="E553" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 25.336 TL; VitrA/Artema 5 ürün; marka dağılımı: Duravit:14, Geberit:7, VitrA:5, Serel:3, Ideal Standard:2, Creavit:1</t>
+          <t>32 ürün okundu; medyan ₺25.336; VitrA/Artema 5 ürün; marka dağılımı: Duravit:14, Geberit:7, VitrA:5, Serel:3, Ideal Standard:2, Creavit:1</t>
         </is>
       </c>
       <c r="F553" s="7" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="E554" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 29.725 TL; VitrA/Artema 31 ürün; marka dağılımı: VitrA:31, Ideal Standard:1</t>
+          <t>32 ürün okundu; medyan ₺29.725; VitrA/Artema 31 ürün; marka dağılımı: VitrA:31, Ideal Standard:1</t>
         </is>
       </c>
       <c r="F554" s="7" t="inlineStr">
@@ -21021,7 +21021,7 @@
       </c>
       <c r="E555" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 10.000 TL; VitrA/Artema 5 ürün; marka dağılımı: Grohe:21, Artema:5, Ideal Standard:3, E.C.A:2, Hansgrohe:1</t>
+          <t>32 ürün okundu; medyan ₺10.000; VitrA/Artema 5 ürün; marka dağılımı: Grohe:21, Artema:5, Ideal Standard:3, E.C.A:2, Hansgrohe:1</t>
         </is>
       </c>
       <c r="F555" s="7" t="inlineStr">
@@ -21058,7 +21058,7 @@
       </c>
       <c r="E556" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 39.917 TL; VitrA/Artema 4 ürün; marka dağılımı: Orka:28, VitrA:4</t>
+          <t>32 ürün okundu; medyan ₺39.917; VitrA/Artema 4 ürün; marka dağılımı: Orka:28, VitrA:4</t>
         </is>
       </c>
       <c r="F556" s="7" t="inlineStr">
@@ -21095,7 +21095,7 @@
       </c>
       <c r="E557" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 31.050 TL; VitrA/Artema 31 ürün; marka dağılımı: VitrA:31, Orka:1</t>
+          <t>32 ürün okundu; medyan ₺31.050; VitrA/Artema 31 ürün; marka dağılımı: VitrA:31, Orka:1</t>
         </is>
       </c>
       <c r="F557" s="7" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="E558" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 13.595 TL; VitrA/Artema 9 ürün; marka dağılımı: Duravit:16, VitrA:9, Creavit:5, Ideal Standard:2</t>
+          <t>32 ürün okundu; medyan ₺13.595; VitrA/Artema 9 ürün; marka dağılımı: Duravit:16, VitrA:9, Creavit:5, Ideal Standard:2</t>
         </is>
       </c>
       <c r="F558" s="7" t="inlineStr">
@@ -21169,7 +21169,7 @@
       </c>
       <c r="E559" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 5.050 TL; VitrA/Artema 4 ürün; marka dağılımı: Grohe:19, E.C.A:8, Artema:3, Ideal Standard:1, VitrA:1</t>
+          <t>32 ürün okundu; medyan ₺5.050; VitrA/Artema 4 ürün; marka dağılımı: Grohe:19, E.C.A:8, Artema:3, Ideal Standard:1, VitrA:1</t>
         </is>
       </c>
       <c r="F559" s="7" t="inlineStr">
@@ -21206,7 +21206,7 @@
       </c>
       <c r="E560" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 6.250 TL; VitrA/Artema 11 ürün; marka dağılımı: Grohe:16, Artema:8, VitrA:3, Hansgrohe:3, Gpd:2</t>
+          <t>32 ürün okundu; medyan ₺6.250; VitrA/Artema 11 ürün; marka dağılımı: Grohe:16, Artema:8, VitrA:3, Hansgrohe:3, Gpd:2</t>
         </is>
       </c>
       <c r="F560" s="7" t="inlineStr">
@@ -21243,7 +21243,7 @@
       </c>
       <c r="E561" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 4.442 TL; VitrA/Artema 7 ürün; marka dağılımı: Grohe:18, Artema:6, E.C.A:5, Duxxa:2, VitrA:1</t>
+          <t>32 ürün okundu; medyan ₺4.442; VitrA/Artema 7 ürün; marka dağılımı: Grohe:18, Artema:6, E.C.A:5, Duxxa:2, VitrA:1</t>
         </is>
       </c>
       <c r="F561" s="7" t="inlineStr">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="E562" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 4.732 TL; VitrA/Artema 16 ürün; marka dağılımı: VitrA:16, Duravit:14, Creavit:1, Ideal Standard:1</t>
+          <t>32 ürün okundu; medyan ₺4.732; VitrA/Artema 16 ürün; marka dağılımı: VitrA:16, Duravit:14, Creavit:1, Ideal Standard:1</t>
         </is>
       </c>
       <c r="F562" s="7" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="E563" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 20.451 TL; VitrA/Artema 9 ürün; marka dağılımı: Duravit:10, VitrA:9, Serel:8, Ideal Standard:2, Creavit:2</t>
+          <t>32 ürün okundu; medyan ₺20.451; VitrA/Artema 9 ürün; marka dağılımı: Duravit:10, VitrA:9, Serel:8, Ideal Standard:2, Creavit:2</t>
         </is>
       </c>
       <c r="F563" s="7" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="E564" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 7.388 TL; VitrA/Artema 7 ürün; marka dağılımı: Grohe:17, Artema:5, E.C.A:3, Gpd:3, VitrA:2, Ideal Standard:1</t>
+          <t>32 ürün okundu; medyan ₺7.388; VitrA/Artema 7 ürün; marka dağılımı: Grohe:17, Artema:5, E.C.A:3, Gpd:3, VitrA:2, Ideal Standard:1</t>
         </is>
       </c>
       <c r="F564" s="7" t="inlineStr">
@@ -21391,7 +21391,7 @@
       </c>
       <c r="E565" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 40.250 TL; VitrA/Artema 32 ürün; marka dağılımı: VitrA:32</t>
+          <t>32 ürün okundu; medyan ₺40.250; VitrA/Artema 32 ürün; marka dağılımı: VitrA:32</t>
         </is>
       </c>
       <c r="F565" s="7" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="E566" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 3.484 TL; VitrA/Artema 10 ürün; marka dağılımı: Creavit:11, VitrA:10, Duravit:8, Serel:2, Ideal Standard:1</t>
+          <t>32 ürün okundu; medyan ₺3.484; VitrA/Artema 10 ürün; marka dağılımı: Creavit:11, VitrA:10, Duravit:8, Serel:2, Ideal Standard:1</t>
         </is>
       </c>
       <c r="F566" s="7" t="inlineStr">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="E567" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 970 TL; VitrA/Artema 12 ürün; marka dağılımı: VitrA:12, Serel:6, Creavit:6, Japar:4, Geberit:1</t>
+          <t>32 ürün okundu; medyan ₺970; VitrA/Artema 12 ürün; marka dağılımı: VitrA:12, Serel:6, Creavit:6, Japar:4, Geberit:1</t>
         </is>
       </c>
       <c r="F567" s="7" t="inlineStr">
@@ -21502,7 +21502,7 @@
       </c>
       <c r="E568" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 32.725 TL; VitrA/Artema 28 ürün; marka dağılımı: VitrA:28, Creavit:4</t>
+          <t>32 ürün okundu; medyan ₺32.725; VitrA/Artema 28 ürün; marka dağılımı: VitrA:28, Creavit:4</t>
         </is>
       </c>
       <c r="F568" s="7" t="inlineStr">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="E569" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 5.094 TL; VitrA/Artema 18 ürün; marka dağılımı: VitrA:18, Duravit:5, Geberit:4, Ideal Standard:2, Serel:1, Bocchi:1</t>
+          <t>32 ürün okundu; medyan ₺5.094; VitrA/Artema 18 ürün; marka dağılımı: VitrA:18, Duravit:5, Geberit:4, Ideal Standard:2, Serel:1, Bocchi:1</t>
         </is>
       </c>
       <c r="F569" s="7" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="E570" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu; medyan 12.100 TL; VitrA/Artema 19 ürün; marka dağılımı: VitrA:19, Duravit:11, Bocchi:2</t>
+          <t>32 ürün okundu; medyan ₺12.100; VitrA/Artema 19 ürün; marka dağılımı: VitrA:19, Duravit:11, Bocchi:2</t>
         </is>
       </c>
       <c r="F570" s="7" t="inlineStr">
@@ -21613,7 +21613,7 @@
       </c>
       <c r="E571" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 22 eşleşen; medyan 15.340 TL; VitrA/Artema 0 ürün; marka dağılımı: Lena:12, Duravit:10</t>
+          <t>24 ürün okundu, 22 eşleşen; medyan ₺15.340; VitrA/Artema 0 ürün; marka dağılımı: Lena:12, Duravit:10</t>
         </is>
       </c>
       <c r="F571" s="7" t="inlineStr">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="E572" s="6" t="inlineStr">
         <is>
-          <t>13 ürün okundu, 7 eşleşen; medyan 8.000 TL; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, Turkuaz:3, Creavit:1</t>
+          <t>13 ürün okundu, 7 eşleşen; medyan ₺8.000; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3, Turkuaz:3, Creavit:1</t>
         </is>
       </c>
       <c r="F572" s="7" t="inlineStr">
@@ -21687,7 +21687,7 @@
       </c>
       <c r="E573" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 2.052 TL; VitrA/Artema 6 ürün; marka dağılımı: Newarc:6, Grohe:4, VitrA:3, Geberit:3, Creavit:3, Artema:3</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺2.052; VitrA/Artema 6 ürün; marka dağılımı: Newarc:6, Grohe:4, VitrA:3, Geberit:3, Creavit:3, Artema:3</t>
         </is>
       </c>
       <c r="F573" s="7" t="inlineStr">
@@ -21761,7 +21761,7 @@
       </c>
       <c r="E575" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 2 eşleşen; medyan 41.850 TL; VitrA/Artema 0 ürün; marka dağılımı: Fontana:2</t>
+          <t>24 ürün okundu, 2 eşleşen; medyan ₺41.850; VitrA/Artema 0 ürün; marka dağılımı: Fontana:2</t>
         </is>
       </c>
       <c r="F575" s="7" t="inlineStr">
@@ -21835,7 +21835,7 @@
       </c>
       <c r="E577" s="6" t="inlineStr">
         <is>
-          <t>13 ürün okundu, 13 eşleşen; medyan 150.552 TL; VitrA/Artema 0 ürün; marka dağılımı: Shower:13</t>
+          <t>13 ürün okundu, 13 eşleşen; medyan ₺150.552; VitrA/Artema 0 ürün; marka dağılımı: Shower:13</t>
         </is>
       </c>
       <c r="F577" s="7" t="inlineStr">
@@ -21872,7 +21872,7 @@
       </c>
       <c r="E578" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 7.624 TL; VitrA/Artema 0 ürün; marka dağılımı: Penta:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺7.624; VitrA/Artema 0 ürün; marka dağılımı: Penta:1</t>
         </is>
       </c>
       <c r="F578" s="7" t="inlineStr">
@@ -21909,7 +21909,7 @@
       </c>
       <c r="E579" s="6" t="inlineStr">
         <is>
-          <t>11 ürün okundu, 9 eşleşen; medyan 2.776 TL; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:7, Penta:1, MesaTeknik:1</t>
+          <t>11 ürün okundu, 9 eşleşen; medyan ₺2.776; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:7, Penta:1, MesaTeknik:1</t>
         </is>
       </c>
       <c r="F579" s="7" t="inlineStr">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="E580" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 2.677 TL; VitrA/Artema 1 ürün; marka dağılımı: Bocchi:17, MesaTeknik:5, Artema:1, Penta:1</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺2.677; VitrA/Artema 1 ürün; marka dağılımı: Bocchi:17, MesaTeknik:5, Artema:1, Penta:1</t>
         </is>
       </c>
       <c r="F580" s="7" t="inlineStr">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="E581" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 3.263 TL; VitrA/Artema 0 ürün; marka dağılımı: Lucco:24</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺3.263; VitrA/Artema 0 ürün; marka dağılımı: Lucco:24</t>
         </is>
       </c>
       <c r="F581" s="7" t="inlineStr">
@@ -22020,7 +22020,7 @@
       </c>
       <c r="E582" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 23 eşleşen; medyan 68.880 TL; VitrA/Artema 0 ürün; marka dağılımı: Grohe:16, Creavit:7</t>
+          <t>24 ürün okundu, 23 eşleşen; medyan ₺68.880; VitrA/Artema 0 ürün; marka dağılımı: Grohe:16, Creavit:7</t>
         </is>
       </c>
       <c r="F582" s="7" t="inlineStr">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="E583" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; medyan 6.318 TL; VitrA/Artema 0 ürün; marka dağılımı: Newarc:3, Grohe:1, Creavit:1, Bocchi:1</t>
+          <t>6 ürün okundu, 6 eşleşen; medyan ₺6.318; VitrA/Artema 0 ürün; marka dağılımı: Newarc:3, Grohe:1, Creavit:1, Bocchi:1</t>
         </is>
       </c>
       <c r="F583" s="7" t="inlineStr">
@@ -22094,7 +22094,7 @@
       </c>
       <c r="E584" s="6" t="inlineStr">
         <is>
-          <t>10 ürün okundu, 10 eşleşen; medyan 1.493 TL; VitrA/Artema 1 ürün; marka dağılımı: Penta:9, Artema:1</t>
+          <t>10 ürün okundu, 10 eşleşen; medyan ₺1.493; VitrA/Artema 1 ürün; marka dağılımı: Penta:9, Artema:1</t>
         </is>
       </c>
       <c r="F584" s="7" t="inlineStr">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="E585" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 17 eşleşen; medyan 2.384 TL; VitrA/Artema 0 ürün; marka dağılımı: MesaTeknik:12, Sukar:5</t>
+          <t>24 ürün okundu, 17 eşleşen; medyan ₺2.384; VitrA/Artema 0 ürün; marka dağılımı: MesaTeknik:12, Sukar:5</t>
         </is>
       </c>
       <c r="F585" s="7" t="inlineStr">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="E586" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 15 eşleşen; medyan 39.700 TL; VitrA/Artema 3 ürün; marka dağılımı: Bocchi:6, Hansgrohe:5, VitrA:3, Grohe:1</t>
+          <t>24 ürün okundu, 15 eşleşen; medyan ₺39.700; VitrA/Artema 3 ürün; marka dağılımı: Bocchi:6, Hansgrohe:5, VitrA:3, Grohe:1</t>
         </is>
       </c>
       <c r="F586" s="7" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="E587" s="6" t="inlineStr">
         <is>
-          <t>7 ürün okundu, 6 eşleşen; medyan 20.222 TL; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:5, Geberit:1</t>
+          <t>7 ürün okundu, 6 eşleşen; medyan ₺20.222; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:5, Geberit:1</t>
         </is>
       </c>
       <c r="F587" s="7" t="inlineStr">
@@ -22242,7 +22242,7 @@
       </c>
       <c r="E588" s="6" t="inlineStr">
         <is>
-          <t>7 ürün okundu, 6 eşleşen; medyan 4.455 TL; VitrA/Artema 0 ürün; marka dağılımı: Hansgrohe:6</t>
+          <t>7 ürün okundu, 6 eşleşen; medyan ₺4.455; VitrA/Artema 0 ürün; marka dağılımı: Hansgrohe:6</t>
         </is>
       </c>
       <c r="F588" s="7" t="inlineStr">
@@ -22279,7 +22279,7 @@
       </c>
       <c r="E589" s="6" t="inlineStr">
         <is>
-          <t>7 ürün okundu, 7 eşleşen; medyan 13.969 TL; VitrA/Artema 6 ürün; marka dağılımı: VitrA:6, Turkuaz:1</t>
+          <t>7 ürün okundu, 7 eşleşen; medyan ₺13.969; VitrA/Artema 6 ürün; marka dağılımı: VitrA:6, Turkuaz:1</t>
         </is>
       </c>
       <c r="F589" s="7" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="E590" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 10.808 TL; VitrA/Artema 6 ürün; marka dağılımı: Bocchi:10, VitrA:6, Creavit:4, Turkuaz:4</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺10.808; VitrA/Artema 6 ürün; marka dağılımı: Bocchi:10, VitrA:6, Creavit:4, Turkuaz:4</t>
         </is>
       </c>
       <c r="F590" s="7" t="inlineStr">
@@ -22353,7 +22353,7 @@
       </c>
       <c r="E591" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 39.645 TL; VitrA/Artema 17 ürün; marka dağılımı: Artema:16, Newarc:3, Grohe:3, VitrA:1, Creavit:1</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺39.645; VitrA/Artema 17 ürün; marka dağılımı: Artema:16, Newarc:3, Grohe:3, VitrA:1, Creavit:1</t>
         </is>
       </c>
       <c r="F591" s="7" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="E592" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 22 eşleşen; medyan 3.829 TL; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:20, Penta:1, Fontana:1</t>
+          <t>24 ürün okundu, 22 eşleşen; medyan ₺3.829; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:20, Penta:1, Fontana:1</t>
         </is>
       </c>
       <c r="F592" s="7" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="E594" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 22 eşleşen; medyan 5.334 TL; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:17, Creavit:3, Turkuaz:1, (markasız):1</t>
+          <t>24 ürün okundu, 22 eşleşen; medyan ₺5.334; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:17, Creavit:3, Turkuaz:1, (markasız):1</t>
         </is>
       </c>
       <c r="F594" s="7" t="inlineStr">
@@ -22501,7 +22501,7 @@
       </c>
       <c r="E595" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 21 eşleşen; medyan 41.400 TL; VitrA/Artema 9 ürün; marka dağılımı: Artema:9, Penta:5, Newarc:3, Grohe:2, Fontana:1, E.C.A:1</t>
+          <t>24 ürün okundu, 21 eşleşen; medyan ₺41.400; VitrA/Artema 9 ürün; marka dağılımı: Artema:9, Penta:5, Newarc:3, Grohe:2, Fontana:1, E.C.A:1</t>
         </is>
       </c>
       <c r="F595" s="7" t="inlineStr">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="E597" s="6" t="inlineStr">
         <is>
-          <t>2 ürün okundu, 2 eşleşen; medyan 1.994 TL; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:2</t>
+          <t>2 ürün okundu, 2 eşleşen; medyan ₺1.994; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:2</t>
         </is>
       </c>
       <c r="F597" s="7" t="inlineStr">
@@ -22612,7 +22612,7 @@
       </c>
       <c r="E598" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 17.442 TL; VitrA/Artema 4 ürün; marka dağılımı: VitrA:4, Penta:1</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺17.442; VitrA/Artema 4 ürün; marka dağılımı: VitrA:4, Penta:1</t>
         </is>
       </c>
       <c r="F598" s="7" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="E599" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 2.540 TL; VitrA/Artema 1 ürün; marka dağılımı: VitrA:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺2.540; VitrA/Artema 1 ürün; marka dağılımı: VitrA:1</t>
         </is>
       </c>
       <c r="F599" s="7" t="inlineStr">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="E600" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 21.168 TL; VitrA/Artema 0 ürün; marka dağılımı: Lucco:20, Lena:3, Bocchi:1</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺21.168; VitrA/Artema 0 ürün; marka dağılımı: Lucco:20, Lena:3, Bocchi:1</t>
         </is>
       </c>
       <c r="F600" s="7" t="inlineStr">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="E601" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 14 eşleşen; medyan 4.487 TL; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:8, Lucco:5, Turkuaz:1</t>
+          <t>24 ürün okundu, 14 eşleşen; medyan ₺4.487; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:8, Lucco:5, Turkuaz:1</t>
         </is>
       </c>
       <c r="F601" s="7" t="inlineStr">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="E602" s="6" t="inlineStr">
         <is>
-          <t>2 ürün okundu, 2 eşleşen; medyan 23.070 TL; VitrA/Artema 1 ürün; marka dağılımı: VitrA:1, Creavit:1</t>
+          <t>2 ürün okundu, 2 eşleşen; medyan ₺23.070; VitrA/Artema 1 ürün; marka dağılımı: VitrA:1, Creavit:1</t>
         </is>
       </c>
       <c r="F602" s="7" t="inlineStr">
@@ -22797,7 +22797,7 @@
       </c>
       <c r="E603" s="6" t="inlineStr">
         <is>
-          <t>2 ürün okundu, 2 eşleşen; medyan 18.110 TL; VitrA/Artema 0 ürün; marka dağılımı: Hansgrohe:2</t>
+          <t>2 ürün okundu, 2 eşleşen; medyan ₺18.110; VitrA/Artema 0 ürün; marka dağılımı: Hansgrohe:2</t>
         </is>
       </c>
       <c r="F603" s="7" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="E604" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; medyan 8.110 TL; VitrA/Artema 4 ürün; marka dağılımı: VitrA:3, Artema:1, E.C.A:1, Grohe:1</t>
+          <t>6 ürün okundu, 6 eşleşen; medyan ₺8.110; VitrA/Artema 4 ürün; marka dağılımı: VitrA:3, Artema:1, E.C.A:1, Grohe:1</t>
         </is>
       </c>
       <c r="F604" s="7" t="inlineStr">
@@ -22871,7 +22871,7 @@
       </c>
       <c r="E605" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 23 eşleşen; medyan 49.020 TL; VitrA/Artema 3 ürün; marka dağılımı: Grohe:17, VitrA:3, Hansgrohe:3</t>
+          <t>24 ürün okundu, 23 eşleşen; medyan ₺49.020; VitrA/Artema 3 ürün; marka dağılımı: Grohe:17, VitrA:3, Hansgrohe:3</t>
         </is>
       </c>
       <c r="F605" s="7" t="inlineStr">
@@ -22908,7 +22908,7 @@
       </c>
       <c r="E606" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu, 18 eşleşen; medyan 12.176 TL; VitrA/Artema 0 ürün; marka dağılımı: (markasız):11, Penta:5, Bocchi:2</t>
+          <t>18 ürün okundu, 18 eşleşen; medyan ₺12.176; VitrA/Artema 0 ürün; marka dağılımı: (markasız):11, Penta:5, Bocchi:2</t>
         </is>
       </c>
       <c r="F606" s="7" t="inlineStr">
@@ -22945,7 +22945,7 @@
       </c>
       <c r="E607" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 3.257 TL; VitrA/Artema 6 ürün; marka dağılımı: Bocchi:16, Artema:6, Fontana:2</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺3.257; VitrA/Artema 6 ürün; marka dağılımı: Bocchi:16, Artema:6, Fontana:2</t>
         </is>
       </c>
       <c r="F607" s="7" t="inlineStr">
@@ -22982,7 +22982,7 @@
       </c>
       <c r="E608" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 14 eşleşen; medyan 17.590 TL; VitrA/Artema 3 ürün; marka dağılımı: Grohe:6, VitrA:3, Hansgrohe:3, Penta:1, Newarc:1</t>
+          <t>24 ürün okundu, 14 eşleşen; medyan ₺17.590; VitrA/Artema 3 ürün; marka dağılımı: Grohe:6, VitrA:3, Hansgrohe:3, Penta:1, Newarc:1</t>
         </is>
       </c>
       <c r="F608" s="7" t="inlineStr">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="E609" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 5.794 TL; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺5.794; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:1</t>
         </is>
       </c>
       <c r="F609" s="7" t="inlineStr">
@@ -23056,7 +23056,7 @@
       </c>
       <c r="E610" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 32.850 TL; VitrA/Artema 1 ürün; marka dağılımı: Lena:15, Duravit:2, VitrA:1</t>
+          <t>18 ürün okundu; medyan ₺32.850; VitrA/Artema 1 ürün; marka dağılımı: Lena:15, Duravit:2, VitrA:1</t>
         </is>
       </c>
       <c r="F610" s="7" t="inlineStr">
@@ -23093,7 +23093,7 @@
       </c>
       <c r="E611" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 25.513 TL; VitrA/Artema 3 ürün; marka dağılımı: Penta:9, Grohe:5, Artema:3, Newarc:1</t>
+          <t>18 ürün okundu; medyan ₺25.513; VitrA/Artema 3 ürün; marka dağılımı: Penta:9, Grohe:5, Artema:3, Newarc:1</t>
         </is>
       </c>
       <c r="F611" s="7" t="inlineStr">
@@ -23130,7 +23130,7 @@
       </c>
       <c r="E612" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 22.825 TL; VitrA/Artema 0 ürün; marka dağılımı: Aquanil:15, Orka:2, FYM:1</t>
+          <t>18 ürün okundu; medyan ₺22.825; VitrA/Artema 0 ürün; marka dağılımı: Aquanil:15, Orka:2, FYM:1</t>
         </is>
       </c>
       <c r="F612" s="7" t="inlineStr">
@@ -23167,7 +23167,7 @@
       </c>
       <c r="E613" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 10.373 TL; VitrA/Artema 1 ürün; marka dağılımı: Duravit:6, Lucco:6, Bocchi:5, VitrA:1</t>
+          <t>18 ürün okundu; medyan ₺10.373; VitrA/Artema 1 ürün; marka dağılımı: Duravit:6, Lucco:6, Bocchi:5, VitrA:1</t>
         </is>
       </c>
       <c r="F613" s="7" t="inlineStr">
@@ -23204,7 +23204,7 @@
       </c>
       <c r="E614" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 19.440 TL; VitrA/Artema 1 ürün; marka dağılımı: Grohe:7, Newarc:5, Mistillo:4, Penta:1, VitrA:1</t>
+          <t>18 ürün okundu; medyan ₺19.440; VitrA/Artema 1 ürün; marka dağılımı: Grohe:7, Newarc:5, Mistillo:4, Penta:1, VitrA:1</t>
         </is>
       </c>
       <c r="F614" s="7" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="E615" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 44.100 TL; VitrA/Artema 1 ürün; marka dağılımı: Grohe:9, Fontana:8, VitrA:1</t>
+          <t>18 ürün okundu; medyan ₺44.100; VitrA/Artema 1 ürün; marka dağılımı: Grohe:9, Fontana:8, VitrA:1</t>
         </is>
       </c>
       <c r="F615" s="7" t="inlineStr">
@@ -23278,7 +23278,7 @@
       </c>
       <c r="E616" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 27.060 TL; VitrA/Artema 0 ürün; marka dağılımı: Aquanil Duş:18</t>
+          <t>18 ürün okundu; medyan ₺27.060; VitrA/Artema 0 ürün; marka dağılımı: Aquanil Duş:18</t>
         </is>
       </c>
       <c r="F616" s="7" t="inlineStr">
@@ -23315,7 +23315,7 @@
       </c>
       <c r="E617" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 3.010 TL; VitrA/Artema 6 ürün; marka dağılımı: VitrA:6, Geberit:6, Creavit:5, Bocchi:1</t>
+          <t>18 ürün okundu; medyan ₺3.010; VitrA/Artema 6 ürün; marka dağılımı: VitrA:6, Geberit:6, Creavit:5, Bocchi:1</t>
         </is>
       </c>
       <c r="F617" s="7" t="inlineStr">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="E618" s="6" t="inlineStr">
         <is>
-          <t>15 ürün okundu; medyan 1.790 TL; VitrA/Artema 3 ürün; marka dağılımı: Creavit:10, VitrA:3, classis:1, Bocchi:1</t>
+          <t>15 ürün okundu; medyan ₺1.790; VitrA/Artema 3 ürün; marka dağılımı: Creavit:10, VitrA:3, classis:1, Bocchi:1</t>
         </is>
       </c>
       <c r="F618" s="7" t="inlineStr">
@@ -23389,7 +23389,7 @@
       </c>
       <c r="E619" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 6.395 TL; VitrA/Artema 11 ürün; marka dağılımı: VitrA:11, Duravit:4, Creavit:3</t>
+          <t>18 ürün okundu; medyan ₺6.395; VitrA/Artema 11 ürün; marka dağılımı: VitrA:11, Duravit:4, Creavit:3</t>
         </is>
       </c>
       <c r="F619" s="7" t="inlineStr">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="E620" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 13.230 TL; VitrA/Artema 2 ürün; marka dağılımı: Creavit:10, Turkuaz:4, classis:2, VitrA:2</t>
+          <t>18 ürün okundu; medyan ₺13.230; VitrA/Artema 2 ürün; marka dağılımı: Creavit:10, Turkuaz:4, classis:2, VitrA:2</t>
         </is>
       </c>
       <c r="F620" s="7" t="inlineStr">
@@ -23463,7 +23463,7 @@
       </c>
       <c r="E621" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 23.445 TL; VitrA/Artema 0 ürün; marka dağılımı: Shower:18</t>
+          <t>18 ürün okundu; medyan ₺23.445; VitrA/Artema 0 ürün; marka dağılımı: Shower:18</t>
         </is>
       </c>
       <c r="F621" s="7" t="inlineStr">
@@ -23500,7 +23500,7 @@
       </c>
       <c r="E622" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 39.616 TL; VitrA/Artema 0 ürün; marka dağılımı: FYM:9, Aquanil:7, Belinza:2</t>
+          <t>18 ürün okundu; medyan ₺39.616; VitrA/Artema 0 ürün; marka dağılımı: FYM:9, Aquanil:7, Belinza:2</t>
         </is>
       </c>
       <c r="F622" s="7" t="inlineStr">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="E623" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 12.600 TL; VitrA/Artema 0 ürün; marka dağılımı: Fontana:15, Penta:2, Grohe:1</t>
+          <t>18 ürün okundu; medyan ₺12.600; VitrA/Artema 0 ürün; marka dağılımı: Fontana:15, Penta:2, Grohe:1</t>
         </is>
       </c>
       <c r="F623" s="7" t="inlineStr">
@@ -23574,7 +23574,7 @@
       </c>
       <c r="E624" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 20.950 TL; VitrA/Artema 0 ürün; marka dağılımı: Duravit:12, Lena:6</t>
+          <t>18 ürün okundu; medyan ₺20.950; VitrA/Artema 0 ürün; marka dağılımı: Duravit:12, Lena:6</t>
         </is>
       </c>
       <c r="F624" s="7" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="E625" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 27.972 TL; VitrA/Artema 0 ürün; marka dağılımı: Lucco:15, Turkuaz:3</t>
+          <t>18 ürün okundu; medyan ₺27.972; VitrA/Artema 0 ürün; marka dağılımı: Lucco:15, Turkuaz:3</t>
         </is>
       </c>
       <c r="F625" s="7" t="inlineStr">
@@ -23648,7 +23648,7 @@
       </c>
       <c r="E626" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu; medyan 25.116 TL; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:17, Creavit:1</t>
+          <t>18 ürün okundu; medyan ₺25.116; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:17, Creavit:1</t>
         </is>
       </c>
       <c r="F626" s="7" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="E627" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 2.270 TL; VitrA/Artema 0 ürün; marka dağılımı: Akd Bagno:11/0, Venüs:6/4, Lider:6/0, Kare:1/0</t>
+          <t>24 ürün okundu; medyan ₺2.270; VitrA/Artema 0 ürün; marka dağılımı: Akd Bagno:11/0, Venüs:6/4, Lider:6/0, Kare:1/0</t>
         </is>
       </c>
       <c r="F627" s="7" t="inlineStr">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="E628" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 6.690 TL; VitrA/Artema 3 ürün; marka dağılımı: ECA:5/0, Grohe:5/0, Adell:4/0, Artema:3/0, Punto:2/0, Penta:2/1, AR:1/0, Camargue:1/0</t>
+          <t>24 ürün okundu; medyan ₺6.690; VitrA/Artema 3 ürün; marka dağılımı: ECA:5/0, Grohe:5/0, Adell:4/0, Artema:3/0, Punto:2/0, Penta:2/1, AR:1/0, Camargue:1/0</t>
         </is>
       </c>
       <c r="F628" s="7" t="inlineStr">
@@ -23759,7 +23759,7 @@
       </c>
       <c r="E629" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 5.500 TL; VitrA/Artema 5 ürün; marka dağılımı: Artema:5/0, Grohe:4/1, ECA:4/0, Adell:4/2, Penta:4/0, Punto:2/1, AR:1/0</t>
+          <t>24 ürün okundu; medyan ₺5.500; VitrA/Artema 5 ürün; marka dağılımı: Artema:5/0, Grohe:4/1, ECA:4/0, Adell:4/2, Penta:4/0, Punto:2/1, AR:1/0</t>
         </is>
       </c>
       <c r="F629" s="7" t="inlineStr">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="E630" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 6.300 TL; VitrA/Artema 0 ürün; marka dağılımı: Movemo:22/1, Fly:2/0</t>
+          <t>24 ürün okundu; medyan ₺6.300; VitrA/Artema 0 ürün; marka dağılımı: Movemo:22/1, Fly:2/0</t>
         </is>
       </c>
       <c r="F630" s="7" t="inlineStr">
@@ -23833,7 +23833,7 @@
       </c>
       <c r="E631" s="6" t="inlineStr">
         <is>
-          <t>4 ürün okundu; medyan 720 TL; VitrA/Artema 0 ürün; marka dağılımı: Penta:3/3, Hansgrohe:1/0</t>
+          <t>4 ürün okundu; medyan ₺720; VitrA/Artema 0 ürün; marka dağılımı: Penta:3/3, Hansgrohe:1/0</t>
         </is>
       </c>
       <c r="F631" s="7" t="inlineStr">
@@ -23870,7 +23870,7 @@
       </c>
       <c r="E632" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 7.790 TL; VitrA/Artema 2 ürün; marka dağılımı: Penta:8/1, AR:3/0, Grohe:3/3, Adell:3/0, ECA:2/0, Punto:2/0, Artema:2/0, Camargue:1/3</t>
+          <t>24 ürün okundu; medyan ₺7.790; VitrA/Artema 2 ürün; marka dağılımı: Penta:8/1, AR:3/0, Grohe:3/3, Adell:3/0, ECA:2/0, Punto:2/0, Artema:2/0, Camargue:1/3</t>
         </is>
       </c>
       <c r="F632" s="7" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="E633" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 14.345 TL; VitrA/Artema 0 ürün; marka dağılımı: Er-Duş:24/0</t>
+          <t>24 ürün okundu; medyan ₺14.345; VitrA/Artema 0 ürün; marka dağılımı: Er-Duş:24/0</t>
         </is>
       </c>
       <c r="F633" s="7" t="inlineStr">
@@ -23921,7 +23921,7 @@
         </is>
       </c>
     </row>
-    <row r="634" ht="43.5" customHeight="1">
+    <row r="634" ht="30" customHeight="1">
       <c r="A634" s="5" t="inlineStr">
         <is>
           <t>https://www.bauhaus.com.tr/bauhaus-banyo-klozet-ve-klozet-kapaklari-klozet-kapaklari</t>
@@ -23944,7 +23944,7 @@
       </c>
       <c r="E634" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 2.590 TL; VitrA/Artema 6 ürün; marka dağılımı: Poseidon:7/3, VitrA:6/4, Serel:4/0, Japar:3/1, Visam:2/0, Rulopak:1/0, Camargue:1/0</t>
+          <t>24 ürün okundu; medyan ₺2.590; VitrA/Artema 6 ürün; marka dağılımı: Poseidon:7/3, VitrA:6/4, Serel:4/0, Japar:3/1, Visam:2/0, Rulopak:1/0, Camargue:1/0</t>
         </is>
       </c>
       <c r="F634" s="7" t="inlineStr">
@@ -23981,7 +23981,7 @@
       </c>
       <c r="E635" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 10.990 TL; VitrA/Artema 10 ürün; marka dağılımı: VitrA:8/3, Serel:8/0, (markasız):3/0, Karen Banyo:1/1, Kale Banyo:1/0, Geberit:1/0, Kale:1</t>
+          <t>24 ürün okundu; medyan ₺10.990; VitrA/Artema 10 ürün; marka dağılımı: VitrA:8/3, Serel:8/0, (markasız):3/0, Karen Banyo:1/1, Kale Banyo:1/0, Geberit:1/0, Kale:1</t>
         </is>
       </c>
       <c r="F635" s="7" t="inlineStr">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="E636" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 6.745 TL; VitrA/Artema 0 ürün; marka dağılımı: Er-Duş:24/0</t>
+          <t>24 ürün okundu; medyan ₺6.745; VitrA/Artema 0 ürün; marka dağılımı: Er-Duş:24/0</t>
         </is>
       </c>
       <c r="F636" s="7" t="inlineStr">
@@ -24055,7 +24055,7 @@
       </c>
       <c r="E637" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 4.545 TL; VitrA/Artema 0 ürün; marka dağılımı: Serel:10/1, Euroser:6/0, Kale Banyo:5/0, Karen Banyo:2/4, Kale:1/0</t>
+          <t>24 ürün okundu; medyan ₺4.545; VitrA/Artema 0 ürün; marka dağılımı: Serel:10/1, Euroser:6/0, Kale Banyo:5/0, Karen Banyo:2/4, Kale:1/0</t>
         </is>
       </c>
       <c r="F637" s="7" t="inlineStr">
@@ -24092,7 +24092,7 @@
       </c>
       <c r="E638" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 1.190 TL; VitrA/Artema 3 ürün; marka dağılımı: Admiral:13/4, Dgvision:4/0, ECA:3/0, Artema:2/0, VitrA:1/0, Camargue:1/0</t>
+          <t>24 ürün okundu; medyan ₺1.190; VitrA/Artema 3 ürün; marka dağılımı: Admiral:13/4, Dgvision:4/0, ECA:3/0, Artema:2/0, VitrA:1/0, Camargue:1/0</t>
         </is>
       </c>
       <c r="F638" s="7" t="inlineStr">
@@ -24129,7 +24129,7 @@
       </c>
       <c r="E639" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 895 TL; VitrA/Artema 3 ürün; marka dağılımı: Serel:5/0, Japar:5/2, VitrA:3/1, Visam:3/2, Admiral:2/1, Norm:2/3, Geberit:2/0, Kale:2/2</t>
+          <t>24 ürün okundu; medyan ₺895; VitrA/Artema 3 ürün; marka dağılımı: Serel:5/0, Japar:5/2, VitrA:3/1, Visam:3/2, Admiral:2/1, Norm:2/3, Geberit:2/0, Kale:2/2</t>
         </is>
       </c>
       <c r="F639" s="7" t="inlineStr">
@@ -24166,7 +24166,7 @@
       </c>
       <c r="E640" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 550 TL; VitrA/Artema 0 ürün; marka dağılımı: Adell:13/2, Admiral:6/2, Japar:2/2, ECA:2/0, İlöz:1/1</t>
+          <t>24 ürün okundu; medyan ₺550; VitrA/Artema 0 ürün; marka dağılımı: Adell:13/2, Admiral:6/2, Japar:2/2, ECA:2/0, İlöz:1/1</t>
         </is>
       </c>
       <c r="F640" s="7" t="inlineStr">
@@ -24203,7 +24203,7 @@
       </c>
       <c r="E641" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu; medyan 749 TL; VitrA/Artema 0 ürün; marka dağılımı: Admiral:16/1, Penta:2/2, Diaqua:1/0, Camargue:1/0, AR:1/0, Yak:1/0, ECA:1/0, Adell:1/0</t>
+          <t>24 ürün okundu; medyan ₺749; VitrA/Artema 0 ürün; marka dağılımı: Admiral:16/1, Penta:2/2, Diaqua:1/0, Camargue:1/0, AR:1/0, Yak:1/0, ECA:1/0, Adell:1/0</t>
         </is>
       </c>
       <c r="F641" s="7" t="inlineStr">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="E642" s="6" t="inlineStr">
         <is>
-          <t>15 ürün okundu, 9 eşleşen; medyan 7.500 TL; VitrA/Artema 0 ürün; marka dağılımı: Kale Banyo:5, Serel:4</t>
+          <t>15 ürün okundu, 9 eşleşen; medyan ₺7.500; VitrA/Artema 0 ürün; marka dağılımı: Kale Banyo:5, Serel:4</t>
         </is>
       </c>
       <c r="F642" s="7" t="inlineStr">
@@ -24425,7 +24425,7 @@
       </c>
       <c r="E647" s="6" t="inlineStr">
         <is>
-          <t>11 ürün okundu, 11 eşleşen; medyan 1.490 TL; VitrA/Artema 2 ürün; marka dağılımı: Admiral:4, Kale:3, VitrA:1, Artema:1, Geberit:1, Camargue:1</t>
+          <t>11 ürün okundu, 11 eşleşen; medyan ₺1.490; VitrA/Artema 2 ürün; marka dağılımı: Admiral:4, Kale:3, VitrA:1, Artema:1, Geberit:1, Camargue:1</t>
         </is>
       </c>
       <c r="F647" s="7" t="inlineStr">
@@ -24610,7 +24610,7 @@
       </c>
       <c r="E652" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 6.890 TL; VitrA/Artema 2 ürün; marka dağılımı: Karen Banyo:10, Bonitobagno:5, Gold Banyo:3, VitrA:2, Polka:2, (markasız):1</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺6.890; VitrA/Artema 2 ürün; marka dağılımı: Karen Banyo:10, Bonitobagno:5, Gold Banyo:3, VitrA:2, Polka:2, (markasız):1</t>
         </is>
       </c>
       <c r="F652" s="7" t="inlineStr">
@@ -24684,7 +24684,7 @@
       </c>
       <c r="E654" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 1.290 TL; VitrA/Artema 0 ürün; marka dağılımı: Primanova:15, Kare:6, Dünya Plastik:1, Aben:1, Asz:1</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺1.290; VitrA/Artema 0 ürün; marka dağılımı: Primanova:15, Kare:6, Dünya Plastik:1, Aben:1, Asz:1</t>
         </is>
       </c>
       <c r="F654" s="7" t="inlineStr">
@@ -24721,7 +24721,7 @@
       </c>
       <c r="E655" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; medyan 984 TL; VitrA/Artema 0 ürün; marka dağılımı: Grohe:3, Primanova:1, Admiral:1, tekno-tel:1</t>
+          <t>6 ürün okundu, 6 eşleşen; medyan ₺984; VitrA/Artema 0 ürün; marka dağılımı: Grohe:3, Primanova:1, Admiral:1, tekno-tel:1</t>
         </is>
       </c>
       <c r="F655" s="7" t="inlineStr">
@@ -24943,7 +24943,7 @@
       </c>
       <c r="E661" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 759 TL; VitrA/Artema 0 ürün; marka dağılımı: Primanova:24</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺759; VitrA/Artema 0 ürün; marka dağılımı: Primanova:24</t>
         </is>
       </c>
       <c r="F661" s="7" t="inlineStr">
@@ -25091,7 +25091,7 @@
       </c>
       <c r="E665" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 459 TL; VitrA/Artema 0 ürün; marka dağılımı: Marin:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺459; VitrA/Artema 0 ürün; marka dağılımı: Marin:1</t>
         </is>
       </c>
       <c r="F665" s="7" t="inlineStr">
@@ -25202,7 +25202,7 @@
       </c>
       <c r="E668" s="6" t="inlineStr">
         <is>
-          <t>4 ürün okundu, 4 eşleşen; medyan 6.390 TL; VitrA/Artema 1 ürün; marka dağılımı: Punto:2, Artema:1, AR:1</t>
+          <t>4 ürün okundu, 4 eşleşen; medyan ₺6.390; VitrA/Artema 1 ürün; marka dağılımı: Punto:2, Artema:1, AR:1</t>
         </is>
       </c>
       <c r="F668" s="7" t="inlineStr">
@@ -25313,7 +25313,7 @@
       </c>
       <c r="E671" s="6" t="inlineStr">
         <is>
-          <t>2 ürün okundu, 2 eşleşen; medyan 1.845 TL; VitrA/Artema 1 ürün; marka dağılımı: Artema:1, Punto:1</t>
+          <t>2 ürün okundu, 2 eşleşen; medyan ₺1.845; VitrA/Artema 1 ürün; marka dağılımı: Artema:1, Punto:1</t>
         </is>
       </c>
       <c r="F671" s="7" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="E672" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 13.500 TL; VitrA/Artema 0 ürün; marka dağılımı: Kale:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺13.500; VitrA/Artema 0 ürün; marka dağılımı: Kale:1</t>
         </is>
       </c>
       <c r="F672" s="7" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="E674" s="6" t="inlineStr">
         <is>
-          <t>2 ürün okundu, 2 eşleşen; medyan 14.990 TL; VitrA/Artema 0 ürün; marka dağılımı: Penta:1, Grohe:1</t>
+          <t>2 ürün okundu, 2 eşleşen; medyan ₺14.990; VitrA/Artema 0 ürün; marka dağılımı: Penta:1, Grohe:1</t>
         </is>
       </c>
       <c r="F674" s="7" t="inlineStr">
@@ -25461,7 +25461,7 @@
       </c>
       <c r="E675" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 13 eşleşen; medyan 469 TL; VitrA/Artema 0 ürün; marka dağılımı: Primanova:5, Okyanus Home:3, Unkatech:2, Kare:2, Camero:1</t>
+          <t>24 ürün okundu, 13 eşleşen; medyan ₺469; VitrA/Artema 0 ürün; marka dağılımı: Primanova:5, Okyanus Home:3, Unkatech:2, Kare:2, Camero:1</t>
         </is>
       </c>
       <c r="F675" s="7" t="inlineStr">
@@ -25794,7 +25794,7 @@
       </c>
       <c r="E684" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 1.690 TL; VitrA/Artema 0 ürün; marka dağılımı: Venüs:4, Kare:1</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺1.690; VitrA/Artema 0 ürün; marka dağılımı: Venüs:4, Kare:1</t>
         </is>
       </c>
       <c r="F684" s="7" t="inlineStr">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="E693" s="6" t="inlineStr">
         <is>
-          <t>4 ürün okundu, 4 eşleşen; medyan 11.790 TL; VitrA/Artema 0 ürün; marka dağılımı: Grohe:2, Hansgrohe:1, ECA:1</t>
+          <t>4 ürün okundu, 4 eşleşen; medyan ₺11.790; VitrA/Artema 0 ürün; marka dağılımı: Grohe:2, Hansgrohe:1, ECA:1</t>
         </is>
       </c>
       <c r="F693" s="7" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="E694" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 1.209 TL; VitrA/Artema 0 ürün; marka dağılımı: Primanova:23, Venüs:1</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺1.209; VitrA/Artema 0 ürün; marka dağılımı: Primanova:23, Venüs:1</t>
         </is>
       </c>
       <c r="F694" s="7" t="inlineStr">
@@ -26201,7 +26201,7 @@
       </c>
       <c r="E695" s="6" t="inlineStr">
         <is>
-          <t>20 ürün okundu, 20 eşleşen; medyan 890 TL; VitrA/Artema 0 ürün; marka dağılımı: Kare:7, tekno-tel:6, Venüs:3, Minimax:2, Marin:2</t>
+          <t>20 ürün okundu, 20 eşleşen; medyan ₺890; VitrA/Artema 0 ürün; marka dağılımı: Kare:7, tekno-tel:6, Venüs:3, Minimax:2, Marin:2</t>
         </is>
       </c>
       <c r="F695" s="7" t="inlineStr">
@@ -26349,7 +26349,7 @@
       </c>
       <c r="E699" s="6" t="inlineStr">
         <is>
-          <t>4 ürün okundu, kategori toplamı 206; medyan 136.275 TL; satıcı sayısı medyanı 1; VitrA/Artema 2 ürün; mağaza ve marka filtresi</t>
+          <t>4 ürün okundu, kategori toplamı 206; medyan ₺136.275; satıcı sayısı medyanı 1; VitrA/Artema 2 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F699" s="7" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="E700" s="6" t="inlineStr">
         <is>
-          <t>31 ürün okundu, 31 eşleşen; medyan 1.460 TL; satıcı sayısı medyanı 4; VitrA/Artema 20 ürün</t>
+          <t>31 ürün okundu, 31 eşleşen; medyan ₺1.460; satıcı sayısı medyanı 4; VitrA/Artema 20 ürün</t>
         </is>
       </c>
       <c r="F700" s="7" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="E701" s="6" t="inlineStr">
         <is>
-          <t>63 ürün okundu, kategori toplamı 1017; medyan 948 TL; satıcı sayısı medyanı 4; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
+          <t>63 ürün okundu, kategori toplamı 1017; medyan ₺948; satıcı sayısı medyanı 4; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F701" s="7" t="inlineStr">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="E702" s="6" t="inlineStr">
         <is>
-          <t>31 ürün okundu, 31 eşleşen; medyan 1.482 TL; satıcı sayısı medyanı 1; VitrA/Artema 1 ürün</t>
+          <t>31 ürün okundu, 31 eşleşen; medyan ₺1.482; satıcı sayısı medyanı 1; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F702" s="7" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="E703" s="6" t="inlineStr">
         <is>
-          <t>27 ürün okundu, 27 eşleşen; medyan 388 TL; satıcı sayısı medyanı 3; VitrA/Artema 0 ürün</t>
+          <t>27 ürün okundu, 27 eşleşen; medyan ₺388; satıcı sayısı medyanı 3; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F703" s="7" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="E704" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 22.808 TL; satıcı sayısı medyanı 3; VitrA/Artema 1 ürün</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺22.808; satıcı sayısı medyanı 3; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F704" s="7" t="inlineStr">
@@ -26571,7 +26571,7 @@
       </c>
       <c r="E705" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 30 eşleşen; medyan 10.144 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 7 ürün</t>
+          <t>30 ürün okundu, 30 eşleşen; medyan ₺10.144; satıcı sayısı medyanı 2.0; VitrA/Artema 7 ürün</t>
         </is>
       </c>
       <c r="F705" s="7" t="inlineStr">
@@ -26608,7 +26608,7 @@
       </c>
       <c r="E706" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 6.923 TL; satıcı sayısı medyanı 7; VitrA/Artema 0 ürün</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺6.923; satıcı sayısı medyanı 7; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F706" s="7" t="inlineStr">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="E707" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 3 eşleşen; medyan 6.600 TL; satıcı sayısı medyanı 6; VitrA/Artema 1 ürün</t>
+          <t>5 ürün okundu, 3 eşleşen; medyan ₺6.600; satıcı sayısı medyanı 6; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F707" s="7" t="inlineStr">
@@ -26682,7 +26682,7 @@
       </c>
       <c r="E708" s="6" t="inlineStr">
         <is>
-          <t>11 ürün okundu, 11 eşleşen; medyan 6.410 TL; satıcı sayısı medyanı 1; VitrA/Artema 2 ürün</t>
+          <t>11 ürün okundu, 11 eşleşen; medyan ₺6.410; satıcı sayısı medyanı 1; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F708" s="7" t="inlineStr">
@@ -26719,7 +26719,7 @@
       </c>
       <c r="E709" s="6" t="inlineStr">
         <is>
-          <t>4 ürün okundu, 4 eşleşen; medyan 15.354 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>4 ürün okundu, 4 eşleşen; medyan ₺15.354; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F709" s="7" t="inlineStr">
@@ -26756,7 +26756,7 @@
       </c>
       <c r="E710" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 30 eşleşen; medyan 410 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
+          <t>30 ürün okundu, 30 eşleşen; medyan ₺410; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F710" s="7" t="inlineStr">
@@ -26793,7 +26793,7 @@
       </c>
       <c r="E711" s="6" t="inlineStr">
         <is>
-          <t>7 ürün okundu, 7 eşleşen; medyan 4.632 TL; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
+          <t>7 ürün okundu, 7 eşleşen; medyan ₺4.632; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F711" s="7" t="inlineStr">
@@ -26830,7 +26830,7 @@
       </c>
       <c r="E712" s="6" t="inlineStr">
         <is>
-          <t>20 ürün okundu, 20 eşleşen; medyan 45.684 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün</t>
+          <t>20 ürün okundu, 20 eşleşen; medyan ₺45.684; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F712" s="7" t="inlineStr">
@@ -26867,7 +26867,7 @@
       </c>
       <c r="E713" s="6" t="inlineStr">
         <is>
-          <t>14 ürün okundu, 14 eşleşen; medyan 4.740 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 5 ürün</t>
+          <t>14 ürün okundu, 14 eşleşen; medyan ₺4.740; satıcı sayısı medyanı 1.0; VitrA/Artema 5 ürün</t>
         </is>
       </c>
       <c r="F713" s="7" t="inlineStr">
@@ -26904,7 +26904,7 @@
       </c>
       <c r="E714" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 30 eşleşen; medyan 1.965 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 12 ürün</t>
+          <t>30 ürün okundu, 30 eşleşen; medyan ₺1.965; satıcı sayısı medyanı 1.0; VitrA/Artema 12 ürün</t>
         </is>
       </c>
       <c r="F714" s="7" t="inlineStr">
@@ -26941,7 +26941,7 @@
       </c>
       <c r="E715" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 30 eşleşen; medyan 15.360 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 14 ürün</t>
+          <t>30 ürün okundu, 30 eşleşen; medyan ₺15.360; satıcı sayısı medyanı 2.0; VitrA/Artema 14 ürün</t>
         </is>
       </c>
       <c r="F715" s="7" t="inlineStr">
@@ -26978,7 +26978,7 @@
       </c>
       <c r="E716" s="6" t="inlineStr">
         <is>
-          <t>11 ürün okundu, 11 eşleşen; medyan 9.550 TL; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
+          <t>11 ürün okundu, 11 eşleşen; medyan ₺9.550; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F716" s="7" t="inlineStr">
@@ -27015,7 +27015,7 @@
       </c>
       <c r="E717" s="6" t="inlineStr">
         <is>
-          <t>31 ürün okundu, 31 eşleşen; medyan 2.508 TL; satıcı sayısı medyanı 3; VitrA/Artema 16 ürün</t>
+          <t>31 ürün okundu, 31 eşleşen; medyan ₺2.508; satıcı sayısı medyanı 3; VitrA/Artema 16 ürün</t>
         </is>
       </c>
       <c r="F717" s="7" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="E718" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu, 18 eşleşen; medyan 38.000 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 1 ürün</t>
+          <t>18 ürün okundu, 18 eşleşen; medyan ₺38.000; satıcı sayısı medyanı 2.0; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F718" s="7" t="inlineStr">
@@ -27089,7 +27089,7 @@
       </c>
       <c r="E719" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 30 eşleşen; medyan 9.554 TL; satıcı sayısı medyanı 3.5; VitrA/Artema 1 ürün</t>
+          <t>30 ürün okundu, 30 eşleşen; medyan ₺9.554; satıcı sayısı medyanı 3.5; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F719" s="7" t="inlineStr">
@@ -27126,7 +27126,7 @@
       </c>
       <c r="E720" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 2.650 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺2.650; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F720" s="7" t="inlineStr">
@@ -27163,7 +27163,7 @@
       </c>
       <c r="E721" s="6" t="inlineStr">
         <is>
-          <t>29 ürün okundu, 29 eşleşen; medyan 44.285 TL; satıcı sayısı medyanı 3; VitrA/Artema 3 ürün</t>
+          <t>29 ürün okundu, 29 eşleşen; medyan ₺44.285; satıcı sayısı medyanı 3; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F721" s="7" t="inlineStr">
@@ -27200,7 +27200,7 @@
       </c>
       <c r="E722" s="6" t="inlineStr">
         <is>
-          <t>3 ürün okundu, 3 eşleşen; medyan 279 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
+          <t>3 ürün okundu, 3 eşleşen; medyan ₺279; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F722" s="7" t="inlineStr">
@@ -27237,7 +27237,7 @@
       </c>
       <c r="E723" s="6" t="inlineStr">
         <is>
-          <t>19 ürün okundu, 19 eşleşen; medyan 1.399 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
+          <t>19 ürün okundu, 19 eşleşen; medyan ₺1.399; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F723" s="7" t="inlineStr">
@@ -27274,7 +27274,7 @@
       </c>
       <c r="E724" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; medyan 1.511 TL; satıcı sayısı medyanı 1.5; VitrA/Artema 1 ürün</t>
+          <t>6 ürün okundu, 6 eşleşen; medyan ₺1.511; satıcı sayısı medyanı 1.5; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F724" s="7" t="inlineStr">
@@ -27311,7 +27311,7 @@
       </c>
       <c r="E725" s="6" t="inlineStr">
         <is>
-          <t>29 ürün okundu, 29 eşleşen; medyan 1.039 TL; satıcı sayısı medyanı 3; VitrA/Artema 2 ürün</t>
+          <t>29 ürün okundu, 29 eşleşen; medyan ₺1.039; satıcı sayısı medyanı 3; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F725" s="7" t="inlineStr">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="E726" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; medyan 17.972 TL; satıcı sayısı medyanı 3.5; VitrA/Artema 5 ürün</t>
+          <t>6 ürün okundu, 6 eşleşen; medyan ₺17.972; satıcı sayısı medyanı 3.5; VitrA/Artema 5 ürün</t>
         </is>
       </c>
       <c r="F726" s="7" t="inlineStr">
@@ -27385,7 +27385,7 @@
       </c>
       <c r="E727" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 3.510 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 16 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺3.510; satıcı sayısı medyanı 3.0; VitrA/Artema 16 ürün</t>
         </is>
       </c>
       <c r="F727" s="7" t="inlineStr">
@@ -27422,7 +27422,7 @@
       </c>
       <c r="E728" s="6" t="inlineStr">
         <is>
-          <t>28 ürün okundu, 28 eşleşen; medyan 3.934 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 7 ürün</t>
+          <t>28 ürün okundu, 28 eşleşen; medyan ₺3.934; satıcı sayısı medyanı 3.0; VitrA/Artema 7 ürün</t>
         </is>
       </c>
       <c r="F728" s="7" t="inlineStr">
@@ -27459,7 +27459,7 @@
       </c>
       <c r="E729" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, 32 eşleşen; medyan 16.973 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 7 ürün</t>
+          <t>32 ürün okundu, 32 eşleşen; medyan ₺16.973; satıcı sayısı medyanı 3.0; VitrA/Artema 7 ürün</t>
         </is>
       </c>
       <c r="F729" s="7" t="inlineStr">
@@ -27496,7 +27496,7 @@
       </c>
       <c r="E730" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 30 eşleşen; medyan 891 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün</t>
+          <t>30 ürün okundu, 30 eşleşen; medyan ₺891; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F730" s="7" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="E731" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 30 eşleşen; medyan 1.013 TL; satıcı sayısı medyanı 3.5; VitrA/Artema 6 ürün</t>
+          <t>30 ürün okundu, 30 eşleşen; medyan ₺1.013; satıcı sayısı medyanı 3.5; VitrA/Artema 6 ürün</t>
         </is>
       </c>
       <c r="F731" s="7" t="inlineStr">
@@ -27570,7 +27570,7 @@
       </c>
       <c r="E732" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 2.800 TL; satıcı sayısı medyanı 3; VitrA/Artema 0 ürün</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺2.800; satıcı sayısı medyanı 3; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F732" s="7" t="inlineStr">
@@ -27607,7 +27607,7 @@
       </c>
       <c r="E733" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 30 eşleşen; medyan 4.445 TL; satıcı sayısı medyanı 2.5; VitrA/Artema 2 ürün</t>
+          <t>30 ürün okundu, 30 eşleşen; medyan ₺4.445; satıcı sayısı medyanı 2.5; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F733" s="7" t="inlineStr">
@@ -27644,7 +27644,7 @@
       </c>
       <c r="E734" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 4.469 TL; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺4.469; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F734" s="7" t="inlineStr">
@@ -27681,7 +27681,7 @@
       </c>
       <c r="E735" s="6" t="inlineStr">
         <is>
-          <t>31 ürün okundu, 31 eşleşen; medyan 7.399 TL; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
+          <t>31 ürün okundu, 31 eşleşen; medyan ₺7.399; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F735" s="7" t="inlineStr">
@@ -27718,7 +27718,7 @@
       </c>
       <c r="E736" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 981 ürün; ilk 30 ürünün fiyatı en düşük 179, medyan 5.390, en yüksek 25.045 TL; marka sırası: Buffer, Artema, Creavit, IKEA, Paşabahçe, VitrA, Dekorister, Grohe, Vivense, Bocchi; mağaza sırası: Koçtaş, PttAVM, Hepsiburada, idefix, Amazon | 59 ürün okundu, kategori toplamı 981; medyan 5.290 TL; satıcı sayısı medyanı 1; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
+          <t>Kategoride 981 ürün; ilk 30 ürünün fiyatı en düşük 179, medyan 5.390, en yüksek ₺25.045; marka sırası: Buffer, Artema, Creavit, IKEA, Paşabahçe, VitrA, Dekorister, Grohe, Vivense, Bocchi; mağaza sırası: Koçtaş, PttAVM, Hepsiburada, idefix, Amazon | 59 ürün okundu, kategori toplamı 981; medyan ₺5.290; satıcı sayısı medyanı 1; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F736" s="7" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="E737" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 1.582 ürün; ilk 32 ürünün fiyatı en düşük 1.038, medyan 3.809, en yüksek 10.089 TL; marka sırası: E.C.A, Artema, GPD, Creavit, Vilas, Grohe, Ar, Sardıcı, Şenpres, Punto; mağaza sırası: Hepsiburada, idefix, PttAVM, Koçtaş, Amazon | 64 ürün okundu, kategori toplamı 1540; medyan 3.836 TL; satıcı sayısı medyanı 10.0; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
+          <t>Kategoride 1.582 ürün; ilk 32 ürünün fiyatı en düşük 1.038, medyan 3.809, en yüksek ₺10.089; marka sırası: E.C.A, Artema, GPD, Creavit, Vilas, Grohe, Ar, Sardıcı, Şenpres, Punto; mağaza sırası: Hepsiburada, idefix, PttAVM, Koçtaş, Amazon | 64 ürün okundu, kategori toplamı 1540; medyan ₺3.836; satıcı sayısı medyanı 10.0; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F737" s="7" t="inlineStr">
@@ -27769,7 +27769,7 @@
         </is>
       </c>
     </row>
-    <row r="738" ht="84" customHeight="1">
+    <row r="738" ht="70.5" customHeight="1">
       <c r="A738" s="5" t="inlineStr">
         <is>
           <t>https://www.cimri.com/banyo-dolabi</t>
@@ -27792,7 +27792,7 @@
       </c>
       <c r="E738" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 3.814 ürün; ilk 32 ürünün fiyatı en düşük 1.428, medyan 5.158, en yüksek 17.744 TL; marka sırası: Kenzlife, Teta Home, Orka, Denko, VitrA, Evdemo, Roomart, Remaks, Creavit, Noowa; mağaza sırası: Hepsiburada, PttAVM, Koçtaş, Trendyol, idefix | 32 ürün okundu, kategori toplamı 3171; medyan 5.004 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 2 ürün; mağaza ve marka filtresi</t>
+          <t>Kategoride 3.814 ürün; ilk 32 ürünün fiyatı en düşük 1.428, medyan 5.158, en yüksek ₺17.744; marka sırası: Kenzlife, Teta Home, Orka, Denko, VitrA, Evdemo, Roomart, Remaks, Creavit, Noowa; mağaza sırası: Hepsiburada, PttAVM, Koçtaş, Trendyol, idefix | 32 ürün okundu, kategori toplamı 3171; medyan ₺5.004; satıcı sayısı medyanı 2.0; VitrA/Artema 2 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F738" s="7" t="inlineStr">
@@ -27829,7 +27829,7 @@
       </c>
       <c r="E739" s="6" t="inlineStr">
         <is>
-          <t>59 ürün okundu, kategori toplamı 11234; medyan 455 TL; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>59 ürün okundu, kategori toplamı 11234; medyan ₺455; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F739" s="7" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="E740" s="6" t="inlineStr">
         <is>
-          <t>59 ürün okundu, kategori toplamı 766; medyan 671 TL; satıcı sayısı medyanı 2; VitrA/Artema 1 ürün; mağaza ve marka filtresi</t>
+          <t>59 ürün okundu, kategori toplamı 766; medyan ₺671; satıcı sayısı medyanı 2; VitrA/Artema 1 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F740" s="7" t="inlineStr">
@@ -27903,7 +27903,7 @@
       </c>
       <c r="E741" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu, kategori toplamı 62; medyan 9.999 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>18 ürün okundu, kategori toplamı 62; medyan ₺9.999; satıcı sayısı medyanı 1.0; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F741" s="7" t="inlineStr">
@@ -27940,7 +27940,7 @@
       </c>
       <c r="E742" s="6" t="inlineStr">
         <is>
-          <t>31 ürün okundu, kategori toplamı 4893; medyan 2.199 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>31 ürün okundu, kategori toplamı 4893; medyan ₺2.199; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F742" s="7" t="inlineStr">
@@ -27977,7 +27977,7 @@
       </c>
       <c r="E743" s="6" t="inlineStr">
         <is>
-          <t>61 ürün okundu, kategori toplamı 140; medyan 3.612 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>61 ürün okundu, kategori toplamı 140; medyan ₺3.612; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F743" s="7" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="E744" s="6" t="inlineStr">
         <is>
-          <t>29 ürün okundu, 24 eşleşen; medyan 6.267 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 7 ürün</t>
+          <t>29 ürün okundu, 24 eşleşen; medyan ₺6.267; satıcı sayısı medyanı 2.0; VitrA/Artema 7 ürün</t>
         </is>
       </c>
       <c r="F744" s="7" t="inlineStr">
@@ -28051,7 +28051,7 @@
       </c>
       <c r="E745" s="6" t="inlineStr">
         <is>
-          <t>63 ürün okundu, kategori toplamı 3486; medyan 1.449 TL; satıcı sayısı medyanı 4; VitrA/Artema 5 ürün; mağaza ve marka filtresi</t>
+          <t>63 ürün okundu, kategori toplamı 3486; medyan ₺1.449; satıcı sayısı medyanı 4; VitrA/Artema 5 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F745" s="7" t="inlineStr">
@@ -28088,7 +28088,7 @@
       </c>
       <c r="E746" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 30 eşleşen; medyan 2.244 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 11 ürün</t>
+          <t>30 ürün okundu, 30 eşleşen; medyan ₺2.244; satıcı sayısı medyanı 2.0; VitrA/Artema 11 ürün</t>
         </is>
       </c>
       <c r="F746" s="7" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="E747" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 4.888 ürün; ilk 32 ürünün fiyatı en düşük 346, medyan 3.368, en yüksek 17.999 TL; marka sırası: E.C.A, Tema, Artema, Grohe, VitrA, Vilas, Creavit, GPD, İtimat, Penta; mağaza sırası: Hepsiburada, idefix, PttAVM, Amazon, Trendruum | 62 ürün okundu, kategori toplamı 4885; medyan 2.568 TL; satıcı sayısı medyanı 6; VitrA/Artema 5 ürün; mağaza ve marka filtresi</t>
+          <t>Kategoride 4.888 ürün; ilk 32 ürünün fiyatı en düşük 346, medyan 3.368, en yüksek ₺17.999; marka sırası: E.C.A, Tema, Artema, Grohe, VitrA, Vilas, Creavit, GPD, İtimat, Penta; mağaza sırası: Hepsiburada, idefix, PttAVM, Amazon, Trendruum | 62 ürün okundu, kategori toplamı 4885; medyan ₺2.568; satıcı sayısı medyanı 6; VitrA/Artema 5 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F747" s="7" t="inlineStr">
@@ -28162,7 +28162,7 @@
       </c>
       <c r="E748" s="6" t="inlineStr">
         <is>
-          <t>61 ürün okundu, kategori toplamı 962; medyan 8.040 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>61 ürün okundu, kategori toplamı 962; medyan ₺8.040; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F748" s="7" t="inlineStr">
@@ -28199,7 +28199,7 @@
       </c>
       <c r="E749" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 18.213 ürün; ilk 32 ürünün fiyatı en düşük 4.997, medyan 5.990, en yüksek 9.230 TL; marka sırası: Durul, Sanica, Teknoduş, VitrA, Nokta, Çet-San, Pal, Nokta Duşakabin, Akdemir, Dusaks; mağaza sırası: Koçtaş, Hepsiburada, idefix, PttAVM, Amazon | 55 ürün okundu, kategori toplamı 7175; medyan 6.490 TL; satıcı sayısı medyanı 11; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>Kategoride 18.213 ürün; ilk 32 ürünün fiyatı en düşük 4.997, medyan 5.990, en yüksek ₺9.230; marka sırası: Durul, Sanica, Teknoduş, VitrA, Nokta, Çet-San, Pal, Nokta Duşakabin, Akdemir, Dusaks; mağaza sırası: Koçtaş, Hepsiburada, idefix, PttAVM, Amazon | 55 ürün okundu, kategori toplamı 7175; medyan ₺6.490; satıcı sayısı medyanı 11; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F749" s="7" t="inlineStr">
@@ -28236,7 +28236,7 @@
       </c>
       <c r="E750" s="6" t="inlineStr">
         <is>
-          <t>31 ürün okundu, 31 eşleşen; medyan 3.608 TL; satıcı sayısı medyanı 3; VitrA/Artema 1 ürün</t>
+          <t>31 ürün okundu, 31 eşleşen; medyan ₺3.608; satıcı sayısı medyanı 3; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F750" s="7" t="inlineStr">
@@ -28273,7 +28273,7 @@
       </c>
       <c r="E751" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, kategori toplamı 2577; medyan 5.725 TL; satıcı sayısı medyanı 3; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>32 ürün okundu, kategori toplamı 2577; medyan ₺5.725; satıcı sayısı medyanı 3; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F751" s="7" t="inlineStr">
@@ -28310,7 +28310,7 @@
       </c>
       <c r="E752" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 145 ürün; ilk 32 ürünün fiyatı en düşük 126, medyan 3.892, en yüksek 18.934 TL; marka sırası: VitrA, Visam, Serel, Geberit, Japar, Tema, Creavit, Nkp, Kale, Grohe; mağaza sırası: Hepsiburada, PttAVM, idefix, Amazon, Yapıdeko | 32 ürün okundu, kategori toplamı 145; medyan 3.441 TL; satıcı sayısı medyanı 3.5; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
+          <t>Kategoride 145 ürün; ilk 32 ürünün fiyatı en düşük 126, medyan 3.892, en yüksek ₺18.934; marka sırası: VitrA, Visam, Serel, Geberit, Japar, Tema, Creavit, Nkp, Kale, Grohe; mağaza sırası: Hepsiburada, PttAVM, idefix, Amazon, Yapıdeko | 32 ürün okundu, kategori toplamı 145; medyan ₺3.441; satıcı sayısı medyanı 3.5; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F752" s="7" t="inlineStr">
@@ -28347,7 +28347,7 @@
       </c>
       <c r="E753" s="6" t="inlineStr">
         <is>
-          <t>50 ürün okundu, kategori toplamı 8011; medyan 3.508 TL; satıcı sayısı medyanı 3; VitrA/Artema 1 ürün; mağaza ve marka filtresi</t>
+          <t>50 ürün okundu, kategori toplamı 8011; medyan ₺3.508; satıcı sayısı medyanı 3; VitrA/Artema 1 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F753" s="7" t="inlineStr">
@@ -28384,7 +28384,7 @@
       </c>
       <c r="E754" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 937 ürün; ilk 32 ürünün fiyatı en düşük 3.120, medyan 6.481, en yüksek 15.999 TL; marka sırası: Creavit, VitrA, Serel, Dura, Bocchi, Geberit, Duravit, Kale, Turkuaz, Karen; mağaza sırası: Hepsiburada, PttAVM, idefix, Yapıdeko, Amazon | 63 ürün okundu, kategori toplamı 934; medyan 8.200 TL; satıcı sayısı medyanı 3; VitrA/Artema 10 ürün; mağaza ve marka filtresi</t>
+          <t>Kategoride 937 ürün; ilk 32 ürünün fiyatı en düşük 3.120, medyan 6.481, en yüksek ₺15.999; marka sırası: Creavit, VitrA, Serel, Dura, Bocchi, Geberit, Duravit, Kale, Turkuaz, Karen; mağaza sırası: Hepsiburada, PttAVM, idefix, Yapıdeko, Amazon | 63 ürün okundu, kategori toplamı 934; medyan ₺8.200; satıcı sayısı medyanı 3; VitrA/Artema 10 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F754" s="7" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="E755" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 3.477 ürün; ilk 32 ürünün fiyatı en düşük 200, medyan 1.080, en yüksek 10.399 TL; marka sırası: VitrA, Visam, Nkp, Creavit, Kale, Serel, Softy, Özbest, T-may, Hakersan; mağaza sırası: Hepsiburada, PttAVM, idefix, Amazon, Yapıdeko | 64 ürün okundu, kategori toplamı 3477; medyan 1.109 TL; satıcı sayısı medyanı 4.0; VitrA/Artema 10 ürün; mağaza ve marka filtresi</t>
+          <t>Kategoride 3.477 ürün; ilk 32 ürünün fiyatı en düşük 200, medyan 1.080, en yüksek ₺10.399; marka sırası: VitrA, Visam, Nkp, Creavit, Kale, Serel, Softy, Özbest, T-may, Hakersan; mağaza sırası: Hepsiburada, PttAVM, idefix, Amazon, Yapıdeko | 64 ürün okundu, kategori toplamı 3477; medyan ₺1.109; satıcı sayısı medyanı 4.0; VitrA/Artema 10 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F755" s="7" t="inlineStr">
@@ -28458,7 +28458,7 @@
       </c>
       <c r="E756" s="6" t="inlineStr">
         <is>
-          <t>25 ürün okundu, kategori toplamı 300; medyan 21.600 TL; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>25 ürün okundu, kategori toplamı 300; medyan ₺21.600; satıcı sayısı medyanı 1; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F756" s="7" t="inlineStr">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="E757" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 5.001 ürün; ilk 31 ürünün fiyatı en düşük 165, medyan 3.608, en yüksek 15.331 TL; marka sırası: Turkuaz, Cerastyle, Creavit, VitrA, Bocchi, Kale, Turkuaz Seramik, Isvea, İdevit, Serel; mağaza sırası: Hepsiburada, PttAVM, idefix, Koçtaş, Amazon | 64 ürün okundu, kategori toplamı 4555; medyan 3.395 TL; satıcı sayısı medyanı 3.0; VitrA/Artema 5 ürün; mağaza ve marka filtresi</t>
+          <t>Kategoride 5.001 ürün; ilk 31 ürünün fiyatı en düşük 165, medyan 3.608, en yüksek ₺15.331; marka sırası: Turkuaz, Cerastyle, Creavit, VitrA, Bocchi, Kale, Turkuaz Seramik, Isvea, İdevit, Serel; mağaza sırası: Hepsiburada, PttAVM, idefix, Koçtaş, Amazon | 64 ürün okundu, kategori toplamı 4555; medyan ₺3.395; satıcı sayısı medyanı 3.0; VitrA/Artema 5 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F757" s="7" t="inlineStr">
@@ -28532,7 +28532,7 @@
       </c>
       <c r="E758" s="6" t="inlineStr">
         <is>
-          <t>14 ürün okundu, 12 eşleşen; medyan 3.599 TL; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün</t>
+          <t>14 ürün okundu, 12 eşleşen; medyan ₺3.599; satıcı sayısı medyanı 2.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F758" s="7" t="inlineStr">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="E759" s="6" t="inlineStr">
         <is>
-          <t>Kategoride 3.047 ürün; ilk 32 ürünün fiyatı en düşük 450, medyan 2.847, en yüksek 5.336 TL; marka sırası: E.C.A, Artema, GPD, Creavit, Vilas, Grohe, Ar, Sardıcı, Şenpres, Punto; mağaza sırası: Hepsiburada, idefix, PttAVM, Koçtaş, Amazon | 64 ürün okundu, kategori toplamı 2974; medyan 3.094 TL; satıcı sayısı medyanı 7.0; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
+          <t>Kategoride 3.047 ürün; ilk 32 ürünün fiyatı en düşük 450, medyan 2.847, en yüksek ₺5.336; marka sırası: E.C.A, Artema, GPD, Creavit, Vilas, Grohe, Ar, Sardıcı, Şenpres, Punto; mağaza sırası: Hepsiburada, idefix, PttAVM, Koçtaş, Amazon | 64 ürün okundu, kategori toplamı 2974; medyan ₺3.094; satıcı sayısı medyanı 7.0; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F759" s="7" t="inlineStr">
@@ -28606,7 +28606,7 @@
       </c>
       <c r="E760" s="6" t="inlineStr">
         <is>
-          <t>28 ürün okundu, 28 eşleşen; medyan 34.204 TL; satıcı sayısı medyanı 1.0; VitrA/Artema 2 ürün</t>
+          <t>28 ürün okundu, 28 eşleşen; medyan ₺34.204; satıcı sayısı medyanı 1.0; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F760" s="7" t="inlineStr">
@@ -28643,7 +28643,7 @@
       </c>
       <c r="E761" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, kategori toplamı 501; medyan 1.650 TL; satıcı sayısı medyanı 4.5; VitrA/Artema 1 ürün; mağaza ve marka filtresi</t>
+          <t>32 ürün okundu, kategori toplamı 501; medyan ₺1.650; satıcı sayısı medyanı 4.5; VitrA/Artema 1 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F761" s="7" t="inlineStr">
@@ -28680,7 +28680,7 @@
       </c>
       <c r="E762" s="6" t="inlineStr">
         <is>
-          <t>59 ürün okundu, kategori toplamı 137; medyan 7.499 TL; satıcı sayısı medyanı 1; VitrA/Artema 6 ürün; mağaza ve marka filtresi</t>
+          <t>59 ürün okundu, kategori toplamı 137; medyan ₺7.499; satıcı sayısı medyanı 1; VitrA/Artema 6 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F762" s="7" t="inlineStr">
@@ -28717,7 +28717,7 @@
       </c>
       <c r="E763" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 4170; medyan 986 TL; satıcı sayısı medyanı 5.0; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
+          <t>64 ürün okundu, kategori toplamı 4170; medyan ₺986; satıcı sayısı medyanı 5.0; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F763" s="7" t="inlineStr">
@@ -28754,7 +28754,7 @@
       </c>
       <c r="E764" s="6" t="inlineStr">
         <is>
-          <t>59 ürün okundu, kategori toplamı 1620; medyan 1.400 TL; satıcı sayısı medyanı 4; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
+          <t>59 ürün okundu, kategori toplamı 1620; medyan ₺1.400; satıcı sayısı medyanı 4; VitrA/Artema 4 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F764" s="7" t="inlineStr">
@@ -28791,7 +28791,7 @@
       </c>
       <c r="E765" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, kategori toplamı 1139; medyan 7.537 TL; satıcı sayısı medyanı 5; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>32 ürün okundu, kategori toplamı 1139; medyan ₺7.537; satıcı sayısı medyanı 5; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F765" s="7" t="inlineStr">
@@ -28828,7 +28828,7 @@
       </c>
       <c r="E766" s="6" t="inlineStr">
         <is>
-          <t>64 ürün okundu, kategori toplamı 948; medyan 8.254 TL; satıcı sayısı medyanı 4; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>64 ürün okundu, kategori toplamı 948; medyan ₺8.254; satıcı sayısı medyanı 4; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F766" s="7" t="inlineStr">
@@ -28865,7 +28865,7 @@
       </c>
       <c r="E767" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, kategori toplamı 133; medyan 700 TL; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>32 ürün okundu, kategori toplamı 133; medyan ₺700; satıcı sayısı medyanı 2; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F767" s="7" t="inlineStr">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="E768" s="6" t="inlineStr">
         <is>
-          <t>32 ürün okundu, kategori toplamı 186; medyan 13.324 TL; satıcı sayısı medyanı 6.5; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
+          <t>32 ürün okundu, kategori toplamı 186; medyan ₺13.324; satıcı sayısı medyanı 6.5; VitrA/Artema 0 ürün; mağaza ve marka filtresi</t>
         </is>
       </c>
       <c r="F768" s="7" t="inlineStr">
@@ -28939,7 +28939,7 @@
       </c>
       <c r="E769" s="6" t="inlineStr">
         <is>
-          <t>Peşin fiyatına 6 ve 9 taksit ifadeleri birlikte görünüyor (banner 9, alt metin 6); 30 gün ücretsiz iade ve değişim; 3.000 TL üzeri ücretsiz kargo</t>
+          <t>Peşin fiyatına 6 ve 9 taksit ifadeleri birlikte görünüyor (banner 9, alt metin 6); 30 gün ücretsiz iade ve değişim; ₺3.000 üzeri ücretsiz kargo</t>
         </is>
       </c>
       <c r="F769" s="7" t="inlineStr">
@@ -28976,7 +28976,7 @@
       </c>
       <c r="E770" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 1.890 TL; VitrA/Artema 0 ürün; marka dağılımı: Sifon:23, Havluluk:15, Tuvalet Kağıtlığı:10, Tuvalet Fırçalığı:6, Çöp Kovası:5, Diş Fırçal</t>
+          <t>0 ürün okundu; medyan ₺1.890; VitrA/Artema 0 ürün; marka dağılımı: Sifon:23, Havluluk:15, Tuvalet Kağıtlığı:10, Tuvalet Fırçalığı:6, Çöp Kovası:5, Diş Fırçal</t>
         </is>
       </c>
       <c r="F770" s="7" t="inlineStr">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="E771" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 7.092 TL; VitrA/Artema 0 ürün; marka dağılımı: Banyo Armatürü:27, Termostatik:2, Duş Seti:1</t>
+          <t>0 ürün okundu; medyan ₺7.092; VitrA/Artema 0 ürün; marka dağılımı: Banyo Armatürü:27, Termostatik:2, Duş Seti:1</t>
         </is>
       </c>
       <c r="F771" s="7" t="inlineStr">
@@ -29050,7 +29050,7 @@
       </c>
       <c r="E772" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 15.072 TL; VitrA/Artema 0 ürün; marka dağılımı: Boy Dolabı:23, Lavabo Dolabı:8</t>
+          <t>0 ürün okundu; medyan ₺15.072; VitrA/Artema 0 ürün; marka dağılımı: Boy Dolabı:23, Lavabo Dolabı:8</t>
         </is>
       </c>
       <c r="F772" s="7" t="inlineStr">
@@ -29087,7 +29087,7 @@
       </c>
       <c r="E773" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 33.462 TL; VitrA/Artema 0 ürün; marka dağılımı: Kapaklı Lavabo Dolabı:20, Çekmeceli:10</t>
+          <t>0 ürün okundu; medyan ₺33.462; VitrA/Artema 0 ürün; marka dağılımı: Kapaklı Lavabo Dolabı:20, Çekmeceli:10</t>
         </is>
       </c>
       <c r="F773" s="7" t="inlineStr">
@@ -29124,7 +29124,7 @@
       </c>
       <c r="E774" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 6.300 TL; VitrA/Artema 0 ürün; marka dağılımı: Duroplast:21, Thermoplast:3</t>
+          <t>0 ürün okundu; medyan ₺6.300; VitrA/Artema 0 ürün; marka dağılımı: Duroplast:21, Thermoplast:3</t>
         </is>
       </c>
       <c r="F774" s="7" t="inlineStr">
@@ -29161,7 +29161,7 @@
       </c>
       <c r="E775" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 13.894 TL; VitrA/Artema 0 ürün; marka dağılımı: Rim-Off Klozet:20, Asma Klozet:15, Kumanda Paneli:7, Set:2</t>
+          <t>0 ürün okundu; medyan ₺13.894; VitrA/Artema 0 ürün; marka dağılımı: Rim-Off Klozet:20, Asma Klozet:15, Kumanda Paneli:7, Set:2</t>
         </is>
       </c>
       <c r="F775" s="7" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="E776" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 1.728 TL; VitrA/Artema 0 ürün; marka dağılımı: Kumanda Paneli:51, Duroplast Klozet Kapağı:21, Gömme Rezervuar:5, Thermoplast Klozet Kapağ</t>
+          <t>0 ürün okundu; medyan ₺1.728; VitrA/Artema 0 ürün; marka dağılımı: Kumanda Paneli:51, Duroplast Klozet Kapağı:21, Gömme Rezervuar:5, Thermoplast Klozet Kapağ</t>
         </is>
       </c>
       <c r="F776" s="7" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="E777" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 1.890 TL; VitrA/Artema 0 ürün; marka dağılımı: Ara Musluk:22, Gömme Rezervuar:1</t>
+          <t>0 ürün okundu; medyan ₺1.890; VitrA/Artema 0 ürün; marka dağılımı: Ara Musluk:22, Gömme Rezervuar:1</t>
         </is>
       </c>
       <c r="F777" s="7" t="inlineStr">
@@ -29272,7 +29272,7 @@
       </c>
       <c r="E778" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 3.780 TL; VitrA/Artema 0 ürün; marka dağılımı: Duş Başlığı:10, Duş Sistemi:2</t>
+          <t>0 ürün okundu; medyan ₺3.780; VitrA/Artema 0 ürün; marka dağılımı: Duş Başlığı:10, Duş Sistemi:2</t>
         </is>
       </c>
       <c r="F778" s="7" t="inlineStr">
@@ -29309,7 +29309,7 @@
       </c>
       <c r="E779" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 2.649 TL; VitrA/Artema 0 ürün; marka dağılımı: El Duş Seti:8, Duş Seti:6, Duş Sistemi:4</t>
+          <t>0 ürün okundu; medyan ₺2.649; VitrA/Artema 0 ürün; marka dağılımı: El Duş Seti:8, Duş Seti:6, Duş Sistemi:4</t>
         </is>
       </c>
       <c r="F779" s="7" t="inlineStr">
@@ -29346,7 +29346,7 @@
       </c>
       <c r="E780" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 11.520 TL; VitrA/Artema 0 ürün; marka dağılımı: Duş Sistemi:9</t>
+          <t>0 ürün okundu; medyan ₺11.520; VitrA/Artema 0 ürün; marka dağılımı: Duş Sistemi:9</t>
         </is>
       </c>
       <c r="F780" s="7" t="inlineStr">
@@ -29383,7 +29383,7 @@
       </c>
       <c r="E781" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 1.728 TL; VitrA/Artema 0 ürün; marka dağılımı: Kumanda Paneli:51, Gömme Rezervuar:5</t>
+          <t>0 ürün okundu; medyan ₺1.728; VitrA/Artema 0 ürün; marka dağılımı: Kumanda Paneli:51, Gömme Rezervuar:5</t>
         </is>
       </c>
       <c r="F781" s="7" t="inlineStr">
@@ -29420,7 +29420,7 @@
       </c>
       <c r="E782" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 6.156 TL; VitrA/Artema 0 ürün; marka dağılımı: Lavabo Armatürü:38, Fotoselli:5, Banyo Armatürü:4</t>
+          <t>0 ürün okundu; medyan ₺6.156; VitrA/Artema 0 ürün; marka dağılımı: Lavabo Armatürü:38, Fotoselli:5, Banyo Armatürü:4</t>
         </is>
       </c>
       <c r="F782" s="7" t="inlineStr">
@@ -29457,7 +29457,7 @@
       </c>
       <c r="E783" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 16.170 TL; VitrA/Artema 0 ürün; marka dağılımı: Kapaklı:58, Çekmeceli:52, Kapaksız:3</t>
+          <t>0 ürün okundu; medyan ₺16.170; VitrA/Artema 0 ürün; marka dağılımı: Kapaklı:58, Çekmeceli:52, Kapaksız:3</t>
         </is>
       </c>
       <c r="F783" s="7" t="inlineStr">
@@ -29494,7 +29494,7 @@
       </c>
       <c r="E784" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 2.385 TL; VitrA/Artema 0 ürün; marka dağılımı: Lavabo Sifonu:9</t>
+          <t>0 ürün okundu; medyan ₺2.385; VitrA/Artema 0 ürün; marka dağılımı: Lavabo Sifonu:9</t>
         </is>
       </c>
       <c r="F784" s="7" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="E785" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 7.848 TL; VitrA/Artema 0 ürün; marka dağılımı: Çanak:67, Etajerli:9, Tezgah Üstü:7, Tezgah Altı:5, Ayaklı:1</t>
+          <t>0 ürün okundu; medyan ₺7.848; VitrA/Artema 0 ürün; marka dağılımı: Çanak:67, Etajerli:9, Tezgah Üstü:7, Tezgah Altı:5, Ayaklı:1</t>
         </is>
       </c>
       <c r="F785" s="7" t="inlineStr">
@@ -29568,7 +29568,7 @@
       </c>
       <c r="E786" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 7.740 TL; VitrA/Artema 0 ürün; marka dağılımı: Mutfak Armatürü:28, Banyo Armatürü:3</t>
+          <t>0 ürün okundu; medyan ₺7.740; VitrA/Artema 0 ürün; marka dağılımı: Mutfak Armatürü:28, Banyo Armatürü:3</t>
         </is>
       </c>
       <c r="F786" s="7" t="inlineStr">
@@ -29605,7 +29605,7 @@
       </c>
       <c r="E787" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 1.575 TL; VitrA/Artema 0 ürün; marka dağılımı: İç Takım:3</t>
+          <t>0 ürün okundu; medyan ₺1.575; VitrA/Artema 0 ürün; marka dağılımı: İç Takım:3</t>
         </is>
       </c>
       <c r="F787" s="7" t="inlineStr">
@@ -29642,7 +29642,7 @@
       </c>
       <c r="E788" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 14.784 TL; VitrA/Artema 0 ürün; marka dağılımı: Rim-Off Klozet:6, Takım Klozet:4, Set:1</t>
+          <t>0 ürün okundu; medyan ₺14.784; VitrA/Artema 0 ürün; marka dağılımı: Rim-Off Klozet:6, Takım Klozet:4, Set:1</t>
         </is>
       </c>
       <c r="F788" s="7" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="E789" s="6" t="inlineStr">
         <is>
-          <t>0 ürün okundu; medyan 17.459 TL; VitrA/Artema 0 ürün; marka dağılımı: Ayna:35, Kapaklı Dolap:14, Çekmeceli:7</t>
+          <t>0 ürün okundu; medyan ₺17.459; VitrA/Artema 0 ürün; marka dağılımı: Ayna:35, Kapaklı Dolap:14, Çekmeceli:7</t>
         </is>
       </c>
       <c r="F789" s="7" t="inlineStr">
@@ -29716,7 +29716,7 @@
       </c>
       <c r="E790" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 7.686 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺7.686; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
         </is>
       </c>
       <c r="F790" s="7" t="inlineStr">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="E791" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 1 eşleşen; medyan 21.186 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:1</t>
+          <t>24 ürün okundu, 1 eşleşen; medyan ₺21.186; VitrA/Artema 0 ürün; marka dağılımı: Creavit:1</t>
         </is>
       </c>
       <c r="F791" s="7" t="inlineStr">
@@ -29790,7 +29790,7 @@
       </c>
       <c r="E792" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 1.728 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺1.728; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
         </is>
       </c>
       <c r="F792" s="7" t="inlineStr">
@@ -29827,7 +29827,7 @@
       </c>
       <c r="E793" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 1 eşleşen; medyan 3.729 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:1</t>
+          <t>24 ürün okundu, 1 eşleşen; medyan ₺3.729; VitrA/Artema 0 ürün; marka dağılımı: Creavit:1</t>
         </is>
       </c>
       <c r="F793" s="7" t="inlineStr">
@@ -29864,7 +29864,7 @@
       </c>
       <c r="E794" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 3 eşleşen; medyan 11.880 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:3</t>
+          <t>24 ürün okundu, 3 eşleşen; medyan ₺11.880; VitrA/Artema 0 ürün; marka dağılımı: Creavit:3</t>
         </is>
       </c>
       <c r="F794" s="7" t="inlineStr">
@@ -29901,7 +29901,7 @@
       </c>
       <c r="E795" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 13 eşleşen; medyan 1.890 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:13</t>
+          <t>24 ürün okundu, 13 eşleşen; medyan ₺1.890; VitrA/Artema 0 ürün; marka dağılımı: Creavit:13</t>
         </is>
       </c>
       <c r="F795" s="7" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="E796" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 3 eşleşen; medyan 7.920 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:3</t>
+          <t>24 ürün okundu, 3 eşleşen; medyan ₺7.920; VitrA/Artema 0 ürün; marka dağılımı: Creavit:3</t>
         </is>
       </c>
       <c r="F796" s="7" t="inlineStr">
@@ -29975,7 +29975,7 @@
       </c>
       <c r="E797" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 14 eşleşen; medyan 8.283 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:14</t>
+          <t>24 ürün okundu, 14 eşleşen; medyan ₺8.283; VitrA/Artema 0 ürün; marka dağılımı: Creavit:14</t>
         </is>
       </c>
       <c r="F797" s="7" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="E798" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 17 eşleşen; medyan 8.085 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:17</t>
+          <t>24 ürün okundu, 17 eşleşen; medyan ₺8.085; VitrA/Artema 0 ürün; marka dağılımı: Creavit:17</t>
         </is>
       </c>
       <c r="F798" s="7" t="inlineStr">
@@ -30086,7 +30086,7 @@
       </c>
       <c r="E800" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 10 eşleşen; medyan 7.012 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:10</t>
+          <t>24 ürün okundu, 10 eşleşen; medyan ₺7.012; VitrA/Artema 0 ürün; marka dağılımı: Creavit:10</t>
         </is>
       </c>
       <c r="F800" s="7" t="inlineStr">
@@ -30160,7 +30160,7 @@
       </c>
       <c r="E802" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 4 eşleşen; medyan 4.788 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:4</t>
+          <t>24 ürün okundu, 4 eşleşen; medyan ₺4.788; VitrA/Artema 0 ürün; marka dağılımı: Creavit:4</t>
         </is>
       </c>
       <c r="F802" s="7" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="E803" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 1 eşleşen; medyan 1.596 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:1</t>
+          <t>24 ürün okundu, 1 eşleşen; medyan ₺1.596; VitrA/Artema 0 ürün; marka dağılımı: Creavit:1</t>
         </is>
       </c>
       <c r="F803" s="7" t="inlineStr">
@@ -30345,7 +30345,7 @@
       </c>
       <c r="E807" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 4 eşleşen; medyan 21.978 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:4</t>
+          <t>24 ürün okundu, 4 eşleşen; medyan ₺21.978; VitrA/Artema 0 ürün; marka dağılımı: Creavit:4</t>
         </is>
       </c>
       <c r="F807" s="7" t="inlineStr">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="E808" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 19 eşleşen; medyan 11.484 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:19</t>
+          <t>24 ürün okundu, 19 eşleşen; medyan ₺11.484; VitrA/Artema 0 ürün; marka dağılımı: Creavit:19</t>
         </is>
       </c>
       <c r="F808" s="7" t="inlineStr">
@@ -30419,7 +30419,7 @@
       </c>
       <c r="E809" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 7 eşleşen; medyan 2.100 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:7</t>
+          <t>24 ürün okundu, 7 eşleşen; medyan ₺2.100; VitrA/Artema 0 ürün; marka dağılımı: Creavit:7</t>
         </is>
       </c>
       <c r="F809" s="7" t="inlineStr">
@@ -30456,7 +30456,7 @@
       </c>
       <c r="E810" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 21 eşleşen; medyan 4.680 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:21</t>
+          <t>24 ürün okundu, 21 eşleşen; medyan ₺4.680; VitrA/Artema 0 ürün; marka dağılımı: Creavit:21</t>
         </is>
       </c>
       <c r="F810" s="7" t="inlineStr">
@@ -30493,7 +30493,7 @@
       </c>
       <c r="E811" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 19 eşleşen; medyan 9.396 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:19</t>
+          <t>24 ürün okundu, 19 eşleşen; medyan ₺9.396; VitrA/Artema 0 ürün; marka dağılımı: Creavit:19</t>
         </is>
       </c>
       <c r="F811" s="7" t="inlineStr">
@@ -30567,7 +30567,7 @@
       </c>
       <c r="E813" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 5 eşleşen; medyan 1.344 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:5</t>
+          <t>24 ürün okundu, 5 eşleşen; medyan ₺1.344; VitrA/Artema 0 ürün; marka dağılımı: Creavit:5</t>
         </is>
       </c>
       <c r="F813" s="7" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="E814" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 1 eşleşen; medyan 8.172 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:1</t>
+          <t>24 ürün okundu, 1 eşleşen; medyan ₺8.172; VitrA/Artema 0 ürün; marka dağılımı: Creavit:1</t>
         </is>
       </c>
       <c r="F814" s="7" t="inlineStr">
@@ -30678,7 +30678,7 @@
       </c>
       <c r="E816" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 10 eşleşen; medyan 16.200 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:10</t>
+          <t>24 ürün okundu, 10 eşleşen; medyan ₺16.200; VitrA/Artema 0 ürün; marka dağılımı: Creavit:10</t>
         </is>
       </c>
       <c r="F816" s="7" t="inlineStr">
@@ -30715,7 +30715,7 @@
       </c>
       <c r="E817" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 10 eşleşen; medyan 1.200 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:10</t>
+          <t>24 ürün okundu, 10 eşleşen; medyan ₺1.200; VitrA/Artema 0 ürün; marka dağılımı: Creavit:10</t>
         </is>
       </c>
       <c r="F817" s="7" t="inlineStr">
@@ -30752,7 +30752,7 @@
       </c>
       <c r="E818" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 10 eşleşen; medyan 7.425 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:10</t>
+          <t>24 ürün okundu, 10 eşleşen; medyan ₺7.425; VitrA/Artema 0 ürün; marka dağılımı: Creavit:10</t>
         </is>
       </c>
       <c r="F818" s="7" t="inlineStr">
@@ -30789,7 +30789,7 @@
       </c>
       <c r="E819" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 4 eşleşen; medyan 1.944 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:4</t>
+          <t>24 ürün okundu, 4 eşleşen; medyan ₺1.944; VitrA/Artema 0 ürün; marka dağılımı: Creavit:4</t>
         </is>
       </c>
       <c r="F819" s="7" t="inlineStr">
@@ -30863,7 +30863,7 @@
       </c>
       <c r="E821" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 7 eşleşen; medyan 5.031 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:7</t>
+          <t>24 ürün okundu, 7 eşleşen; medyan ₺5.031; VitrA/Artema 0 ürün; marka dağılımı: Creavit:7</t>
         </is>
       </c>
       <c r="F821" s="7" t="inlineStr">
@@ -30937,7 +30937,7 @@
       </c>
       <c r="E823" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 13 eşleşen; medyan 1.890 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:13</t>
+          <t>24 ürün okundu, 13 eşleşen; medyan ₺1.890; VitrA/Artema 0 ürün; marka dağılımı: Creavit:13</t>
         </is>
       </c>
       <c r="F823" s="7" t="inlineStr">
@@ -31122,7 +31122,7 @@
       </c>
       <c r="E828" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 1.728 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺1.728; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
         </is>
       </c>
       <c r="F828" s="7" t="inlineStr">
@@ -31196,7 +31196,7 @@
       </c>
       <c r="E830" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 1 eşleşen; medyan 9.720 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:1</t>
+          <t>24 ürün okundu, 1 eşleşen; medyan ₺9.720; VitrA/Artema 0 ürün; marka dağılımı: Creavit:1</t>
         </is>
       </c>
       <c r="F830" s="7" t="inlineStr">
@@ -31233,7 +31233,7 @@
       </c>
       <c r="E831" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 22 eşleşen; medyan 1.800 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:22</t>
+          <t>24 ürün okundu, 22 eşleşen; medyan ₺1.800; VitrA/Artema 0 ürün; marka dağılımı: Creavit:22</t>
         </is>
       </c>
       <c r="F831" s="7" t="inlineStr">
@@ -31270,7 +31270,7 @@
       </c>
       <c r="E832" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 9.212 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺9.212; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
         </is>
       </c>
       <c r="F832" s="7" t="inlineStr">
@@ -31344,7 +31344,7 @@
       </c>
       <c r="E834" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 1.728 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺1.728; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
         </is>
       </c>
       <c r="F834" s="7" t="inlineStr">
@@ -31492,7 +31492,7 @@
       </c>
       <c r="E838" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 6 eşleşen; medyan 3.348 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:6</t>
+          <t>24 ürün okundu, 6 eşleşen; medyan ₺3.348; VitrA/Artema 0 ürün; marka dağılımı: Creavit:6</t>
         </is>
       </c>
       <c r="F838" s="7" t="inlineStr">
@@ -31566,7 +31566,7 @@
       </c>
       <c r="E840" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 1.728 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺1.728; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
         </is>
       </c>
       <c r="F840" s="7" t="inlineStr">
@@ -31603,7 +31603,7 @@
       </c>
       <c r="E841" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 4 eşleşen; medyan 29.160 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:4</t>
+          <t>24 ürün okundu, 4 eşleşen; medyan ₺29.160; VitrA/Artema 0 ürün; marka dağılımı: Creavit:4</t>
         </is>
       </c>
       <c r="F841" s="7" t="inlineStr">
@@ -31640,7 +31640,7 @@
       </c>
       <c r="E842" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 8 eşleşen; medyan 2.328 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:8</t>
+          <t>24 ürün okundu, 8 eşleşen; medyan ₺2.328; VitrA/Artema 0 ürün; marka dağılımı: Creavit:8</t>
         </is>
       </c>
       <c r="F842" s="7" t="inlineStr">
@@ -31677,7 +31677,7 @@
       </c>
       <c r="E843" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 13 eşleşen; medyan 2.310 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:13</t>
+          <t>24 ürün okundu, 13 eşleşen; medyan ₺2.310; VitrA/Artema 0 ürün; marka dağılımı: Creavit:13</t>
         </is>
       </c>
       <c r="F843" s="7" t="inlineStr">
@@ -31714,7 +31714,7 @@
       </c>
       <c r="E844" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 7 eşleşen; medyan 6.930 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:7</t>
+          <t>24 ürün okundu, 7 eşleşen; medyan ₺6.930; VitrA/Artema 0 ürün; marka dağılımı: Creavit:7</t>
         </is>
       </c>
       <c r="F844" s="7" t="inlineStr">
@@ -31751,7 +31751,7 @@
       </c>
       <c r="E845" s="6" t="inlineStr">
         <is>
-          <t>24 ürün okundu, 24 eşleşen; medyan 7.350 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
+          <t>24 ürün okundu, 24 eşleşen; medyan ₺7.350; VitrA/Artema 0 ürün; marka dağılımı: Creavit:24</t>
         </is>
       </c>
       <c r="F845" s="7" t="inlineStr">
@@ -31825,7 +31825,7 @@
       </c>
       <c r="E847" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 9138; medyan 439 TL; toplam değerlendirme 8208; platform satış payı %6.9; VitrA/Artema 14 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 9138; medyan ₺439; toplam değerlendirme 8208; platform satış payı %6.9; VitrA/Artema 14 ürün</t>
         </is>
       </c>
       <c r="F847" s="7" t="inlineStr">
@@ -31862,7 +31862,7 @@
       </c>
       <c r="E848" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 32 eşleşen; toplam 2711; medyan 3.925 TL; VitrA/Artema 9 ürün; satıcı sayısı 13</t>
+          <t>36 ürün okundu, 32 eşleşen; toplam 2711; medyan ₺3.925; VitrA/Artema 9 ürün; satıcı sayısı 13</t>
         </is>
       </c>
       <c r="F848" s="7" t="inlineStr">
@@ -31899,7 +31899,7 @@
       </c>
       <c r="E849" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 34 eşleşen; toplam 1659; medyan 625 TL; VitrA/Artema 0 ürün; satıcı sayısı 17</t>
+          <t>36 ürün okundu, 34 eşleşen; toplam 1659; medyan ₺625; VitrA/Artema 0 ürün; satıcı sayısı 17</t>
         </is>
       </c>
       <c r="F849" s="7" t="inlineStr">
@@ -31936,7 +31936,7 @@
       </c>
       <c r="E850" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, kategori toplamı 805; medyan 2.222 TL; toplam değerlendirme 520; platform satış payı %0.0; VitrA/Artema 2 ürün</t>
+          <t>36 ürün okundu, kategori toplamı 805; medyan ₺2.222; toplam değerlendirme 520; platform satış payı %0.0; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F850" s="7" t="inlineStr">
@@ -31973,7 +31973,7 @@
       </c>
       <c r="E851" s="6" t="inlineStr">
         <is>
-          <t>7 ürün okundu, 7 eşleşen; toplam 7; medyan 4.932 TL; VitrA/Artema 3 ürün; satıcı sayısı 3</t>
+          <t>7 ürün okundu, 7 eşleşen; toplam 7; medyan ₺4.932; VitrA/Artema 3 ürün; satıcı sayısı 3</t>
         </is>
       </c>
       <c r="F851" s="7" t="inlineStr">
@@ -32010,7 +32010,7 @@
       </c>
       <c r="E852" s="6" t="inlineStr">
         <is>
-          <t>13 ürün okundu, 13 eşleşen; toplam 13; medyan 1.392 TL; VitrA/Artema 0 ürün; satıcı sayısı 10</t>
+          <t>13 ürün okundu, 13 eşleşen; toplam 13; medyan ₺1.392; VitrA/Artema 0 ürün; satıcı sayısı 10</t>
         </is>
       </c>
       <c r="F852" s="7" t="inlineStr">
@@ -32047,7 +32047,7 @@
       </c>
       <c r="E853" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, kategori toplamı 4657; medyan 5.920 TL; toplam değerlendirme 220; platform satış payı %0.0; VitrA/Artema 16 ürün</t>
+          <t>36 ürün okundu, kategori toplamı 4657; medyan ₺5.920; toplam değerlendirme 220; platform satış payı %0.0; VitrA/Artema 16 ürün</t>
         </is>
       </c>
       <c r="F853" s="7" t="inlineStr">
@@ -32084,7 +32084,7 @@
       </c>
       <c r="E854" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 98; medyan 7.348 TL; VitrA/Artema 4 ürün; satıcı sayısı 25</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 98; medyan ₺7.348; VitrA/Artema 4 ürün; satıcı sayısı 25</t>
         </is>
       </c>
       <c r="F854" s="7" t="inlineStr">
@@ -32121,7 +32121,7 @@
       </c>
       <c r="E855" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 443; medyan 968 TL; VitrA/Artema 21 ürün; satıcı sayısı 26</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 443; medyan ₺968; VitrA/Artema 21 ürün; satıcı sayısı 26</t>
         </is>
       </c>
       <c r="F855" s="7" t="inlineStr">
@@ -32158,7 +32158,7 @@
       </c>
       <c r="E856" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 2 eşleşen; toplam 2738; medyan 16.760 TL; VitrA/Artema 2 ürün; satıcı sayısı 1</t>
+          <t>36 ürün okundu, 2 eşleşen; toplam 2738; medyan ₺16.760; VitrA/Artema 2 ürün; satıcı sayısı 1</t>
         </is>
       </c>
       <c r="F856" s="7" t="inlineStr">
@@ -32195,7 +32195,7 @@
       </c>
       <c r="E857" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 26 eşleşen; toplam 449; medyan 6.525 TL; VitrA/Artema 8 ürün; satıcı sayısı 13</t>
+          <t>36 ürün okundu, 26 eşleşen; toplam 449; medyan ₺6.525; VitrA/Artema 8 ürün; satıcı sayısı 13</t>
         </is>
       </c>
       <c r="F857" s="7" t="inlineStr">
@@ -32232,7 +32232,7 @@
       </c>
       <c r="E858" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, kategori toplamı 2740; medyan 7.090 TL; toplam değerlendirme 847; platform satış payı %47.2; VitrA/Artema 10 ürün</t>
+          <t>36 ürün okundu, kategori toplamı 2740; medyan ₺7.090; toplam değerlendirme 847; platform satış payı %47.2; VitrA/Artema 10 ürün</t>
         </is>
       </c>
       <c r="F858" s="7" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="E859" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 14 eşleşen; toplam 225; medyan 3.993 TL; VitrA/Artema 1 ürün; satıcı sayısı 13</t>
+          <t>36 ürün okundu, 14 eşleşen; toplam 225; medyan ₺3.993; VitrA/Artema 1 ürün; satıcı sayısı 13</t>
         </is>
       </c>
       <c r="F859" s="7" t="inlineStr">
@@ -32306,7 +32306,7 @@
       </c>
       <c r="E860" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 800; medyan 6.528 TL; VitrA/Artema 0 ürün; satıcı sayısı 18</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 800; medyan ₺6.528; VitrA/Artema 0 ürün; satıcı sayısı 18</t>
         </is>
       </c>
       <c r="F860" s="7" t="inlineStr">
@@ -32343,7 +32343,7 @@
       </c>
       <c r="E861" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, kategori toplamı 767; medyan 6.508 TL; toplam değerlendirme 1450; platform satış payı %0.0; VitrA/Artema 3 ürün | 36 ürün okundu, 23 eşleşen; toplam 766; medyan 2.950 TL; VitrA/Artema 1 ürün; satıcı sayısı 10</t>
+          <t>36 ürün okundu, kategori toplamı 767; medyan ₺6.508; toplam değerlendirme 1450; platform satış payı %0.0; VitrA/Artema 3 ürün | 36 ürün okundu, 23 eşleşen; toplam 766; medyan ₺2.950; VitrA/Artema 1 ürün; satıcı sayısı 10</t>
         </is>
       </c>
       <c r="F861" s="7" t="inlineStr">
@@ -32380,7 +32380,7 @@
       </c>
       <c r="E862" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 27 eşleşen; toplam 10000; medyan 107.900 TL; VitrA/Artema 1 ürün; satıcı sayısı 14</t>
+          <t>36 ürün okundu, 27 eşleşen; toplam 10000; medyan ₺107.900; VitrA/Artema 1 ürün; satıcı sayısı 14</t>
         </is>
       </c>
       <c r="F862" s="7" t="inlineStr">
@@ -32417,7 +32417,7 @@
       </c>
       <c r="E863" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan 1.094 TL; VitrA/Artema 0 ürün; satıcı sayısı 17</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan ₺1.094; VitrA/Artema 0 ürün; satıcı sayısı 17</t>
         </is>
       </c>
       <c r="F863" s="7" t="inlineStr">
@@ -32454,7 +32454,7 @@
       </c>
       <c r="E864" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan 150 TL; VitrA/Artema 1 ürün; satıcı sayısı 22</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan ₺150; VitrA/Artema 1 ürün; satıcı sayısı 22</t>
         </is>
       </c>
       <c r="F864" s="7" t="inlineStr">
@@ -32491,7 +32491,7 @@
       </c>
       <c r="E865" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, kategori toplamı 10000; medyan 3.585 TL; toplam değerlendirme 1740; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, kategori toplamı 10000; medyan ₺3.585; toplam değerlendirme 1740; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F865" s="7" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="E866" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 29 eşleşen; toplam 241; medyan 716 TL; VitrA/Artema 0 ürün; satıcı sayısı 5</t>
+          <t>36 ürün okundu, 29 eşleşen; toplam 241; medyan ₺716; VitrA/Artema 0 ürün; satıcı sayısı 5</t>
         </is>
       </c>
       <c r="F866" s="7" t="inlineStr">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="E867" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 853; medyan 97 TL; VitrA/Artema 0 ürün; satıcı sayısı 11</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 853; medyan ₺97; VitrA/Artema 0 ürün; satıcı sayısı 11</t>
         </is>
       </c>
       <c r="F867" s="7" t="inlineStr">
@@ -32602,7 +32602,7 @@
       </c>
       <c r="E868" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 24 eşleşen; toplam 811; medyan 2.146 TL; VitrA/Artema 0 ürün; satıcı sayısı 10</t>
+          <t>36 ürün okundu, 24 eşleşen; toplam 811; medyan ₺2.146; VitrA/Artema 0 ürün; satıcı sayısı 10</t>
         </is>
       </c>
       <c r="F868" s="7" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="E869" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 1 eşleşen; toplam 10000; medyan 4.999 TL; VitrA/Artema 0 ürün; satıcı sayısı 1</t>
+          <t>36 ürün okundu, 1 eşleşen; toplam 10000; medyan ₺4.999; VitrA/Artema 0 ürün; satıcı sayısı 1</t>
         </is>
       </c>
       <c r="F869" s="7" t="inlineStr">
@@ -32676,7 +32676,7 @@
       </c>
       <c r="E870" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 632; medyan 8.399 TL; VitrA/Artema 3 ürün; satıcı sayısı 16</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 632; medyan ₺8.399; VitrA/Artema 3 ürün; satıcı sayısı 16</t>
         </is>
       </c>
       <c r="F870" s="7" t="inlineStr">
@@ -32713,7 +32713,7 @@
       </c>
       <c r="E871" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 10000; medyan 337 TL; toplam değerlendirme 15225; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 10000; medyan ₺337; toplam değerlendirme 15225; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F871" s="7" t="inlineStr">
@@ -32750,7 +32750,7 @@
       </c>
       <c r="E872" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan 341 TL; VitrA/Artema 0 ürün; satıcı sayısı 31</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan ₺341; VitrA/Artema 0 ürün; satıcı sayısı 31</t>
         </is>
       </c>
       <c r="F872" s="7" t="inlineStr">
@@ -32787,7 +32787,7 @@
       </c>
       <c r="E873" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 26 eşleşen; toplam 10000; medyan 2.720 TL; VitrA/Artema 1 ürün; satıcı sayısı 8</t>
+          <t>36 ürün okundu, 26 eşleşen; toplam 10000; medyan ₺2.720; VitrA/Artema 1 ürün; satıcı sayısı 8</t>
         </is>
       </c>
       <c r="F873" s="7" t="inlineStr">
@@ -32824,7 +32824,7 @@
       </c>
       <c r="E874" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 182; medyan 16.140 TL; VitrA/Artema 4 ürün; satıcı sayısı 23</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 182; medyan ₺16.140; VitrA/Artema 4 ürün; satıcı sayısı 23</t>
         </is>
       </c>
       <c r="F874" s="7" t="inlineStr">
@@ -32861,7 +32861,7 @@
       </c>
       <c r="E875" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 1159; medyan 1.827 TL; VitrA/Artema 1 ürün; satıcı sayısı 20</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 1159; medyan ₺1.827; VitrA/Artema 1 ürün; satıcı sayısı 20</t>
         </is>
       </c>
       <c r="F875" s="7" t="inlineStr">
@@ -32898,7 +32898,7 @@
       </c>
       <c r="E876" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 1013; medyan 2.067 TL; toplam değerlendirme 758; platform satış payı %0.0; VitrA/Artema 1 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 1013; medyan ₺2.067; toplam değerlendirme 758; platform satış payı %0.0; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F876" s="7" t="inlineStr">
@@ -32935,7 +32935,7 @@
       </c>
       <c r="E877" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 10000; medyan 1.990 TL; toplam değerlendirme 11459; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 10000; medyan ₺1.990; toplam değerlendirme 11459; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F877" s="7" t="inlineStr">
@@ -32972,7 +32972,7 @@
       </c>
       <c r="E878" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 1873; medyan 934 TL; VitrA/Artema 6 ürün; satıcı sayısı 25</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 1873; medyan ₺934; VitrA/Artema 6 ürün; satıcı sayısı 25</t>
         </is>
       </c>
       <c r="F878" s="7" t="inlineStr">
@@ -33009,7 +33009,7 @@
       </c>
       <c r="E879" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 4 eşleşen; toplam 6; medyan 2.148 TL; VitrA/Artema 0 ürün; satıcı sayısı 3</t>
+          <t>6 ürün okundu, 4 eşleşen; toplam 6; medyan ₺2.148; VitrA/Artema 0 ürün; satıcı sayısı 3</t>
         </is>
       </c>
       <c r="F879" s="7" t="inlineStr">
@@ -33046,7 +33046,7 @@
       </c>
       <c r="E880" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 1876; medyan 697 TL; VitrA/Artema 0 ürün; satıcı sayısı 28</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 1876; medyan ₺697; VitrA/Artema 0 ürün; satıcı sayısı 28</t>
         </is>
       </c>
       <c r="F880" s="7" t="inlineStr">
@@ -33083,7 +33083,7 @@
       </c>
       <c r="E881" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 442; medyan 6.900 TL; VitrA/Artema 18 ürün; satıcı sayısı 22</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 442; medyan ₺6.900; VitrA/Artema 18 ürün; satıcı sayısı 22</t>
         </is>
       </c>
       <c r="F881" s="7" t="inlineStr">
@@ -33120,7 +33120,7 @@
       </c>
       <c r="E882" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 262; medyan 10.205 TL; VitrA/Artema 0 ürün; satıcı sayısı 8</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 262; medyan ₺10.205; VitrA/Artema 0 ürün; satıcı sayısı 8</t>
         </is>
       </c>
       <c r="F882" s="7" t="inlineStr">
@@ -33157,7 +33157,7 @@
       </c>
       <c r="E883" s="6" t="inlineStr">
         <is>
-          <t>10 ürün okundu, 10 eşleşen; toplam 10; medyan 9.000 TL; VitrA/Artema 0 ürün; satıcı sayısı 7</t>
+          <t>10 ürün okundu, 10 eşleşen; toplam 10; medyan ₺9.000; VitrA/Artema 0 ürün; satıcı sayısı 7</t>
         </is>
       </c>
       <c r="F883" s="7" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="E884" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 17 eşleşen; toplam 10000; medyan 2.000 TL; VitrA/Artema 7 ürün; satıcı sayısı 12</t>
+          <t>36 ürün okundu, 17 eşleşen; toplam 10000; medyan ₺2.000; VitrA/Artema 7 ürün; satıcı sayısı 12</t>
         </is>
       </c>
       <c r="F884" s="7" t="inlineStr">
@@ -33231,7 +33231,7 @@
       </c>
       <c r="E885" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 34 eşleşen; toplam 135; medyan 3.259 TL; VitrA/Artema 0 ürün; satıcı sayısı 14</t>
+          <t>36 ürün okundu, 34 eşleşen; toplam 135; medyan ₺3.259; VitrA/Artema 0 ürün; satıcı sayısı 14</t>
         </is>
       </c>
       <c r="F885" s="7" t="inlineStr">
@@ -33268,7 +33268,7 @@
       </c>
       <c r="E886" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 655; medyan 3.430 TL; VitrA/Artema 1 ürün; satıcı sayısı 4</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 655; medyan ₺3.430; VitrA/Artema 1 ürün; satıcı sayısı 4</t>
         </is>
       </c>
       <c r="F886" s="7" t="inlineStr">
@@ -33305,7 +33305,7 @@
       </c>
       <c r="E887" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 34 eşleşen; toplam 588; medyan 8.425 TL; VitrA/Artema 4 ürün; satıcı sayısı 21</t>
+          <t>36 ürün okundu, 34 eşleşen; toplam 588; medyan ₺8.425; VitrA/Artema 4 ürün; satıcı sayısı 21</t>
         </is>
       </c>
       <c r="F887" s="7" t="inlineStr">
@@ -33342,7 +33342,7 @@
       </c>
       <c r="E888" s="6" t="inlineStr">
         <is>
-          <t>sonuç sayısı 3.406; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 3302; medyan 670 TL; toplam değerlendirme 4659; platform satış payı %0.0; VitrA/Artema 18 ürün</t>
+          <t>sonuç sayısı 3.406; ilk 36 ürün (ilk sayfa): satıcı türü (platform, VitrA mağazası, 3. taraf), liste ve sepet fiyatı, puan, değerlendirme sayısı | 72 ürün okundu, kategori toplamı 3302; medyan ₺670; toplam değerlendirme 4659; platform satış payı %0.0; VitrA/Artema 18 ürün</t>
         </is>
       </c>
       <c r="F888" s="7" t="inlineStr">
@@ -33379,7 +33379,7 @@
       </c>
       <c r="E889" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan 199 TL; VitrA/Artema 1 ürün; satıcı sayısı 24</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan ₺199; VitrA/Artema 1 ürün; satıcı sayısı 24</t>
         </is>
       </c>
       <c r="F889" s="7" t="inlineStr">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="E890" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 94; medyan 90.408 TL; VitrA/Artema 0 ürün; satıcı sayısı 1</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 94; medyan ₺90.408; VitrA/Artema 0 ürün; satıcı sayısı 1</t>
         </is>
       </c>
       <c r="F890" s="7" t="inlineStr">
@@ -33453,7 +33453,7 @@
       </c>
       <c r="E891" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 16 eşleşen; toplam 2172; medyan 2.650 TL; VitrA/Artema 0 ürün; satıcı sayısı 12</t>
+          <t>36 ürün okundu, 16 eşleşen; toplam 2172; medyan ₺2.650; VitrA/Artema 0 ürün; satıcı sayısı 12</t>
         </is>
       </c>
       <c r="F891" s="7" t="inlineStr">
@@ -33490,7 +33490,7 @@
       </c>
       <c r="E892" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 1731; medyan 6.620 TL; VitrA/Artema 3 ürün; satıcı sayısı 24</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 1731; medyan ₺6.620; VitrA/Artema 3 ürün; satıcı sayısı 24</t>
         </is>
       </c>
       <c r="F892" s="7" t="inlineStr">
@@ -33527,7 +33527,7 @@
       </c>
       <c r="E893" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 35 eşleşen; toplam 667; medyan 800 TL; VitrA/Artema 0 ürün; satıcı sayısı 20</t>
+          <t>36 ürün okundu, 35 eşleşen; toplam 667; medyan ₺800; VitrA/Artema 0 ürün; satıcı sayısı 20</t>
         </is>
       </c>
       <c r="F893" s="7" t="inlineStr">
@@ -33564,7 +33564,7 @@
       </c>
       <c r="E894" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 11 eşleşen; toplam 406; medyan 22.166 TL; VitrA/Artema 0 ürün; satıcı sayısı 4</t>
+          <t>36 ürün okundu, 11 eşleşen; toplam 406; medyan ₺22.166; VitrA/Artema 0 ürün; satıcı sayısı 4</t>
         </is>
       </c>
       <c r="F894" s="7" t="inlineStr">
@@ -33601,7 +33601,7 @@
       </c>
       <c r="E895" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, kategori toplamı 10000; medyan 500 TL; toplam değerlendirme 32905; platform satış payı %0.0; VitrA/Artema 1 ürün</t>
+          <t>36 ürün okundu, kategori toplamı 10000; medyan ₺500; toplam değerlendirme 32905; platform satış payı %0.0; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F895" s="7" t="inlineStr">
@@ -33675,7 +33675,7 @@
       </c>
       <c r="E897" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 2 eşleşen; toplam 5; medyan 1.435 TL; VitrA/Artema 1 ürün; satıcı sayısı 2</t>
+          <t>5 ürün okundu, 2 eşleşen; toplam 5; medyan ₺1.435; VitrA/Artema 1 ürün; satıcı sayısı 2</t>
         </is>
       </c>
       <c r="F897" s="7" t="inlineStr">
@@ -33712,7 +33712,7 @@
       </c>
       <c r="E898" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 462; medyan 997 TL; VitrA/Artema 4 ürün; satıcı sayısı 27</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 462; medyan ₺997; VitrA/Artema 4 ürün; satıcı sayısı 27</t>
         </is>
       </c>
       <c r="F898" s="7" t="inlineStr">
@@ -33749,7 +33749,7 @@
       </c>
       <c r="E899" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 4479; medyan 3.990 TL; toplam değerlendirme 221; platform satış payı %0.0; VitrA/Artema 1 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 4479; medyan ₺3.990; toplam değerlendirme 221; platform satış payı %0.0; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F899" s="7" t="inlineStr">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="E900" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan 232 TL; VitrA/Artema 0 ürün; satıcı sayısı 24</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan ₺232; VitrA/Artema 0 ürün; satıcı sayısı 24</t>
         </is>
       </c>
       <c r="F900" s="7" t="inlineStr">
@@ -33823,7 +33823,7 @@
       </c>
       <c r="E901" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 30 eşleşen; toplam 1110; medyan 6.410 TL; VitrA/Artema 4 ürün; satıcı sayısı 15</t>
+          <t>36 ürün okundu, 30 eşleşen; toplam 1110; medyan ₺6.410; VitrA/Artema 4 ürün; satıcı sayısı 15</t>
         </is>
       </c>
       <c r="F901" s="7" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="E902" s="6" t="inlineStr">
         <is>
-          <t>17 ürün okundu, 17 eşleşen; toplam 17; medyan 1.500 TL; VitrA/Artema 9 ürün; satıcı sayısı 15</t>
+          <t>17 ürün okundu, 17 eşleşen; toplam 17; medyan ₺1.500; VitrA/Artema 9 ürün; satıcı sayısı 15</t>
         </is>
       </c>
       <c r="F902" s="7" t="inlineStr">
@@ -33897,7 +33897,7 @@
       </c>
       <c r="E903" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 106; medyan 26.877 TL; VitrA/Artema 1 ürün; satıcı sayısı 14</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 106; medyan ₺26.877; VitrA/Artema 1 ürün; satıcı sayısı 14</t>
         </is>
       </c>
       <c r="F903" s="7" t="inlineStr">
@@ -33934,7 +33934,7 @@
       </c>
       <c r="E904" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 41; medyan 4.775 TL; VitrA/Artema 1 ürün; satıcı sayısı 10</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 41; medyan ₺4.775; VitrA/Artema 1 ürün; satıcı sayısı 10</t>
         </is>
       </c>
       <c r="F904" s="7" t="inlineStr">
@@ -33971,7 +33971,7 @@
       </c>
       <c r="E905" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 71; medyan 14.949 TL; VitrA/Artema 9 ürün; satıcı sayısı 34</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 71; medyan ₺14.949; VitrA/Artema 9 ürün; satıcı sayısı 34</t>
         </is>
       </c>
       <c r="F905" s="7" t="inlineStr">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="E906" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 33 eşleşen; toplam 562; medyan 3.250 TL; VitrA/Artema 21 ürün; satıcı sayısı 26</t>
+          <t>36 ürün okundu, 33 eşleşen; toplam 562; medyan ₺3.250; VitrA/Artema 21 ürün; satıcı sayısı 26</t>
         </is>
       </c>
       <c r="F906" s="7" t="inlineStr">
@@ -34045,7 +34045,7 @@
       </c>
       <c r="E907" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 878; medyan 5.781 TL; VitrA/Artema 23 ürün; satıcı sayısı 26</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 878; medyan ₺5.781; VitrA/Artema 23 ürün; satıcı sayısı 26</t>
         </is>
       </c>
       <c r="F907" s="7" t="inlineStr">
@@ -34082,7 +34082,7 @@
       </c>
       <c r="E908" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 10000; medyan 2.888 TL; toplam değerlendirme 14339; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 10000; medyan ₺2.888; toplam değerlendirme 14339; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F908" s="7" t="inlineStr">
@@ -34119,7 +34119,7 @@
       </c>
       <c r="E909" s="6" t="inlineStr">
         <is>
-          <t>4 ürün okundu, 4 eşleşen; toplam 4; medyan 12.444 TL; VitrA/Artema 4 ürün; satıcı sayısı 3</t>
+          <t>4 ürün okundu, 4 eşleşen; toplam 4; medyan ₺12.444; VitrA/Artema 4 ürün; satıcı sayısı 3</t>
         </is>
       </c>
       <c r="F909" s="7" t="inlineStr">
@@ -34156,7 +34156,7 @@
       </c>
       <c r="E910" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 836; medyan 14.299 TL; toplam değerlendirme 7848; platform satış payı %5.6; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 836; medyan ₺14.299; toplam değerlendirme 7848; platform satış payı %5.6; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F910" s="7" t="inlineStr">
@@ -34193,7 +34193,7 @@
       </c>
       <c r="E911" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 13 eşleşen; toplam 2624; medyan 6.300 TL; VitrA/Artema 1 ürün; satıcı sayısı 12</t>
+          <t>36 ürün okundu, 13 eşleşen; toplam 2624; medyan ₺6.300; VitrA/Artema 1 ürün; satıcı sayısı 12</t>
         </is>
       </c>
       <c r="F911" s="7" t="inlineStr">
@@ -34230,7 +34230,7 @@
       </c>
       <c r="E912" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, kategori toplamı 3440; medyan 3.150 TL; toplam değerlendirme 626; platform satış payı %52.8; VitrA/Artema 1 ürün</t>
+          <t>36 ürün okundu, kategori toplamı 3440; medyan ₺3.150; toplam değerlendirme 626; platform satış payı %52.8; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F912" s="7" t="inlineStr">
@@ -34267,7 +34267,7 @@
       </c>
       <c r="E913" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 1106; medyan 629 TL; toplam değerlendirme 1811; platform satış payı %0.0; VitrA/Artema 1 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 1106; medyan ₺629; toplam değerlendirme 1811; platform satış payı %0.0; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F913" s="7" t="inlineStr">
@@ -34304,7 +34304,7 @@
       </c>
       <c r="E914" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan 200 TL; VitrA/Artema 0 ürün; satıcı sayısı 26</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan ₺200; VitrA/Artema 0 ürün; satıcı sayısı 26</t>
         </is>
       </c>
       <c r="F914" s="7" t="inlineStr">
@@ -34341,7 +34341,7 @@
       </c>
       <c r="E915" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan 225 TL; VitrA/Artema 2 ürün; satıcı sayısı 24</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 10000; medyan ₺225; VitrA/Artema 2 ürün; satıcı sayısı 24</t>
         </is>
       </c>
       <c r="F915" s="7" t="inlineStr">
@@ -34378,7 +34378,7 @@
       </c>
       <c r="E916" s="6" t="inlineStr">
         <is>
-          <t>15 ürün okundu, 4 eşleşen; toplam 15; medyan 3.000 TL; VitrA/Artema 0 ürün; satıcı sayısı 4</t>
+          <t>15 ürün okundu, 4 eşleşen; toplam 15; medyan ₺3.000; VitrA/Artema 0 ürün; satıcı sayısı 4</t>
         </is>
       </c>
       <c r="F916" s="7" t="inlineStr">
@@ -34415,7 +34415,7 @@
       </c>
       <c r="E917" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 184; medyan 4.815 TL; VitrA/Artema 0 ürün; satıcı sayısı 24</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 184; medyan ₺4.815; VitrA/Artema 0 ürün; satıcı sayısı 24</t>
         </is>
       </c>
       <c r="F917" s="7" t="inlineStr">
@@ -34452,7 +34452,7 @@
       </c>
       <c r="E918" s="6" t="inlineStr">
         <is>
-          <t>13 ürün okundu, 13 eşleşen; toplam 13; medyan 6.199 TL; VitrA/Artema 0 ürün; satıcı sayısı 10</t>
+          <t>13 ürün okundu, 13 eşleşen; toplam 13; medyan ₺6.199; VitrA/Artema 0 ürün; satıcı sayısı 10</t>
         </is>
       </c>
       <c r="F918" s="7" t="inlineStr">
@@ -34489,7 +34489,7 @@
       </c>
       <c r="E919" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 1724; medyan 5.400 TL; toplam değerlendirme 253; platform satış payı %0.0; VitrA/Artema 2 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 1724; medyan ₺5.400; toplam değerlendirme 253; platform satış payı %0.0; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F919" s="7" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="E920" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 4693; medyan 5.701 TL; toplam değerlendirme 33; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 4693; medyan ₺5.701; toplam değerlendirme 33; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F920" s="7" t="inlineStr">
@@ -34563,7 +34563,7 @@
       </c>
       <c r="E921" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 10000; medyan 662 TL; toplam değerlendirme 41136; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 10000; medyan ₺662; toplam değerlendirme 41136; platform satış payı %0.0; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F921" s="7" t="inlineStr">
@@ -34600,7 +34600,7 @@
       </c>
       <c r="E922" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 3.870 TL; VitrA/Artema 0 ürün; marka dağılımı: Brat:19/1, Selim:11/0, (markasız):8/7, Cepahir:4/0, Nysamo:3/0, Enc Home:2/16</t>
+          <t>48 ürün okundu; medyan ₺3.870; VitrA/Artema 0 ürün; marka dağılımı: Brat:19/1, Selim:11/0, (markasız):8/7, Cepahir:4/0, Nysamo:3/0, Enc Home:2/16</t>
         </is>
       </c>
       <c r="F922" s="7" t="inlineStr">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="E923" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 4.062 TL; VitrA/Artema 1 ürün; marka dağılımı: Orka:12/11, Roomart:11/32, Özceden:8/1, Denko Banyo:3/0, Mobilique:2/8, Teta Home:2/2</t>
+          <t>48 ürün okundu; medyan ₺4.062; VitrA/Artema 1 ürün; marka dağılımı: Orka:12/11, Roomart:11/32, Özceden:8/1, Denko Banyo:3/0, Mobilique:2/8, Teta Home:2/2</t>
         </is>
       </c>
       <c r="F923" s="7" t="inlineStr">
@@ -34674,7 +34674,7 @@
       </c>
       <c r="E924" s="6" t="inlineStr">
         <is>
-          <t>49 ürün okundu; medyan 9.399 TL; VitrA/Artema 0 ürün; marka dağılımı: Roomart:18/102, Karen Banyo:12/268, Dmz Home Concept:9/24, Teta Home:5/25, Balneom:2/16, Ö</t>
+          <t>49 ürün okundu; medyan ₺9.399; VitrA/Artema 0 ürün; marka dağılımı: Roomart:18/102, Karen Banyo:12/268, Dmz Home Concept:9/24, Teta Home:5/25, Balneom:2/16, Ö</t>
         </is>
       </c>
       <c r="F924" s="7" t="inlineStr">
@@ -34711,7 +34711,7 @@
       </c>
       <c r="E925" s="6" t="inlineStr">
         <is>
-          <t>49 ürün okundu; medyan 6.899 TL; VitrA/Artema 0 ürün; marka dağılımı: Karen Banyo:14/255, Roomart:8/82, Dmz Home Concept:7/23, Asratrend:4/1, Kzy Mobilya:2/47,</t>
+          <t>49 ürün okundu; medyan ₺6.899; VitrA/Artema 0 ürün; marka dağılımı: Karen Banyo:14/255, Roomart:8/82, Dmz Home Concept:7/23, Asratrend:4/1, Kzy Mobilya:2/47,</t>
         </is>
       </c>
       <c r="F925" s="7" t="inlineStr">
@@ -34748,7 +34748,7 @@
       </c>
       <c r="E926" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 1.999 TL; VitrA/Artema 1 ürün; marka dağılımı: Tema:7/33, Grohe:5/43, Fawer:5/24, Armour Armatür:4/68, Robo:3/0, Sardıcı :2/8</t>
+          <t>48 ürün okundu; medyan ₺1.999; VitrA/Artema 1 ürün; marka dağılımı: Tema:7/33, Grohe:5/43, Fawer:5/24, Armour Armatür:4/68, Robo:3/0, Sardıcı :2/8</t>
         </is>
       </c>
       <c r="F926" s="7" t="inlineStr">
@@ -34785,7 +34785,7 @@
       </c>
       <c r="E927" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 4.470 TL; VitrA/Artema 3 ürün; marka dağılımı: Tema:12/3, Grohe:6/27, Creavit:4/14, Sardıcı:4/60, Depolife:3/12, Artema:3/11</t>
+          <t>48 ürün okundu; medyan ₺4.470; VitrA/Artema 3 ürün; marka dağılımı: Tema:12/3, Grohe:6/27, Creavit:4/14, Sardıcı:4/60, Depolife:3/12, Artema:3/11</t>
         </is>
       </c>
       <c r="F927" s="7" t="inlineStr">
@@ -34822,7 +34822,7 @@
       </c>
       <c r="E928" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 3.204 TL; VitrA/Artema 5 ürün; marka dağılımı: Sardıcı:12/231, Rena Design:7/18, Artema:5/16, ECA:4/65, GPD:4/8, Creavit:3/48</t>
+          <t>48 ürün okundu; medyan ₺3.204; VitrA/Artema 5 ürün; marka dağılımı: Sardıcı:12/231, Rena Design:7/18, Artema:5/16, ECA:4/65, GPD:4/8, Creavit:3/48</t>
         </is>
       </c>
       <c r="F928" s="7" t="inlineStr">
@@ -34859,7 +34859,7 @@
       </c>
       <c r="E929" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 1.238 TL; VitrA/Artema 8 ürün; marka dağılımı: VitrA:6/0, GPD:6/0, ECA:4/16, Fause:4/0, Artema:3/0, Ar:3/3</t>
+          <t>48 ürün okundu; medyan ₺1.238; VitrA/Artema 8 ürün; marka dağılımı: VitrA:6/0, GPD:6/0, ECA:4/16, Fause:4/0, Artema:3/0, Ar:3/3</t>
         </is>
       </c>
       <c r="F929" s="7" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="E930" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 9.040 TL; VitrA/Artema 0 ürün; marka dağılımı: İskit Duşakabin:16/3, Durul:11/48, Monaqua:6/1, Venita:3/10, EYM:3/3, İkon Duş Sistemleri:</t>
+          <t>48 ürün okundu; medyan ₺9.040; VitrA/Artema 0 ürün; marka dağılımı: İskit Duşakabin:16/3, Durul:11/48, Monaqua:6/1, Venita:3/10, EYM:3/3, İkon Duş Sistemleri:</t>
         </is>
       </c>
       <c r="F930" s="7" t="inlineStr">
@@ -34933,7 +34933,7 @@
       </c>
       <c r="E931" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 9.214 TL; VitrA/Artema 3 ürün; marka dağılımı: Creavit:22/28, Turkuaz:7/4, VitrA:3/2, Kale:2/2, Newarc:2/2, Turavit:2/11, Seramiksan:2/0</t>
+          <t>48 ürün okundu; medyan ₺9.214; VitrA/Artema 3 ürün; marka dağılımı: Creavit:22/28, Turkuaz:7/4, VitrA:3/2, Kale:2/2, Newarc:2/2, Turavit:2/11, Seramiksan:2/0</t>
         </is>
       </c>
       <c r="F931" s="7" t="inlineStr">
@@ -34970,7 +34970,7 @@
       </c>
       <c r="E932" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 14.052 TL; VitrA/Artema 3 ürün; marka dağılımı: Creavit:14/3, NORMO:13/0, Kale:6/123, VitrA:3/18, Norm:2/75, Serel:2/38, Turavit:2/6</t>
+          <t>48 ürün okundu; medyan ₺14.052; VitrA/Artema 3 ürün; marka dağılımı: Creavit:14/3, NORMO:13/0, Kale:6/123, VitrA:3/18, Norm:2/75, Serel:2/38, Turavit:2/6</t>
         </is>
       </c>
       <c r="F932" s="7" t="inlineStr">
@@ -34984,7 +34984,7 @@
         </is>
       </c>
     </row>
-    <row r="933" ht="43.5" customHeight="1">
+    <row r="933" ht="30" customHeight="1">
       <c r="A933" s="5" t="inlineStr">
         <is>
           <t>https://www.koctas.com.tr/lavabolar/canak-lavabolar/c/103019003?sort=bestseller-desc</t>
@@ -35007,7 +35007,7 @@
       </c>
       <c r="E933" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 5.140 TL; VitrA/Artema 0 ürün; marka dağılımı: Lena:19/1, Creavit:13/4, Kale:5/0, Turavit:2/9, Seramiksan:2/0, Bien:1/0, İsvea:1/0</t>
+          <t>48 ürün okundu; medyan ₺5.140; VitrA/Artema 0 ürün; marka dağılımı: Lena:19/1, Creavit:13/4, Kale:5/0, Turavit:2/9, Seramiksan:2/0, Bien:1/0, İsvea:1/0</t>
         </is>
       </c>
       <c r="F933" s="7" t="inlineStr">
@@ -35044,7 +35044,7 @@
       </c>
       <c r="E934" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 982 TL; VitrA/Artema 6 ürün; marka dağılımı: VitrA:7/73, Melek Yapı Malzemeleri:5/2, Creavit:5/10, Visam:4/29, Japar:4/1, Siamp:4/10</t>
+          <t>48 ürün okundu; medyan ₺982; VitrA/Artema 6 ürün; marka dağılımı: VitrA:7/73, Melek Yapı Malzemeleri:5/2, Creavit:5/10, Visam:4/29, Japar:4/1, Siamp:4/10</t>
         </is>
       </c>
       <c r="F934" s="7" t="inlineStr">
@@ -35081,7 +35081,7 @@
       </c>
       <c r="E935" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 1.894 TL; VitrA/Artema 8 ürün; marka dağılımı: VitrA:17/2, İsvea:8/0, Geberit:7/0, Creavit:5/0, Nkp:2/1, Kale:2/0</t>
+          <t>48 ürün okundu; medyan ₺1.894; VitrA/Artema 8 ürün; marka dağılımı: VitrA:17/2, İsvea:8/0, Geberit:7/0, Creavit:5/0, Nkp:2/1, Kale:2/0</t>
         </is>
       </c>
       <c r="F935" s="7" t="inlineStr">
@@ -35118,7 +35118,7 @@
       </c>
       <c r="E936" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 5.900 TL; VitrA/Artema 6 ürün; marka dağılımı: VitrA:8/1, İsaoğlu Yapı:7/0, Geberit:6/3, Creavit:6/1, (markasız):4/1, Serel:2/11</t>
+          <t>48 ürün okundu; medyan ₺5.900; VitrA/Artema 6 ürün; marka dağılımı: VitrA:8/1, İsaoğlu Yapı:7/0, Geberit:6/3, Creavit:6/1, (markasız):4/1, Serel:2/11</t>
         </is>
       </c>
       <c r="F936" s="7" t="inlineStr">
@@ -35155,7 +35155,7 @@
       </c>
       <c r="E937" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 22 eşleşen; medyan 5.315 TL; VitrA/Artema 0 ürün; marka dağılımı: Creavit:9, Kale:4, Turavit:2, Lena:1, İsvea:1, Turkuaz Seramik:1</t>
+          <t>48 ürün okundu, 22 eşleşen; medyan ₺5.315; VitrA/Artema 0 ürün; marka dağılımı: Creavit:9, Kale:4, Turavit:2, Lena:1, İsvea:1, Turkuaz Seramik:1</t>
         </is>
       </c>
       <c r="F937" s="7" t="inlineStr">
@@ -35192,7 +35192,7 @@
       </c>
       <c r="E938" s="6" t="inlineStr">
         <is>
-          <t>3 ürün okundu, 3 eşleşen; medyan 1.200 TL; VitrA/Artema 0 ürün; marka dağılımı: Nkp:1, Aqua Bagno:1, T MAY:1</t>
+          <t>3 ürün okundu, 3 eşleşen; medyan ₺1.200; VitrA/Artema 0 ürün; marka dağılımı: Nkp:1, Aqua Bagno:1, T MAY:1</t>
         </is>
       </c>
       <c r="F938" s="7" t="inlineStr">
@@ -35229,7 +35229,7 @@
       </c>
       <c r="E939" s="6" t="inlineStr">
         <is>
-          <t>47 ürün okundu, 43 eşleşen; medyan 3.584 TL; VitrA/Artema 4 ürün; marka dağılımı: Grohe:17, Creavit:9, VitrA:4, Kale:3, Geberit:3, Serel:2</t>
+          <t>47 ürün okundu, 43 eşleşen; medyan ₺3.584; VitrA/Artema 4 ürün; marka dağılımı: Grohe:17, Creavit:9, VitrA:4, Kale:3, Geberit:3, Serel:2</t>
         </is>
       </c>
       <c r="F939" s="7" t="inlineStr">
@@ -35266,7 +35266,7 @@
       </c>
       <c r="E940" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 5.869 TL; VitrA/Artema 1 ürün; marka dağılımı: VitrA:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺5.869; VitrA/Artema 1 ürün; marka dağılımı: VitrA:1</t>
         </is>
       </c>
       <c r="F940" s="7" t="inlineStr">
@@ -35303,7 +35303,7 @@
       </c>
       <c r="E941" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 5.707 TL; VitrA/Artema 1 ürün; marka dağılımı: VitrA:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺5.707; VitrA/Artema 1 ürün; marka dağılımı: VitrA:1</t>
         </is>
       </c>
       <c r="F941" s="7" t="inlineStr">
@@ -35340,7 +35340,7 @@
       </c>
       <c r="E942" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 1.104 TL; VitrA/Artema 0 ürün; marka dağılımı: Punto:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺1.104; VitrA/Artema 0 ürün; marka dağılımı: Punto:1</t>
         </is>
       </c>
       <c r="F942" s="7" t="inlineStr">
@@ -35414,7 +35414,7 @@
       </c>
       <c r="E944" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 11.620 TL; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺11.620; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz:1</t>
         </is>
       </c>
       <c r="F944" s="7" t="inlineStr">
@@ -35488,7 +35488,7 @@
       </c>
       <c r="E946" s="6" t="inlineStr">
         <is>
-          <t>49 ürün okundu, 34 eşleşen; medyan 7.716 TL; VitrA/Artema 0 ürün; marka dağılımı: Orka:18, Kale:5, Creavit:4, Özceden:4, Newarc:1, Roomart:1</t>
+          <t>49 ürün okundu, 34 eşleşen; medyan ₺7.716; VitrA/Artema 0 ürün; marka dağılımı: Orka:18, Kale:5, Creavit:4, Özceden:4, Newarc:1, Roomart:1</t>
         </is>
       </c>
       <c r="F946" s="7" t="inlineStr">
@@ -35525,7 +35525,7 @@
       </c>
       <c r="E947" s="6" t="inlineStr">
         <is>
-          <t>49 ürün okundu, 35 eşleşen; medyan 6.035 TL; VitrA/Artema 0 ürün; marka dağılımı: Roomart:19, Karen Banyo:10, Balneom:2, Furniqo:1, Dekorister:1, Dmz Home Concept:1</t>
+          <t>49 ürün okundu, 35 eşleşen; medyan ₺6.035; VitrA/Artema 0 ürün; marka dağılımı: Roomart:19, Karen Banyo:10, Balneom:2, Furniqo:1, Dekorister:1, Dmz Home Concept:1</t>
         </is>
       </c>
       <c r="F947" s="7" t="inlineStr">
@@ -35562,7 +35562,7 @@
       </c>
       <c r="E948" s="6" t="inlineStr">
         <is>
-          <t>18 ürün okundu, 4 eşleşen; medyan 17.812 TL; VitrA/Artema 0 ürün; marka dağılımı: GPD:4</t>
+          <t>18 ürün okundu, 4 eşleşen; medyan ₺17.812; VitrA/Artema 0 ürün; marka dağılımı: GPD:4</t>
         </is>
       </c>
       <c r="F948" s="7" t="inlineStr">
@@ -35599,7 +35599,7 @@
       </c>
       <c r="E949" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 36 eşleşen; medyan 974 TL; VitrA/Artema 1 ürün; marka dağılımı: (markasız):8, Primanova:3, Temel:3, SAS:2, Motek:2, Geseus:2</t>
+          <t>48 ürün okundu, 36 eşleşen; medyan ₺974; VitrA/Artema 1 ürün; marka dağılımı: (markasız):8, Primanova:3, Temel:3, SAS:2, Motek:2, Geseus:2</t>
         </is>
       </c>
       <c r="F949" s="7" t="inlineStr">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="E950" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 46 eşleşen; medyan 824 TL; VitrA/Artema 0 ürün; marka dağılımı: Durevo:12, SAS:6, Tema:6, Unisoft:4, Çelik Banyo:3, Ceraware:2</t>
+          <t>48 ürün okundu, 46 eşleşen; medyan ₺824; VitrA/Artema 0 ürün; marka dağılımı: Durevo:12, SAS:6, Tema:6, Unisoft:4, Çelik Banyo:3, Ceraware:2</t>
         </is>
       </c>
       <c r="F950" s="7" t="inlineStr">
@@ -35673,7 +35673,7 @@
       </c>
       <c r="E951" s="6" t="inlineStr">
         <is>
-          <t>50 ürün okundu, 1 eşleşen; medyan 5.699 TL; VitrA/Artema 0 ürün; marka dağılımı: Esmopa Mobilya:1</t>
+          <t>50 ürün okundu, 1 eşleşen; medyan ₺5.699; VitrA/Artema 0 ürün; marka dağılımı: Esmopa Mobilya:1</t>
         </is>
       </c>
       <c r="F951" s="7" t="inlineStr">
@@ -35710,7 +35710,7 @@
       </c>
       <c r="E952" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 48 eşleşen; medyan 120 TL; VitrA/Artema 0 ürün; marka dağılımı: Pomerol:48</t>
+          <t>48 ürün okundu, 48 eşleşen; medyan ₺120; VitrA/Artema 0 ürün; marka dağılımı: Pomerol:48</t>
         </is>
       </c>
       <c r="F952" s="7" t="inlineStr">
@@ -35747,7 +35747,7 @@
       </c>
       <c r="E953" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 16 eşleşen; medyan 7.199 TL; VitrA/Artema 0 ürün; marka dağılımı: Nysamo:6, Alonex:4, Fly Mutfak ve Banyo:2, Netdeko:2, Konsolplus:1, Adore Mobilya:1</t>
+          <t>36 ürün okundu, 16 eşleşen; medyan ₺7.199; VitrA/Artema 0 ürün; marka dağılımı: Nysamo:6, Alonex:4, Fly Mutfak ve Banyo:2, Netdeko:2, Konsolplus:1, Adore Mobilya:1</t>
         </is>
       </c>
       <c r="F953" s="7" t="inlineStr">
@@ -35784,7 +35784,7 @@
       </c>
       <c r="E954" s="6" t="inlineStr">
         <is>
-          <t>50 ürün okundu, 1 eşleşen; medyan 7.199 TL; VitrA/Artema 0 ürün; marka dağılımı: Roomart:1</t>
+          <t>50 ürün okundu, 1 eşleşen; medyan ₺7.199; VitrA/Artema 0 ürün; marka dağılımı: Roomart:1</t>
         </is>
       </c>
       <c r="F954" s="7" t="inlineStr">
@@ -35821,7 +35821,7 @@
       </c>
       <c r="E955" s="6" t="inlineStr">
         <is>
-          <t>50 ürün okundu, 19 eşleşen; medyan 10.189 TL; VitrA/Artema 1 ürün; marka dağılımı: Cennet Yatak:3, Midoser:2, Eymense:2, Durevo:2, Setay Mobilya:2, VitrA:1</t>
+          <t>50 ürün okundu, 19 eşleşen; medyan ₺10.189; VitrA/Artema 1 ürün; marka dağılımı: Cennet Yatak:3, Midoser:2, Eymense:2, Durevo:2, Setay Mobilya:2, VitrA:1</t>
         </is>
       </c>
       <c r="F955" s="7" t="inlineStr">
@@ -35858,7 +35858,7 @@
       </c>
       <c r="E956" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 48 eşleşen; medyan 454 TL; VitrA/Artema 1 ürün; marka dağılımı: Kobos:10, Koçtaş Basic:7, Primanova:4, (markasız):3, Meleni Home:3, Koçtaş Plus:2</t>
+          <t>48 ürün okundu, 48 eşleşen; medyan ₺454; VitrA/Artema 1 ürün; marka dağılımı: Kobos:10, Koçtaş Basic:7, Primanova:4, (markasız):3, Meleni Home:3, Koçtaş Plus:2</t>
         </is>
       </c>
       <c r="F956" s="7" t="inlineStr">
@@ -35895,7 +35895,7 @@
       </c>
       <c r="E957" s="6" t="inlineStr">
         <is>
-          <t>17 ürün okundu, 3 eşleşen; medyan 9.399 TL; VitrA/Artema 0 ürün; marka dağılımı: Atolye 10:2, Karen Banyo:1</t>
+          <t>17 ürün okundu, 3 eşleşen; medyan ₺9.399; VitrA/Artema 0 ürün; marka dağılımı: Atolye 10:2, Karen Banyo:1</t>
         </is>
       </c>
       <c r="F957" s="7" t="inlineStr">
@@ -35932,7 +35932,7 @@
       </c>
       <c r="E958" s="6" t="inlineStr">
         <is>
-          <t>37 ürün okundu, 32 eşleşen; medyan 16.700 TL; VitrA/Artema 2 ürün; marka dağılımı: Grohe:13, Tema:4, Armour Armatür:3, Duxxa:3, Penta:2, Latte:2</t>
+          <t>37 ürün okundu, 32 eşleşen; medyan ₺16.700; VitrA/Artema 2 ürün; marka dağılımı: Grohe:13, Tema:4, Armour Armatür:3, Duxxa:3, Penta:2, Latte:2</t>
         </is>
       </c>
       <c r="F958" s="7" t="inlineStr">
@@ -35969,7 +35969,7 @@
       </c>
       <c r="E959" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 13.516 TL; VitrA/Artema 2 ürün; marka dağılımı: Grohe:2, VitrA:1, Hansgrohe:1, Artema:1</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺13.516; VitrA/Artema 2 ürün; marka dağılımı: Grohe:2, VitrA:1, Hansgrohe:1, Artema:1</t>
         </is>
       </c>
       <c r="F959" s="7" t="inlineStr">
@@ -36006,7 +36006,7 @@
       </c>
       <c r="E960" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 48 eşleşen; medyan 4.894 TL; VitrA/Artema 8 ürün; marka dağılımı: System Banyo Aksesuarları:27, Kobos:9, VitrA:4, Artema:4, İsaoğlu Yapı:2, İntema:1</t>
+          <t>48 ürün okundu, 48 eşleşen; medyan ₺4.894; VitrA/Artema 8 ürün; marka dağılımı: System Banyo Aksesuarları:27, Kobos:9, VitrA:4, Artema:4, İsaoğlu Yapı:2, İntema:1</t>
         </is>
       </c>
       <c r="F960" s="7" t="inlineStr">
@@ -36043,7 +36043,7 @@
       </c>
       <c r="E961" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 41 eşleşen; medyan 6.020 TL; VitrA/Artema 10 ürün; marka dağılımı: Grohe:26, Artema:8, VitrA:2, Hansgrohe:2, Roca:1, ECA:1</t>
+          <t>48 ürün okundu, 41 eşleşen; medyan ₺6.020; VitrA/Artema 10 ürün; marka dağılımı: Grohe:26, Artema:8, VitrA:2, Hansgrohe:2, Roca:1, ECA:1</t>
         </is>
       </c>
       <c r="F961" s="7" t="inlineStr">
@@ -36080,7 +36080,7 @@
       </c>
       <c r="E962" s="6" t="inlineStr">
         <is>
-          <t>2 ürün okundu, 2 eşleşen; medyan 6.013 TL; VitrA/Artema 0 ürün; marka dağılımı: Kale:2</t>
+          <t>2 ürün okundu, 2 eşleşen; medyan ₺6.013; VitrA/Artema 0 ürün; marka dağılımı: Kale:2</t>
         </is>
       </c>
       <c r="F962" s="7" t="inlineStr">
@@ -36117,7 +36117,7 @@
       </c>
       <c r="E963" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 40 eşleşen; medyan 11.164 TL; VitrA/Artema 14 ürün; marka dağılımı: Artema:7, VitrA:7, Hansgrohe:6, Armour Armatür:3, Ar Muslukçuluk:3, Sam Banyo:3</t>
+          <t>48 ürün okundu, 40 eşleşen; medyan ₺11.164; VitrA/Artema 14 ürün; marka dağılımı: Artema:7, VitrA:7, Hansgrohe:6, Armour Armatür:3, Ar Muslukçuluk:3, Sam Banyo:3</t>
         </is>
       </c>
       <c r="F963" s="7" t="inlineStr">
@@ -36154,7 +36154,7 @@
       </c>
       <c r="E964" s="6" t="inlineStr">
         <is>
-          <t>3 ürün okundu, 3 eşleşen; medyan 14.783 TL; VitrA/Artema 0 ürün; marka dağılımı: Sanacryl:3</t>
+          <t>3 ürün okundu, 3 eşleşen; medyan ₺14.783; VitrA/Artema 0 ürün; marka dağılımı: Sanacryl:3</t>
         </is>
       </c>
       <c r="F964" s="7" t="inlineStr">
@@ -36191,7 +36191,7 @@
       </c>
       <c r="E965" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 6.899 TL; VitrA/Artema 0 ürün; marka dağılımı: Mega:2, Kale:1, İsvea:1, Creavit:1</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺6.899; VitrA/Artema 0 ürün; marka dağılımı: Mega:2, Kale:1, İsvea:1, Creavit:1</t>
         </is>
       </c>
       <c r="F965" s="7" t="inlineStr">
@@ -36228,7 +36228,7 @@
       </c>
       <c r="E966" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 48 eşleşen; medyan 3.250 TL; VitrA/Artema 20 ürün; marka dağılımı: Artema:12, VitrA:8, Tema:5, Kale:5, Monavit:4, Fause:4</t>
+          <t>48 ürün okundu, 48 eşleşen; medyan ₺3.250; VitrA/Artema 20 ürün; marka dağılımı: Artema:12, VitrA:8, Tema:5, Kale:5, Monavit:4, Fause:4</t>
         </is>
       </c>
       <c r="F966" s="7" t="inlineStr">
@@ -36265,7 +36265,7 @@
       </c>
       <c r="E967" s="6" t="inlineStr">
         <is>
-          <t>15 ürün okundu, 15 eşleşen; medyan 40.000 TL; VitrA/Artema 0 ürün; marka dağılımı: NORMO:15</t>
+          <t>15 ürün okundu, 15 eşleşen; medyan ₺40.000; VitrA/Artema 0 ürün; marka dağılımı: NORMO:15</t>
         </is>
       </c>
       <c r="F967" s="7" t="inlineStr">
@@ -36302,7 +36302,7 @@
       </c>
       <c r="E968" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 48 eşleşen; medyan 11.385 TL; VitrA/Artema 2 ürün; marka dağılımı: Real Stone:32, Creavit:11, VitrA:2, Turkuaz Seramik:2, Kale:1</t>
+          <t>48 ürün okundu, 48 eşleşen; medyan ₺11.385; VitrA/Artema 2 ürün; marka dağılımı: Real Stone:32, Creavit:11, VitrA:2, Turkuaz Seramik:2, Kale:1</t>
         </is>
       </c>
       <c r="F968" s="7" t="inlineStr">
@@ -36339,7 +36339,7 @@
       </c>
       <c r="E969" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 47 eşleşen; medyan 14.700 TL; VitrA/Artema 9 ürün; marka dağılımı: Creavit:10, Grohe:10, VitrA:7, GPD:6, Omnipazar:4, Artema:2</t>
+          <t>48 ürün okundu, 47 eşleşen; medyan ₺14.700; VitrA/Artema 9 ürün; marka dağılımı: Creavit:10, Grohe:10, VitrA:7, GPD:6, Omnipazar:4, Artema:2</t>
         </is>
       </c>
       <c r="F969" s="7" t="inlineStr">
@@ -36376,7 +36376,7 @@
       </c>
       <c r="E970" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 48 eşleşen; medyan 620 TL; VitrA/Artema 1 ürün; marka dağılımı: Tema:4, Özgü Banyo:3, Çelik Banyo:3, SAS:3, Mk Yapı:3, Durevo:3</t>
+          <t>48 ürün okundu, 48 eşleşen; medyan ₺620; VitrA/Artema 1 ürün; marka dağılımı: Tema:4, Özgü Banyo:3, Çelik Banyo:3, SAS:3, Mk Yapı:3, Durevo:3</t>
         </is>
       </c>
       <c r="F970" s="7" t="inlineStr">
@@ -36413,7 +36413,7 @@
       </c>
       <c r="E971" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 48 eşleşen; medyan 27.782 TL; VitrA/Artema 0 ürün; marka dağılımı: Sırduş:36, Creavit:3, Nkp:2, Tema:2, M3decorium:2, Karen Banyo:1</t>
+          <t>48 ürün okundu, 48 eşleşen; medyan ₺27.782; VitrA/Artema 0 ürün; marka dağılımı: Sırduş:36, Creavit:3, Nkp:2, Tema:2, M3decorium:2, Karen Banyo:1</t>
         </is>
       </c>
       <c r="F971" s="7" t="inlineStr">
@@ -36450,7 +36450,7 @@
       </c>
       <c r="E972" s="6" t="inlineStr">
         <is>
-          <t>15 ürün okundu, 15 eşleşen; medyan 3.165 TL; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz:3, (markasız):3, Turkuaz Seramik:2, ESVİT:2, Creavit:2, Fildişi:1</t>
+          <t>15 ürün okundu, 15 eşleşen; medyan ₺3.165; VitrA/Artema 0 ürün; marka dağılımı: Turkuaz:3, (markasız):3, Turkuaz Seramik:2, ESVİT:2, Creavit:2, Fildişi:1</t>
         </is>
       </c>
       <c r="F972" s="7" t="inlineStr">
@@ -36487,7 +36487,7 @@
       </c>
       <c r="E973" s="6" t="inlineStr">
         <is>
-          <t>49 ürün okundu, 48 eşleşen; medyan 31.673 TL; VitrA/Artema 2 ürün; marka dağılımı: Grohe:18, Tema:11, İsaoğlu Yapı:6, LPD:5, Armour Armatür:3, ECA:2</t>
+          <t>49 ürün okundu, 48 eşleşen; medyan ₺31.673; VitrA/Artema 2 ürün; marka dağılımı: Grohe:18, Tema:11, İsaoğlu Yapı:6, LPD:5, Armour Armatür:3, ECA:2</t>
         </is>
       </c>
       <c r="F973" s="7" t="inlineStr">
@@ -36524,7 +36524,7 @@
       </c>
       <c r="E974" s="6" t="inlineStr">
         <is>
-          <t>3 ürün okundu, 3 eşleşen; medyan 699 TL; VitrA/Artema 0 ürün; marka dağılımı: Bant Evi:2, Geseus:1</t>
+          <t>3 ürün okundu, 3 eşleşen; medyan ₺699; VitrA/Artema 0 ürün; marka dağılımı: Bant Evi:2, Geseus:1</t>
         </is>
       </c>
       <c r="F974" s="7" t="inlineStr">
@@ -36561,7 +36561,7 @@
       </c>
       <c r="E975" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; medyan 7.175 TL; VitrA/Artema 0 ürün; marka dağılımı: Sam Banyo:6</t>
+          <t>6 ürün okundu, 6 eşleşen; medyan ₺7.175; VitrA/Artema 0 ürün; marka dağılımı: Sam Banyo:6</t>
         </is>
       </c>
       <c r="F975" s="7" t="inlineStr">
@@ -36598,7 +36598,7 @@
       </c>
       <c r="E976" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 1 eşleşen; medyan 135 TL; VitrA/Artema 0 ürün; marka dağılımı: Primanova:1</t>
+          <t>48 ürün okundu, 1 eşleşen; medyan ₺135; VitrA/Artema 0 ürün; marka dağılımı: Primanova:1</t>
         </is>
       </c>
       <c r="F976" s="7" t="inlineStr">
@@ -36635,7 +36635,7 @@
       </c>
       <c r="E977" s="6" t="inlineStr">
         <is>
-          <t>1 ürün okundu, 1 eşleşen; medyan 1.459 TL; VitrA/Artema 0 ürün; marka dağılımı: Ege Vitrifiye:1</t>
+          <t>1 ürün okundu, 1 eşleşen; medyan ₺1.459; VitrA/Artema 0 ürün; marka dağılımı: Ege Vitrifiye:1</t>
         </is>
       </c>
       <c r="F977" s="7" t="inlineStr">
@@ -36672,7 +36672,7 @@
       </c>
       <c r="E978" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 48 eşleşen; medyan 996 TL; VitrA/Artema 8 ürün; marka dağılımı: Fkn:15, İsaoğlu Yapı:13, VitrA:7, LPD:5, Bocchi:4, Melek Yapı Malzemeleri:1</t>
+          <t>48 ürün okundu, 48 eşleşen; medyan ₺996; VitrA/Artema 8 ürün; marka dağılımı: Fkn:15, İsaoğlu Yapı:13, VitrA:7, LPD:5, Bocchi:4, Melek Yapı Malzemeleri:1</t>
         </is>
       </c>
       <c r="F978" s="7" t="inlineStr">
@@ -36709,7 +36709,7 @@
       </c>
       <c r="E979" s="6" t="inlineStr">
         <is>
-          <t>22 ürün okundu, 22 eşleşen; medyan 8.757 TL; VitrA/Artema 0 ürün; marka dağılımı: Bimossa:6, Setay Mobilya:4, sarmobi:4, Eymense:3, Noiss:2, Aeka:1</t>
+          <t>22 ürün okundu, 22 eşleşen; medyan ₺8.757; VitrA/Artema 0 ürün; marka dağılımı: Bimossa:6, Setay Mobilya:4, sarmobi:4, Eymense:3, Noiss:2, Aeka:1</t>
         </is>
       </c>
       <c r="F979" s="7" t="inlineStr">
@@ -36746,7 +36746,7 @@
       </c>
       <c r="E980" s="6" t="inlineStr">
         <is>
-          <t>21 ürün okundu, 14 eşleşen; medyan 17.684 TL; VitrA/Artema 9 ürün; marka dağılımı: VitrA:9, Flow Yapı:2, Sam Banyo:2, GPD:1</t>
+          <t>21 ürün okundu, 14 eşleşen; medyan ₺17.684; VitrA/Artema 9 ürün; marka dağılımı: VitrA:9, Flow Yapı:2, Sam Banyo:2, GPD:1</t>
         </is>
       </c>
       <c r="F980" s="7" t="inlineStr">
@@ -36783,7 +36783,7 @@
       </c>
       <c r="E981" s="6" t="inlineStr">
         <is>
-          <t>3 ürün okundu, 3 eşleşen; medyan 3.500 TL; VitrA/Artema 2 ürün; marka dağılımı: VitrA:2, Grohe:1</t>
+          <t>3 ürün okundu, 3 eşleşen; medyan ₺3.500; VitrA/Artema 2 ürün; marka dağılımı: VitrA:2, Grohe:1</t>
         </is>
       </c>
       <c r="F981" s="7" t="inlineStr">
@@ -36820,7 +36820,7 @@
       </c>
       <c r="E982" s="6" t="inlineStr">
         <is>
-          <t>39 ürün okundu, 39 eşleşen; medyan 37.500 TL; VitrA/Artema 0 ürün; marka dağılımı: (markasız):20, Bocchi:14, Turavit:2, Newarc:1, Creavit:1, Lena:1</t>
+          <t>39 ürün okundu, 39 eşleşen; medyan ₺37.500; VitrA/Artema 0 ürün; marka dağılımı: (markasız):20, Bocchi:14, Turavit:2, Newarc:1, Creavit:1, Lena:1</t>
         </is>
       </c>
       <c r="F982" s="7" t="inlineStr">
@@ -36857,7 +36857,7 @@
       </c>
       <c r="E983" s="6" t="inlineStr">
         <is>
-          <t>9 ürün okundu, 9 eşleşen; medyan 3.750 TL; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:9</t>
+          <t>9 ürün okundu, 9 eşleşen; medyan ₺3.750; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:9</t>
         </is>
       </c>
       <c r="F983" s="7" t="inlineStr">
@@ -36894,7 +36894,7 @@
       </c>
       <c r="E984" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, 5 eşleşen; medyan 3.199 TL; VitrA/Artema 1 ürün; marka dağılımı: Creavit:3, VitrA:1, Grohe:1</t>
+          <t>5 ürün okundu, 5 eşleşen; medyan ₺3.199; VitrA/Artema 1 ürün; marka dağılımı: Creavit:3, VitrA:1, Grohe:1</t>
         </is>
       </c>
       <c r="F984" s="7" t="inlineStr">
@@ -36931,7 +36931,7 @@
       </c>
       <c r="E985" s="6" t="inlineStr">
         <is>
-          <t>47 ürün okundu, 46 eşleşen; medyan 3.808 TL; VitrA/Artema 33 ürün; marka dağılımı: Artema:21, VitrA:12, Tema:4, Armour Armatür:3, Kale:3, Çanakkale Seramik:1</t>
+          <t>47 ürün okundu, 46 eşleşen; medyan ₺3.808; VitrA/Artema 33 ürün; marka dağılımı: Artema:21, VitrA:12, Tema:4, Armour Armatür:3, Kale:3, Çanakkale Seramik:1</t>
         </is>
       </c>
       <c r="F985" s="7" t="inlineStr">
@@ -36968,7 +36968,7 @@
       </c>
       <c r="E986" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 30 eşleşen; medyan 7.419 TL; VitrA/Artema 8 ürün; marka dağılımı: ECA:15, Grohe:6, Artema:5, VitrA:3, Roca:1</t>
+          <t>48 ürün okundu, 30 eşleşen; medyan ₺7.419; VitrA/Artema 8 ürün; marka dağılımı: ECA:15, Grohe:6, Artema:5, VitrA:3, Roca:1</t>
         </is>
       </c>
       <c r="F986" s="7" t="inlineStr">
@@ -37005,7 +37005,7 @@
       </c>
       <c r="E987" s="6" t="inlineStr">
         <is>
-          <t>3 ürün okundu, 3 eşleşen; medyan 11.246 TL; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3</t>
+          <t>3 ürün okundu, 3 eşleşen; medyan ₺11.246; VitrA/Artema 3 ürün; marka dağılımı: VitrA:3</t>
         </is>
       </c>
       <c r="F987" s="7" t="inlineStr">
@@ -37042,7 +37042,7 @@
       </c>
       <c r="E988" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 26 eşleşen; medyan 27.954 TL; VitrA/Artema 1 ürün; marka dağılımı: Grohe:17, ECA:7, Kale:1, Artema:1</t>
+          <t>48 ürün okundu, 26 eşleşen; medyan ₺27.954; VitrA/Artema 1 ürün; marka dağılımı: Grohe:17, ECA:7, Kale:1, Artema:1</t>
         </is>
       </c>
       <c r="F988" s="7" t="inlineStr">
@@ -37079,7 +37079,7 @@
       </c>
       <c r="E989" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 48 eşleşen; medyan 998 TL; VitrA/Artema 0 ürün; marka dağılımı: Primanova:11, Selim:10, Kobos:8, Efe:3, (markasız):3, SAS:2</t>
+          <t>48 ürün okundu, 48 eşleşen; medyan ₺998; VitrA/Artema 0 ürün; marka dağılımı: Primanova:11, Selim:10, Kobos:8, Efe:3, (markasız):3, SAS:2</t>
         </is>
       </c>
       <c r="F989" s="7" t="inlineStr">
@@ -37116,7 +37116,7 @@
       </c>
       <c r="E990" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 48 eşleşen; medyan 441 TL; VitrA/Artema 3 ürün; marka dağılımı: MultiStore:11, Çelik Banyo:7, SAS:5, Özgü Banyo:5, Tema:3, Fause:2</t>
+          <t>48 ürün okundu, 48 eşleşen; medyan ₺441; VitrA/Artema 3 ürün; marka dağılımı: MultiStore:11, Çelik Banyo:7, SAS:5, Özgü Banyo:5, Tema:3, Fause:2</t>
         </is>
       </c>
       <c r="F990" s="7" t="inlineStr">
@@ -37153,7 +37153,7 @@
       </c>
       <c r="E991" s="6" t="inlineStr">
         <is>
-          <t>4 ürün okundu, 4 eşleşen; medyan 8.155 TL; VitrA/Artema 1 ürün; marka dağılımı: Creavit:3, VitrA:1</t>
+          <t>4 ürün okundu, 4 eşleşen; medyan ₺8.155; VitrA/Artema 1 ürün; marka dağılımı: Creavit:3, VitrA:1</t>
         </is>
       </c>
       <c r="F991" s="7" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="E992" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu, 47 eşleşen; medyan 5.601 TL; VitrA/Artema 0 ürün; marka dağılımı: LPD:16, İsaoğlu Yapı:9, Durevo:8, Rena Design:5, Fause:4, Roca:4</t>
+          <t>48 ürün okundu, 47 eşleşen; medyan ₺5.601; VitrA/Artema 0 ürün; marka dağılımı: LPD:16, İsaoğlu Yapı:9, Durevo:8, Rena Design:5, Fause:4, Roca:4</t>
         </is>
       </c>
       <c r="F992" s="7" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="E993" s="6" t="inlineStr">
         <is>
-          <t>2 ürün okundu, 2 eşleşen; medyan 3.346 TL; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:1, Serel:1</t>
+          <t>2 ürün okundu, 2 eşleşen; medyan ₺3.346; VitrA/Artema 0 ürün; marka dağılımı: Bocchi:1, Serel:1</t>
         </is>
       </c>
       <c r="F993" s="7" t="inlineStr">
@@ -37264,7 +37264,7 @@
       </c>
       <c r="E994" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 1.250 TL; VitrA/Artema 7 ürün; marka dağılımı: Nkp:10/21, VitrA:7/56, Visam:6/36, Serel:5/50, Housera:5/19, Kale:4/41, Geseus:3/4, Creavi</t>
+          <t>48 ürün okundu; medyan ₺1.250; VitrA/Artema 7 ürün; marka dağılımı: Nkp:10/21, VitrA:7/56, Visam:6/36, Serel:5/50, Housera:5/19, Kale:4/41, Geseus:3/4, Creavi</t>
         </is>
       </c>
       <c r="F994" s="7" t="inlineStr">
@@ -37301,7 +37301,7 @@
       </c>
       <c r="E995" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 9.416 TL; VitrA/Artema 4 ürün; marka dağılımı: Creavit:19/23, Kale:7/125, VitrA:4/18, Norm:3/80, Turavit:3/14, Turkuaz Seramik:2/5, Serel</t>
+          <t>48 ürün okundu; medyan ₺9.416; VitrA/Artema 4 ürün; marka dağılımı: Creavit:19/23, Kale:7/125, VitrA:4/18, Norm:3/80, Turavit:3/14, Turkuaz Seramik:2/5, Serel</t>
         </is>
       </c>
       <c r="F995" s="7" t="inlineStr">
@@ -37338,7 +37338,7 @@
       </c>
       <c r="E996" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 3.540 TL; VitrA/Artema 2 ürün; marka dağılımı: Creavit:7/6, Kale:6/0, ESVİT:5/3, Karen Seramik:3/10, Turavit:3/10, Seramiksan:3/0, (marka</t>
+          <t>48 ürün okundu; medyan ₺3.540; VitrA/Artema 2 ürün; marka dağılımı: Creavit:7/6, Kale:6/0, ESVİT:5/3, Karen Seramik:3/10, Turavit:3/10, Seramiksan:3/0, (marka</t>
         </is>
       </c>
       <c r="F996" s="7" t="inlineStr">
@@ -37375,7 +37375,7 @@
       </c>
       <c r="E997" s="6" t="inlineStr">
         <is>
-          <t>48 ürün okundu; medyan 8.095 TL; VitrA/Artema 6 ürün; marka dağılımı: Bocchi:24/0, Creavit:7/0, VitrA:7/0, Newarc:2/0, Turavit:2/0, Dura Tiles:2/0</t>
+          <t>48 ürün okundu; medyan ₺8.095; VitrA/Artema 6 ürün; marka dağılımı: Bocchi:24/0, Creavit:7/0, VitrA:7/0, Newarc:2/0, Turavit:2/0, Dura Tiles:2/0</t>
         </is>
       </c>
       <c r="F997" s="7" t="inlineStr">
@@ -37412,7 +37412,7 @@
       </c>
       <c r="E998" s="6" t="inlineStr">
         <is>
-          <t>8 ürün okundu, kategori toplamı 1688; medyan 3.281 TL; toplam değerlendirme 9335; 7 marka; VitrA/Artema 0 ürün</t>
+          <t>8 ürün okundu, kategori toplamı 1688; medyan ₺3.281; toplam değerlendirme 9335; 7 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F998" s="7" t="inlineStr">
@@ -37449,7 +37449,7 @@
       </c>
       <c r="E999" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 25 eşleşen; toplam 1420; medyan 3.500 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 25 eşleşen; toplam 1420; medyan ₺3.500; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F999" s="7" t="inlineStr">
@@ -37486,7 +37486,7 @@
       </c>
       <c r="E1000" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 19 eşleşen; toplam 2238; medyan 484 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 19 eşleşen; toplam 2238; medyan ₺484; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1000" s="7" t="inlineStr">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="E1001" s="6" t="inlineStr">
         <is>
-          <t>13 ürün okundu, kategori toplamı 1069; medyan 2.590 TL; toplam değerlendirme 2451; 8 marka; VitrA/Artema 5 ürün</t>
+          <t>13 ürün okundu, kategori toplamı 1069; medyan ₺2.590; toplam değerlendirme 2451; 8 marka; VitrA/Artema 5 ürün</t>
         </is>
       </c>
       <c r="F1001" s="7" t="inlineStr">
@@ -37560,7 +37560,7 @@
       </c>
       <c r="E1002" s="6" t="inlineStr">
         <is>
-          <t>2 ürün okundu, 2 eşleşen; toplam 2; medyan 26.752 TL; VitrA/Artema 2 ürün</t>
+          <t>2 ürün okundu, 2 eşleşen; toplam 2; medyan ₺26.752; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F1002" s="7" t="inlineStr">
@@ -37597,7 +37597,7 @@
       </c>
       <c r="E1003" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 8 eşleşen; toplam 1010; medyan 1.600 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 8 eşleşen; toplam 1010; medyan ₺1.600; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1003" s="7" t="inlineStr">
@@ -37634,7 +37634,7 @@
       </c>
       <c r="E1004" s="6" t="inlineStr">
         <is>
-          <t>13 ürün okundu, kategori toplamı 2086; medyan 1.250 TL; toplam değerlendirme 605; 6 marka; VitrA/Artema 8 ürün</t>
+          <t>13 ürün okundu, kategori toplamı 2086; medyan ₺1.250; toplam değerlendirme 605; 6 marka; VitrA/Artema 8 ürün</t>
         </is>
       </c>
       <c r="F1004" s="7" t="inlineStr">
@@ -37671,7 +37671,7 @@
       </c>
       <c r="E1005" s="6" t="inlineStr">
         <is>
-          <t>30 ürün okundu, 30 eşleşen; toplam 30; medyan 13.356 TL; VitrA/Artema 11 ürün</t>
+          <t>30 ürün okundu, 30 eşleşen; toplam 30; medyan ₺13.356; VitrA/Artema 11 ürün</t>
         </is>
       </c>
       <c r="F1005" s="7" t="inlineStr">
@@ -37708,7 +37708,7 @@
       </c>
       <c r="E1006" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 8 eşleşen; toplam 1010; medyan 657 TL; VitrA/Artema 2 ürün</t>
+          <t>36 ürün okundu, 8 eşleşen; toplam 1010; medyan ₺657; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F1006" s="7" t="inlineStr">
@@ -37745,7 +37745,7 @@
       </c>
       <c r="E1007" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 4208; medyan 385 TL; toplam değerlendirme 8156; 35 marka; VitrA/Artema 9 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 4208; medyan ₺385; toplam değerlendirme 8156; 35 marka; VitrA/Artema 9 ürün</t>
         </is>
       </c>
       <c r="F1007" s="7" t="inlineStr">
@@ -37782,7 +37782,7 @@
       </c>
       <c r="E1008" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, kategori toplamı 978; medyan 8.274 TL; toplam değerlendirme 221; 2 marka; VitrA/Artema 0 ürün</t>
+          <t>6 ürün okundu, kategori toplamı 978; medyan ₺8.274; toplam değerlendirme 221; 2 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1008" s="7" t="inlineStr">
@@ -37819,7 +37819,7 @@
       </c>
       <c r="E1009" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 7 eşleşen; toplam 1657; medyan 1.938 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 7 eşleşen; toplam 1657; medyan ₺1.938; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1009" s="7" t="inlineStr">
@@ -37856,7 +37856,7 @@
       </c>
       <c r="E1010" s="6" t="inlineStr">
         <is>
-          <t>2 ürün okundu, 2 eşleşen; toplam 2; medyan 13.319 TL; VitrA/Artema 0 ürün</t>
+          <t>2 ürün okundu, 2 eşleşen; toplam 2; medyan ₺13.319; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1010" s="7" t="inlineStr">
@@ -37893,7 +37893,7 @@
       </c>
       <c r="E1011" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, kategori toplamı 1711; medyan 2.660 TL; toplam değerlendirme 528; 23 marka; VitrA/Artema 4 ürün</t>
+          <t>36 ürün okundu, kategori toplamı 1711; medyan ₺2.660; toplam değerlendirme 528; 23 marka; VitrA/Artema 4 ürün</t>
         </is>
       </c>
       <c r="F1011" s="7" t="inlineStr">
@@ -37930,7 +37930,7 @@
       </c>
       <c r="E1012" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 19 eşleşen; toplam 975; medyan 9.622 TL; VitrA/Artema 2 ürün</t>
+          <t>36 ürün okundu, 19 eşleşen; toplam 975; medyan ₺9.622; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F1012" s="7" t="inlineStr">
@@ -37967,7 +37967,7 @@
       </c>
       <c r="E1013" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 2 eşleşen; toplam 1281; medyan 199 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 2 eşleşen; toplam 1281; medyan ₺199; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1013" s="7" t="inlineStr">
@@ -38004,7 +38004,7 @@
       </c>
       <c r="E1014" s="6" t="inlineStr">
         <is>
-          <t>8 ürün okundu, kategori toplamı 1524; medyan 1.189 TL; toplam değerlendirme 7975; 3 marka; VitrA/Artema 0 ürün | 36 ürün okundu, 11 eşleşen; toplam 1514; medyan 1.175 TL; VitrA/Artema 0 ürün</t>
+          <t>8 ürün okundu, kategori toplamı 1524; medyan ₺1.189; toplam değerlendirme 7975; 3 marka; VitrA/Artema 0 ürün | 36 ürün okundu, 11 eşleşen; toplam 1514; medyan ₺1.175; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1014" s="7" t="inlineStr">
@@ -38041,7 +38041,7 @@
       </c>
       <c r="E1015" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 1012; medyan 954 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 1012; medyan ₺954; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1015" s="7" t="inlineStr">
@@ -38078,7 +38078,7 @@
       </c>
       <c r="E1016" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 21 eşleşen; toplam 4963; medyan 299 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 21 eşleşen; toplam 4963; medyan ₺299; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1016" s="7" t="inlineStr">
@@ -38115,7 +38115,7 @@
       </c>
       <c r="E1017" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 31529; medyan 570 TL; toplam değerlendirme 69138; 26 marka; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 31529; medyan ₺570; toplam değerlendirme 69138; 26 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1017" s="7" t="inlineStr">
@@ -38152,7 +38152,7 @@
       </c>
       <c r="E1018" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 21 eşleşen; toplam 31054; medyan 149 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 21 eşleşen; toplam 31054; medyan ₺149; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1018" s="7" t="inlineStr">
@@ -38189,7 +38189,7 @@
       </c>
       <c r="E1019" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 6647; medyan 2.312 TL; toplam değerlendirme 10124; 26 marka; VitrA/Artema 7 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 6647; medyan ₺2.312; toplam değerlendirme 10124; 26 marka; VitrA/Artema 7 ürün</t>
         </is>
       </c>
       <c r="F1019" s="7" t="inlineStr">
@@ -38226,7 +38226,7 @@
       </c>
       <c r="E1020" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, kategori toplamı 9509; medyan 2.626 TL; toplam değerlendirme 9090; 5 marka; VitrA/Artema 0 ürün</t>
+          <t>6 ürün okundu, kategori toplamı 9509; medyan ₺2.626; toplam değerlendirme 9090; 5 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1020" s="7" t="inlineStr">
@@ -38263,7 +38263,7 @@
       </c>
       <c r="E1021" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 35 eşleşen; toplam 1423; medyan 110 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 35 eşleşen; toplam 1423; medyan ₺110; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1021" s="7" t="inlineStr">
@@ -38300,7 +38300,7 @@
       </c>
       <c r="E1022" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 35 eşleşen; toplam 2012; medyan 50 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 35 eşleşen; toplam 2012; medyan ₺50; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1022" s="7" t="inlineStr">
@@ -38337,7 +38337,7 @@
       </c>
       <c r="E1023" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 14 eşleşen; toplam 2020; medyan 1.320 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 14 eşleşen; toplam 2020; medyan ₺1.320; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1023" s="7" t="inlineStr">
@@ -38374,7 +38374,7 @@
       </c>
       <c r="E1024" s="6" t="inlineStr">
         <is>
-          <t>4 ürün okundu, 4 eşleşen; toplam 4; medyan 5.838 TL; VitrA/Artema 2 ürün</t>
+          <t>4 ürün okundu, 4 eşleşen; toplam 4; medyan ₺5.838; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F1024" s="7" t="inlineStr">
@@ -38411,7 +38411,7 @@
       </c>
       <c r="E1025" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 35 eşleşen; toplam 218; medyan 7.500 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 35 eşleşen; toplam 218; medyan ₺7.500; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1025" s="7" t="inlineStr">
@@ -38448,7 +38448,7 @@
       </c>
       <c r="E1026" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 34945; medyan 248 TL; toplam değerlendirme 202768; 35 marka; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 34945; medyan ₺248; toplam değerlendirme 202768; 35 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1026" s="7" t="inlineStr">
@@ -38485,7 +38485,7 @@
       </c>
       <c r="E1027" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 16533; medyan 199 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 16533; medyan ₺199; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1027" s="7" t="inlineStr">
@@ -38522,7 +38522,7 @@
       </c>
       <c r="E1028" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 31 eşleşen; toplam 13959; medyan 227 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 31 eşleşen; toplam 13959; medyan ₺227; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1028" s="7" t="inlineStr">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="E1029" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 35 eşleşen; toplam 146; medyan 13.905 TL; VitrA/Artema 5 ürün</t>
+          <t>36 ürün okundu, 35 eşleşen; toplam 146; medyan ₺13.905; VitrA/Artema 5 ürün</t>
         </is>
       </c>
       <c r="F1029" s="7" t="inlineStr">
@@ -38596,7 +38596,7 @@
       </c>
       <c r="E1030" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 22 eşleşen; toplam 236; medyan 1.524 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 22 eşleşen; toplam 236; medyan ₺1.524; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1030" s="7" t="inlineStr">
@@ -38633,7 +38633,7 @@
       </c>
       <c r="E1031" s="6" t="inlineStr">
         <is>
-          <t>5 ürün okundu, kategori toplamı 3850; medyan 905 TL; toplam değerlendirme 218; 2 marka; VitrA/Artema 5 ürün</t>
+          <t>5 ürün okundu, kategori toplamı 3850; medyan ₺905; toplam değerlendirme 218; 2 marka; VitrA/Artema 5 ürün</t>
         </is>
       </c>
       <c r="F1031" s="7" t="inlineStr">
@@ -38670,7 +38670,7 @@
       </c>
       <c r="E1032" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 8031; medyan 1.650 TL; toplam değerlendirme 132368; 29 marka; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 8031; medyan ₺1.650; toplam değerlendirme 132368; 29 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1032" s="7" t="inlineStr">
@@ -38707,7 +38707,7 @@
       </c>
       <c r="E1033" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 557; medyan 279 TL; VitrA/Artema 3 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 557; medyan ₺279; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F1033" s="7" t="inlineStr">
@@ -38744,7 +38744,7 @@
       </c>
       <c r="E1034" s="6" t="inlineStr">
         <is>
-          <t>2 ürün okundu, 2 eşleşen; toplam 2; medyan 629 TL; VitrA/Artema 0 ürün</t>
+          <t>2 ürün okundu, 2 eşleşen; toplam 2; medyan ₺629; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1034" s="7" t="inlineStr">
@@ -38818,7 +38818,7 @@
       </c>
       <c r="E1036" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 21 eşleşen; toplam 1103; medyan 305 TL; VitrA/Artema 1 ürün</t>
+          <t>36 ürün okundu, 21 eşleşen; toplam 1103; medyan ₺305; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F1036" s="7" t="inlineStr">
@@ -38855,7 +38855,7 @@
       </c>
       <c r="E1037" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 32 eşleşen; toplam 1233; medyan 1.370 TL; VitrA/Artema 2 ürün</t>
+          <t>36 ürün okundu, 32 eşleşen; toplam 1233; medyan ₺1.370; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F1037" s="7" t="inlineStr">
@@ -38892,7 +38892,7 @@
       </c>
       <c r="E1038" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 501; medyan 6.543 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 501; medyan ₺6.543; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1038" s="7" t="inlineStr">
@@ -38929,7 +38929,7 @@
       </c>
       <c r="E1039" s="6" t="inlineStr">
         <is>
-          <t>6 ürün okundu, 6 eşleşen; toplam 6; medyan 14.760 TL; VitrA/Artema 1 ürün</t>
+          <t>6 ürün okundu, 6 eşleşen; toplam 6; medyan ₺14.760; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F1039" s="7" t="inlineStr">
@@ -38966,7 +38966,7 @@
       </c>
       <c r="E1040" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, kategori toplamı 76; medyan 10.210 TL; toplam değerlendirme 676; 14 marka; VitrA/Artema 3 ürün</t>
+          <t>36 ürün okundu, kategori toplamı 76; medyan ₺10.210; toplam değerlendirme 676; 14 marka; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F1040" s="7" t="inlineStr">
@@ -39003,7 +39003,7 @@
       </c>
       <c r="E1041" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 9 eşleşen; toplam 1378; medyan 1.499 TL; VitrA/Artema 3 ürün</t>
+          <t>36 ürün okundu, 9 eşleşen; toplam 1378; medyan ₺1.499; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F1041" s="7" t="inlineStr">
@@ -39040,7 +39040,7 @@
       </c>
       <c r="E1042" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 43; medyan 2.137 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 43; medyan ₺2.137; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1042" s="7" t="inlineStr">
@@ -39077,7 +39077,7 @@
       </c>
       <c r="E1043" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 5 eşleşen; toplam 996; medyan 4.092 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 5 eşleşen; toplam 996; medyan ₺4.092; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1043" s="7" t="inlineStr">
@@ -39114,7 +39114,7 @@
       </c>
       <c r="E1044" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 2 eşleşen; toplam 994; medyan 5.425 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 2 eşleşen; toplam 994; medyan ₺5.425; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1044" s="7" t="inlineStr">
@@ -39151,7 +39151,7 @@
       </c>
       <c r="E1045" s="6" t="inlineStr">
         <is>
-          <t>ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 3283; medyan 490 TL; toplam değerlendirme 4832; 22 marka; VitrA/Artema 12 ürün</t>
+          <t>ilk 36 ürün: satıcı türü (VitrA mağazası, 3. taraf), liste ve eski fiyat, puan, değerlendirme sayısı, kargo etiketi | 72 ürün okundu, kategori toplamı 3283; medyan ₺490; toplam değerlendirme 4832; 22 marka; VitrA/Artema 12 ürün</t>
         </is>
       </c>
       <c r="F1045" s="7" t="inlineStr">
@@ -39188,7 +39188,7 @@
       </c>
       <c r="E1046" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 8 eşleşen; toplam 14326; medyan 166 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 8 eşleşen; toplam 14326; medyan ₺166; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1046" s="7" t="inlineStr">
@@ -39225,7 +39225,7 @@
       </c>
       <c r="E1047" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 4210; medyan 180 TL; toplam değerlendirme 24535; 45 marka; VitrA/Artema 2 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 4210; medyan ₺180; toplam değerlendirme 24535; 45 marka; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F1047" s="7" t="inlineStr">
@@ -39262,7 +39262,7 @@
       </c>
       <c r="E1048" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 6 eşleşen; toplam 337; medyan 47.531 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 6 eşleşen; toplam 337; medyan ₺47.531; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1048" s="7" t="inlineStr">
@@ -39299,7 +39299,7 @@
       </c>
       <c r="E1049" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 16 eşleşen; toplam 1341; medyan 184 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 16 eşleşen; toplam 1341; medyan ₺184; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1049" s="7" t="inlineStr">
@@ -39336,7 +39336,7 @@
       </c>
       <c r="E1050" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 30 eşleşen; toplam 1045; medyan 1.523 TL; VitrA/Artema 2 ürün</t>
+          <t>36 ürün okundu, 30 eşleşen; toplam 1045; medyan ₺1.523; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F1050" s="7" t="inlineStr">
@@ -39373,7 +39373,7 @@
       </c>
       <c r="E1051" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 1174; medyan 357 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 1174; medyan ₺357; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1051" s="7" t="inlineStr">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="E1052" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 14 eşleşen; toplam 137; medyan 15.698 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 14 eşleşen; toplam 137; medyan ₺15.698; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1052" s="7" t="inlineStr">
@@ -39484,7 +39484,7 @@
       </c>
       <c r="E1054" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 3 eşleşen; toplam 1585; medyan 199 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 3 eşleşen; toplam 1585; medyan ₺199; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1054" s="7" t="inlineStr">
@@ -39521,7 +39521,7 @@
       </c>
       <c r="E1055" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 9980; medyan 1.022 TL; toplam değerlendirme 14846; 27 marka; VitrA/Artema 1 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 9980; medyan ₺1.022; toplam değerlendirme 14846; 27 marka; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F1055" s="7" t="inlineStr">
@@ -39558,7 +39558,7 @@
       </c>
       <c r="E1056" s="6" t="inlineStr">
         <is>
-          <t>3 ürün okundu, kategori toplamı 2109; medyan 1.249 TL; toplam değerlendirme 4540; 2 marka; VitrA/Artema 0 ürün</t>
+          <t>3 ürün okundu, kategori toplamı 2109; medyan ₺1.249; toplam değerlendirme 4540; 2 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1056" s="7" t="inlineStr">
@@ -39595,7 +39595,7 @@
       </c>
       <c r="E1057" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 249; medyan 325 TL; VitrA/Artema 3 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 249; medyan ₺325; VitrA/Artema 3 ürün</t>
         </is>
       </c>
       <c r="F1057" s="7" t="inlineStr">
@@ -39632,7 +39632,7 @@
       </c>
       <c r="E1058" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 2395; medyan 190 TL; toplam değerlendirme 19410; 43 marka; VitrA/Artema 1 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 2395; medyan ₺190; toplam değerlendirme 19410; 43 marka; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F1058" s="7" t="inlineStr">
@@ -39669,7 +39669,7 @@
       </c>
       <c r="E1059" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 3430; medyan 1.009 TL; toplam değerlendirme 32062; 46 marka; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 3430; medyan ₺1.009; toplam değerlendirme 32062; 46 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1059" s="7" t="inlineStr">
@@ -39706,7 +39706,7 @@
       </c>
       <c r="E1060" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 31 eşleşen; toplam 14016; medyan 237 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 31 eşleşen; toplam 14016; medyan ₺237; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1060" s="7" t="inlineStr">
@@ -39743,7 +39743,7 @@
       </c>
       <c r="E1061" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 25 eşleşen; toplam 1298; medyan 350 TL; VitrA/Artema 2 ürün</t>
+          <t>36 ürün okundu, 25 eşleşen; toplam 1298; medyan ₺350; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F1061" s="7" t="inlineStr">
@@ -39780,7 +39780,7 @@
       </c>
       <c r="E1062" s="6" t="inlineStr">
         <is>
-          <t>3 ürün okundu, 3 eşleşen; toplam 3; medyan 2.000 TL; VitrA/Artema 2 ürün</t>
+          <t>3 ürün okundu, 3 eşleşen; toplam 3; medyan ₺2.000; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F1062" s="7" t="inlineStr">
@@ -39854,7 +39854,7 @@
       </c>
       <c r="E1064" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 8546; medyan 608 TL; toplam değerlendirme 53076; 32 marka; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 8546; medyan ₺608; toplam değerlendirme 53076; 32 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1064" s="7" t="inlineStr">
@@ -39891,7 +39891,7 @@
       </c>
       <c r="E1065" s="6" t="inlineStr">
         <is>
-          <t>29 ürün okundu, 29 eşleşen; toplam 29; medyan 5.199 TL; VitrA/Artema 1 ürün</t>
+          <t>29 ürün okundu, 29 eşleşen; toplam 29; medyan ₺5.199; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F1065" s="7" t="inlineStr">
@@ -39928,7 +39928,7 @@
       </c>
       <c r="E1066" s="6" t="inlineStr">
         <is>
-          <t>13 ürün okundu, 13 eşleşen; toplam 13; medyan 12.437 TL; VitrA/Artema 7 ürün</t>
+          <t>13 ürün okundu, 13 eşleşen; toplam 13; medyan ₺12.437; VitrA/Artema 7 ürün</t>
         </is>
       </c>
       <c r="F1066" s="7" t="inlineStr">
@@ -39965,7 +39965,7 @@
       </c>
       <c r="E1067" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 3925; medyan 342 TL; toplam değerlendirme 6063; 25 marka; VitrA/Artema 14 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 3925; medyan ₺342; toplam değerlendirme 6063; 25 marka; VitrA/Artema 14 ürün</t>
         </is>
       </c>
       <c r="F1067" s="7" t="inlineStr">
@@ -40002,7 +40002,7 @@
       </c>
       <c r="E1068" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 69; medyan 3.788 TL; VitrA/Artema 26 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 69; medyan ₺3.788; VitrA/Artema 26 ürün</t>
         </is>
       </c>
       <c r="F1068" s="7" t="inlineStr">
@@ -40039,7 +40039,7 @@
       </c>
       <c r="E1069" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 381; medyan 3.193 TL; VitrA/Artema 19 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 381; medyan ₺3.193; VitrA/Artema 19 ürün</t>
         </is>
       </c>
       <c r="F1069" s="7" t="inlineStr">
@@ -40076,7 +40076,7 @@
       </c>
       <c r="E1070" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 6685; medyan 2.101 TL; toplam değerlendirme 20541; 31 marka; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 6685; medyan ₺2.101; toplam değerlendirme 20541; 31 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1070" s="7" t="inlineStr">
@@ -40113,7 +40113,7 @@
       </c>
       <c r="E1071" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 2594; medyan 350 TL; toplam değerlendirme 10759; 40 marka; VitrA/Artema 5 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 2594; medyan ₺350; toplam değerlendirme 10759; 40 marka; VitrA/Artema 5 ürün</t>
         </is>
       </c>
       <c r="F1071" s="7" t="inlineStr">
@@ -40150,7 +40150,7 @@
       </c>
       <c r="E1072" s="6" t="inlineStr">
         <is>
-          <t>9 ürün okundu, 9 eşleşen; toplam 9; medyan 11.037 TL; VitrA/Artema 9 ürün</t>
+          <t>9 ürün okundu, 9 eşleşen; toplam 9; medyan ₺11.037; VitrA/Artema 9 ürün</t>
         </is>
       </c>
       <c r="F1072" s="7" t="inlineStr">
@@ -40187,7 +40187,7 @@
       </c>
       <c r="E1073" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 417; medyan 15.072 TL; toplam değerlendirme 3487; 21 marka; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 417; medyan ₺15.072; toplam değerlendirme 3487; 21 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1073" s="7" t="inlineStr">
@@ -40224,7 +40224,7 @@
       </c>
       <c r="E1074" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 4 eşleşen; toplam 1106; medyan 9.404 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 4 eşleşen; toplam 1106; medyan ₺9.404; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1074" s="7" t="inlineStr">
@@ -40261,7 +40261,7 @@
       </c>
       <c r="E1075" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 663; medyan 792 TL; toplam değerlendirme 2123; 27 marka; VitrA/Artema 1 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 663; medyan ₺792; toplam değerlendirme 2123; 27 marka; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F1075" s="7" t="inlineStr">
@@ -40298,7 +40298,7 @@
       </c>
       <c r="E1076" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 4271; medyan 197 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 4271; medyan ₺197; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1076" s="7" t="inlineStr">
@@ -40335,7 +40335,7 @@
       </c>
       <c r="E1077" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 8397; medyan 184 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 8397; medyan ₺184; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1077" s="7" t="inlineStr">
@@ -40372,7 +40372,7 @@
       </c>
       <c r="E1078" s="6" t="inlineStr">
         <is>
-          <t>27 ürün okundu, 13 eşleşen; toplam 27; medyan 707 TL; VitrA/Artema 0 ürün</t>
+          <t>27 ürün okundu, 13 eşleşen; toplam 27; medyan ₺707; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1078" s="7" t="inlineStr">
@@ -40409,7 +40409,7 @@
       </c>
       <c r="E1079" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, 36 eşleşen; toplam 255; medyan 3.411 TL; VitrA/Artema 0 ürün</t>
+          <t>36 ürün okundu, 36 eşleşen; toplam 255; medyan ₺3.411; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1079" s="7" t="inlineStr">
@@ -40446,7 +40446,7 @@
       </c>
       <c r="E1080" s="6" t="inlineStr">
         <is>
-          <t>12 ürün okundu, 10 eşleşen; toplam 12; medyan 6.779 TL; VitrA/Artema 0 ürün</t>
+          <t>12 ürün okundu, 10 eşleşen; toplam 12; medyan ₺6.779; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1080" s="7" t="inlineStr">
@@ -40483,7 +40483,7 @@
       </c>
       <c r="E1081" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 681; medyan 2.561 TL; toplam değerlendirme 13688; 38 marka; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 681; medyan ₺2.561; toplam değerlendirme 13688; 38 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1081" s="7" t="inlineStr">
@@ -40520,7 +40520,7 @@
       </c>
       <c r="E1082" s="6" t="inlineStr">
         <is>
-          <t>72 ürün okundu, kategori toplamı 56941; medyan 381 TL; toplam değerlendirme 70023; 37 marka; VitrA/Artema 0 ürün</t>
+          <t>72 ürün okundu, kategori toplamı 56941; medyan ₺381; toplam değerlendirme 70023; 37 marka; VitrA/Artema 0 ürün</t>
         </is>
       </c>
       <c r="F1082" s="7" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="E1083" s="6" t="inlineStr">
         <is>
-          <t>36 ürün okundu, kategori toplamı 1263; medyan 3.340 TL; toplam değerlendirme 1766; 12 marka; VitrA/Artema 1 ürün</t>
+          <t>36 ürün okundu, kategori toplamı 1263; medyan ₺3.340; toplam değerlendirme 1766; 12 marka; VitrA/Artema 1 ürün</t>
         </is>
       </c>
       <c r="F1083" s="7" t="inlineStr">
@@ -40594,7 +40594,7 @@
       </c>
       <c r="E1084" s="6" t="inlineStr">
         <is>
-          <t>4 ürün okundu, kategori toplamı 1019; medyan 5.135 TL; toplam değerlendirme 42; 3 marka; VitrA/Artema 2 ürün</t>
+          <t>4 ürün okundu, kategori toplamı 1019; medyan ₺5.135; toplam değerlendirme 42; 3 marka; VitrA/Artema 2 ürün</t>
         </is>
       </c>
       <c r="F1084" s="7" t="inlineStr">
@@ -40631,7 +40631,7 @@
       </c>
       <c r="E1085" s="6" t="inlineStr">
         <is>
-          <t>2 varyant kartı; liste fiyatı 29.729 - 29.729 TL; stoklu 1, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/2; ücretsiz montaj listesinde 0 ürün</t>
+          <t>2 varyant kartı; liste fiyatı 29.729 - ₺29.729; stoklu 1, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/2; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1085" s="7" t="inlineStr">
@@ -40645,7 +40645,7 @@
         </is>
       </c>
     </row>
-    <row r="1086" ht="43.5" customHeight="1">
+    <row r="1086" ht="30" customHeight="1">
       <c r="A1086" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-ankastre-dus-yonlendiriciler</t>
@@ -40668,7 +40668,7 @@
       </c>
       <c r="E1086" s="6" t="inlineStr">
         <is>
-          <t>36 varyant kartı; liste fiyatı 1.938 - 23.955 TL; stoklu 16, stokta yok 20; ilk sayfada Sepette indirim etiketi 17/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>36 varyant kartı; liste fiyatı 1.938 - ₺23.955; stoklu 16, stokta yok 20; ilk sayfada Sepette indirim etiketi 17/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1086" s="7" t="inlineStr">
@@ -40705,7 +40705,7 @@
       </c>
       <c r="E1087" s="6" t="inlineStr">
         <is>
-          <t>32 varyant kartı; liste fiyatı 759 - 4.183 TL; stoklu 22, stokta yok 10; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>32 varyant kartı; liste fiyatı 759 - ₺4.183; stoklu 22, stokta yok 10; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1087" s="7" t="inlineStr">
@@ -40742,7 +40742,7 @@
       </c>
       <c r="E1088" s="6" t="inlineStr">
         <is>
-          <t>3 varyant kartı; liste fiyatı 26.111 - 44.390 TL; stoklu 1, stokta yok 2; ilk sayfada Sepette indirim etiketi 3/3; ücretsiz montaj listesinde 1 ürün</t>
+          <t>3 varyant kartı; liste fiyatı 26.111 - ₺44.390; stoklu 1, stokta yok 2; ilk sayfada Sepette indirim etiketi 3/3; ücretsiz montaj listesinde 1 ürün</t>
         </is>
       </c>
       <c r="F1088" s="7" t="inlineStr">
@@ -40779,7 +40779,7 @@
       </c>
       <c r="E1089" s="6" t="inlineStr">
         <is>
-          <t>180 varyant kartı; liste fiyatı 9.526 - 67.142 TL; stoklu 21, stokta yok 159; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 15 ürün</t>
+          <t>180 varyant kartı; liste fiyatı 9.526 - ₺67.142; stoklu 21, stokta yok 159; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 15 ürün</t>
         </is>
       </c>
       <c r="F1089" s="7" t="inlineStr">
@@ -40816,7 +40816,7 @@
       </c>
       <c r="E1090" s="6" t="inlineStr">
         <is>
-          <t>37 varyant kartı; liste fiyatı 397 - 6.627 TL; stoklu 15, stokta yok 22; ilk sayfada Sepette indirim etiketi 18/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>37 varyant kartı; liste fiyatı 397 - ₺6.627; stoklu 15, stokta yok 22; ilk sayfada Sepette indirim etiketi 18/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1090" s="7" t="inlineStr">
@@ -40830,7 +40830,7 @@
         </is>
       </c>
     </row>
-    <row r="1091" ht="43.5" customHeight="1">
+    <row r="1091" ht="30" customHeight="1">
       <c r="A1091" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-banyo-batarya-cikis-uclari</t>
@@ -40853,7 +40853,7 @@
       </c>
       <c r="E1091" s="6" t="inlineStr">
         <is>
-          <t>75 varyant kartı; liste fiyatı 4.222 - 12.209 TL; stoklu 43, stokta yok 32; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>75 varyant kartı; liste fiyatı 4.222 - ₺12.209; stoklu 43, stokta yok 32; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1091" s="7" t="inlineStr">
@@ -40890,7 +40890,7 @@
       </c>
       <c r="E1092" s="6" t="inlineStr">
         <is>
-          <t>10 varyant kartı; liste fiyatı 1.634 - 20.199 TL; stoklu 4, stokta yok 6; ilk sayfada Sepette indirim etiketi 10/10; ücretsiz montaj listesinde 0 ürün</t>
+          <t>10 varyant kartı; liste fiyatı 1.634 - ₺20.199; stoklu 4, stokta yok 6; ilk sayfada Sepette indirim etiketi 10/10; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1092" s="7" t="inlineStr">
@@ -40927,7 +40927,7 @@
       </c>
       <c r="E1093" s="6" t="inlineStr">
         <is>
-          <t>5 varyant kartı; liste fiyatı 455 - 1.139 TL; stoklu 3, stokta yok 2; ilk sayfada Sepette indirim etiketi 5/5; ücretsiz montaj listesinde 1 ürün</t>
+          <t>5 varyant kartı; liste fiyatı 455 - ₺1.139; stoklu 3, stokta yok 2; ilk sayfada Sepette indirim etiketi 5/5; ücretsiz montaj listesinde 1 ürün</t>
         </is>
       </c>
       <c r="F1093" s="7" t="inlineStr">
@@ -40964,7 +40964,7 @@
       </c>
       <c r="E1094" s="6" t="inlineStr">
         <is>
-          <t>4 varyant kartı; liste fiyatı 1.454 - 1.838 TL; stoklu 0, stokta yok 4; ilk sayfada Sepette indirim etiketi 4/4; ücretsiz montaj listesinde 1 ürün</t>
+          <t>4 varyant kartı; liste fiyatı 1.454 - ₺1.838; stoklu 0, stokta yok 4; ilk sayfada Sepette indirim etiketi 4/4; ücretsiz montaj listesinde 1 ürün</t>
         </is>
       </c>
       <c r="F1094" s="7" t="inlineStr">
@@ -41001,7 +41001,7 @@
       </c>
       <c r="E1095" s="6" t="inlineStr">
         <is>
-          <t>1 varyant kartı; liste fiyatı 9.214 - 9.214 TL; stoklu 0, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/1; ücretsiz montaj listesinde 0 ürün</t>
+          <t>1 varyant kartı; liste fiyatı 9.214 - ₺9.214; stoklu 0, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/1; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1095" s="7" t="inlineStr">
@@ -41038,7 +41038,7 @@
       </c>
       <c r="E1096" s="6" t="inlineStr">
         <is>
-          <t>5 varyant kartı; liste fiyatı 801 - 3.747 TL; stoklu 2, stokta yok 3; ilk sayfada Sepette indirim etiketi 5/5; ücretsiz montaj listesinde 0 ürün</t>
+          <t>5 varyant kartı; liste fiyatı 801 - ₺3.747; stoklu 2, stokta yok 3; ilk sayfada Sepette indirim etiketi 5/5; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1096" s="7" t="inlineStr">
@@ -41075,7 +41075,7 @@
       </c>
       <c r="E1097" s="6" t="inlineStr">
         <is>
-          <t>18 varyant kartı; liste fiyatı 8.745 - 17.779 TL; stoklu 3, stokta yok 15; ilk sayfada Sepette indirim etiketi 18/18; ücretsiz montaj listesinde 0 ürün</t>
+          <t>18 varyant kartı; liste fiyatı 8.745 - ₺17.779; stoklu 3, stokta yok 15; ilk sayfada Sepette indirim etiketi 18/18; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1097" s="7" t="inlineStr">
@@ -41089,7 +41089,7 @@
         </is>
       </c>
     </row>
-    <row r="1098" ht="43.5" customHeight="1">
+    <row r="1098" ht="30" customHeight="1">
       <c r="A1098" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-banyo-tezgahlari</t>
@@ -41112,7 +41112,7 @@
       </c>
       <c r="E1098" s="6" t="inlineStr">
         <is>
-          <t>102 varyant kartı; liste fiyatı 1.006 - 127.618 TL; stoklu 6, stokta yok 96; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 1 ürün</t>
+          <t>102 varyant kartı; liste fiyatı 1.006 - ₺127.618; stoklu 6, stokta yok 96; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 1 ürün</t>
         </is>
       </c>
       <c r="F1098" s="7" t="inlineStr">
@@ -41126,7 +41126,7 @@
         </is>
       </c>
     </row>
-    <row r="1099" ht="43.5" customHeight="1">
+    <row r="1099" ht="30" customHeight="1">
       <c r="A1099" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-bataryali-dus-sistemleri</t>
@@ -41149,7 +41149,7 @@
       </c>
       <c r="E1099" s="6" t="inlineStr">
         <is>
-          <t>56 varyant kartı; liste fiyatı 9.217 - 113.050 TL; stoklu 15, stokta yok 41; ilk sayfada Sepette indirim etiketi 12/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>56 varyant kartı; liste fiyatı 9.217 - ₺113.050; stoklu 15, stokta yok 41; ilk sayfada Sepette indirim etiketi 12/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1099" s="7" t="inlineStr">
@@ -41186,7 +41186,7 @@
       </c>
       <c r="E1100" s="6" t="inlineStr">
         <is>
-          <t>33 varyant kartı; liste fiyatı 6.355 - 40.779 TL; stoklu 0, stokta yok 33; ilk sayfada Sepette indirim etiketi 8/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>33 varyant kartı; liste fiyatı 6.355 - ₺40.779; stoklu 0, stokta yok 33; ilk sayfada Sepette indirim etiketi 8/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1100" s="7" t="inlineStr">
@@ -41200,7 +41200,7 @@
         </is>
       </c>
     </row>
-    <row r="1101" ht="43.5" customHeight="1">
+    <row r="1101" ht="30" customHeight="1">
       <c r="A1101" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-canak-lavabo-bataryalari</t>
@@ -41223,7 +41223,7 @@
       </c>
       <c r="E1101" s="6" t="inlineStr">
         <is>
-          <t>68 varyant kartı; liste fiyatı 9.610 - 36.489 TL; stoklu 37, stokta yok 31; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>68 varyant kartı; liste fiyatı 9.610 - ₺36.489; stoklu 37, stokta yok 31; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1101" s="7" t="inlineStr">
@@ -41260,7 +41260,7 @@
       </c>
       <c r="E1102" s="6" t="inlineStr">
         <is>
-          <t>163 varyant kartı; liste fiyatı 5.680 - 26.707 TL; stoklu 72, stokta yok 91; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>163 varyant kartı; liste fiyatı 5.680 - ₺26.707; stoklu 72, stokta yok 91; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1102" s="7" t="inlineStr">
@@ -41297,7 +41297,7 @@
       </c>
       <c r="E1103" s="6" t="inlineStr">
         <is>
-          <t>18 varyant kartı; liste fiyatı 611 - 6.993 TL; stoklu 8, stokta yok 10; ilk sayfada Sepette indirim etiketi 11/18; ücretsiz montaj listesinde 0 ürün</t>
+          <t>18 varyant kartı; liste fiyatı 611 - ₺6.993; stoklu 8, stokta yok 10; ilk sayfada Sepette indirim etiketi 11/18; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1103" s="7" t="inlineStr">
@@ -41334,7 +41334,7 @@
       </c>
       <c r="E1104" s="6" t="inlineStr">
         <is>
-          <t>31 varyant kartı; liste fiyatı 1.079 - 2.359 TL; stoklu 18, stokta yok 13; ilk sayfada Sepette indirim etiketi 18/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>31 varyant kartı; liste fiyatı 1.079 - ₺2.359; stoklu 18, stokta yok 13; ilk sayfada Sepette indirim etiketi 18/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1104" s="7" t="inlineStr">
@@ -41348,7 +41348,7 @@
         </is>
       </c>
     </row>
-    <row r="1105" ht="43.5" customHeight="1">
+    <row r="1105" ht="30" customHeight="1">
       <c r="A1105" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-dus-kanallari</t>
@@ -41371,7 +41371,7 @@
       </c>
       <c r="E1105" s="6" t="inlineStr">
         <is>
-          <t>172 varyant kartı; liste fiyatı 659 - 15.070 TL; stoklu 15, stokta yok 157; ilk sayfada Sepette indirim etiketi 19/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>172 varyant kartı; liste fiyatı 659 - ₺15.070; stoklu 15, stokta yok 157; ilk sayfada Sepette indirim etiketi 19/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1105" s="7" t="inlineStr">
@@ -41385,7 +41385,7 @@
         </is>
       </c>
     </row>
-    <row r="1106" ht="43.5" customHeight="1">
+    <row r="1106" ht="30" customHeight="1">
       <c r="A1106" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-dus-kolonlari</t>
@@ -41408,7 +41408,7 @@
       </c>
       <c r="E1106" s="6" t="inlineStr">
         <is>
-          <t>23 varyant kartı; liste fiyatı 10.310 - 52.660 TL; stoklu 21, stokta yok 2; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>23 varyant kartı; liste fiyatı 10.310 - ₺52.660; stoklu 21, stokta yok 2; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1106" s="7" t="inlineStr">
@@ -41445,7 +41445,7 @@
       </c>
       <c r="E1107" s="6" t="inlineStr">
         <is>
-          <t>1 varyant kartı; liste fiyatı 1.960 - 1.960 TL; stoklu 0, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/1; ücretsiz montaj listesinde 0 ürün</t>
+          <t>1 varyant kartı; liste fiyatı 1.960 - ₺1.960; stoklu 0, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/1; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1107" s="7" t="inlineStr">
@@ -41482,7 +41482,7 @@
       </c>
       <c r="E1108" s="6" t="inlineStr">
         <is>
-          <t>119 varyant kartı; liste fiyatı 47.680 - 160.889 TL; stoklu 0, stokta yok 119; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>119 varyant kartı; liste fiyatı 47.680 - ₺160.889; stoklu 0, stokta yok 119; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1108" s="7" t="inlineStr">
@@ -41519,7 +41519,7 @@
       </c>
       <c r="E1109" s="6" t="inlineStr">
         <is>
-          <t>8 varyant kartı; liste fiyatı 33.563 - 40.552 TL; stoklu 0, stokta yok 8; ilk sayfada Sepette indirim etiketi 4/8; ücretsiz montaj listesinde 0 ürün</t>
+          <t>8 varyant kartı; liste fiyatı 33.563 - ₺40.552; stoklu 0, stokta yok 8; ilk sayfada Sepette indirim etiketi 4/8; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1109" s="7" t="inlineStr">
@@ -41533,7 +41533,7 @@
         </is>
       </c>
     </row>
-    <row r="1110" ht="43.5" customHeight="1">
+    <row r="1110" ht="30" customHeight="1">
       <c r="A1110" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-duvardan-banyo-bataryalari</t>
@@ -41556,7 +41556,7 @@
       </c>
       <c r="E1110" s="6" t="inlineStr">
         <is>
-          <t>100 varyant kartı; liste fiyatı 7.736 - 38.545 TL; stoklu 25, stokta yok 75; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>100 varyant kartı; liste fiyatı 7.736 - ₺38.545; stoklu 25, stokta yok 75; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1110" s="7" t="inlineStr">
@@ -41593,7 +41593,7 @@
       </c>
       <c r="E1111" s="6" t="inlineStr">
         <is>
-          <t>64 varyant kartı; liste fiyatı 1.924 - 21.039 TL; stoklu 57, stokta yok 7; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>64 varyant kartı; liste fiyatı 1.924 - ₺21.039; stoklu 57, stokta yok 7; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1111" s="7" t="inlineStr">
@@ -41630,7 +41630,7 @@
       </c>
       <c r="E1112" s="6" t="inlineStr">
         <is>
-          <t>47 varyant kartı; liste fiyatı 4.801 - 26.872 TL; stoklu 9, stokta yok 38; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>47 varyant kartı; liste fiyatı 4.801 - ₺26.872; stoklu 9, stokta yok 38; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1112" s="7" t="inlineStr">
@@ -41667,7 +41667,7 @@
       </c>
       <c r="E1113" s="6" t="inlineStr">
         <is>
-          <t>43 varyant kartı; liste fiyatı 611 - 18.617 TL; stoklu 26, stokta yok 17; ilk sayfada Sepette indirim etiketi 19/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>43 varyant kartı; liste fiyatı 611 - ₺18.617; stoklu 26, stokta yok 17; ilk sayfada Sepette indirim etiketi 19/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1113" s="7" t="inlineStr">
@@ -41704,7 +41704,7 @@
       </c>
       <c r="E1114" s="6" t="inlineStr">
         <is>
-          <t>23 varyant kartı; liste fiyatı 122.097 - 404.490 TL; stoklu 0, stokta yok 23; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>23 varyant kartı; liste fiyatı 122.097 - ₺404.490; stoklu 0, stokta yok 23; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1114" s="7" t="inlineStr">
@@ -41718,7 +41718,7 @@
         </is>
       </c>
     </row>
-    <row r="1115" ht="43.5" customHeight="1">
+    <row r="1115" ht="30" customHeight="1">
       <c r="A1115" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-hidromasajli-standart-kuvetler</t>
@@ -41741,7 +41741,7 @@
       </c>
       <c r="E1115" s="6" t="inlineStr">
         <is>
-          <t>61 varyant kartı; liste fiyatı 64.636 - 244.857 TL; stoklu 1, stokta yok 60; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>61 varyant kartı; liste fiyatı 64.636 - ₺244.857; stoklu 1, stokta yok 60; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1115" s="7" t="inlineStr">
@@ -41755,7 +41755,7 @@
         </is>
       </c>
     </row>
-    <row r="1116" ht="43.5" customHeight="1">
+    <row r="1116" ht="30" customHeight="1">
       <c r="A1116" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-hidromasajsiz-bagimsiz-kuvetler</t>
@@ -41778,7 +41778,7 @@
       </c>
       <c r="E1116" s="6" t="inlineStr">
         <is>
-          <t>44 varyant kartı; liste fiyatı 72.646 - 112.913 TL; stoklu 0, stokta yok 44; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>44 varyant kartı; liste fiyatı 72.646 - ₺112.913; stoklu 0, stokta yok 44; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1116" s="7" t="inlineStr">
@@ -41829,7 +41829,7 @@
         </is>
       </c>
     </row>
-    <row r="1118" ht="43.5" customHeight="1">
+    <row r="1118" ht="30" customHeight="1">
       <c r="A1118" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-kuvet-bataryalari</t>
@@ -41852,7 +41852,7 @@
       </c>
       <c r="E1118" s="6" t="inlineStr">
         <is>
-          <t>61 varyant kartı; liste fiyatı 29.882 - 84.199 TL; stoklu 7, stokta yok 54; ilk sayfada Sepette indirim etiketi 12/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>61 varyant kartı; liste fiyatı 29.882 - ₺84.199; stoklu 7, stokta yok 54; ilk sayfada Sepette indirim etiketi 12/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1118" s="7" t="inlineStr">
@@ -41889,7 +41889,7 @@
       </c>
       <c r="E1119" s="6" t="inlineStr">
         <is>
-          <t>9 varyant kartı; liste fiyatı 3.859 - 22.686 TL; stoklu 1, stokta yok 8; ilk sayfada Sepette indirim etiketi 9/9; ücretsiz montaj listesinde 0 ürün</t>
+          <t>9 varyant kartı; liste fiyatı 3.859 - ₺22.686; stoklu 1, stokta yok 8; ilk sayfada Sepette indirim etiketi 9/9; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1119" s="7" t="inlineStr">
@@ -41903,7 +41903,7 @@
         </is>
       </c>
     </row>
-    <row r="1120" ht="43.5" customHeight="1">
+    <row r="1120" ht="30" customHeight="1">
       <c r="A1120" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-lavabo-sifon-ve-suzgecleri</t>
@@ -41926,7 +41926,7 @@
       </c>
       <c r="E1120" s="6" t="inlineStr">
         <is>
-          <t>54 varyant kartı; liste fiyatı 1.203 - 60.892 TL; stoklu 32, stokta yok 22; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>54 varyant kartı; liste fiyatı 1.203 - ₺60.892; stoklu 32, stokta yok 22; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1120" s="7" t="inlineStr">
@@ -41963,7 +41963,7 @@
       </c>
       <c r="E1121" s="6" t="inlineStr">
         <is>
-          <t>15 varyant kartı; liste fiyatı 1.371 - 16.123 TL; stoklu 7, stokta yok 8; ilk sayfada Sepette indirim etiketi 15/15; ücretsiz montaj listesinde 0 ürün</t>
+          <t>15 varyant kartı; liste fiyatı 1.371 - ₺16.123; stoklu 7, stokta yok 8; ilk sayfada Sepette indirim etiketi 15/15; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1121" s="7" t="inlineStr">
@@ -42000,7 +42000,7 @@
       </c>
       <c r="E1122" s="6" t="inlineStr">
         <is>
-          <t>2 varyant kartı; liste fiyatı 18.642 - 18.642 TL; stoklu 0, stokta yok 2; ilk sayfada Sepette indirim etiketi 0/2; ücretsiz montaj listesinde 0 ürün</t>
+          <t>2 varyant kartı; liste fiyatı 18.642 - ₺18.642; stoklu 0, stokta yok 2; ilk sayfada Sepette indirim etiketi 0/2; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1122" s="7" t="inlineStr">
@@ -42014,7 +42014,7 @@
         </is>
       </c>
     </row>
-    <row r="1123" ht="43.5" customHeight="1">
+    <row r="1123" ht="30" customHeight="1">
       <c r="A1123" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-mekanik-kumanda-panelleri</t>
@@ -42037,7 +42037,7 @@
       </c>
       <c r="E1123" s="6" t="inlineStr">
         <is>
-          <t>35 varyant kartı; liste fiyatı 1.158 - 15.048 TL; stoklu 21, stokta yok 14; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>35 varyant kartı; liste fiyatı 1.158 - ₺15.048; stoklu 21, stokta yok 14; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1123" s="7" t="inlineStr">
@@ -42074,7 +42074,7 @@
       </c>
       <c r="E1124" s="6" t="inlineStr">
         <is>
-          <t>8 varyant kartı; liste fiyatı 92.019 - 134.580 TL; stoklu 3, stokta yok 5; ilk sayfada Sepette indirim etiketi 3/8; ücretsiz montaj listesinde 0 ürün</t>
+          <t>8 varyant kartı; liste fiyatı 92.019 - ₺134.580; stoklu 3, stokta yok 5; ilk sayfada Sepette indirim etiketi 3/8; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1124" s="7" t="inlineStr">
@@ -42148,7 +42148,7 @@
       </c>
       <c r="E1126" s="6" t="inlineStr">
         <is>
-          <t>1 varyant kartı; liste fiyatı 4.059 - 4.059 TL; stoklu 0, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/1; ücretsiz montaj listesinde 0 ürün</t>
+          <t>1 varyant kartı; liste fiyatı 4.059 - ₺4.059; stoklu 0, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/1; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1126" s="7" t="inlineStr">
@@ -42185,7 +42185,7 @@
       </c>
       <c r="E1127" s="6" t="inlineStr">
         <is>
-          <t>12 varyant kartı; liste fiyatı 7.412 - 12.468 TL; stoklu 0, stokta yok 12; ilk sayfada Sepette indirim etiketi 12/12; ücretsiz montaj listesinde 0 ürün</t>
+          <t>12 varyant kartı; liste fiyatı 7.412 - ₺12.468; stoklu 0, stokta yok 12; ilk sayfada Sepette indirim etiketi 12/12; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1127" s="7" t="inlineStr">
@@ -42222,7 +42222,7 @@
       </c>
       <c r="E1128" s="6" t="inlineStr">
         <is>
-          <t>70 varyant kartı; liste fiyatı 611 - 25.014 TL; stoklu 21, stokta yok 49; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 8 ürün</t>
+          <t>70 varyant kartı; liste fiyatı 611 - ₺25.014; stoklu 21, stokta yok 49; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 8 ürün</t>
         </is>
       </c>
       <c r="F1128" s="7" t="inlineStr">
@@ -42236,7 +42236,7 @@
         </is>
       </c>
     </row>
-    <row r="1129" ht="43.5" customHeight="1">
+    <row r="1129" ht="30" customHeight="1">
       <c r="A1129" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-standart-lavabo-ve-ayaklari</t>
@@ -42259,7 +42259,7 @@
       </c>
       <c r="E1129" s="6" t="inlineStr">
         <is>
-          <t>101 varyant kartı; liste fiyatı 2.966 - 16.330 TL; stoklu 13, stokta yok 88; ilk sayfada Sepette indirim etiketi 19/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>101 varyant kartı; liste fiyatı 2.966 - ₺16.330; stoklu 13, stokta yok 88; ilk sayfada Sepette indirim etiketi 19/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1129" s="7" t="inlineStr">
@@ -42296,7 +42296,7 @@
       </c>
       <c r="E1130" s="6" t="inlineStr">
         <is>
-          <t>30 varyant kartı; liste fiyatı 3.504 - 15.726 TL; stoklu 26, stokta yok 4; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>30 varyant kartı; liste fiyatı 3.504 - ₺15.726; stoklu 26, stokta yok 4; ilk sayfada Sepette indirim etiketi 20/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1130" s="7" t="inlineStr">
@@ -42333,7 +42333,7 @@
       </c>
       <c r="E1131" s="6" t="inlineStr">
         <is>
-          <t>3 varyant kartı; liste fiyatı 9.662 - 10.637 TL; stoklu 0, stokta yok 3; ilk sayfada Sepette indirim etiketi 3/3; ücretsiz montaj listesinde 0 ürün</t>
+          <t>3 varyant kartı; liste fiyatı 9.662 - ₺10.637; stoklu 0, stokta yok 3; ilk sayfada Sepette indirim etiketi 3/3; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1131" s="7" t="inlineStr">
@@ -42370,7 +42370,7 @@
       </c>
       <c r="E1132" s="6" t="inlineStr">
         <is>
-          <t>6 varyant kartı; liste fiyatı 12.515 - 15.312 TL; stoklu 2, stokta yok 4; ilk sayfada Sepette indirim etiketi 6/6; ücretsiz montaj listesinde 0 ürün</t>
+          <t>6 varyant kartı; liste fiyatı 12.515 - ₺15.312; stoklu 2, stokta yok 4; ilk sayfada Sepette indirim etiketi 6/6; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1132" s="7" t="inlineStr">
@@ -42407,7 +42407,7 @@
       </c>
       <c r="E1133" s="6" t="inlineStr">
         <is>
-          <t>63 varyant kartı; liste fiyatı 11.902 - 49.996 TL; stoklu 16, stokta yok 47; ilk sayfada Sepette indirim etiketi 16/20; ücretsiz montaj listesinde 12 ürün</t>
+          <t>63 varyant kartı; liste fiyatı 11.902 - ₺49.996; stoklu 16, stokta yok 47; ilk sayfada Sepette indirim etiketi 16/20; ücretsiz montaj listesinde 12 ürün</t>
         </is>
       </c>
       <c r="F1133" s="7" t="inlineStr">
@@ -42444,7 +42444,7 @@
       </c>
       <c r="E1134" s="6" t="inlineStr">
         <is>
-          <t>110 varyant kartı; liste fiyatı 10.775 - 68.515 TL; stoklu 24, stokta yok 86; ilk sayfada Sepette indirim etiketi 18/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>110 varyant kartı; liste fiyatı 10.775 - ₺68.515; stoklu 24, stokta yok 86; ilk sayfada Sepette indirim etiketi 18/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1134" s="7" t="inlineStr">
@@ -42458,7 +42458,7 @@
         </is>
       </c>
     </row>
-    <row r="1135" ht="43.5" customHeight="1">
+    <row r="1135" ht="30" customHeight="1">
       <c r="A1135" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/c-tuvalet-fircalari</t>
@@ -42481,7 +42481,7 @@
       </c>
       <c r="E1135" s="6" t="inlineStr">
         <is>
-          <t>27 varyant kartı; liste fiyatı 1.402 - 15.070 TL; stoklu 12, stokta yok 15; ilk sayfada Sepette indirim etiketi 13/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>27 varyant kartı; liste fiyatı 1.402 - ₺15.070; stoklu 12, stokta yok 15; ilk sayfada Sepette indirim etiketi 13/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1135" s="7" t="inlineStr">
@@ -42518,7 +42518,7 @@
       </c>
       <c r="E1136" s="6" t="inlineStr">
         <is>
-          <t>47 varyant kartı; liste fiyatı 854 - 5.085 TL; stoklu 21, stokta yok 26; ilk sayfada Sepette indirim etiketi 18/20; ücretsiz montaj listesinde 0 ürün</t>
+          <t>47 varyant kartı; liste fiyatı 854 - ₺5.085; stoklu 21, stokta yok 26; ilk sayfada Sepette indirim etiketi 18/20; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1136" s="7" t="inlineStr">
@@ -42555,7 +42555,7 @@
       </c>
       <c r="E1137" s="6" t="inlineStr">
         <is>
-          <t>2 varyant kartı; liste fiyatı 5.420 - 5.420 TL; stoklu 1, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/2; ücretsiz montaj listesinde 0 ürün</t>
+          <t>2 varyant kartı; liste fiyatı 5.420 - ₺5.420; stoklu 1, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/2; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1137" s="7" t="inlineStr">
@@ -42592,7 +42592,7 @@
       </c>
       <c r="E1138" s="6" t="inlineStr">
         <is>
-          <t>2 varyant kartı; liste fiyatı 4.566 - 4.566 TL; stoklu 1, stokta yok 1; ilk sayfada Sepette indirim etiketi 2/2; ücretsiz montaj listesinde 0 ürün</t>
+          <t>2 varyant kartı; liste fiyatı 4.566 - ₺4.566; stoklu 1, stokta yok 1; ilk sayfada Sepette indirim etiketi 2/2; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1138" s="7" t="inlineStr">
@@ -42666,7 +42666,7 @@
       </c>
       <c r="E1140" s="6" t="inlineStr">
         <is>
-          <t>1 varyant kartı; liste fiyatı 758 - 758 TL; stoklu 0, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/1; ücretsiz montaj listesinde 0 ürün</t>
+          <t>1 varyant kartı; liste fiyatı 758 - ₺758; stoklu 0, stokta yok 1; ilk sayfada Sepette indirim etiketi 1/1; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1140" s="7" t="inlineStr">
@@ -42703,7 +42703,7 @@
       </c>
       <c r="E1141" s="6" t="inlineStr">
         <is>
-          <t>2 varyant kartı; liste fiyatı 6.100 - 7.014 TL; stoklu 0, stokta yok 2; ilk sayfada Sepette indirim etiketi 2/2; ücretsiz montaj listesinde 0 ürün</t>
+          <t>2 varyant kartı; liste fiyatı 6.100 - ₺7.014; stoklu 0, stokta yok 2; ilk sayfada Sepette indirim etiketi 2/2; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1141" s="7" t="inlineStr">
@@ -42740,7 +42740,7 @@
       </c>
       <c r="E1142" s="6" t="inlineStr">
         <is>
-          <t>13 varyant kartı; liste fiyatı 8.393 - 51.510 TL; stoklu 3, stokta yok 10; ilk sayfada Sepette indirim etiketi 8/13; ücretsiz montaj listesinde 0 ürün</t>
+          <t>13 varyant kartı; liste fiyatı 8.393 - ₺51.510; stoklu 3, stokta yok 10; ilk sayfada Sepette indirim etiketi 8/13; ücretsiz montaj listesinde 0 ürün</t>
         </is>
       </c>
       <c r="F1142" s="7" t="inlineStr">
@@ -43147,7 +43147,7 @@
       </c>
       <c r="E1153" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 9.000 TL; satıcı: Newbanyo</t>
+          <t>Koçtaş liste fiyatı ₺9.000; satıcı: Newbanyo</t>
         </is>
       </c>
       <c r="F1153" s="7" t="inlineStr">
@@ -43184,7 +43184,7 @@
       </c>
       <c r="E1154" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 4742,7 TL, sepette 4.500 TL; satıcı: Banyoline; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı ₺4742,7, sepette ₺4.500; satıcı: Banyoline; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1154" s="7" t="inlineStr">
@@ -43221,7 +43221,7 @@
       </c>
       <c r="E1155" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 14744,9 TL; satıcı: Banyoatelier; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı ₺14744,9; satıcı: Banyoatelier; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1155" s="7" t="inlineStr">
@@ -43258,7 +43258,7 @@
       </c>
       <c r="E1156" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 1.799 TL; satıcı: Bataryamarket; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı ₺1.799; satıcı: Bataryamarket; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1156" s="7" t="inlineStr">
@@ -43295,7 +43295,7 @@
       </c>
       <c r="E1157" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 18.095 TL; satıcı: Hace Yapı</t>
+          <t>Koçtaş liste fiyatı ₺18.095; satıcı: Hace Yapı</t>
         </is>
       </c>
       <c r="F1157" s="7" t="inlineStr">
@@ -43332,7 +43332,7 @@
       </c>
       <c r="E1158" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 3.998 TL, sepette 3.998 TL; satıcı: Serhat Yapı</t>
+          <t>Koçtaş liste fiyatı ₺3.998, sepette ₺3.998; satıcı: Serhat Yapı</t>
         </is>
       </c>
       <c r="F1158" s="7" t="inlineStr">
@@ -43369,7 +43369,7 @@
       </c>
       <c r="E1159" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 11852,6 TL, sepette 10667,3 TL; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı ₺11852,6, sepette ₺10667,3; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1159" s="7" t="inlineStr">
@@ -43406,7 +43406,7 @@
       </c>
       <c r="E1160" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 961,5 TL, sepette 961,5 TL; satıcı: Evdeniste</t>
+          <t>Koçtaş liste fiyatı ₺961,5, sepette ₺961,5; satıcı: Evdeniste</t>
         </is>
       </c>
       <c r="F1160" s="7" t="inlineStr">
@@ -43443,7 +43443,7 @@
       </c>
       <c r="E1161" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 6778,6 TL; satıcı: Evdeniste</t>
+          <t>Koçtaş liste fiyatı ₺6778,6; satıcı: Evdeniste</t>
         </is>
       </c>
       <c r="F1161" s="7" t="inlineStr">
@@ -43480,7 +43480,7 @@
       </c>
       <c r="E1162" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 20562,9 TL; satıcı: Banyoatelier</t>
+          <t>Koçtaş liste fiyatı ₺20562,9; satıcı: Banyoatelier</t>
         </is>
       </c>
       <c r="F1162" s="7" t="inlineStr">
@@ -43517,7 +43517,7 @@
       </c>
       <c r="E1163" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 5690,5 TL, sepette 5121,5 TL; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı ₺5690,5, sepette ₺5121,5; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1163" s="7" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="E1164" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 7655,4 TL, sepette 6889,9 TL; satıcı: Evdema</t>
+          <t>Koçtaş liste fiyatı ₺7655,4, sepette ₺6889,9; satıcı: Evdema</t>
         </is>
       </c>
       <c r="F1164" s="7" t="inlineStr">
@@ -43591,7 +43591,7 @@
       </c>
       <c r="E1165" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 5813,2 TL, sepette 5231,8 TL; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
+          <t>Koçtaş liste fiyatı ₺5813,2, sepette ₺5231,8; satıcı: Evdema; ürün sayfasında montaj hizmeti satın alınabiliyor</t>
         </is>
       </c>
       <c r="F1165" s="7" t="inlineStr">
@@ -43628,7 +43628,7 @@
       </c>
       <c r="E1166" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 32941,3 TL, sepette 28000,1 TL; satıcı: Banyoline</t>
+          <t>Koçtaş liste fiyatı ₺32941,3, sepette ₺28000,1; satıcı: Banyoline</t>
         </is>
       </c>
       <c r="F1166" s="7" t="inlineStr">
@@ -43665,7 +43665,7 @@
       </c>
       <c r="E1167" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 1764,5 TL; satıcı: Evdeniste</t>
+          <t>Koçtaş liste fiyatı ₺1764,5; satıcı: Evdeniste</t>
         </is>
       </c>
       <c r="F1167" s="7" t="inlineStr">
@@ -43702,7 +43702,7 @@
       </c>
       <c r="E1168" s="6" t="inlineStr">
         <is>
-          <t>Koçtaş liste fiyatı 5.605 TL, sepette 5044,5 TL; satıcı: Banyome</t>
+          <t>Koçtaş liste fiyatı ₺5.605, sepette ₺5044,5; satıcı: Banyome</t>
         </is>
       </c>
       <c r="F1168" s="7" t="inlineStr">
@@ -43850,7 +43850,7 @@
       </c>
       <c r="E1172" s="6" t="inlineStr">
         <is>
-          <t>kod 768-1851-01; liste fiyatı 5.730 TL; sepette 5.157 TL; stokta; en düşük liste fiyatı 4923,9 TL (TY 3P (YAPIEVİ)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 768-1851-01; liste fiyatı ₺5.730; sepette ₺5.157; stokta; en düşük liste fiyatı ₺4923,9 (TY 3P (YAPIEVİ)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1172" s="7" t="inlineStr">
@@ -43887,7 +43887,7 @@
       </c>
       <c r="E1173" s="6" t="inlineStr">
         <is>
-          <t>kod 7041B003-0090; liste fiyatı 12.027 TL; sepette 10824,3 TL; stokta; en düşük liste fiyatı 11852,6 TL (TY 3P (Evdema)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 7041B003-0090; liste fiyatı ₺12.027; sepette ₺10824,3; stokta; en düşük liste fiyatı ₺11852,6 (TY 3P (Evdema)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1173" s="7" t="inlineStr">
@@ -43924,7 +43924,7 @@
       </c>
       <c r="E1174" s="6" t="inlineStr">
         <is>
-          <t>kod 5505L003-0868; liste fiyatı 6.455 TL; sepette 5809,5 TL; stokta yok; en düşük liste fiyatı 6.455 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 5505L003-0868; liste fiyatı ₺6.455; sepette ₺5809,5; stokta yok; en düşük liste fiyatı ₺6.455 (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1174" s="7" t="inlineStr">
@@ -43961,7 +43961,7 @@
       </c>
       <c r="E1175" s="6" t="inlineStr">
         <is>
-          <t>kod 5618L003-0850; liste fiyatı 8.663 TL; sepette 7363,6 TL; stokta yok; en düşük liste fiyatı 8.663 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 5618L003-0850; liste fiyatı ₺8.663; sepette ₺7363,6; stokta yok; en düşük liste fiyatı ₺8.663 (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1175" s="7" t="inlineStr">
@@ -43998,7 +43998,7 @@
       </c>
       <c r="E1176" s="6" t="inlineStr">
         <is>
-          <t>kod 7748B003-0559; liste fiyatı 14.767 TL; sepette 12552,0 TL; stokta; en düşük liste fiyatı 14.767 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 7748B003-0559; liste fiyatı ₺14.767; sepette ₺12552,0; stokta; en düşük liste fiyatı ₺14.767 (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1176" s="7" t="inlineStr">
@@ -44035,7 +44035,7 @@
       </c>
       <c r="E1177" s="6" t="inlineStr">
         <is>
-          <t>kod 66166; liste fiyatı 9.992 TL; sepette 8493,2 TL; stokta; en düşük liste fiyatı 9.992 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 66166; liste fiyatı ₺9.992; sepette ₺8493,2; stokta; en düşük liste fiyatı ₺9.992 (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1177" s="7" t="inlineStr">
@@ -44072,7 +44072,7 @@
       </c>
       <c r="E1178" s="6" t="inlineStr">
         <is>
-          <t>kod 60848; liste fiyatı 27.377 TL; sepette 23270,5 TL; stokta; en düşük liste fiyatı 27.377 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 60848; liste fiyatı ₺27.377; sepette ₺23270,5; stokta; en düşük liste fiyatı ₺27.377 (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1178" s="7" t="inlineStr">
@@ -44109,7 +44109,7 @@
       </c>
       <c r="E1179" s="6" t="inlineStr">
         <is>
-          <t>kod 67093; liste fiyatı 13.881 TL; sepette 12492,9 TL; stokta yok; en düşük liste fiyatı 12.500 TL (HB buybox (Damla Yapıı)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 67093; liste fiyatı ₺13.881; sepette ₺12492,9; stokta yok; en düşük liste fiyatı ₺12.500 (HB buybox (Damla Yapıı)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1179" s="7" t="inlineStr">
@@ -44146,7 +44146,7 @@
       </c>
       <c r="E1180" s="6" t="inlineStr">
         <is>
-          <t>kod 75102; liste fiyatı 12.387 TL; sepette 11148,3 TL; stokta yok; en düşük liste fiyatı 12.387 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 75102; liste fiyatı ₺12.387; sepette ₺11148,3; stokta yok; en düşük liste fiyatı ₺12.387 (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1180" s="7" t="inlineStr">
@@ -44183,7 +44183,7 @@
       </c>
       <c r="E1181" s="6" t="inlineStr">
         <is>
-          <t>kod A49321; liste fiyatı 16.578 TL; sepette 14091,3 TL; stokta yok; en düşük liste fiyatı 13.450 TL (HB buybox (Cemretesyapi)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A49321; liste fiyatı ₺16.578; sepette ₺14091,3; stokta yok; en düşük liste fiyatı ₺13.450 (HB buybox (Cemretesyapi)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1181" s="7" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="E1182" s="6" t="inlineStr">
         <is>
-          <t>kod A43057; liste fiyatı 7.112 TL; sepette 6045,2 TL; stokta yok; en düşük liste fiyatı 4.190 TL (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A43057; liste fiyatı ₺7.112; sepette ₺6045,2; stokta yok; en düşük liste fiyatı ₺4.190 (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1182" s="7" t="inlineStr">
@@ -44257,7 +44257,7 @@
       </c>
       <c r="E1183" s="6" t="inlineStr">
         <is>
-          <t>kod A41994; liste fiyatı 5.907 TL; sepette 5316,3 TL; stokta yok; en düşük liste fiyatı 4.390 TL (TY 3P (AL-BA HOME)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A41994; liste fiyatı ₺5.907; sepette ₺5316,3; stokta yok; en düşük liste fiyatı ₺4.390 (TY 3P (AL-BA HOME)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1183" s="7" t="inlineStr">
@@ -44294,7 +44294,7 @@
       </c>
       <c r="E1184" s="6" t="inlineStr">
         <is>
-          <t>kod 800-1896; liste fiyatı 8.385 TL; stokta yok; en düşük liste fiyatı 5438,6 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 800-1896; liste fiyatı ₺8.385; stokta yok; en düşük liste fiyatı ₺5438,6 (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1184" s="7" t="inlineStr">
@@ -44331,7 +44331,7 @@
       </c>
       <c r="E1185" s="6" t="inlineStr">
         <is>
-          <t>kod 800-2025; liste fiyatı 11.042 TL; stokta yok; en düşük liste fiyatı 9.000 TL (Koçtaş); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 800-2025; liste fiyatı ₺11.042; stokta yok; en düşük liste fiyatı ₺9.000 (Koçtaş); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1185" s="7" t="inlineStr">
@@ -44368,7 +44368,7 @@
       </c>
       <c r="E1186" s="6" t="inlineStr">
         <is>
-          <t>kod 109-003-909; liste fiyatı 1.720 TL; sepette 1.462 TL; stokta; en düşük liste fiyatı 1.190 TL (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 109-003-909; liste fiyatı ₺1.720; sepette ₺1.462; stokta; en düşük liste fiyatı ₺1.190 (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1186" s="7" t="inlineStr">
@@ -44405,7 +44405,7 @@
       </c>
       <c r="E1187" s="6" t="inlineStr">
         <is>
-          <t>kod 121-003-909; liste fiyatı 1.720 TL; sepette 1.462 TL; stokta; en düşük liste fiyatı 1426,6 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 121-003-909; liste fiyatı ₺1.720; sepette ₺1.462; stokta; en düşük liste fiyatı ₺1426,6 (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1187" s="7" t="inlineStr">
@@ -44442,7 +44442,7 @@
       </c>
       <c r="E1188" s="6" t="inlineStr">
         <is>
-          <t>kod 84-003-009; liste fiyatı 2.612 TL; sepette 2220,2 TL; stokta; en düşük liste fiyatı 1900,9 TL (HB buybox (GEYLANİ DAYANIKLI TÜKETİM)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 84-003-009; liste fiyatı ₺2.612; sepette ₺2220,2; stokta; en düşük liste fiyatı ₺1900,9 (HB buybox (GEYLANİ DAYANIKLI TÜKETİM)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1188" s="7" t="inlineStr">
@@ -44479,7 +44479,7 @@
       </c>
       <c r="E1189" s="6" t="inlineStr">
         <is>
-          <t>kod 60785; liste fiyatı 32.596 TL; sepette 27706,6 TL; stokta; en düşük liste fiyatı 32.596 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 60785; liste fiyatı ₺32.596; sepette ₺27706,6; stokta; en düşük liste fiyatı ₺32.596 (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1189" s="7" t="inlineStr">
@@ -44516,7 +44516,7 @@
       </c>
       <c r="E1190" s="6" t="inlineStr">
         <is>
-          <t>kod 60812; liste fiyatı 29.464 TL; sepette 26517,6 TL; stokta yok; en düşük liste fiyatı 29.464 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 60812; liste fiyatı ₺29.464; sepette ₺26517,6; stokta yok; en düşük liste fiyatı ₺29.464 (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1190" s="7" t="inlineStr">
@@ -44553,7 +44553,7 @@
       </c>
       <c r="E1191" s="6" t="inlineStr">
         <is>
-          <t>kod A45200; liste fiyatı 427 TL; sepette 362,9 TL; stokta; en düşük liste fiyatı 311,1 TL (TY 3P (YAPIEVİ)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A45200; liste fiyatı ₺427; sepette ₺362,9; stokta; en düşük liste fiyatı ₺311,1 (TY 3P (YAPIEVİ)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1191" s="7" t="inlineStr">
@@ -44590,7 +44590,7 @@
       </c>
       <c r="E1192" s="6" t="inlineStr">
         <is>
-          <t>kod A45228; liste fiyatı 427 TL; sepette 362,9 TL; stokta; en düşük liste fiyatı 360 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A45228; liste fiyatı ₺427; sepette ₺362,9; stokta; en düşük liste fiyatı ₺360 (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1192" s="7" t="inlineStr">
@@ -44627,7 +44627,7 @@
       </c>
       <c r="E1193" s="6" t="inlineStr">
         <is>
-          <t>kod 330B1314; liste fiyatı 896 TL; sepette 761,6 TL; stokta; en düşük liste fiyatı 675 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 330B1314; liste fiyatı ₺896; sepette ₺761,6; stokta; en düşük liste fiyatı ₺675 (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1193" s="7" t="inlineStr">
@@ -44664,7 +44664,7 @@
       </c>
       <c r="E1194" s="6" t="inlineStr">
         <is>
-          <t>kod 5501L003-0001; liste fiyatı 4.791 TL; sepette 4072,3 TL; stokta yok; en düşük liste fiyatı 4.791 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 5501L003-0001; liste fiyatı ₺4.791; sepette ₺4072,3; stokta yok; en düşük liste fiyatı ₺4.791 (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1194" s="7" t="inlineStr">
@@ -44701,7 +44701,7 @@
       </c>
       <c r="E1195" s="6" t="inlineStr">
         <is>
-          <t>kod 7783L003-0092; liste fiyatı 8.813 TL; sepette 7931,7 TL; stokta yok; en düşük liste fiyatı 8.813 TL (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 7783L003-0092; liste fiyatı ₺8.813; sepette ₺7931,7; stokta yok; en düşük liste fiyatı ₺8.813 (vitra.com.tr); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1195" s="7" t="inlineStr">
@@ -44738,7 +44738,7 @@
       </c>
       <c r="E1196" s="6" t="inlineStr">
         <is>
-          <t>kod A42923; liste fiyatı 4.707 TL; sepette 4000,9 TL; stokta yok; en düşük liste fiyatı 2.999 TL (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A42923; liste fiyatı ₺4.707; sepette ₺4000,9; stokta yok; en düşük liste fiyatı ₺2.999 (TY 3P (ASİL BANYOVİT)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1196" s="7" t="inlineStr">
@@ -44775,7 +44775,7 @@
       </c>
       <c r="E1197" s="6" t="inlineStr">
         <is>
-          <t>kod A43715; liste fiyatı 4.707 TL; sepette 4236,3 TL; stokta; en düşük liste fiyatı 2.989 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A43715; liste fiyatı ₺4.707; sepette ₺4236,3; stokta; en düşük liste fiyatı ₺2.989 (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1197" s="7" t="inlineStr">
@@ -44812,7 +44812,7 @@
       </c>
       <c r="E1198" s="6" t="inlineStr">
         <is>
-          <t>kod A42484; liste fiyatı 5.016 TL; sepette 4514,4 TL; stokta yok; en düşük liste fiyatı 3821,3 TL (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A42484; liste fiyatı ₺5.016; sepette ₺4514,4; stokta yok; en düşük liste fiyatı ₺3821,3 (HB buybox (Hepsiburada)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1198" s="7" t="inlineStr">
@@ -44849,7 +44849,7 @@
       </c>
       <c r="E1199" s="6" t="inlineStr">
         <is>
-          <t>kod A47055EXPS; liste fiyatı 13.892 TL; sepette 12502,8 TL; stokta; en düşük liste fiyatı 9.390 TL (HB buybox (uygunyapimarket)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod A47055EXPS; liste fiyatı ₺13.892; sepette ₺12502,8; stokta; en düşük liste fiyatı ₺9.390 (HB buybox (uygunyapimarket)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1199" s="7" t="inlineStr">
@@ -44886,7 +44886,7 @@
       </c>
       <c r="E1200" s="6" t="inlineStr">
         <is>
-          <t>kod 5473B003-0618; liste fiyatı 4.913 TL; sepette 4176,1 TL; stokta yok; en düşük liste fiyatı 4.555 TL (HB buybox (Seçkin Banyo)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
+          <t>kod 5473B003-0618; liste fiyatı ₺4.913; sepette ₺4176,1; stokta yok; en düşük liste fiyatı ₺4.555 (HB buybox (Seçkin Banyo)); Trendyol, Hepsiburada ve Koçtaş liste fiyatlarıyla 4 kanalda karşılaştırıldı</t>
         </is>
       </c>
       <c r="F1200" s="7" t="inlineStr">
@@ -45367,7 +45367,7 @@
       </c>
       <c r="E1213" s="6" t="inlineStr">
         <is>
-          <t>3 iş günü içinde kargoya, kargo 1-3 gün; stokta yoksa 4-30 gün; ücretsiz kargo seçili ürünlerde (banner'da İstanbul içi 250 TL, güncelliği belirsiz)</t>
+          <t>3 iş günü içinde kargoya, kargo 1-3 gün; stokta yoksa 4-30 gün; ücretsiz kargo seçili ürünlerde (banner'da İstanbul içi ₺250, güncelliği belirsiz)</t>
         </is>
       </c>
       <c r="F1213" s="7" t="inlineStr">
@@ -45515,7 +45515,7 @@
       </c>
       <c r="E1217" s="6" t="inlineStr">
         <is>
-          <t>2.500 TL ve üzeri alışverişte anlaşmalı banka kartlarıyla vade farksız (online ve şubeler); azami taksit yazmıyor</t>
+          <t>₺2.500 ve üzeri alışverişte anlaşmalı banka kartlarıyla vade farksız (online ve şubeler); azami taksit yazmıyor</t>
         </is>
       </c>
       <c r="F1217" s="7" t="inlineStr">
@@ -45552,7 +45552,7 @@
       </c>
       <c r="E1218" s="6" t="inlineStr">
         <is>
-          <t>1.000 TL ve üzeri (belirlenen ürünlerde) ücretsiz kargo; şubelerden 40.000 TL ve üzeri şehir içi 30 km'ye kadar ücretsiz nakliye; 30 desi altı Yurtiçi/KolayGelsin, üstü Horoz/Arvato</t>
+          <t>₺1.000 ve üzeri (belirlenen ürünlerde) ücretsiz kargo; şubelerden ₺40.000 ve üzeri şehir içi 30 km'ye kadar ücretsiz nakliye; 30 desi altı Yurtiçi/KolayGelsin, üstü Horoz/Arvato</t>
         </is>
       </c>
       <c r="F1218" s="7" t="inlineStr">
@@ -45663,7 +45663,7 @@
       </c>
       <c r="E1221" s="6" t="inlineStr">
         <is>
-          <t>11 kalem: asma ve takım klozet 2.450 TL, rezervuar ve iç takım 1.750, armatür ve duş 1.750, lavabo 2.450, banyo mobilyası alt modül 2.450, boy dolabı 1.400, demonte takım 3.900 TL (söküm hariç)</t>
+          <t>11 kalem: asma ve takım klozet ₺2.450, rezervuar ve iç takım 1.750, armatür ve duş 1.750, lavabo 2.450, banyo mobilyası alt modül 2.450, boy dolabı 1.400, demonte takım ₺3.900 (söküm hariç)</t>
         </is>
       </c>
       <c r="F1221" s="7" t="inlineStr">
@@ -45737,7 +45737,7 @@
       </c>
       <c r="E1223" s="6" t="inlineStr">
         <is>
-          <t>Banka onayından sonra 5 iş günü içinde kargoya, kargo 1-5 gün; 3.000 TL üzeri ücretsiz kargo; 30 gün ücretsiz iade ve değişim</t>
+          <t>Banka onayından sonra 5 iş günü içinde kargoya, kargo 1-5 gün; ₺3.000 üzeri ücretsiz kargo; 30 gün ücretsiz iade ve değişim</t>
         </is>
       </c>
       <c r="F1223" s="7" t="inlineStr">
@@ -46329,7 +46329,7 @@
       </c>
       <c r="E1239" s="6" t="inlineStr">
         <is>
-          <t>12 aya varan taksit (Hepsiburada limiti); uygun ürünlerde kapıda nakit ödeme, üst limit 7.000 TL; alışveriş kredisi; kurumsal fatura (arama özeti)</t>
+          <t>12 aya varan taksit (Hepsiburada limiti); uygun ürünlerde kapıda nakit ödeme, üst limit ₺7.000; alışveriş kredisi; kurumsal fatura (arama özeti)</t>
         </is>
       </c>
       <c r="F1239" s="7" t="inlineStr">
@@ -46662,7 +46662,7 @@
       </c>
       <c r="E1248" s="6" t="inlineStr">
         <is>
-          <t>Arvato, Horoz, HepsiJET, Yurtiçi, KolayGelsin; şehir içi ayrı nakliye hizmeti; daire kapısına kadar teslim; minimum sipariş 500 TL, kargo 299 TL (1.500 TL'ye kadar) ve 799 TL (7.500 TL'ye kadar), üstünde %11</t>
+          <t>Arvato, Horoz, HepsiJET, Yurtiçi, KolayGelsin; şehir içi ayrı nakliye hizmeti; daire kapısına kadar teslim; minimum sipariş ₺500, kargo ₺299 (₺1.500'e kadar) ve ₺799 (₺7.500'e kadar), üstünde %11</t>
         </is>
       </c>
       <c r="F1248" s="7" t="inlineStr">
@@ -46699,7 +46699,7 @@
       </c>
       <c r="E1249" s="6" t="inlineStr">
         <is>
-          <t>1.500 TL üzeri 3 taksit; IKEA Aile üyelerine 7.500 TL üzeri 6 ve 20.000 TL üzeri 9 taksit (belirli kartlar); 5 Ocak 2026 - 3 Ocak 2027 arası geçerli; kapıda ödeme yok (Full 3D kart)</t>
+          <t>₺1.500 üzeri 3 taksit; IKEA Aile üyelerine ₺7.500 üzeri 6 ve ₺20.000 üzeri 9 taksit (belirli kartlar); 5 Ocak 2026 - 3 Ocak 2027 arası geçerli; kapıda ödeme yok (Full 3D kart)</t>
         </is>
       </c>
       <c r="F1249" s="7" t="inlineStr">
@@ -47217,7 +47217,7 @@
       </c>
       <c r="E1263" s="6" t="inlineStr">
         <is>
-          <t>Online 5.000 TL üzeri 7 taksite kadar vade farksız (mağazada 10.000 TL üzeri); vade farklı 9 taksite kadar; Flexi kart, aidatsız kart ve TEB Worldcard kapsam dışı; alışveriş kredisi bulunamadı</t>
+          <t>Online ₺5.000 üzeri 7 taksite kadar vade farksız (mağazada ₺10.000 üzeri); vade farklı 9 taksite kadar; Flexi kart, aidatsız kart ve TEB Worldcard kapsam dışı; alışveriş kredisi bulunamadı</t>
         </is>
       </c>
       <c r="F1263" s="7" t="inlineStr">
@@ -47291,7 +47291,7 @@
       </c>
       <c r="E1265" s="6" t="inlineStr">
         <is>
-          <t>Mağaza bazlı 300 TL şartlı kargo ifadesi (sayfada bulunamadı); arama sonucu özeti</t>
+          <t>Mağaza bazlı ₺300 şartlı kargo ifadesi (sayfada bulunamadı); arama sonucu özeti</t>
         </is>
       </c>
       <c r="F1265" s="7" t="inlineStr">
@@ -47661,7 +47661,7 @@
       </c>
       <c r="E1275" s="6" t="inlineStr">
         <is>
-          <t>Satıcı bareminin 350 TL olduğu ifadesi (alıcı eşiği doğrulanamadı); arama sonucu özeti</t>
+          <t>Satıcı bareminin ₺350 olduğu ifadesi (alıcı eşiği doğrulanamadı); arama sonucu özeti</t>
         </is>
       </c>
       <c r="F1275" s="7" t="inlineStr">
@@ -47772,7 +47772,7 @@
       </c>
       <c r="E1278" s="6" t="inlineStr">
         <is>
-          <t>Standart kargo ücreti 59,99 TL; 'kargo bedava' kampanyalı ürünlerde ücretsiz; genel alıcı eşiği yok</t>
+          <t>Standart kargo ücreti ₺59,99; 'kargo bedava' kampanyalı ürünlerde ücretsiz; genel alıcı eşiği yok</t>
         </is>
       </c>
       <c r="F1278" s="7" t="inlineStr">
@@ -47883,7 +47883,7 @@
       </c>
       <c r="E1281" s="6" t="inlineStr">
         <is>
-          <t>Ürün tablosunda 12 taksite kadar seçenek (8, 9 ve 12 taksit çoğu kartta vade farklı, 2-3-4-6 taksit eşit tutar); tahmini kargoya teslim tarihi; 30 güne kadar ücretsiz iade ifadesi; montaj hizmeti seçeneği (+5.300 TL)</t>
+          <t>Ürün tablosunda 12 taksite kadar seçenek (8, 9 ve 12 taksit çoğu kartta vade farklı, 2-3-4-6 taksit eşit tutar); tahmini kargoya teslim tarihi; 30 güne kadar ücretsiz iade ifadesi; montaj hizmeti seçeneği (+₺5.300)</t>
         </is>
       </c>
       <c r="F1281" s="7" t="inlineStr">
@@ -47994,7 +47994,7 @@
       </c>
       <c r="E1284" s="6" t="inlineStr">
         <is>
-          <t>21 Eylül - 30 Kasım 2026: seçili renkli ürünlerde %40 indirim, 9 aya varan taksit, 40.000 TL ve üzeri alışverişte ücretsiz montaj</t>
+          <t>21 Eylül - 30 Kasım 2026: seçili renkli ürünlerde %40 indirim, 9 aya varan taksit, ₺40.000 ve üzeri alışverişte ücretsiz montaj</t>
         </is>
       </c>
       <c r="F1284" s="7" t="inlineStr">

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -1517,7 +1517,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Click · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar</t>
+          <t>06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Click · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>06 GSC - Organik Kanal · 15 Set, Komple Banyo ve Ürün + Hizmet · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>06 GSC - Organik Kanal · 15 Set, Komple Banyo ve Ürün + Hizmet · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları · 26 Kanal Rolleri ve Etkileşim Modeli · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları · 26 Kanal Rolleri ve Etkileşim Modeli · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -6568,7 +6568,7 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="111" customHeight="1">
+    <row r="165" ht="97.5" customHeight="1">
       <c r="A165" s="5" t="inlineStr">
         <is>
           <t>https://www.banyoline.com</t>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>14 Yeni Kategori ve Segment Fırsatları · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>14 Yeni Kategori ve Segment Fırsatları · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="D200" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E200" s="6" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="D201" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E201" s="6" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="D202" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E202" s="6" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar</t>
         </is>
       </c>
       <c r="E204" s="6" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="D207" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E207" s="6" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="D209" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E209" s="6" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E210" s="6" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="D211" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E211" s="6" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E212" s="6" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="D213" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E213" s="6" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E214" s="6" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="D215" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E215" s="6" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="D216" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="D218" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="D220" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E220" s="6" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E226" s="6" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="D227" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E227" s="6" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="D230" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E230" s="6" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="D231" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E231" s="6" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="D232" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E232" s="6" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i · 28 Sonraki Adımlar</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E234" s="6" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D235" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E235" s="6" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="D236" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E236" s="6" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="D237" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E237" s="6" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="D239" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E239" s="6" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="D241" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="E241" s="6" t="inlineStr">
@@ -50712,7 +50712,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>12 Şikayetvar: Satış Sonrası Deneyim · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>12 Şikayetvar: Satış Sonrası Deneyim · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -50837,7 +50837,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -50937,7 +50937,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
+          <t>14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -51037,7 +51037,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -51087,7 +51087,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -51162,7 +51162,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
@@ -51187,7 +51187,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>12 Şikayetvar: Satış Sonrası Deneyim · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları</t>
+          <t>12 Şikayetvar: Satış Sonrası Deneyim · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
@@ -51312,7 +51312,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
@@ -51412,7 +51412,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
@@ -51437,7 +51437,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -51512,7 +51512,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
@@ -51562,7 +51562,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
@@ -51587,7 +51587,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -51687,7 +51687,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -51737,7 +51737,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -51787,7 +51787,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -51812,7 +51812,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -51837,7 +51837,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -51912,7 +51912,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -51987,7 +51987,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -52037,7 +52037,7 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -52062,7 +52062,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
@@ -52137,7 +52137,7 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -52162,7 +52162,7 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -52262,7 +52262,7 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
@@ -52287,7 +52287,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
@@ -52312,7 +52312,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Traffic'i</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -52489,7 +52489,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Aralık 2025'te www.vitra.com.tr traffic'i aynı mülke katıldığı için session ve conversion rate Aralık öncesi ve sonrası kıyaslanmaz; revenue ve purchase kıyaslanabilir. Giriş sayfası raporunda bir session birden fazla giriş sayfasında sayılabildiği için session pay olarak verilmiştir; revenue genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır. Ürün raporunda sepete eklenen ürün (Items added to cart) beş ürün kodunda hatalı adet taşıdığı için bu kodlar, sepete ekleme olayının hatalı tetiklendiği Eylül 2026 ile birlikte oran hesabına katılmamış; ürün revenue'su genel bakıştaki revenue'dan farklı hesaplandığı için pay olarak verilmiştir. Sepet sayfasında session ve kullanıcı çerezi yenilendiği için kullanıcı düzeyindeki kırılımlar (yeni ve geri dönen kullanıcı, ilk kez satın alan) kullanılmamıştır. www.vitra.com.tr sayfaları (blog, koleksiyon, servis) bu mülkte Aralık 2025'ten itibaren ölçülmektedir. Sipariş onay sayfası keşiflerinde (1 Eki 2025 - 30 Eyl 2026) bazı aylar örneklendiği için yalnız paylar kullanılmış; purchase'ın kaynak / ortamı GA4 atama modeline göre, session kanalı ise session kanal grubuna göre verilmiştir</t>
+          <t>Aralık 2025'te www.vitra.com.tr trafiği aynı mülke katıldığı için session ve conversion rate Aralık öncesi ve sonrası kıyaslanmaz; revenue ve purchase kıyaslanabilir. Giriş sayfası raporunda bir session birden fazla giriş sayfasında sayılabildiği için session pay olarak verilmiştir; revenue genel bakışla birebir aynıdır. Anahtar olay (key event) satın alma dışında sepete ekleme, ödeme adımları, dosya indirme, favori ve üyelik olaylarını da kapsadığından kullanılmamıştır. Ürün raporunda sepete eklenen ürün (Items added to cart) beş ürün kodunda hatalı adet taşıdığı için bu kodlar, sepete ekleme olayının hatalı tetiklendiği Eylül 2026 ile birlikte oran hesabına katılmamış; ürün revenue'su genel bakıştaki revenue'dan farklı hesaplandığı için pay olarak verilmiştir. Sepet sayfasında session ve kullanıcı çerezi yenilendiği için kullanıcı düzeyindeki kırılımlar (yeni ve geri dönen kullanıcı, ilk kez satın alan) kullanılmamıştır. www.vitra.com.tr sayfaları (blog, koleksiyon, servis) bu mülkte Aralık 2025'ten itibaren ölçülmektedir. Sipariş onay sayfası keşiflerinde (1 Eki 2025 - 30 Eyl 2026) bazı aylar örneklendiği için yalnız paylar kullanılmış; purchase'ın kaynak / ortamı GA4 atama modeline göre, session kanalı ise session kanal grubuna göre verilmiştir</t>
         </is>
       </c>
     </row>
@@ -52555,7 +52555,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Organik ve paid traffic değerleri Ahrefs tahminidir; gerçek visit sayısı değildir</t>
+          <t>Organik ve paid trafik değerleri Ahrefs tahminidir; gerçek visit sayısı değildir</t>
         </is>
       </c>
     </row>
@@ -52797,7 +52797,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Kategori traffic'i listelenen sayfalarla sınırlıdır ve alt sınır olarak okunmalıdır</t>
+          <t>Kategori trafiği listelenen sayfalarla sınırlıdır ve alt sınır olarak okunmalıdır</t>
         </is>
       </c>
     </row>
@@ -53024,7 +53024,7 @@
     <row r="33" ht="43.5" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Similarweb site traffic'i</t>
+          <t>Similarweb site trafiği</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -925,7 +925,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>02 Ekonomik Ortam: Harcama, Güven ve Konut Piyasası · 28 Sonraki Adımlar</t>
+          <t>02 Ekonomik Ortam: Harcama, Güven ve Konut Piyasası · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 14 Yeni Kategori ve Segment Fırsatları · 28 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 14 Yeni Kategori ve Segment Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 GSC - Organik Kanal · 09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 13 Katalog ve Talep Eşleşmesi · 14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 04 SSG ve BM: Derin Talep İncelemesi · 05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 GSC - Organik Kanal · 09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 13 Katalog ve Talep Eşleşmesi · 14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>04 SSG ve BM: Derin Talep İncelemesi · 13 Katalog ve Talep Eşleşmesi · 14 Yeni Kategori ve Segment Fırsatları · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 21 Pazaryeri Yorumları ve Soru-Cevap: Sentiment ve Pain Point Analizi · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar</t>
+          <t>04 SSG ve BM: Derin Talep İncelemesi · 13 Katalog ve Talep Eşleşmesi · 14 Yeni Kategori ve Segment Fırsatları · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 21 Pazaryeri Yorumları ve Soru-Cevap: Sentiment ve Pain Point Analizi · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Click · 08 GA4 - Site ve E-Ticaret Performansı · 09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 11 YouTube: Montaj, Tamir ve Karar Videoları · 13 Katalog ve Talep Eşleşmesi · 15 Set, Komple Banyo ve Ürün + Hizmet · 26 Kanal Rolleri ve Etkileşim Modeli · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>05 İhtiyaç Dili: Kullanıcı Ne Arıyor? · 06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Click · 08 GA4 - Site ve E-Ticaret Performansı · 09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 11 YouTube: Montaj, Tamir ve Karar Videoları · 13 Katalog ve Talep Eşleşmesi · 15 Set, Komple Banyo ve Ürün + Hizmet · 26 Kanal Rolleri ve Etkileşim Modeli · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1517,7 +1517,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Click · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar</t>
+          <t>06 GSC - Organik Kanal · 07 Google Yapay Zeka Özellikleri ve Organik Click · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları · 26 Kanal Rolleri ve Etkileşim Modeli · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>09 Marka Aramaları ve Autocomplete · 10 Google Arama Sonuçları ve AI Overview · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 23 Kanal Politikaları ve Keşif Kanalları · 26 Kanal Rolleri ve Etkileşim Modeli · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>11 YouTube: Montaj, Tamir ve Karar Videoları · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>11 YouTube: Montaj, Tamir ve Karar Videoları · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>11 YouTube: Montaj, Tamir ve Karar Videoları · 28 Sonraki Adımlar</t>
+          <t>11 YouTube: Montaj, Tamir ve Karar Videoları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>12 Şikayetvar: Satış Sonrası Deneyim · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 21 Pazaryeri Yorumları ve Soru-Cevap: Sentiment ve Pain Point Analizi · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar</t>
+          <t>12 Şikayetvar: Satış Sonrası Deneyim · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 21 Pazaryeri Yorumları ve Soru-Cevap: Sentiment ve Pain Point Analizi · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>12 Şikayetvar: Satış Sonrası Deneyim · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>12 Şikayetvar: Satış Sonrası Deneyim · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>12 Şikayetvar: Satış Sonrası Deneyim · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>12 Şikayetvar: Satış Sonrası Deneyim · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>13 Katalog ve Talep Eşleşmesi · 14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar</t>
+          <t>13 Katalog ve Talep Eşleşmesi · 14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>13 Katalog ve Talep Eşleşmesi · 14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar</t>
+          <t>13 Katalog ve Talep Eşleşmesi · 14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>13 Katalog ve Talep Eşleşmesi · 14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar</t>
+          <t>13 Katalog ve Talep Eşleşmesi · 14 Yeni Kategori ve Segment Fırsatları · 15 Set, Komple Banyo ve Ürün + Hizmet · 26 Kanal Rolleri ve Etkileşim Modeli · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>14 Yeni Kategori ve Segment Fırsatları · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar</t>
+          <t>14 Yeni Kategori ve Segment Fırsatları · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
@@ -6901,7 +6901,7 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="43.5" customHeight="1">
+    <row r="174" ht="57" customHeight="1">
       <c r="A174" s="5" t="inlineStr">
         <is>
           <t>https://www.bauhaus.info/service/leistungen/montageservice/komplettbad</t>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>15 Set, Komple Banyo ve Ürün + Hizmet · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>15 Set, Komple Banyo ve Ürün + Hizmet · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -7197,7 +7197,7 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="43.5" customHeight="1">
+    <row r="182" ht="57" customHeight="1">
       <c r="A182" s="5" t="inlineStr">
         <is>
           <t>https://www.koctas.com.tr/banyo-tadilati</t>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>15 Set, Komple Banyo ve Ürün + Hizmet · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>15 Set, Komple Banyo ve Ürün + Hizmet · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -7271,7 +7271,7 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="43.5" customHeight="1">
+    <row r="184" ht="57" customHeight="1">
       <c r="A184" s="5" t="inlineStr">
         <is>
           <t>https://reveal.kohler.com/en</t>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>15 Set, Komple Banyo ve Ürün + Hizmet · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>15 Set, Komple Banyo ve Ürün + Hizmet · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E208" s="6" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D233" s="6" t="inlineStr">
         <is>
-          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği · 28 Sonraki Adımlar</t>
+          <t>17 Marka ve Uzman Sitelerde Kategori Trafiği · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E233" s="6" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="D309" s="6" t="inlineStr">
         <is>
-          <t>18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 28 Sonraki Adımlar</t>
+          <t>18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E309" s="6" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="D311" s="6" t="inlineStr">
         <is>
-          <t>18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar</t>
+          <t>18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E311" s="6" t="inlineStr">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="D412" s="6" t="inlineStr">
         <is>
-          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar</t>
+          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E412" s="6" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="D545" s="6" t="inlineStr">
         <is>
-          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar</t>
+          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E545" s="6" t="inlineStr">
@@ -26640,7 +26640,7 @@
       </c>
       <c r="D707" s="6" t="inlineStr">
         <is>
-          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar</t>
+          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E707" s="6" t="inlineStr">
@@ -32116,7 +32116,7 @@
       </c>
       <c r="D855" s="6" t="inlineStr">
         <is>
-          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar</t>
+          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E855" s="6" t="inlineStr">
@@ -35150,7 +35150,7 @@
       </c>
       <c r="D937" s="6" t="inlineStr">
         <is>
-          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar</t>
+          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E937" s="6" t="inlineStr">
@@ -39997,7 +39997,7 @@
       </c>
       <c r="D1068" s="6" t="inlineStr">
         <is>
-          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar</t>
+          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1068" s="6" t="inlineStr">
@@ -41255,7 +41255,7 @@
       </c>
       <c r="D1102" s="6" t="inlineStr">
         <is>
-          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar</t>
+          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1102" s="6" t="inlineStr">
@@ -41477,7 +41477,7 @@
       </c>
       <c r="D1108" s="6" t="inlineStr">
         <is>
-          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar</t>
+          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1108" s="6" t="inlineStr">
@@ -41810,7 +41810,7 @@
       </c>
       <c r="D1117" s="6" t="inlineStr">
         <is>
-          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar</t>
+          <t>19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1117" s="6" t="inlineStr">
@@ -42772,7 +42772,7 @@
       </c>
       <c r="D1143" s="6" t="inlineStr">
         <is>
-          <t>20 VitrA Resmi Mağaza: Pazaryeri Panel Verisi · 21 Pazaryeri Yorumları ve Soru-Cevap: Sentiment ve Pain Point Analizi · 28 Sonraki Adımlar</t>
+          <t>20 VitrA Resmi Mağaza: Pazaryeri Panel Verisi · 21 Pazaryeri Yorumları ve Soru-Cevap: Sentiment ve Pain Point Analizi · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1143" s="6" t="inlineStr">
@@ -42809,7 +42809,7 @@
       </c>
       <c r="D1144" s="6" t="inlineStr">
         <is>
-          <t>20 VitrA Resmi Mağaza: Pazaryeri Panel Verisi · 21 Pazaryeri Yorumları ve Soru-Cevap: Sentiment ve Pain Point Analizi · 28 Sonraki Adımlar</t>
+          <t>20 VitrA Resmi Mağaza: Pazaryeri Panel Verisi · 21 Pazaryeri Yorumları ve Soru-Cevap: Sentiment ve Pain Point Analizi · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1144" s="6" t="inlineStr">
@@ -43013,7 +43013,7 @@
         </is>
       </c>
     </row>
-    <row r="1150" ht="43.5" customHeight="1">
+    <row r="1150" ht="57" customHeight="1">
       <c r="A1150" s="5" t="inlineStr">
         <is>
           <t>https://shopping.google.com</t>
@@ -43031,7 +43031,7 @@
       </c>
       <c r="D1150" s="6" t="inlineStr">
         <is>
-          <t>22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1150" s="6" t="inlineStr">
@@ -45214,7 +45214,7 @@
       </c>
       <c r="D1209" s="6" t="inlineStr">
         <is>
-          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar</t>
+          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1209" s="6" t="inlineStr">
@@ -45510,7 +45510,7 @@
       </c>
       <c r="D1217" s="6" t="inlineStr">
         <is>
-          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar</t>
+          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1217" s="6" t="inlineStr">
@@ -46287,7 +46287,7 @@
       </c>
       <c r="D1238" s="6" t="inlineStr">
         <is>
-          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar</t>
+          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1238" s="6" t="inlineStr">
@@ -46694,7 +46694,7 @@
       </c>
       <c r="D1249" s="6" t="inlineStr">
         <is>
-          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar</t>
+          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1249" s="6" t="inlineStr">
@@ -47212,7 +47212,7 @@
       </c>
       <c r="D1263" s="6" t="inlineStr">
         <is>
-          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar</t>
+          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1263" s="6" t="inlineStr">
@@ -47915,7 +47915,7 @@
       </c>
       <c r="D1282" s="6" t="inlineStr">
         <is>
-          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar</t>
+          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1282" s="6" t="inlineStr">
@@ -48063,7 +48063,7 @@
       </c>
       <c r="D1286" s="6" t="inlineStr">
         <is>
-          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar</t>
+          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1286" s="6" t="inlineStr">
@@ -48137,7 +48137,7 @@
       </c>
       <c r="D1288" s="6" t="inlineStr">
         <is>
-          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar</t>
+          <t>23 Kanal Politikaları ve Keşif Kanalları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1288" s="6" t="inlineStr">
@@ -48359,7 +48359,7 @@
       </c>
       <c r="D1294" s="6" t="inlineStr">
         <is>
-          <t>24 vitra.com.tr Satın Alma Yolculuğu: Site İçi Arama, Sepet ve Ödeme · 28 Sonraki Adımlar</t>
+          <t>24 vitra.com.tr Satın Alma Yolculuğu: Site İçi Arama, Sepet ve Ödeme · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1294" s="6" t="inlineStr">
@@ -48396,7 +48396,7 @@
       </c>
       <c r="D1295" s="6" t="inlineStr">
         <is>
-          <t>24 vitra.com.tr Satın Alma Yolculuğu: Site İçi Arama, Sepet ve Ödeme · 28 Sonraki Adımlar</t>
+          <t>24 vitra.com.tr Satın Alma Yolculuğu: Site İçi Arama, Sepet ve Ödeme · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1295" s="6" t="inlineStr">
@@ -48415,7 +48415,7 @@
         </is>
       </c>
     </row>
-    <row r="1296" ht="30" customHeight="1">
+    <row r="1296" ht="43.5" customHeight="1">
       <c r="A1296" s="5" t="inlineStr">
         <is>
           <t>https://www.duravit.com/en-us/service/bathroom-planner/</t>
@@ -48433,7 +48433,7 @@
       </c>
       <c r="D1296" s="6" t="inlineStr">
         <is>
-          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1296" s="6" t="inlineStr">
@@ -48452,7 +48452,7 @@
         </is>
       </c>
     </row>
-    <row r="1297" ht="30" customHeight="1">
+    <row r="1297" ht="43.5" customHeight="1">
       <c r="A1297" s="5" t="inlineStr">
         <is>
           <t>https://www.geberit.de/badezimmerprodukte/wcs-urinale/dusch-wcs-geberit-aquaclean/testen/</t>
@@ -48470,7 +48470,7 @@
       </c>
       <c r="D1297" s="6" t="inlineStr">
         <is>
-          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1297" s="6" t="inlineStr">
@@ -48489,7 +48489,7 @@
         </is>
       </c>
     </row>
-    <row r="1298" ht="30" customHeight="1">
+    <row r="1298" ht="43.5" customHeight="1">
       <c r="A1298" s="5" t="inlineStr">
         <is>
           <t>https://www.grohe.com/en-GB/service-support/spare-parts-finder</t>
@@ -48507,7 +48507,7 @@
       </c>
       <c r="D1298" s="6" t="inlineStr">
         <is>
-          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1298" s="6" t="inlineStr">
@@ -48526,7 +48526,7 @@
         </is>
       </c>
     </row>
-    <row r="1299" ht="30" customHeight="1">
+    <row r="1299" ht="43.5" customHeight="1">
       <c r="A1299" s="5" t="inlineStr">
         <is>
           <t>https://www.hansgrohe-usa.com/service/spare-parts-search</t>
@@ -48544,7 +48544,7 @@
       </c>
       <c r="D1299" s="6" t="inlineStr">
         <is>
-          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1299" s="6" t="inlineStr">
@@ -48600,7 +48600,7 @@
         </is>
       </c>
     </row>
-    <row r="1301" ht="30" customHeight="1">
+    <row r="1301" ht="43.5" customHeight="1">
       <c r="A1301" s="5" t="inlineStr">
         <is>
           <t>https://www.villeroy-boch.co.uk/r/bathroom-ideas/planning/bathroom-planner-online/</t>
@@ -48618,7 +48618,7 @@
       </c>
       <c r="D1301" s="6" t="inlineStr">
         <is>
-          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1301" s="6" t="inlineStr">
@@ -48637,7 +48637,7 @@
         </is>
       </c>
     </row>
-    <row r="1302" ht="30" customHeight="1">
+    <row r="1302" ht="43.5" customHeight="1">
       <c r="A1302" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr/banyonu-tasarla</t>
@@ -48655,7 +48655,7 @@
       </c>
       <c r="D1302" s="6" t="inlineStr">
         <is>
-          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1302" s="6" t="inlineStr">
@@ -48877,7 +48877,7 @@
       </c>
       <c r="D1308" s="6" t="inlineStr">
         <is>
-          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1308" s="6" t="inlineStr">
@@ -48914,7 +48914,7 @@
       </c>
       <c r="D1309" s="6" t="inlineStr">
         <is>
-          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1309" s="6" t="inlineStr">
@@ -48951,7 +48951,7 @@
       </c>
       <c r="D1310" s="6" t="inlineStr">
         <is>
-          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1310" s="6" t="inlineStr">
@@ -48988,7 +48988,7 @@
       </c>
       <c r="D1311" s="6" t="inlineStr">
         <is>
-          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="E1311" s="6" t="inlineStr">
@@ -50462,7 +50462,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>12 Şikayetvar: Satış Sonrası Deneyim · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>12 Şikayetvar: Satış Sonrası Deneyim · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -50587,7 +50587,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>11 YouTube: Montaj, Tamir ve Karar Videoları · 23 Kanal Politikaları ve Keşif Kanalları · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>11 YouTube: Montaj, Tamir ve Karar Videoları · 23 Kanal Politikaları ve Keşif Kanalları · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -50612,7 +50612,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>16 Rakip Görünürlüğü ve Kanal Ölçeği · 18 Pazaryerleri: Kategori Yapısı ve Çok Satanlar · 19 Pazaryeri Alt Kategori Derinliği: Çok Satanlar ve Rakip Mağazalar · 22 Fiyat ve Satıcı Manzarası: Shopping, Trendyol, Hepsiburada · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -50912,7 +50912,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>02 Ekonomik Ortam: Harcama, Güven ve Konut Piyasası · 28 Sonraki Adımlar</t>
+          <t>02 Ekonomik Ortam: Harcama, Güven ve Konut Piyasası · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -51112,7 +51112,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>23 Kanal Politikaları ve Keşif Kanalları · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -51262,7 +51262,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -51287,7 +51287,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
@@ -51387,7 +51387,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>15 Set, Komple Banyo ve Ürün + Hizmet · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>15 Set, Komple Banyo ve Ürün + Hizmet · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -51487,7 +51487,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -51637,7 +51637,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
@@ -51662,7 +51662,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>03 Kategori Talebi ve Dönemsel Değişim · 14 Yeni Kategori ve Segment Fırsatları · 28 Sonraki Adımlar</t>
+          <t>03 Kategori Talebi ve Dönemsel Değişim · 14 Yeni Kategori ve Segment Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -51712,7 +51712,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -51862,7 +51862,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>15 Set, Komple Banyo ve Ürün + Hizmet · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>15 Set, Komple Banyo ve Ürün + Hizmet · 25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -51987,7 +51987,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar</t>
+          <t>10 Google Arama Sonuçları ve AI Overview · 16 Rakip Görünürlüğü ve Kanal Ölçeği · 17 Marka ve Uzman Sitelerde Kategori Trafiği · 27 AI Arama ve GEO Fırsatları · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar</t>
+          <t>25 Benchmark: E-Ticaret Modelleri ve Dijital Deneyim · 28 Sonraki Adımlar İçin Öneriler</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">

--- a/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
+++ b/VitrA_E-Ticaret_Kaynak_Siteler.xlsx
@@ -1536,7 +1536,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="124.5" customHeight="1">
+    <row r="29" ht="84" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>https://www.vitra.com.tr</t>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>VitrA ana sayfa: şerit mesajları ve Banyo Asistanı akışı (taksit, kargo ve hizmet mesajı) | Rakip görünürlüğü ve kanal ölçeği: vitra.com.tr alan adı metrikleri (Ahrefs, Türkiye) | Marka ve uzman sitelerde kategori trafiği: vitra.com.tr tema × trafik matrisi (Ahrefs, Türkiye) | vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (ana sayfa)</t>
+          <t>VitrA ana sayfa: şerit mesajları (taksit ve kargo) | Rakip görünürlüğü ve kanal ölçeği: vitra.com.tr alan adı metrikleri (Ahrefs, Türkiye) | Marka ve uzman sitelerde kategori trafiği: vitra.com.tr tema × trafik matrisi (Ahrefs, Türkiye) | vitra.com.tr organik kanal performansı: sayfa bazında tıklama ve gösterim (ana sayfa)</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Şeritte 'tüm ürünlerde vade farksız 6 ay taksit' ve 'tüm ürünlerde ücretsiz kargo'; Banyo Asistanı (Banyomu Yenilemek İstiyorum) 4 adımlı lead akışı: telefon, mağaza veya görüntülü görüşme seçimi, slot, WhatsApp teyidi; %40'a varan indirim, 9 taksit, ücretsiz mimari projelendirme | Batch Analysis: DR 66, 7.428 organik kelime, ilk 3'te 4.127 kelime, 330.499 organik ve 50.286 paid trafik (Ahrefs tahmini, 27.09.2026) | Ahrefs site toplamı: DR 66, 7.428 organik kelime, 330.499 aylık organik trafik; top pages: 138 sayfa 40'tan fazla temaya eşlendi (28.09.2026) | 1 Eki 2025 - 30 Eyl 2026: 134.587 tıklama, 4.500.313 gösterim, ortalama sıra 10</t>
+          <t>Şeritte 'tüm ürünlerde vade farksız 9 ay taksit' ve 'tüm ürünlerde ücretsiz kargo' | Batch Analysis: DR 66, 7.428 organik kelime, ilk 3'te 4.127 kelime, 330.499 organik ve 50.286 paid trafik (Ahrefs tahmini, 27.09.2026) | Ahrefs site toplamı: DR 66, 7.428 organik kelime, 330.499 aylık organik trafik; top pages: 138 sayfa 40'tan fazla temaya eşlendi (28.09.2026) | 1 Eki 2025 - 30 Eyl 2026: 134.587 tıklama, 4.500.313 gösterim, ortalama sıra 10</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>27.09.2026 · 28.09.2026 · 29.09.2026</t>
+          <t>27.09.2026 · 28.09.2026 · 10.10.2026</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -47883,7 +47883,7 @@
       </c>
       <c r="E1281" s="6" t="inlineStr">
         <is>
-          <t>Ürün tablosunda 12 taksite kadar seçenek (8, 9 ve 12 taksit çoğu kartta vade farklı, 2-3-4-6 taksit eşit tutar); tahmini kargoya teslim tarihi; 30 güne kadar ücretsiz iade ifadesi; montaj hizmeti seçeneği (+₺5.300)</t>
+          <t>Ürün tablosunda vade farkıyla 12 taksite kadar seçenek; tahmini kargoya teslim tarihi; 30 güne kadar ücretsiz iade ifadesi; montaj hizmeti seçeneği (+₺5.300)</t>
         </is>
       </c>
       <c r="F1281" s="7" t="inlineStr">
@@ -50551,7 +50551,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="43.5" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>vitra.com.tr</t>
@@ -50572,7 +50572,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>27.09.2026 · 28.09.2026 · 29.09.2026 · 30.09.2026 · 02.10.2026 · 04.10.2026</t>
+          <t>27.09.2026 · 28.09.2026 · 29.09.2026 · 30.09.2026 · 02.10.2026 · 04.10.2026 · 10.10.2026</t>
         </is>
       </c>
     </row>
@@ -52589,7 +52589,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>7.804 ürün adresi · hizmet, kategori ve ürün sayfaları · Banyo Asistanı · 28.09.2026</t>
+          <t>7.804 ürün adresi · hizmet, kategori ve ürün sayfaları · 28.09.2026</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
